--- a/assets/data/12guys1cup-cheat-sheet.xlsx
+++ b/assets/data/12guys1cup-cheat-sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cheat Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 200" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Cheat Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Top 200" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -56,6 +56,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00B8386B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="002E7D32"/>
       <sz val="10"/>
     </font>
@@ -69,12 +75,6 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00E65100"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00B8386B"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -120,6 +120,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F8D7E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D5ECD5"/>
       </patternFill>
     </fill>
@@ -131,11 +136,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -156,14 +156,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -193,7 +191,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6417,7 +6414,7 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Excludes K &amp; DST · Full PPR · 1QB/2RB/2WR/1TE/1FLEX · 12 Teams</t>
         </is>
@@ -6456,20 +6453,20 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>Bijan Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Josh Allen (BUF)</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D4" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>2.09</t>
         </is>
       </c>
     </row>
@@ -6502,7 +6499,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Christian McCaffrey (SF)</t>
+          <t>Bijan Robinson (ATL)</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
@@ -6511,11 +6508,11 @@
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.03</t>
         </is>
       </c>
     </row>
@@ -6525,7 +6522,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Puka Nacua (LAR)</t>
+          <t>Ja'Marr Chase (CIN)</t>
         </is>
       </c>
       <c r="C7" s="18" t="inlineStr">
@@ -6534,11 +6531,11 @@
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>
@@ -6548,20 +6545,20 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Jonathan Taylor (IND)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Puka Nacua (LAR)</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.05</t>
         </is>
       </c>
     </row>
@@ -6571,20 +6568,20 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase (CIN)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brock Bowers (LV)</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -6594,20 +6591,20 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>De'Von Achane (MIA)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Trey McBride (ARI)</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -6617,20 +6614,20 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba (SEA)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Lamar Jackson (BAL)</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>3.09</t>
         </is>
       </c>
     </row>
@@ -6640,20 +6637,20 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown (DET)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Christian McCaffrey (SF)</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.06</t>
         </is>
       </c>
     </row>
@@ -6663,20 +6660,20 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Trey McBride (ARI)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jaxon Smith-Njigba (SEA)</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6686,20 +6683,20 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>James Cook III (BUF)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Amon-Ra St. Brown (DET)</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6709,20 +6706,20 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Ashton Jeanty (LV)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>CeeDee Lamb (DAL)</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6729,7 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Brock Bowers (LV)</t>
+          <t>Tyler Warren (IND)</t>
         </is>
       </c>
       <c r="C16" s="19" t="inlineStr">
@@ -6745,7 +6742,7 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>4.11</t>
         </is>
       </c>
     </row>
@@ -6755,20 +6752,20 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Chase Brown (CIN)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Colston Loveland (CHI)</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>4.04</t>
         </is>
       </c>
     </row>
@@ -6778,20 +6775,20 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Derrick Henry (BAL)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jalen Hurts (PHI)</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>5.12</t>
         </is>
       </c>
     </row>
@@ -6801,20 +6798,20 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Saquon Barkley (PHI)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jayden Daniels (WAS)</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>6.04</t>
         </is>
       </c>
     </row>
@@ -6824,20 +6821,20 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Kenneth Walker (KC)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Joe Burrow (CIN)</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -6847,20 +6844,20 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Drake London (ATL)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonathan Taylor (IND)</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6867,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Jeremiyah Love (ARI)</t>
+          <t>James Cook III (BUF)</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
@@ -6879,11 +6876,11 @@
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>1.11</t>
         </is>
       </c>
     </row>
@@ -6893,7 +6890,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>CeeDee Lamb (DAL)</t>
+          <t>Justin Jefferson (MIN)</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
@@ -6902,11 +6899,11 @@
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6916,20 +6913,20 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Colston Loveland (CHI)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>A.J. Brown (NE)</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -6939,20 +6936,20 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Omarion Hampton (LAC)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Chris Olave (NO)</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.07</t>
         </is>
       </c>
     </row>
@@ -6962,20 +6959,20 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Josh Allen (BUF)</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Nico Collins (HOU)</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -6985,20 +6982,20 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Josh Jacobs (GB)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Garrett Wilson (NYJ)</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7005,7 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Justin Jefferson (MIN)</t>
+          <t>Drake London (ATL)</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
@@ -7017,11 +7014,11 @@
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -7031,7 +7028,7 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>A.J. Brown (NE)</t>
+          <t>George Pickens (DAL)</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
@@ -7040,11 +7037,11 @@
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -7054,20 +7051,20 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Breece Hall (NYJ)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rashee Rice (KC)</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -7077,20 +7074,20 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>George Pickens (DAL)</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Harold Fannin Jr. (CLE)</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7097,7 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Tyler Warren (IND)</t>
+          <t>Tucker Kraft (GB)</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
@@ -7109,11 +7106,11 @@
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -7123,20 +7120,20 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Javonte Williams (DAL)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>George Kittle (SF)</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -7146,20 +7143,20 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Chris Olave (NO)</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Drake Maye (NE)</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -7169,20 +7166,20 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>Kyren Williams (LAR)</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jaxson Dart (NYG)</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -7192,20 +7189,20 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Nico Collins (HOU)</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Caleb Williams (CHI)</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D36" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -7215,20 +7212,20 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Rashee Rice (KC)</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Trevor Lawrence (JAX)</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7235,7 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Cam Skattebo (NYG)</t>
+          <t>De'Von Achane (MIA)</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
@@ -7247,11 +7244,11 @@
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -7261,20 +7258,20 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Garrett Wilson (NYJ)</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kenneth Walker (KC)</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -7284,20 +7281,20 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>DeVonta Smith (PHI)</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chase Brown (CIN)</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D40" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7307,20 +7304,20 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Harold Fannin Jr. (CLE)</t>
-        </is>
-      </c>
-      <c r="C41" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Malik Nabers (NYG)</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -7330,20 +7327,20 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr. (NO)</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Zay Flowers (BAL)</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D42" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.05</t>
         </is>
       </c>
     </row>
@@ -7353,20 +7350,20 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Sam LaPorta (DET)</t>
-        </is>
-      </c>
-      <c r="C43" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>DeVonta Smith (PHI)</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>3.12</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7373,7 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Tucker Kraft (GB)</t>
+          <t>Sam LaPorta (DET)</t>
         </is>
       </c>
       <c r="C44" s="19" t="inlineStr">
@@ -7385,11 +7382,11 @@
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -7399,20 +7396,20 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Lamar Jackson (BAL)</t>
-        </is>
-      </c>
-      <c r="C45" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Kyle Pitts Sr. (ATL)</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>6.1</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7419,7 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>George Kittle (SF)</t>
+          <t>Juwan Johnson (NO)</t>
         </is>
       </c>
       <c r="C46" s="19" t="inlineStr">
@@ -7435,7 +7432,7 @@
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -7445,20 +7442,20 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Tee Higgins (CIN)</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dalton Schultz (HOU)</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>17.01</t>
         </is>
       </c>
     </row>
@@ -7468,20 +7465,20 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Zay Flowers (BAL)</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Travis Kelce (KC)</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D48" s="14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>8.08</t>
         </is>
       </c>
     </row>
@@ -7491,20 +7488,20 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan (CAR)</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jake Ferguson (DAL)</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D49" s="14" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>9.02</t>
         </is>
       </c>
     </row>
@@ -7514,20 +7511,20 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Ladd McConkey (LAC)</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Isaiah Likely (NYG)</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -7537,12 +7534,12 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Terry McLaurin (WAS)</t>
-        </is>
-      </c>
-      <c r="C51" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dalton Kincaid (BUF)</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D51" s="14" t="n">
@@ -7550,7 +7547,7 @@
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -7560,12 +7557,12 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Bucky Irving (TB)</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dallas Goedert (PHI)</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D52" s="14" t="n">
@@ -7573,7 +7570,7 @@
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -7583,20 +7580,20 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Quinshon Judkins (CLE)</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dak Prescott (DAL)</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>7.07</t>
         </is>
       </c>
     </row>
@@ -7606,20 +7603,20 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>Kyle Pitts Sr. (ATL)</t>
-        </is>
-      </c>
-      <c r="C54" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Bo Nix (DEN)</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>10.12</t>
         </is>
       </c>
     </row>
@@ -7629,20 +7626,20 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>D'Andre Swift (CHI)</t>
-        </is>
-      </c>
-      <c r="C55" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Justin Herbert (LAC)</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -7652,20 +7649,20 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Travis Kelce (KC)</t>
-        </is>
-      </c>
-      <c r="C56" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Omarion Hampton (LAC)</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7675,20 +7672,20 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Jayden Daniels (WAS)</t>
-        </is>
-      </c>
-      <c r="C57" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Ashton Jeanty (LV)</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D57" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -7698,20 +7695,20 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Drake Maye (NE)</t>
-        </is>
-      </c>
-      <c r="C58" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Saquon Barkley (PHI)</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D58" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7718,12 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Jalen Hurts (PHI)</t>
-        </is>
-      </c>
-      <c r="C59" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jaylen Waddle (DEN)</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D59" s="14" t="n">
@@ -7734,7 +7731,7 @@
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -7744,20 +7741,20 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>David Montgomery (HOU)</t>
-        </is>
-      </c>
-      <c r="C60" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ladd McConkey (LAC)</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D60" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.02</t>
         </is>
       </c>
     </row>
@@ -7767,20 +7764,20 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Joe Burrow (CIN)</t>
-        </is>
-      </c>
-      <c r="C61" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Emeka Egbuka (TB)</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>4.03</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7787,7 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Waddle (DEN)</t>
+          <t>Tetairoa McMillan (CAR)</t>
         </is>
       </c>
       <c r="C62" s="18" t="inlineStr">
@@ -7799,11 +7796,11 @@
         </is>
       </c>
       <c r="D62" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.01</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7810,7 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Davante Adams (LAR)</t>
+          <t>Tee Higgins (CIN)</t>
         </is>
       </c>
       <c r="C63" s="18" t="inlineStr">
@@ -7822,11 +7819,11 @@
         </is>
       </c>
       <c r="D63" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>3.11</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7833,7 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Emeka Egbuka (TB)</t>
+          <t>Carnell Tate (TEN)</t>
         </is>
       </c>
       <c r="C64" s="18" t="inlineStr">
@@ -7845,11 +7842,11 @@
         </is>
       </c>
       <c r="D64" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7856,7 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Jake Ferguson (DAL)</t>
+          <t>Brenton Strange (JAX)</t>
         </is>
       </c>
       <c r="C65" s="19" t="inlineStr">
@@ -7868,11 +7865,11 @@
         </is>
       </c>
       <c r="D65" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>13.08</t>
         </is>
       </c>
     </row>
@@ -7882,20 +7879,20 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson (NE)</t>
-        </is>
-      </c>
-      <c r="C66" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Mark Andrews (BAL)</t>
+        </is>
+      </c>
+      <c r="C66" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D66" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>11.09</t>
         </is>
       </c>
     </row>
@@ -7905,20 +7902,20 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>Malik Nabers (NYG)</t>
-        </is>
-      </c>
-      <c r="C67" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Hunter Henry (NE)</t>
+        </is>
+      </c>
+      <c r="C67" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D67" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -7928,20 +7925,20 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Warren (PIT)</t>
-        </is>
-      </c>
-      <c r="C68" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Brock Purdy (SF)</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D68" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>11.02</t>
         </is>
       </c>
     </row>
@@ -7951,20 +7948,20 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Dallas Goedert (PHI)</t>
-        </is>
-      </c>
-      <c r="C69" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jared Goff (DET)</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D69" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>12.03</t>
         </is>
       </c>
     </row>
@@ -7974,20 +7971,20 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Dak Prescott (DAL)</t>
-        </is>
-      </c>
-      <c r="C70" s="20" t="inlineStr">
+          <t>Matthew Stafford (LAR)</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
       <c r="D70" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>9.01</t>
         </is>
       </c>
     </row>
@@ -7997,20 +7994,20 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>Justin Herbert (LAC)</t>
-        </is>
-      </c>
-      <c r="C71" s="20" t="inlineStr">
+          <t>Tyler Shough (NO)</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>16.07</t>
         </is>
       </c>
     </row>
@@ -8020,20 +8017,20 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Luther Burden III (CHI)</t>
-        </is>
-      </c>
-      <c r="C72" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kyler Murray (MIN)</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>14.03</t>
         </is>
       </c>
     </row>
@@ -8043,20 +8040,20 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Dalton Kincaid (BUF)</t>
-        </is>
-      </c>
-      <c r="C73" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Baker Mayfield (TB)</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -8066,20 +8063,20 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Jaxson Dart (NYG)</t>
-        </is>
-      </c>
-      <c r="C74" s="20" t="inlineStr">
+          <t>Patrick Mahomes (KC)</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
       <c r="D74" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -8089,20 +8086,20 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>Trevor Lawrence (JAX)</t>
-        </is>
-      </c>
-      <c r="C75" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Derrick Henry (BAL)</t>
+        </is>
+      </c>
+      <c r="C75" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>2.08</t>
         </is>
       </c>
     </row>
@@ -8112,20 +8109,20 @@
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Brock Purdy (SF)</t>
-        </is>
-      </c>
-      <c r="C76" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jeremiyah Love (ARI)</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D76" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8132,7 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten (JAX)</t>
+          <t>Kyren Williams (LAR)</t>
         </is>
       </c>
       <c r="C77" s="17" t="inlineStr">
@@ -8144,11 +8141,11 @@
         </is>
       </c>
       <c r="D77" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
@@ -8158,20 +8155,20 @@
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Mike Evans (SF)</t>
-        </is>
-      </c>
-      <c r="C78" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Breece Hall (NYJ)</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D78" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -8181,20 +8178,20 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>Carnell Tate (TEN)</t>
-        </is>
-      </c>
-      <c r="C79" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>D'Andre Swift (CHI)</t>
+        </is>
+      </c>
+      <c r="C79" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D79" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8201,7 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson (NE)</t>
+          <t>Javonte Williams (DAL)</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
@@ -8213,11 +8210,11 @@
         </is>
       </c>
       <c r="D80" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -8227,20 +8224,20 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>Jameson Williams (DET)</t>
-        </is>
-      </c>
-      <c r="C81" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Cam Skattebo (NYG)</t>
+        </is>
+      </c>
+      <c r="C81" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D81" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>4.08</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8247,7 @@
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Jadarian Price (SEA)</t>
+          <t>Bucky Irving (TB)</t>
         </is>
       </c>
       <c r="C82" s="17" t="inlineStr">
@@ -8259,11 +8256,11 @@
         </is>
       </c>
       <c r="D82" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>4.06</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8270,7 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>DK Metcalf (PIT)</t>
+          <t>Luther Burden III (CHI)</t>
         </is>
       </c>
       <c r="C83" s="18" t="inlineStr">
@@ -8282,11 +8279,11 @@
         </is>
       </c>
       <c r="D83" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -8296,20 +8293,20 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Caleb Williams (CHI)</t>
-        </is>
-      </c>
-      <c r="C84" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Parker Washington (JAX)</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D84" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>7.04</t>
         </is>
       </c>
     </row>
@@ -8319,20 +8316,20 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>Tony Pollard (TEN)</t>
-        </is>
-      </c>
-      <c r="C85" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Christian Watson (GB)</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D85" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8339,7 @@
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Rome Odunze (CHI)</t>
+          <t>Terry McLaurin (WAS)</t>
         </is>
       </c>
       <c r="C86" s="18" t="inlineStr">
@@ -8351,11 +8348,11 @@
         </is>
       </c>
       <c r="D86" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -8365,20 +8362,20 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>Isaiah Likely (NYG)</t>
-        </is>
-      </c>
-      <c r="C87" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jameson Williams (DET)</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D87" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -8388,20 +8385,20 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Mark Andrews (BAL)</t>
-        </is>
-      </c>
-      <c r="C88" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>DJ Moore (BUF)</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D88" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>5.09</t>
         </is>
       </c>
     </row>
@@ -8411,20 +8408,20 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>Patrick Mahomes (KC)</t>
-        </is>
-      </c>
-      <c r="C89" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Davante Adams (LAR)</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D89" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>5.02</t>
         </is>
       </c>
     </row>
@@ -8434,20 +8431,20 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Christian Watson (GB)</t>
-        </is>
-      </c>
-      <c r="C90" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chig Okonkwo (WAS)</t>
+        </is>
+      </c>
+      <c r="C90" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D90" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -8457,20 +8454,20 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>Michael Pittman Jr. (PIT)</t>
-        </is>
-      </c>
-      <c r="C91" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Greg Dulcich (MIA)</t>
+        </is>
+      </c>
+      <c r="C91" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8477,7 @@
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>Brenton Strange (JAX)</t>
+          <t>T.J. Hockenson (MIN)</t>
         </is>
       </c>
       <c r="C92" s="19" t="inlineStr">
@@ -8489,11 +8486,11 @@
         </is>
       </c>
       <c r="D92" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -8503,20 +8500,20 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>Bo Nix (DEN)</t>
-        </is>
-      </c>
-      <c r="C93" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Kenyon Sadiq (NYJ)</t>
+        </is>
+      </c>
+      <c r="C93" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D93" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>13.1</t>
         </is>
       </c>
     </row>
@@ -8526,12 +8523,12 @@
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>Rico Dowdle (PIT)</t>
-        </is>
-      </c>
-      <c r="C94" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Pat Freiermuth (PIT)</t>
+        </is>
+      </c>
+      <c r="C94" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D94" s="14" t="n">
@@ -8539,7 +8536,7 @@
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -8549,20 +8546,20 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr. (ARI)</t>
-        </is>
-      </c>
-      <c r="C95" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Malik Willis (MIA)</t>
+        </is>
+      </c>
+      <c r="C95" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D95" s="14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -8572,12 +8569,12 @@
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Hunter Henry (NE)</t>
-        </is>
-      </c>
-      <c r="C96" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jordan Love (GB)</t>
+        </is>
+      </c>
+      <c r="C96" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D96" s="14" t="n">
@@ -8585,7 +8582,7 @@
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>13.05</t>
         </is>
       </c>
     </row>
@@ -8595,12 +8592,12 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>Juwan Johnson (NO)</t>
-        </is>
-      </c>
-      <c r="C97" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Travis Etienne Jr. (NO)</t>
+        </is>
+      </c>
+      <c r="C97" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
@@ -8608,7 +8605,7 @@
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>4.09</t>
         </is>
       </c>
     </row>
@@ -8618,20 +8615,20 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>Courtland Sutton (DEN)</t>
-        </is>
-      </c>
-      <c r="C98" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Bhayshul Tuten (JAX)</t>
+        </is>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D98" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8641,20 +8638,20 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq (NYJ)</t>
-        </is>
-      </c>
-      <c r="C99" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Quinshon Judkins (CLE)</t>
+        </is>
+      </c>
+      <c r="C99" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -8664,20 +8661,20 @@
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>Alec Pierce (IND)</t>
-        </is>
-      </c>
-      <c r="C100" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>TreVeyon Henderson (NE)</t>
+        </is>
+      </c>
+      <c r="C100" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D100" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -8687,20 +8684,20 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>Matthew Stafford (LAR)</t>
-        </is>
-      </c>
-      <c r="C101" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>David Montgomery (HOU)</t>
+        </is>
+      </c>
+      <c r="C101" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -8710,20 +8707,20 @@
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Parker Washington (JAX)</t>
-        </is>
-      </c>
-      <c r="C102" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jadarian Price (SEA)</t>
+        </is>
+      </c>
+      <c r="C102" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D102" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8730,7 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>DJ Moore (BUF)</t>
+          <t>Mike Evans (SF)</t>
         </is>
       </c>
       <c r="C103" s="18" t="inlineStr">
@@ -8742,11 +8739,11 @@
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8753,7 @@
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>Stefon Diggs (WAS)</t>
+          <t>Rome Odunze (CHI)</t>
         </is>
       </c>
       <c r="C104" s="18" t="inlineStr">
@@ -8765,11 +8762,11 @@
         </is>
       </c>
       <c r="D104" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>6.05</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8776,7 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>Jordyn Tyson (NO)</t>
+          <t>Marvin Harrison Jr. (ARI)</t>
         </is>
       </c>
       <c r="C105" s="18" t="inlineStr">
@@ -8788,11 +8785,11 @@
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -8802,20 +8799,20 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>T.J. Hockenson (MIN)</t>
-        </is>
-      </c>
-      <c r="C106" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>DK Metcalf (PIT)</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D106" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -8825,20 +8822,20 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Jared Goff (DET)</t>
-        </is>
-      </c>
-      <c r="C107" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Cade Otton (TB)</t>
+        </is>
+      </c>
+      <c r="C107" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>20.06</t>
         </is>
       </c>
     </row>
@@ -8848,20 +8845,20 @@
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>Kyler Murray (MIN)</t>
-        </is>
-      </c>
-      <c r="C108" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>AJ Barner (SEA)</t>
+        </is>
+      </c>
+      <c r="C108" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D108" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -8871,20 +8868,20 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>Chuba Hubbard (CAR)</t>
-        </is>
-      </c>
-      <c r="C109" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Oronde Gadsden (LAC)</t>
+        </is>
+      </c>
+      <c r="C109" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
@@ -8894,20 +8891,20 @@
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr. (TB)</t>
-        </is>
-      </c>
-      <c r="C110" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Colby Parkinson (LAR)</t>
+        </is>
+      </c>
+      <c r="C110" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D110" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>21.11</t>
         </is>
       </c>
     </row>
@@ -8917,20 +8914,20 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>J.K. Dobbins (DEN)</t>
-        </is>
-      </c>
-      <c r="C111" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>David Njoku (LAC)</t>
+        </is>
+      </c>
+      <c r="C111" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>18.04</t>
         </is>
       </c>
     </row>
@@ -8940,20 +8937,20 @@
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C112" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Darren Waller (CAR)</t>
+        </is>
+      </c>
+      <c r="C112" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D112" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8963,20 +8960,20 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>Michael Wilson (ARI)</t>
-        </is>
-      </c>
-      <c r="C113" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Mike Gesicki (CIN)</t>
+        </is>
+      </c>
+      <c r="C113" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8986,20 +8983,20 @@
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Jakobi Meyers (JAX)</t>
-        </is>
-      </c>
-      <c r="C114" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Cole Kmet (CHI)</t>
+        </is>
+      </c>
+      <c r="C114" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D114" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9009,7 +9006,7 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>Chig Okonkwo (WAS)</t>
+          <t>Gunnar Helm (TEN)</t>
         </is>
       </c>
       <c r="C115" s="19" t="inlineStr">
@@ -9018,11 +9015,11 @@
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>20.05</t>
         </is>
       </c>
     </row>
@@ -9032,12 +9029,12 @@
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>Makai Lemon (PHI)</t>
-        </is>
-      </c>
-      <c r="C116" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Evan Engram (DEN)</t>
+        </is>
+      </c>
+      <c r="C116" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D116" s="14" t="n">
@@ -9045,7 +9042,7 @@
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9055,12 +9052,12 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>Jordan Love (GB)</t>
-        </is>
-      </c>
-      <c r="C117" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Terrance Ferguson (LAR)</t>
+        </is>
+      </c>
+      <c r="C117" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D117" s="14" t="n">
@@ -9068,7 +9065,7 @@
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>18.03</t>
         </is>
       </c>
     </row>
@@ -9078,20 +9075,20 @@
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>Baker Mayfield (TB)</t>
-        </is>
-      </c>
-      <c r="C118" s="20" t="inlineStr">
+          <t>Cam Ward (TEN)</t>
+        </is>
+      </c>
+      <c r="C118" s="16" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
       <c r="D118" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -9101,20 +9098,20 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>Jayden Reed (GB)</t>
-        </is>
-      </c>
-      <c r="C119" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>C.J. Stroud (HOU)</t>
+        </is>
+      </c>
+      <c r="C119" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>18.01</t>
         </is>
       </c>
     </row>
@@ -9124,20 +9121,20 @@
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Josh Downs (IND)</t>
-        </is>
-      </c>
-      <c r="C120" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Sam Darnold (SEA)</t>
+        </is>
+      </c>
+      <c r="C120" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D120" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>14.05</t>
         </is>
       </c>
     </row>
@@ -9147,20 +9144,20 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>Kenny Gainwell (TB)</t>
-        </is>
-      </c>
-      <c r="C121" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Daniel Jones (IND)</t>
+        </is>
+      </c>
+      <c r="C121" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D121" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>17.11</t>
         </is>
       </c>
     </row>
@@ -9170,20 +9167,20 @@
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr. (MIN)</t>
-        </is>
-      </c>
-      <c r="C122" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Bryce Young (CAR)</t>
+        </is>
+      </c>
+      <c r="C122" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>19.12</t>
         </is>
       </c>
     </row>
@@ -9193,20 +9190,20 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>Jordan Addison (MIN)</t>
-        </is>
-      </c>
-      <c r="C123" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Aaron Rodgers (PIT)</t>
+        </is>
+      </c>
+      <c r="C123" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -9216,20 +9213,20 @@
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>Dalton Schultz (HOU)</t>
-        </is>
-      </c>
-      <c r="C124" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Geno Smith (NYJ)</t>
+        </is>
+      </c>
+      <c r="C124" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D124" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9239,12 +9236,12 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>Romeo Doubs (NE)</t>
-        </is>
-      </c>
-      <c r="C125" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rhamondre Stevenson (NE)</t>
+        </is>
+      </c>
+      <c r="C125" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D125" s="14" t="n">
@@ -9252,7 +9249,7 @@
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -9262,20 +9259,20 @@
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>Oronde Gadsden (LAC)</t>
-        </is>
-      </c>
-      <c r="C126" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Rico Dowdle (PIT)</t>
+        </is>
+      </c>
+      <c r="C126" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>8.01</t>
         </is>
       </c>
     </row>
@@ -9285,20 +9282,20 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>Tyler Shough (NO)</t>
-        </is>
-      </c>
-      <c r="C127" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Josh Jacobs (GB)</t>
+        </is>
+      </c>
+      <c r="C127" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>3.08</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9305,7 @@
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>Kyle Monangai (CHI)</t>
+          <t>Jacory Croskey-Merritt (WAS)</t>
         </is>
       </c>
       <c r="C128" s="17" t="inlineStr">
@@ -9317,11 +9314,11 @@
         </is>
       </c>
       <c r="D128" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>10.06</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9328,7 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>RJ Harvey (DEN)</t>
+          <t>Kenny Gainwell (TB)</t>
         </is>
       </c>
       <c r="C129" s="17" t="inlineStr">
@@ -9344,7 +9341,7 @@
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -9354,12 +9351,12 @@
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>Pat Freiermuth (PIT)</t>
-        </is>
-      </c>
-      <c r="C130" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jaylen Warren (PIT)</t>
+        </is>
+      </c>
+      <c r="C130" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D130" s="14" t="n">
@@ -9367,7 +9364,7 @@
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -9377,20 +9374,20 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson (TEN)</t>
-        </is>
-      </c>
-      <c r="C131" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chuba Hubbard (CAR)</t>
+        </is>
+      </c>
+      <c r="C131" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>7.05</t>
         </is>
       </c>
     </row>
@@ -9400,20 +9397,20 @@
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>Malik Willis (MIA)</t>
-        </is>
-      </c>
-      <c r="C132" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tony Pollard (TEN)</t>
+        </is>
+      </c>
+      <c r="C132" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D132" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>7.12</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9420,7 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>Rachaad White (WAS)</t>
+          <t>J.K. Dobbins (DEN)</t>
         </is>
       </c>
       <c r="C133" s="17" t="inlineStr">
@@ -9432,11 +9429,11 @@
         </is>
       </c>
       <c r="D133" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>8.1</t>
         </is>
       </c>
     </row>
@@ -9446,20 +9443,20 @@
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Greg Dulcich (MIA)</t>
-        </is>
-      </c>
-      <c r="C134" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jonathon Brooks (CAR)</t>
+        </is>
+      </c>
+      <c r="C134" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D134" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>9.1</t>
         </is>
       </c>
     </row>
@@ -9469,20 +9466,20 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>Xavier Worthy (KC)</t>
-        </is>
-      </c>
-      <c r="C135" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kyle Monangai (CHI)</t>
+        </is>
+      </c>
+      <c r="C135" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -9492,20 +9489,20 @@
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>C.J. Stroud (HOU)</t>
-        </is>
-      </c>
-      <c r="C136" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jordan Mason (MIN)</t>
+        </is>
+      </c>
+      <c r="C136" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D136" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>10.07</t>
         </is>
       </c>
     </row>
@@ -9515,12 +9512,12 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>Quentin Johnston (LAC)</t>
-        </is>
-      </c>
-      <c r="C137" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rachaad White (WAS)</t>
+        </is>
+      </c>
+      <c r="C137" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D137" s="14" t="n">
@@ -9528,7 +9525,7 @@
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -9538,20 +9535,20 @@
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>Khalil Shakir (BUF)</t>
-        </is>
-      </c>
-      <c r="C138" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Blake Corum (LAR)</t>
+        </is>
+      </c>
+      <c r="C138" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>9.08</t>
         </is>
       </c>
     </row>
@@ -9561,20 +9558,20 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>Gunnar Helm (TEN)</t>
-        </is>
-      </c>
-      <c r="C139" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Alec Pierce (IND)</t>
+        </is>
+      </c>
+      <c r="C139" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>9.05</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9581,7 @@
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>Matthew Golden (GB)</t>
+          <t>Brian Thomas Jr. (JAX)</t>
         </is>
       </c>
       <c r="C140" s="18" t="inlineStr">
@@ -9593,11 +9590,11 @@
         </is>
       </c>
       <c r="D140" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>7.02</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9604,12 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>Cade Otton (TB)</t>
-        </is>
-      </c>
-      <c r="C141" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Chris Godwin Jr. (TB)</t>
+        </is>
+      </c>
+      <c r="C141" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
@@ -9620,7 +9617,7 @@
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>8.12</t>
         </is>
       </c>
     </row>
@@ -9630,20 +9627,20 @@
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>Daniel Jones (IND)</t>
-        </is>
-      </c>
-      <c r="C142" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Quentin Johnston (LAC)</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>10.05</t>
         </is>
       </c>
     </row>
@@ -9653,20 +9650,20 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>Jacoby Brissett (ARI)</t>
-        </is>
-      </c>
-      <c r="C143" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Michael Pittman Jr. (PIT)</t>
+        </is>
+      </c>
+      <c r="C143" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>9.07</t>
         </is>
       </c>
     </row>
@@ -9676,20 +9673,20 @@
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>Jordan Mason (MIN)</t>
-        </is>
-      </c>
-      <c r="C144" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Wan'Dale Robinson (TEN)</t>
+        </is>
+      </c>
+      <c r="C144" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>10.09</t>
         </is>
       </c>
     </row>
@@ -9699,20 +9696,20 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>KC Concepcion (CLE)</t>
-        </is>
-      </c>
-      <c r="C145" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Mason Taylor (NYJ)</t>
+        </is>
+      </c>
+      <c r="C145" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>19.08</t>
         </is>
       </c>
     </row>
@@ -9722,20 +9719,20 @@
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>Sam Darnold (SEA)</t>
-        </is>
-      </c>
-      <c r="C146" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Charlie Kolar (LAC)</t>
+        </is>
+      </c>
+      <c r="C146" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9745,20 +9742,20 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Blake Corum (LAR)</t>
-        </is>
-      </c>
-      <c r="C147" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Michael Mayer (LV)</t>
+        </is>
+      </c>
+      <c r="C147" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9768,20 +9765,20 @@
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>Jalen Coker (CAR)</t>
-        </is>
-      </c>
-      <c r="C148" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dawson Knox (BUF)</t>
+        </is>
+      </c>
+      <c r="C148" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9791,7 +9788,7 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>AJ Barner (SEA)</t>
+          <t>Eli Stowers (PHI)</t>
         </is>
       </c>
       <c r="C149" s="19" t="inlineStr">
@@ -9800,11 +9797,11 @@
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>20.11</t>
         </is>
       </c>
     </row>
@@ -9814,20 +9811,20 @@
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>Deebo Samuel Sr. (SF)</t>
-        </is>
-      </c>
-      <c r="C150" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Luke Musgrave (GB)</t>
+        </is>
+      </c>
+      <c r="C150" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9837,20 +9834,20 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Tyjae Spears (TEN)</t>
-        </is>
-      </c>
-      <c r="C151" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ja'Tavion Sanders (CAR)</t>
+        </is>
+      </c>
+      <c r="C151" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D151" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9860,7 +9857,7 @@
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Mason Taylor (NYJ)</t>
+          <t>Theo Johnson (NYG)</t>
         </is>
       </c>
       <c r="C152" s="19" t="inlineStr">
@@ -9869,11 +9866,11 @@
         </is>
       </c>
       <c r="D152" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>20.04</t>
         </is>
       </c>
     </row>
@@ -9883,20 +9880,20 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>Fernando Mendoza (LV)</t>
-        </is>
-      </c>
-      <c r="C153" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Noah Gray (KC)</t>
+        </is>
+      </c>
+      <c r="C153" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>16.01</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9903,7 @@
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>Darnell Washington (PIT)</t>
+          <t>Tommy Tremble (CAR)</t>
         </is>
       </c>
       <c r="C154" s="19" t="inlineStr">
@@ -9915,7 +9912,7 @@
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
@@ -9929,7 +9926,7 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>David Njoku (LAC)</t>
+          <t>Elijah Arroyo (SEA)</t>
         </is>
       </c>
       <c r="C155" s="19" t="inlineStr">
@@ -9938,11 +9935,11 @@
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9952,20 +9949,20 @@
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Rashid Shaheed (SEA)</t>
-        </is>
-      </c>
-      <c r="C156" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Darnell Washington (PIT)</t>
+        </is>
+      </c>
+      <c r="C156" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9975,7 +9972,7 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Colby Parkinson (LAR)</t>
+          <t>Max Klare (LAR)</t>
         </is>
       </c>
       <c r="C157" s="19" t="inlineStr">
@@ -9988,7 +9985,7 @@
       </c>
       <c r="E157" s="14" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>21.09</t>
         </is>
       </c>
     </row>
@@ -9998,20 +9995,20 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Cam Ward (TEN)</t>
-        </is>
-      </c>
-      <c r="C158" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jake Tonges (SF)</t>
+        </is>
+      </c>
+      <c r="C158" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>21.01</t>
         </is>
       </c>
     </row>
@@ -10021,20 +10018,20 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Bryce Young (CAR)</t>
-        </is>
-      </c>
-      <c r="C159" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Ben Sinnott (WAS)</t>
+        </is>
+      </c>
+      <c r="C159" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E159" s="14" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10044,16 +10041,16 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>Geno Smith (NYJ)</t>
-        </is>
-      </c>
-      <c r="C160" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Noah Fant (NO)</t>
+        </is>
+      </c>
+      <c r="C160" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
@@ -10067,20 +10064,20 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt (WAS)</t>
-        </is>
-      </c>
-      <c r="C161" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Justin Joly (DEN)</t>
+        </is>
+      </c>
+      <c r="C161" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E161" s="14" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10087,7 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Terrance Ferguson (LAR)</t>
+          <t>Nate Boerkircher (JAX)</t>
         </is>
       </c>
       <c r="C162" s="19" t="inlineStr">
@@ -10099,11 +10096,11 @@
         </is>
       </c>
       <c r="D162" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10113,20 +10110,20 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>Denzel Boston (CLE)</t>
-        </is>
-      </c>
-      <c r="C163" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Oscar Delp (NO)</t>
+        </is>
+      </c>
+      <c r="C163" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E163" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10136,20 +10133,20 @@
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Mike Gesicki (CIN)</t>
-        </is>
-      </c>
-      <c r="C164" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jacoby Brissett (ARI)</t>
+        </is>
+      </c>
+      <c r="C164" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21.03</t>
         </is>
       </c>
     </row>
@@ -10159,20 +10156,20 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>Jonathon Brooks (CAR)</t>
-        </is>
-      </c>
-      <c r="C165" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tua Tagovailoa (ATL)</t>
+        </is>
+      </c>
+      <c r="C165" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E165" s="14" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>20.09</t>
         </is>
       </c>
     </row>
@@ -10182,20 +10179,20 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Omar Cooper Jr. (NYJ)</t>
-        </is>
-      </c>
-      <c r="C166" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Shedeur Sanders (CLE)</t>
+        </is>
+      </c>
+      <c r="C166" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>20.08</t>
         </is>
       </c>
     </row>
@@ -10205,20 +10202,20 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>Darren Waller (CAR)</t>
-        </is>
-      </c>
-      <c r="C167" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Fernando Mendoza (LV)</t>
+        </is>
+      </c>
+      <c r="C167" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E167" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16.01</t>
         </is>
       </c>
     </row>
@@ -10228,20 +10225,20 @@
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>Evan Engram (DEN)</t>
-        </is>
-      </c>
-      <c r="C168" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Michael Penix Jr. (ATL)</t>
+        </is>
+      </c>
+      <c r="C168" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19.12</t>
         </is>
       </c>
     </row>
@@ -10251,12 +10248,12 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>Tre Tucker (LV)</t>
-        </is>
-      </c>
-      <c r="C169" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kirk Cousins (LV)</t>
+        </is>
+      </c>
+      <c r="C169" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D169" s="14" t="n">
@@ -10264,7 +10261,7 @@
       </c>
       <c r="E169" s="14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10274,20 +10271,20 @@
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Chris Rodriguez Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C170" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Deshaun Watson (CLE)</t>
+        </is>
+      </c>
+      <c r="C170" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10297,20 +10294,20 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>Jauan Jennings (MIN)</t>
-        </is>
-      </c>
-      <c r="C171" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Carson Beck (ARI)</t>
+        </is>
+      </c>
+      <c r="C171" s="16" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
-          <t>17.06</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10317,12 @@
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Jalen McMillan (TB)</t>
-        </is>
-      </c>
-      <c r="C172" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>RJ Harvey (DEN)</t>
+        </is>
+      </c>
+      <c r="C172" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D172" s="14" t="n">
@@ -10333,7 +10330,7 @@
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>7.08</t>
         </is>
       </c>
     </row>
@@ -10343,20 +10340,20 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>Aaron Rodgers (PIT)</t>
-        </is>
-      </c>
-      <c r="C173" s="20" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>MarShawn Lloyd (GB)</t>
+        </is>
+      </c>
+      <c r="C173" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>15.06</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10363,7 @@
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Woody Marks (HOU)</t>
+          <t>Aaron Jones Sr. (MIN)</t>
         </is>
       </c>
       <c r="C174" s="17" t="inlineStr">
@@ -10375,11 +10372,11 @@
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -10389,20 +10386,20 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>Michael Mayer (LV)</t>
-        </is>
-      </c>
-      <c r="C175" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tyjae Spears (TEN)</t>
+        </is>
+      </c>
+      <c r="C175" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E175" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -10412,20 +10409,20 @@
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>Cole Kmet (CHI)</t>
-        </is>
-      </c>
-      <c r="C176" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Woody Marks (HOU)</t>
+        </is>
+      </c>
+      <c r="C176" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D176" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.04</t>
         </is>
       </c>
     </row>
@@ -10435,20 +10432,20 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Adonai Mitchell (NYJ)</t>
-        </is>
-      </c>
-      <c r="C177" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chris Rodriguez Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C177" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E177" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>12.08</t>
         </is>
       </c>
     </row>
@@ -10458,16 +10455,16 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Jalen Nailor (LV)</t>
-        </is>
-      </c>
-      <c r="C178" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Isiah Pacheco (DET)</t>
+        </is>
+      </c>
+      <c r="C178" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
@@ -10481,20 +10478,20 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Isiah Pacheco (DET)</t>
-        </is>
-      </c>
-      <c r="C179" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Michael Wilson (ARI)</t>
+        </is>
+      </c>
+      <c r="C179" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E179" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>7.11</t>
         </is>
       </c>
     </row>
@@ -10504,7 +10501,7 @@
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Jerry Jeudy (CLE)</t>
+          <t>Stefon Diggs (WAS)</t>
         </is>
       </c>
       <c r="C180" s="18" t="inlineStr">
@@ -10513,11 +10510,11 @@
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>10.02</t>
         </is>
       </c>
     </row>
@@ -10527,20 +10524,20 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>Dawson Knox (BUF)</t>
-        </is>
-      </c>
-      <c r="C181" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Courtland Sutton (DEN)</t>
+        </is>
+      </c>
+      <c r="C181" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.09</t>
         </is>
       </c>
     </row>
@@ -10550,7 +10547,7 @@
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Chris Bell (MIA)</t>
+          <t>Jordan Addison (MIN)</t>
         </is>
       </c>
       <c r="C182" s="18" t="inlineStr">
@@ -10563,7 +10560,7 @@
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
-          <t>21.01</t>
+          <t>9.09</t>
         </is>
       </c>
     </row>
@@ -10573,7 +10570,7 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>Calvin Ridley (TEN)</t>
+          <t>De'Zhaun Stribling (SF)</t>
         </is>
       </c>
       <c r="C183" s="18" t="inlineStr">
@@ -10582,11 +10579,11 @@
         </is>
       </c>
       <c r="D183" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E183" s="14" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>12.07</t>
         </is>
       </c>
     </row>
@@ -10596,20 +10593,20 @@
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr. (NYG)</t>
-        </is>
-      </c>
-      <c r="C184" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jayden Reed (GB)</t>
+        </is>
+      </c>
+      <c r="C184" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D184" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -10619,20 +10616,20 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Dylan Sampson (CLE)</t>
-        </is>
-      </c>
-      <c r="C185" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Josh Downs (IND)</t>
+        </is>
+      </c>
+      <c r="C185" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E185" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>10.01</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10639,7 @@
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Ryan Flournoy (DAL)</t>
+          <t>Jakobi Meyers (JAX)</t>
         </is>
       </c>
       <c r="C186" s="18" t="inlineStr">
@@ -10651,11 +10648,11 @@
         </is>
       </c>
       <c r="D186" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>10.1</t>
         </is>
       </c>
     </row>
@@ -10665,12 +10662,12 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>Brian Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C187" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Romeo Doubs (NE)</t>
+        </is>
+      </c>
+      <c r="C187" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D187" s="14" t="n">
@@ -10678,7 +10675,7 @@
       </c>
       <c r="E187" s="14" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -10688,7 +10685,7 @@
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Antonio Williams (WAS)</t>
+          <t>Khalil Shakir (BUF)</t>
         </is>
       </c>
       <c r="C188" s="18" t="inlineStr">
@@ -10701,7 +10698,7 @@
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>12.11</t>
         </is>
       </c>
     </row>
@@ -10711,7 +10708,7 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Justice Hill (BAL)</t>
+          <t>Keaton Mitchell (LAC)</t>
         </is>
       </c>
       <c r="C189" s="17" t="inlineStr">
@@ -10720,11 +10717,11 @@
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E189" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10734,20 +10731,20 @@
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Theo Johnson (NYG)</t>
-        </is>
-      </c>
-      <c r="C190" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Zach Charbonnet (SEA)</t>
+        </is>
+      </c>
+      <c r="C190" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D190" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E190" s="14" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>13.04</t>
         </is>
       </c>
     </row>
@@ -10757,20 +10754,20 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>Jake Tonges (SF)</t>
-        </is>
-      </c>
-      <c r="C191" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tyler Allgeier (ARI)</t>
+        </is>
+      </c>
+      <c r="C191" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E191" s="14" t="inlineStr">
         <is>
-          <t>21.01</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -10780,20 +10777,20 @@
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Germie Bernard (PIT)</t>
-        </is>
-      </c>
-      <c r="C192" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dylan Sampson (CLE)</t>
+        </is>
+      </c>
+      <c r="C192" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D192" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -10803,20 +10800,20 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Rashod Bateman (BAL)</t>
-        </is>
-      </c>
-      <c r="C193" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonah Coleman (DEN)</t>
+        </is>
+      </c>
+      <c r="C193" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>15.03</t>
         </is>
       </c>
     </row>
@@ -10826,7 +10823,7 @@
       </c>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>Alvin Kamara (NO)</t>
+          <t>Mike Washington Jr. (LV)</t>
         </is>
       </c>
       <c r="C194" s="17" t="inlineStr">
@@ -10835,11 +10832,11 @@
         </is>
       </c>
       <c r="D194" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E194" s="14" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>15.05</t>
         </is>
       </c>
     </row>
@@ -10849,7 +10846,7 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Tyler Allgeier (ARI)</t>
+          <t>Tyrone Tracy Jr. (NYG)</t>
         </is>
       </c>
       <c r="C195" s="17" t="inlineStr">
@@ -10858,11 +10855,11 @@
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E195" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10872,7 +10869,7 @@
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>Samaje Perine (CIN)</t>
+          <t>Tank Bigsby (PHI)</t>
         </is>
       </c>
       <c r="C196" s="17" t="inlineStr">
@@ -10881,11 +10878,11 @@
         </is>
       </c>
       <c r="D196" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E196" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10895,20 +10892,20 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>Travis Hunter (JAX)</t>
-        </is>
-      </c>
-      <c r="C197" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Alvin Kamara (NO)</t>
+        </is>
+      </c>
+      <c r="C197" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D197" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E197" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>14.07</t>
         </is>
       </c>
     </row>
@@ -10918,20 +10915,20 @@
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Isaac TeSlaa (DET)</t>
-        </is>
-      </c>
-      <c r="C198" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brian Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C198" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D198" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>13.12</t>
         </is>
       </c>
     </row>
@@ -10941,20 +10938,20 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>Keenan Allen (IND)</t>
-        </is>
-      </c>
-      <c r="C199" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jordan James (SF)</t>
+        </is>
+      </c>
+      <c r="C199" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E199" s="14" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10964,20 +10961,20 @@
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Troy Franklin (DEN)</t>
-        </is>
-      </c>
-      <c r="C200" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kimani Vidal (LAC)</t>
+        </is>
+      </c>
+      <c r="C200" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D200" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>21.02</t>
+          <t>20.1</t>
         </is>
       </c>
     </row>
@@ -10987,20 +10984,20 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>Malik Washington (MIA)</t>
-        </is>
-      </c>
-      <c r="C201" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Justice Hill (BAL)</t>
+        </is>
+      </c>
+      <c r="C201" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D201" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11010,16 +11007,16 @@
       </c>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>Ja'Tavion Sanders (CAR)</t>
-        </is>
-      </c>
-      <c r="C202" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Samaje Perine (CIN)</t>
+        </is>
+      </c>
+      <c r="C202" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D202" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E202" s="14" t="inlineStr">
         <is>
@@ -11033,12 +11030,12 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>Noah Gray (KC)</t>
-        </is>
-      </c>
-      <c r="C203" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Emmett Johnson (KC)</t>
+        </is>
+      </c>
+      <c r="C203" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D203" s="14" t="n">
@@ -11046,7 +11043,7 @@
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18.05</t>
         </is>
       </c>
     </row>

--- a/assets/data/12guys1cup-cheat-sheet.xlsx
+++ b/assets/data/12guys1cup-cheat-sheet.xlsx
@@ -56,12 +56,6 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00B8386B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="002E7D32"/>
       <sz val="10"/>
     </font>
@@ -75,6 +69,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00E65100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00B8386B"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -120,11 +120,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D5ECD5"/>
       </patternFill>
     </fill>
@@ -136,6 +131,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -6453,20 +6453,20 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>Josh Allen (BUF)</t>
+          <t>Jahmyr Gibbs (DET)</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D4" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.02</t>
         </is>
       </c>
     </row>
@@ -6476,20 +6476,20 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Jahmyr Gibbs (DET)</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
+          <t>Bijan Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.03</t>
         </is>
       </c>
     </row>
@@ -6499,20 +6499,20 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Bijan Robinson (ATL)</t>
+          <t>Ja'Marr Chase (CIN)</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>
@@ -6522,20 +6522,20 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase (CIN)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
+          <t>Puka Nacua (LAR)</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
     </row>
@@ -6545,20 +6545,20 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Puka Nacua (LAR)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Christian McCaffrey (SF)</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
     </row>
@@ -6568,20 +6568,20 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Brock Bowers (LV)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jaxon Smith-Njigba (SEA)</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6591,20 +6591,20 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Trey McBride (ARI)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Amon-Ra St. Brown (DET)</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6614,20 +6614,20 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Lamar Jackson (BAL)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>CeeDee Lamb (DAL)</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6637,20 +6637,20 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Christian McCaffrey (SF)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
+          <t>Jonathan Taylor (IND)</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6660,20 +6660,20 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba (SEA)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>James Cook III (BUF)</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.11</t>
         </is>
       </c>
     </row>
@@ -6683,12 +6683,12 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown (DET)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>De'Von Achane (MIA)</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6706,20 +6706,20 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>CeeDee Lamb (DAL)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kenneth Walker (KC)</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -6729,20 +6729,20 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Tyler Warren (IND)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Chase Brown (CIN)</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -6752,20 +6752,20 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Colston Loveland (CHI)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Justin Jefferson (MIN)</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6775,20 +6775,20 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Jalen Hurts (PHI)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>A.J. Brown (NE)</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -6798,20 +6798,20 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Jayden Daniels (WAS)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Chris Olave (NO)</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>3.07</t>
         </is>
       </c>
     </row>
@@ -6821,20 +6821,20 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Joe Burrow (CIN)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Brock Bowers (LV)</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -6844,20 +6844,20 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Jonathan Taylor (IND)</t>
+          <t>Nico Collins (HOU)</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -6867,20 +6867,20 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>James Cook III (BUF)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Trey McBride (ARI)</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -6890,20 +6890,20 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Justin Jefferson (MIN)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
+          <t>Garrett Wilson (NYJ)</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -6913,10 +6913,10 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>A.J. Brown (NE)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
+          <t>Drake London (ATL)</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -6936,20 +6936,20 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Chris Olave (NO)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
+          <t>George Pickens (DAL)</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -6959,20 +6959,20 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Nico Collins (HOU)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
+          <t>Rashee Rice (KC)</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -6982,20 +6982,20 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Garrett Wilson (NYJ)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Omarion Hampton (LAC)</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7005,20 +7005,20 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Drake London (ATL)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Ashton Jeanty (LV)</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -7028,20 +7028,20 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>George Pickens (DAL)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
+          <t>Malik Nabers (NYG)</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -7051,20 +7051,20 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Rashee Rice (KC)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Saquon Barkley (PHI)</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -7074,20 +7074,20 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Harold Fannin Jr. (CLE)</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Zay Flowers (BAL)</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>4.05</t>
         </is>
       </c>
     </row>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Tucker Kraft (GB)</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Derrick Henry (BAL)</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.08</t>
         </is>
       </c>
     </row>
@@ -7120,20 +7120,20 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>George Kittle (SF)</t>
-        </is>
-      </c>
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>DeVonta Smith (PHI)</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>3.12</t>
         </is>
       </c>
     </row>
@@ -7143,20 +7143,20 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Drake Maye (NE)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jaylen Waddle (DEN)</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -7166,20 +7166,20 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>Jaxson Dart (NYG)</t>
+          <t>Jeremiyah Love (ARI)</t>
         </is>
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7189,20 +7189,20 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Caleb Williams (CHI)</t>
+          <t>Kyren Williams (LAR)</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D36" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Trevor Lawrence (JAX)</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Ladd McConkey (LAC)</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>4.02</t>
         </is>
       </c>
     </row>
@@ -7235,20 +7235,20 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>De'Von Achane (MIA)</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="inlineStr">
+          <t>Breece Hall (NYJ)</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7258,20 +7258,20 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Kenneth Walker (KC)</t>
+          <t>Emeka Egbuka (TB)</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>4.03</t>
         </is>
       </c>
     </row>
@@ -7281,20 +7281,20 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>Chase Brown (CIN)</t>
-        </is>
-      </c>
-      <c r="C40" s="17" t="inlineStr">
+          <t>D'Andre Swift (CHI)</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D40" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -7304,20 +7304,20 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Malik Nabers (NYG)</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="inlineStr">
+          <t>Tetairoa McMillan (CAR)</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>4.01</t>
         </is>
       </c>
     </row>
@@ -7327,20 +7327,20 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Zay Flowers (BAL)</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="inlineStr">
+          <t>Tee Higgins (CIN)</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D42" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.11</t>
         </is>
       </c>
     </row>
@@ -7350,20 +7350,20 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>DeVonta Smith (PHI)</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
+          <t>Carnell Tate (TEN)</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -7373,20 +7373,20 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Sam LaPorta (DET)</t>
-        </is>
-      </c>
-      <c r="C44" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Javonte Williams (DAL)</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7396,20 +7396,20 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Kyle Pitts Sr. (ATL)</t>
+          <t>Josh Allen (BUF)</t>
         </is>
       </c>
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>2.09</t>
         </is>
       </c>
     </row>
@@ -7419,20 +7419,20 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>Juwan Johnson (NO)</t>
-        </is>
-      </c>
-      <c r="C46" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Luther Burden III (CHI)</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D46" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -7442,20 +7442,20 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Dalton Schultz (HOU)</t>
-        </is>
-      </c>
-      <c r="C47" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Christian Watson (GB)</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -7465,20 +7465,20 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Travis Kelce (KC)</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Bucky Irving (TB)</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D48" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>4.06</t>
         </is>
       </c>
     </row>
@@ -7488,20 +7488,20 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>Jake Ferguson (DAL)</t>
-        </is>
-      </c>
-      <c r="C49" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Parker Washington (JAX)</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D49" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>7.04</t>
         </is>
       </c>
     </row>
@@ -7511,12 +7511,12 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Isaiah Likely (NYG)</t>
-        </is>
-      </c>
-      <c r="C50" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Travis Etienne Jr. (NO)</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D50" s="14" t="n">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>4.09</t>
         </is>
       </c>
     </row>
@@ -7534,20 +7534,20 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Dalton Kincaid (BUF)</t>
-        </is>
-      </c>
-      <c r="C51" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Cam Skattebo (NYG)</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D51" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>4.08</t>
         </is>
       </c>
     </row>
@@ -7557,20 +7557,20 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Dallas Goedert (PHI)</t>
-        </is>
-      </c>
-      <c r="C52" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Terry McLaurin (WAS)</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D52" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -7580,20 +7580,20 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Dak Prescott (DAL)</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jameson Williams (DET)</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -7603,20 +7603,20 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>Bo Nix (DEN)</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>DJ Moore (BUF)</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>5.09</t>
         </is>
       </c>
     </row>
@@ -7626,12 +7626,12 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Justin Herbert (LAC)</t>
+          <t>Bhayshul Tuten (JAX)</t>
         </is>
       </c>
       <c r="C55" s="16" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -7649,20 +7649,20 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Omarion Hampton (LAC)</t>
+          <t>Davante Adams (LAR)</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>5.02</t>
         </is>
       </c>
     </row>
@@ -7672,20 +7672,20 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Ashton Jeanty (LV)</t>
+          <t>Mike Evans (SF)</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D57" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -7695,12 +7695,12 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Saquon Barkley (PHI)</t>
+          <t>Rome Odunze (CHI)</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D58" s="14" t="n">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>6.05</t>
         </is>
       </c>
     </row>
@@ -7718,20 +7718,20 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Waddle (DEN)</t>
-        </is>
-      </c>
-      <c r="C59" s="18" t="inlineStr">
+          <t>Marvin Harrison Jr. (ARI)</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D59" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -7741,20 +7741,20 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>Ladd McConkey (LAC)</t>
-        </is>
-      </c>
-      <c r="C60" s="18" t="inlineStr">
+          <t>DK Metcalf (PIT)</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D60" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -7764,20 +7764,20 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Emeka Egbuka (TB)</t>
+          <t>Tyler Warren (IND)</t>
         </is>
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.11</t>
         </is>
       </c>
     </row>
@@ -7787,20 +7787,20 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan (CAR)</t>
+          <t>Colston Loveland (CHI)</t>
         </is>
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D62" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.04</t>
         </is>
       </c>
     </row>
@@ -7810,20 +7810,20 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Tee Higgins (CIN)</t>
-        </is>
-      </c>
-      <c r="C63" s="18" t="inlineStr">
+          <t>Alec Pierce (IND)</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D63" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>9.05</t>
         </is>
       </c>
     </row>
@@ -7833,20 +7833,20 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Carnell Tate (TEN)</t>
-        </is>
-      </c>
-      <c r="C64" s="18" t="inlineStr">
+          <t>Brian Thomas Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D64" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>7.02</t>
         </is>
       </c>
     </row>
@@ -7856,20 +7856,20 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Brenton Strange (JAX)</t>
-        </is>
-      </c>
-      <c r="C65" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Quinshon Judkins (CLE)</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D65" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -7879,20 +7879,20 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>Mark Andrews (BAL)</t>
-        </is>
-      </c>
-      <c r="C66" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>TreVeyon Henderson (NE)</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D66" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -7902,20 +7902,20 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>Hunter Henry (NE)</t>
-        </is>
-      </c>
-      <c r="C67" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>David Montgomery (HOU)</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D67" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -7925,20 +7925,20 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Brock Purdy (SF)</t>
-        </is>
-      </c>
-      <c r="C68" s="16" t="inlineStr">
+          <t>Lamar Jackson (BAL)</t>
+        </is>
+      </c>
+      <c r="C68" s="19" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
       <c r="D68" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>3.09</t>
         </is>
       </c>
     </row>
@@ -7948,20 +7948,20 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Jared Goff (DET)</t>
-        </is>
-      </c>
-      <c r="C69" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Chris Godwin Jr. (TB)</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D69" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>8.12</t>
         </is>
       </c>
     </row>
@@ -7971,12 +7971,12 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Matthew Stafford (LAR)</t>
+          <t>Jadarian Price (SEA)</t>
         </is>
       </c>
       <c r="C70" s="16" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D70" s="14" t="n">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -7994,20 +7994,20 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>Tyler Shough (NO)</t>
+          <t>MarShawn Lloyd (GB)</t>
         </is>
       </c>
       <c r="C71" s="16" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>15.06</t>
         </is>
       </c>
     </row>
@@ -8017,20 +8017,20 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Kyler Murray (MIN)</t>
+          <t>Rhamondre Stevenson (NE)</t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -8040,20 +8040,20 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Baker Mayfield (TB)</t>
-        </is>
-      </c>
-      <c r="C73" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Quentin Johnston (LAC)</t>
+        </is>
+      </c>
+      <c r="C73" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>10.05</t>
         </is>
       </c>
     </row>
@@ -8063,20 +8063,20 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Patrick Mahomes (KC)</t>
-        </is>
-      </c>
-      <c r="C74" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Michael Pittman Jr. (PIT)</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D74" s="14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.07</t>
         </is>
       </c>
     </row>
@@ -8086,20 +8086,20 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>Derrick Henry (BAL)</t>
-        </is>
-      </c>
-      <c r="C75" s="17" t="inlineStr">
+          <t>Rico Dowdle (PIT)</t>
+        </is>
+      </c>
+      <c r="C75" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.01</t>
         </is>
       </c>
     </row>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Jeremiyah Love (ARI)</t>
+          <t>Wan'Dale Robinson (TEN)</t>
         </is>
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D76" s="14" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>10.09</t>
         </is>
       </c>
     </row>
@@ -8132,12 +8132,12 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>Kyren Williams (LAR)</t>
-        </is>
-      </c>
-      <c r="C77" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Harold Fannin Jr. (CLE)</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D77" s="14" t="n">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -8155,20 +8155,20 @@
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Breece Hall (NYJ)</t>
+          <t>Michael Wilson (ARI)</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D78" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>7.11</t>
         </is>
       </c>
     </row>
@@ -8178,20 +8178,20 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>D'Andre Swift (CHI)</t>
+          <t>Stefon Diggs (WAS)</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D79" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>10.02</t>
         </is>
       </c>
     </row>
@@ -8201,20 +8201,20 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Javonte Williams (DAL)</t>
+          <t>Courtland Sutton (DEN)</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D80" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>7.09</t>
         </is>
       </c>
     </row>
@@ -8224,20 +8224,20 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>Cam Skattebo (NYG)</t>
-        </is>
-      </c>
-      <c r="C81" s="17" t="inlineStr">
+          <t>Jacory Croskey-Merritt (WAS)</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D81" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>10.06</t>
         </is>
       </c>
     </row>
@@ -8247,10 +8247,10 @@
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Bucky Irving (TB)</t>
-        </is>
-      </c>
-      <c r="C82" s="17" t="inlineStr">
+          <t>Kenny Gainwell (TB)</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8270,20 +8270,20 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>Luther Burden III (CHI)</t>
-        </is>
-      </c>
-      <c r="C83" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jaylen Warren (PIT)</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D83" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -8293,20 +8293,20 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Parker Washington (JAX)</t>
-        </is>
-      </c>
-      <c r="C84" s="18" t="inlineStr">
+          <t>Jordan Addison (MIN)</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D84" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>9.09</t>
         </is>
       </c>
     </row>
@@ -8316,20 +8316,20 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>Christian Watson (GB)</t>
-        </is>
-      </c>
-      <c r="C85" s="18" t="inlineStr">
+          <t>De'Zhaun Stribling (SF)</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D85" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>12.07</t>
         </is>
       </c>
     </row>
@@ -8339,20 +8339,20 @@
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Terry McLaurin (WAS)</t>
+          <t>Tucker Kraft (GB)</t>
         </is>
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D86" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8362,20 +8362,20 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>Jameson Williams (DET)</t>
-        </is>
-      </c>
-      <c r="C87" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jalen Hurts (PHI)</t>
+        </is>
+      </c>
+      <c r="C87" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D87" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.12</t>
         </is>
       </c>
     </row>
@@ -8385,20 +8385,20 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>DJ Moore (BUF)</t>
-        </is>
-      </c>
-      <c r="C88" s="18" t="inlineStr">
+          <t>Jayden Reed (GB)</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D88" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8408,20 +8408,20 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>Davante Adams (LAR)</t>
-        </is>
-      </c>
-      <c r="C89" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jayden Daniels (WAS)</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D89" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>6.04</t>
         </is>
       </c>
     </row>
@@ -8431,20 +8431,20 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Chig Okonkwo (WAS)</t>
+          <t>Joe Burrow (CIN)</t>
         </is>
       </c>
       <c r="C90" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D90" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -8454,20 +8454,20 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>Greg Dulcich (MIA)</t>
-        </is>
-      </c>
-      <c r="C91" s="19" t="inlineStr">
+          <t>George Kittle (SF)</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -8477,20 +8477,20 @@
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>T.J. Hockenson (MIN)</t>
-        </is>
-      </c>
-      <c r="C92" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Chuba Hubbard (CAR)</t>
+        </is>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D92" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>7.05</t>
         </is>
       </c>
     </row>
@@ -8500,20 +8500,20 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq (NYJ)</t>
-        </is>
-      </c>
-      <c r="C93" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>J.K. Dobbins (DEN)</t>
+        </is>
+      </c>
+      <c r="C93" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D93" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>8.1</t>
         </is>
       </c>
     </row>
@@ -8523,12 +8523,12 @@
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>Pat Freiermuth (PIT)</t>
-        </is>
-      </c>
-      <c r="C94" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tony Pollard (TEN)</t>
+        </is>
+      </c>
+      <c r="C94" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D94" s="14" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>7.12</t>
         </is>
       </c>
     </row>
@@ -8546,20 +8546,20 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>Malik Willis (MIA)</t>
-        </is>
-      </c>
-      <c r="C95" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Josh Downs (IND)</t>
+        </is>
+      </c>
+      <c r="C95" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D95" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>10.01</t>
         </is>
       </c>
     </row>
@@ -8569,20 +8569,20 @@
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Jordan Love (GB)</t>
+          <t>Jonathon Brooks (CAR)</t>
         </is>
       </c>
       <c r="C96" s="16" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D96" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>9.1</t>
         </is>
       </c>
     </row>
@@ -8592,20 +8592,20 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr. (NO)</t>
+          <t>Jakobi Meyers (JAX)</t>
         </is>
       </c>
       <c r="C97" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>10.1</t>
         </is>
       </c>
     </row>
@@ -8615,20 +8615,20 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten (JAX)</t>
+          <t>Romeo Doubs (NE)</t>
         </is>
       </c>
       <c r="C98" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D98" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -8638,20 +8638,20 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>Quinshon Judkins (CLE)</t>
-        </is>
-      </c>
-      <c r="C99" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Sam LaPorta (DET)</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -8661,20 +8661,20 @@
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson (NE)</t>
+          <t>Khalil Shakir (BUF)</t>
         </is>
       </c>
       <c r="C100" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D100" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>12.11</t>
         </is>
       </c>
     </row>
@@ -8684,20 +8684,20 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>David Montgomery (HOU)</t>
-        </is>
-      </c>
-      <c r="C101" s="17" t="inlineStr">
+          <t>Kyle Monangai (CHI)</t>
+        </is>
+      </c>
+      <c r="C101" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -8707,20 +8707,20 @@
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Jadarian Price (SEA)</t>
+          <t>Makai Lemon (PHI)</t>
         </is>
       </c>
       <c r="C102" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D102" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -8730,20 +8730,20 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>Mike Evans (SF)</t>
-        </is>
-      </c>
-      <c r="C103" s="18" t="inlineStr">
+          <t>Xavier Worthy (KC)</t>
+        </is>
+      </c>
+      <c r="C103" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -8753,20 +8753,20 @@
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>Rome Odunze (CHI)</t>
-        </is>
-      </c>
-      <c r="C104" s="18" t="inlineStr">
+          <t>Malik Washington (MIA)</t>
+        </is>
+      </c>
+      <c r="C104" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D104" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -8776,20 +8776,20 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr. (ARI)</t>
-        </is>
-      </c>
-      <c r="C105" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jordan Mason (MIN)</t>
+        </is>
+      </c>
+      <c r="C105" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>10.07</t>
         </is>
       </c>
     </row>
@@ -8799,20 +8799,20 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>DK Metcalf (PIT)</t>
-        </is>
-      </c>
-      <c r="C106" s="18" t="inlineStr">
+          <t>Jalen Coker (CAR)</t>
+        </is>
+      </c>
+      <c r="C106" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D106" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>13.02</t>
         </is>
       </c>
     </row>
@@ -8822,20 +8822,20 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Cade Otton (TB)</t>
-        </is>
-      </c>
-      <c r="C107" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Rashid Shaheed (SEA)</t>
+        </is>
+      </c>
+      <c r="C107" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>13.03</t>
         </is>
       </c>
     </row>
@@ -8845,12 +8845,12 @@
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>AJ Barner (SEA)</t>
-        </is>
-      </c>
-      <c r="C108" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>KC Concepcion (CLE)</t>
+        </is>
+      </c>
+      <c r="C108" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D108" s="14" t="n">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>11.01</t>
         </is>
       </c>
     </row>
@@ -8868,20 +8868,20 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>Oronde Gadsden (LAC)</t>
-        </is>
-      </c>
-      <c r="C109" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kayshon Boutte (HOU)</t>
+        </is>
+      </c>
+      <c r="C109" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>19.08</t>
         </is>
       </c>
     </row>
@@ -8891,12 +8891,12 @@
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>Colby Parkinson (LAR)</t>
+          <t>Drake Maye (NE)</t>
         </is>
       </c>
       <c r="C110" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D110" s="14" t="n">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -8914,12 +8914,12 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>David Njoku (LAC)</t>
-        </is>
-      </c>
-      <c r="C111" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Rachaad White (WAS)</t>
+        </is>
+      </c>
+      <c r="C111" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D111" s="14" t="n">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -8937,20 +8937,20 @@
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Darren Waller (CAR)</t>
-        </is>
-      </c>
-      <c r="C112" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Matthew Golden (GB)</t>
+        </is>
+      </c>
+      <c r="C112" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D112" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.07</t>
         </is>
       </c>
     </row>
@@ -8960,20 +8960,20 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>Mike Gesicki (CIN)</t>
+          <t>Jaxson Dart (NYG)</t>
         </is>
       </c>
       <c r="C113" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -8983,20 +8983,20 @@
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Cole Kmet (CHI)</t>
-        </is>
-      </c>
-      <c r="C114" s="19" t="inlineStr">
+          <t>Kyle Pitts Sr. (ATL)</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D114" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.1</t>
         </is>
       </c>
     </row>
@@ -9006,20 +9006,20 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>Gunnar Helm (TEN)</t>
-        </is>
-      </c>
-      <c r="C115" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Keenan Allen (IND)</t>
+        </is>
+      </c>
+      <c r="C115" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>17.07</t>
         </is>
       </c>
     </row>
@@ -9029,12 +9029,12 @@
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>Evan Engram (DEN)</t>
+          <t>Caleb Williams (CHI)</t>
         </is>
       </c>
       <c r="C116" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D116" s="14" t="n">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -9052,20 +9052,20 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>Terrance Ferguson (LAR)</t>
+          <t>Trevor Lawrence (JAX)</t>
         </is>
       </c>
       <c r="C117" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -9075,20 +9075,20 @@
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>Cam Ward (TEN)</t>
+          <t>Blake Corum (LAR)</t>
         </is>
       </c>
       <c r="C118" s="16" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D118" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>9.08</t>
         </is>
       </c>
     </row>
@@ -9098,20 +9098,20 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>C.J. Stroud (HOU)</t>
+          <t>RJ Harvey (DEN)</t>
         </is>
       </c>
       <c r="C119" s="16" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>7.08</t>
         </is>
       </c>
     </row>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Sam Darnold (SEA)</t>
-        </is>
-      </c>
-      <c r="C120" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Juwan Johnson (NO)</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D120" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9144,20 +9144,20 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>Daniel Jones (IND)</t>
-        </is>
-      </c>
-      <c r="C121" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jordyn Tyson (NO)</t>
+        </is>
+      </c>
+      <c r="C121" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D121" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>8.07</t>
         </is>
       </c>
     </row>
@@ -9167,20 +9167,20 @@
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>Bryce Young (CAR)</t>
-        </is>
-      </c>
-      <c r="C122" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Dalton Schultz (HOU)</t>
+        </is>
+      </c>
+      <c r="C122" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>17.01</t>
         </is>
       </c>
     </row>
@@ -9190,20 +9190,20 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>Aaron Rodgers (PIT)</t>
-        </is>
-      </c>
-      <c r="C123" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Travis Kelce (KC)</t>
+        </is>
+      </c>
+      <c r="C123" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>8.08</t>
         </is>
       </c>
     </row>
@@ -9213,12 +9213,12 @@
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>Geno Smith (NYJ)</t>
-        </is>
-      </c>
-      <c r="C124" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tre Tucker (LV)</t>
+        </is>
+      </c>
+      <c r="C124" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D124" s="14" t="n">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17.1</t>
         </is>
       </c>
     </row>
@@ -9236,20 +9236,20 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson (NE)</t>
-        </is>
-      </c>
-      <c r="C125" s="17" t="inlineStr">
+          <t>Aaron Jones Sr. (MIN)</t>
+        </is>
+      </c>
+      <c r="C125" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -9259,20 +9259,20 @@
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>Rico Dowdle (PIT)</t>
-        </is>
-      </c>
-      <c r="C126" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jake Ferguson (DAL)</t>
+        </is>
+      </c>
+      <c r="C126" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>9.02</t>
         </is>
       </c>
     </row>
@@ -9282,20 +9282,20 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>Josh Jacobs (GB)</t>
-        </is>
-      </c>
-      <c r="C127" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dak Prescott (DAL)</t>
+        </is>
+      </c>
+      <c r="C127" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>7.07</t>
         </is>
       </c>
     </row>
@@ -9305,12 +9305,12 @@
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt (WAS)</t>
-        </is>
-      </c>
-      <c r="C128" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dalton Kincaid (BUF)</t>
+        </is>
+      </c>
+      <c r="C128" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D128" s="14" t="n">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -9328,20 +9328,20 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>Kenny Gainwell (TB)</t>
-        </is>
-      </c>
-      <c r="C129" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Isaiah Likely (NYG)</t>
+        </is>
+      </c>
+      <c r="C129" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D129" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -9351,10 +9351,10 @@
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Warren (PIT)</t>
-        </is>
-      </c>
-      <c r="C130" s="17" t="inlineStr">
+          <t>Tyjae Spears (TEN)</t>
+        </is>
+      </c>
+      <c r="C130" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -9374,20 +9374,20 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>Chuba Hubbard (CAR)</t>
-        </is>
-      </c>
-      <c r="C131" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Justin Herbert (LAC)</t>
+        </is>
+      </c>
+      <c r="C131" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -9397,20 +9397,20 @@
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>Tony Pollard (TEN)</t>
-        </is>
-      </c>
-      <c r="C132" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dallas Goedert (PHI)</t>
+        </is>
+      </c>
+      <c r="C132" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D132" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -9420,12 +9420,12 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>J.K. Dobbins (DEN)</t>
-        </is>
-      </c>
-      <c r="C133" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Bo Nix (DEN)</t>
+        </is>
+      </c>
+      <c r="C133" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D133" s="14" t="n">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>10.12</t>
         </is>
       </c>
     </row>
@@ -9443,20 +9443,20 @@
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Jonathon Brooks (CAR)</t>
-        </is>
-      </c>
-      <c r="C134" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Brock Purdy (SF)</t>
+        </is>
+      </c>
+      <c r="C134" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D134" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>11.02</t>
         </is>
       </c>
     </row>
@@ -9466,20 +9466,20 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>Kyle Monangai (CHI)</t>
+          <t>Omar Cooper Jr. (NYJ)</t>
         </is>
       </c>
       <c r="C135" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>17.02</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>Jordan Mason (MIN)</t>
-        </is>
-      </c>
-      <c r="C136" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jared Goff (DET)</t>
+        </is>
+      </c>
+      <c r="C136" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D136" s="14" t="n">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>12.03</t>
         </is>
       </c>
     </row>
@@ -9512,20 +9512,20 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>Rachaad White (WAS)</t>
+          <t>Deebo Samuel Sr. (SF)</t>
         </is>
       </c>
       <c r="C137" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>11.11</t>
         </is>
       </c>
     </row>
@@ -9535,20 +9535,20 @@
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>Blake Corum (LAR)</t>
-        </is>
-      </c>
-      <c r="C138" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tyler Shough (NO)</t>
+        </is>
+      </c>
+      <c r="C138" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>16.07</t>
         </is>
       </c>
     </row>
@@ -9558,20 +9558,20 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>Alec Pierce (IND)</t>
-        </is>
-      </c>
-      <c r="C139" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Matthew Stafford (LAR)</t>
+        </is>
+      </c>
+      <c r="C139" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.01</t>
         </is>
       </c>
     </row>
@@ -9581,20 +9581,20 @@
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C140" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kyler Murray (MIN)</t>
+        </is>
+      </c>
+      <c r="C140" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D140" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>14.03</t>
         </is>
       </c>
     </row>
@@ -9604,20 +9604,20 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr. (TB)</t>
-        </is>
-      </c>
-      <c r="C141" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jordan Love (GB)</t>
+        </is>
+      </c>
+      <c r="C141" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>13.05</t>
         </is>
       </c>
     </row>
@@ -9627,20 +9627,20 @@
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>Quentin Johnston (LAC)</t>
-        </is>
-      </c>
-      <c r="C142" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Baker Mayfield (TB)</t>
+        </is>
+      </c>
+      <c r="C142" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -9650,20 +9650,20 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>Michael Pittman Jr. (PIT)</t>
-        </is>
-      </c>
-      <c r="C143" s="18" t="inlineStr">
+          <t>Denzel Boston (CLE)</t>
+        </is>
+      </c>
+      <c r="C143" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9673,20 +9673,20 @@
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson (TEN)</t>
-        </is>
-      </c>
-      <c r="C144" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Patrick Mahomes (KC)</t>
+        </is>
+      </c>
+      <c r="C144" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -9696,20 +9696,20 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>Mason Taylor (NYJ)</t>
-        </is>
-      </c>
-      <c r="C145" s="19" t="inlineStr">
+          <t>Brenton Strange (JAX)</t>
+        </is>
+      </c>
+      <c r="C145" s="18" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>13.08</t>
         </is>
       </c>
     </row>
@@ -9719,16 +9719,16 @@
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>Charlie Kolar (LAC)</t>
-        </is>
-      </c>
-      <c r="C146" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Dontayvion Wicks (PHI)</t>
+        </is>
+      </c>
+      <c r="C146" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
@@ -9742,10 +9742,10 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Michael Mayer (LV)</t>
-        </is>
-      </c>
-      <c r="C147" s="19" t="inlineStr">
+          <t>Mark Andrews (BAL)</t>
+        </is>
+      </c>
+      <c r="C147" s="18" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.09</t>
         </is>
       </c>
     </row>
@@ -9765,20 +9765,20 @@
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>Dawson Knox (BUF)</t>
-        </is>
-      </c>
-      <c r="C148" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Pat Bryant (DEN)</t>
+        </is>
+      </c>
+      <c r="C148" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19.11</t>
         </is>
       </c>
     </row>
@@ -9788,20 +9788,20 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>Eli Stowers (PHI)</t>
+          <t>Malik Willis (MIA)</t>
         </is>
       </c>
       <c r="C149" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -9811,20 +9811,20 @@
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>Luke Musgrave (GB)</t>
-        </is>
-      </c>
-      <c r="C150" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jalen Nailor (LV)</t>
+        </is>
+      </c>
+      <c r="C150" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -9834,20 +9834,20 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Ja'Tavion Sanders (CAR)</t>
-        </is>
-      </c>
-      <c r="C151" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Woody Marks (HOU)</t>
+        </is>
+      </c>
+      <c r="C151" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D151" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.04</t>
         </is>
       </c>
     </row>
@@ -9857,20 +9857,20 @@
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Theo Johnson (NYG)</t>
-        </is>
-      </c>
-      <c r="C152" s="19" t="inlineStr">
+          <t>Hunter Henry (NE)</t>
+        </is>
+      </c>
+      <c r="C152" s="18" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -9880,20 +9880,20 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>Noah Gray (KC)</t>
-        </is>
-      </c>
-      <c r="C153" s="19" t="inlineStr">
+          <t>Chig Okonkwo (WAS)</t>
+        </is>
+      </c>
+      <c r="C153" s="18" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9903,20 +9903,20 @@
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>Tommy Tremble (CAR)</t>
-        </is>
-      </c>
-      <c r="C154" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Chris Rodriguez Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C154" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12.08</t>
         </is>
       </c>
     </row>
@@ -9926,20 +9926,20 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>Elijah Arroyo (SEA)</t>
-        </is>
-      </c>
-      <c r="C155" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Travis Hunter (JAX)</t>
+        </is>
+      </c>
+      <c r="C155" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9949,20 +9949,20 @@
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Darnell Washington (PIT)</t>
-        </is>
-      </c>
-      <c r="C156" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Cooper Kupp (SEA)</t>
+        </is>
+      </c>
+      <c r="C156" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19.05</t>
         </is>
       </c>
     </row>
@@ -9972,12 +9972,12 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Max Klare (LAR)</t>
-        </is>
-      </c>
-      <c r="C157" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jerry Jeudy (CLE)</t>
+        </is>
+      </c>
+      <c r="C157" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D157" s="14" t="n">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="E157" s="14" t="inlineStr">
         <is>
-          <t>21.09</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -9995,20 +9995,20 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Jake Tonges (SF)</t>
+          <t>Cam Ward (TEN)</t>
         </is>
       </c>
       <c r="C158" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>21.01</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10018,20 +10018,20 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Ben Sinnott (WAS)</t>
-        </is>
-      </c>
-      <c r="C159" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Isiah Pacheco (DET)</t>
+        </is>
+      </c>
+      <c r="C159" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E159" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -10041,12 +10041,12 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>Noah Fant (NO)</t>
+          <t>C.J. Stroud (HOU)</t>
         </is>
       </c>
       <c r="C160" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18.01</t>
         </is>
       </c>
     </row>
@@ -10064,16 +10064,16 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>Justin Joly (DEN)</t>
-        </is>
-      </c>
-      <c r="C161" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>DeMario Douglas (NE)</t>
+        </is>
+      </c>
+      <c r="C161" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E161" s="14" t="inlineStr">
         <is>
@@ -10087,20 +10087,20 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Nate Boerkircher (JAX)</t>
-        </is>
-      </c>
-      <c r="C162" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Malachi Fields (NYG)</t>
+        </is>
+      </c>
+      <c r="C162" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D162" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19.04</t>
         </is>
       </c>
     </row>
@@ -10110,20 +10110,20 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>Oscar Delp (NO)</t>
+          <t>Sam Darnold (SEA)</t>
         </is>
       </c>
       <c r="C163" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E163" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.05</t>
         </is>
       </c>
     </row>
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Jacoby Brissett (ARI)</t>
+          <t>Keaton Mitchell (LAC)</t>
         </is>
       </c>
       <c r="C164" s="16" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10156,20 +10156,20 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>Tua Tagovailoa (ATL)</t>
-        </is>
-      </c>
-      <c r="C165" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Adonai Mitchell (NYJ)</t>
+        </is>
+      </c>
+      <c r="C165" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E165" s="14" t="inlineStr">
         <is>
-          <t>20.09</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10179,20 +10179,20 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Shedeur Sanders (CLE)</t>
-        </is>
-      </c>
-      <c r="C166" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Ja'Kobi Lane (BAL)</t>
+        </is>
+      </c>
+      <c r="C166" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>14.02</t>
         </is>
       </c>
     </row>
@@ -10202,10 +10202,10 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>Fernando Mendoza (LV)</t>
-        </is>
-      </c>
-      <c r="C167" s="16" t="inlineStr">
+          <t>Daniel Jones (IND)</t>
+        </is>
+      </c>
+      <c r="C167" s="19" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -10215,7 +10215,7 @@
       </c>
       <c r="E167" s="14" t="inlineStr">
         <is>
-          <t>16.01</t>
+          <t>17.11</t>
         </is>
       </c>
     </row>
@@ -10225,20 +10225,20 @@
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>Michael Penix Jr. (ATL)</t>
-        </is>
-      </c>
-      <c r="C168" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tank Dell (HOU)</t>
+        </is>
+      </c>
+      <c r="C168" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10248,20 +10248,20 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>Kirk Cousins (LV)</t>
-        </is>
-      </c>
-      <c r="C169" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Germie Bernard (PIT)</t>
+        </is>
+      </c>
+      <c r="C169" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E169" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10271,12 +10271,12 @@
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Deshaun Watson (CLE)</t>
+          <t>Zach Charbonnet (SEA)</t>
         </is>
       </c>
       <c r="C170" s="16" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D170" s="14" t="n">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.04</t>
         </is>
       </c>
     </row>
@@ -10294,20 +10294,20 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>Carson Beck (ARI)</t>
-        </is>
-      </c>
-      <c r="C171" s="16" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Cyrus Allen (KC)</t>
+        </is>
+      </c>
+      <c r="C171" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -10317,20 +10317,20 @@
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>RJ Harvey (DEN)</t>
-        </is>
-      </c>
-      <c r="C172" s="17" t="inlineStr">
+          <t>Tyler Allgeier (ARI)</t>
+        </is>
+      </c>
+      <c r="C172" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -10340,10 +10340,10 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd (GB)</t>
-        </is>
-      </c>
-      <c r="C173" s="17" t="inlineStr">
+          <t>Dylan Sampson (CLE)</t>
+        </is>
+      </c>
+      <c r="C173" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -10363,20 +10363,20 @@
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr. (MIN)</t>
+          <t>Kyle Williams (NE)</t>
         </is>
       </c>
       <c r="C174" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>19.06</t>
         </is>
       </c>
     </row>
@@ -10386,12 +10386,12 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>Tyjae Spears (TEN)</t>
+          <t>Calvin Ridley (TEN)</t>
         </is>
       </c>
       <c r="C175" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="E175" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>22.01</t>
         </is>
       </c>
     </row>
@@ -10409,20 +10409,20 @@
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>Woody Marks (HOU)</t>
-        </is>
-      </c>
-      <c r="C176" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>T.J. Hockenson (MIN)</t>
+        </is>
+      </c>
+      <c r="C176" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D176" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -10432,20 +10432,20 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Chris Rodriguez Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C177" s="17" t="inlineStr">
+          <t>Mike Washington Jr. (LV)</t>
+        </is>
+      </c>
+      <c r="C177" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E177" s="14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>15.05</t>
         </is>
       </c>
     </row>
@@ -10455,12 +10455,12 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Isiah Pacheco (DET)</t>
-        </is>
-      </c>
-      <c r="C178" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Greg Dulcich (MIA)</t>
+        </is>
+      </c>
+      <c r="C178" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10478,20 +10478,20 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Michael Wilson (ARI)</t>
+          <t>Kenyon Sadiq (NYJ)</t>
         </is>
       </c>
       <c r="C179" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E179" s="14" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>13.1</t>
         </is>
       </c>
     </row>
@@ -10501,20 +10501,20 @@
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Stefon Diggs (WAS)</t>
-        </is>
-      </c>
-      <c r="C180" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonah Coleman (DEN)</t>
+        </is>
+      </c>
+      <c r="C180" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>15.03</t>
         </is>
       </c>
     </row>
@@ -10524,20 +10524,20 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>Courtland Sutton (DEN)</t>
-        </is>
-      </c>
-      <c r="C181" s="18" t="inlineStr">
+          <t>Tre' Harris (LAC)</t>
+        </is>
+      </c>
+      <c r="C181" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10547,20 +10547,20 @@
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Jordan Addison (MIN)</t>
-        </is>
-      </c>
-      <c r="C182" s="18" t="inlineStr">
+          <t>Keon Coleman (BUF)</t>
+        </is>
+      </c>
+      <c r="C182" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D182" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>20.07</t>
         </is>
       </c>
     </row>
@@ -10570,12 +10570,12 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling (SF)</t>
-        </is>
-      </c>
-      <c r="C183" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyrone Tracy Jr. (NYG)</t>
+        </is>
+      </c>
+      <c r="C183" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D183" s="14" t="n">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="E183" s="14" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10593,20 +10593,20 @@
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>Jayden Reed (GB)</t>
+          <t>Pat Freiermuth (PIT)</t>
         </is>
       </c>
       <c r="C184" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D184" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10616,20 +10616,20 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Josh Downs (IND)</t>
-        </is>
-      </c>
-      <c r="C185" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Aaron Rodgers (PIT)</t>
+        </is>
+      </c>
+      <c r="C185" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E185" s="14" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10639,20 +10639,20 @@
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Jakobi Meyers (JAX)</t>
-        </is>
-      </c>
-      <c r="C186" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Bryce Young (CAR)</t>
+        </is>
+      </c>
+      <c r="C186" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D186" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>19.12</t>
         </is>
       </c>
     </row>
@@ -10662,10 +10662,10 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>Romeo Doubs (NE)</t>
-        </is>
-      </c>
-      <c r="C187" s="18" t="inlineStr">
+          <t>Zachariah Branch (ATL)</t>
+        </is>
+      </c>
+      <c r="C187" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -10675,7 +10675,7 @@
       </c>
       <c r="E187" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -10685,20 +10685,20 @@
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Khalil Shakir (BUF)</t>
-        </is>
-      </c>
-      <c r="C188" s="18" t="inlineStr">
+          <t>Ryan Flournoy (DAL)</t>
+        </is>
+      </c>
+      <c r="C188" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D188" s="14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10708,20 +10708,20 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Keaton Mitchell (LAC)</t>
-        </is>
-      </c>
-      <c r="C189" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Cade Otton (TB)</t>
+        </is>
+      </c>
+      <c r="C189" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E189" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>20.06</t>
         </is>
       </c>
     </row>
@@ -10731,20 +10731,20 @@
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Zach Charbonnet (SEA)</t>
-        </is>
-      </c>
-      <c r="C190" s="17" t="inlineStr">
+          <t>Tank Bigsby (PHI)</t>
+        </is>
+      </c>
+      <c r="C190" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D190" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E190" s="14" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10754,20 +10754,20 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>Tyler Allgeier (ARI)</t>
-        </is>
-      </c>
-      <c r="C191" s="17" t="inlineStr">
+          <t>Alvin Kamara (NO)</t>
+        </is>
+      </c>
+      <c r="C191" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E191" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>14.07</t>
         </is>
       </c>
     </row>
@@ -10777,20 +10777,20 @@
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Dylan Sampson (CLE)</t>
+          <t>Caleb Douglas (MIA)</t>
         </is>
       </c>
       <c r="C192" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D192" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>18.09</t>
         </is>
       </c>
     </row>
@@ -10800,20 +10800,20 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Jonah Coleman (DEN)</t>
-        </is>
-      </c>
-      <c r="C193" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Geno Smith (NYJ)</t>
+        </is>
+      </c>
+      <c r="C193" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10823,20 +10823,20 @@
       </c>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>Mike Washington Jr. (LV)</t>
-        </is>
-      </c>
-      <c r="C194" s="17" t="inlineStr">
+          <t>Najee Harris (NYG)</t>
+        </is>
+      </c>
+      <c r="C194" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D194" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E194" s="14" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10846,20 +10846,20 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr. (NYG)</t>
-        </is>
-      </c>
-      <c r="C195" s="17" t="inlineStr">
+          <t>Brian Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C195" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E195" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>13.12</t>
         </is>
       </c>
     </row>
@@ -10869,20 +10869,20 @@
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>Tank Bigsby (PHI)</t>
+          <t>Devaughn Vele (NO)</t>
         </is>
       </c>
       <c r="C196" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D196" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E196" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10892,20 +10892,20 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>Alvin Kamara (NO)</t>
-        </is>
-      </c>
-      <c r="C197" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>AJ Barner (SEA)</t>
+        </is>
+      </c>
+      <c r="C197" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D197" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E197" s="14" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10915,20 +10915,20 @@
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Brian Robinson (ATL)</t>
+          <t>Jaylin Noel (HOU)</t>
         </is>
       </c>
       <c r="C198" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D198" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>18.1</t>
         </is>
       </c>
     </row>
@@ -10938,12 +10938,12 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>Jordan James (SF)</t>
+          <t>Darius Slayton (NYG)</t>
         </is>
       </c>
       <c r="C199" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D199" s="14" t="n">
@@ -10961,12 +10961,12 @@
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Kimani Vidal (LAC)</t>
-        </is>
-      </c>
-      <c r="C200" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Oronde Gadsden (LAC)</t>
+        </is>
+      </c>
+      <c r="C200" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D200" s="14" t="n">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
@@ -10984,12 +10984,12 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>Justice Hill (BAL)</t>
+          <t>Rashod Bateman (BAL)</t>
         </is>
       </c>
       <c r="C201" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D201" s="14" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.05</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>Samaje Perine (CIN)</t>
+          <t>Jalen Tolbert (MIA)</t>
         </is>
       </c>
       <c r="C202" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D202" s="14" t="n">
@@ -11030,20 +11030,20 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>Emmett Johnson (KC)</t>
+          <t>Tory Horton (SEA)</t>
         </is>
       </c>
       <c r="C203" s="17" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D203" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>

--- a/assets/data/12guys1cup-cheat-sheet.xlsx
+++ b/assets/data/12guys1cup-cheat-sheet.xlsx
@@ -56,13 +56,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="002E7D32"/>
+      <color rgb="001565C0"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001565C0"/>
+      <color rgb="002E7D32"/>
       <sz val="10"/>
     </font>
     <font>
@@ -120,12 +120,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5ECD5"/>
+        <fgColor rgb="00D4E4F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4E4F7"/>
+        <fgColor rgb="00D5ECD5"/>
       </patternFill>
     </fill>
     <fill>
@@ -6453,20 +6453,20 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>Jahmyr Gibbs (DET)</t>
+          <t>Puka Nacua (LAR)</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D4" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
     </row>
@@ -6476,20 +6476,20 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Bijan Robinson (ATL)</t>
+          <t>Ja'Marr Chase (CIN)</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>
@@ -6499,20 +6499,20 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase (CIN)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
+          <t>Jaxon Smith-Njigba (SEA)</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6522,20 +6522,20 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Puka Nacua (LAR)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
+          <t>Amon-Ra St. Brown (DET)</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6545,20 +6545,20 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Christian McCaffrey (SF)</t>
+          <t>Drake London (ATL)</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -6568,20 +6568,20 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba (SEA)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
+          <t>Justin Jefferson (MIN)</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6591,16 +6591,16 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown (DET)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
+          <t>CeeDee Lamb (DAL)</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
@@ -6614,20 +6614,20 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>CeeDee Lamb (DAL)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
+          <t>Rashee Rice (KC)</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -6637,20 +6637,20 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Jonathan Taylor (IND)</t>
+          <t>Chris Olave (NO)</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>3.07</t>
         </is>
       </c>
     </row>
@@ -6660,20 +6660,20 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>James Cook III (BUF)</t>
+          <t>A.J. Brown (NE)</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -6683,20 +6683,20 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>De'Von Achane (MIA)</t>
+          <t>George Pickens (DAL)</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -6706,20 +6706,20 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Kenneth Walker (KC)</t>
+          <t>Nico Collins (HOU)</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -6729,20 +6729,20 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Chase Brown (CIN)</t>
+          <t>Garrett Wilson (NYJ)</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -6752,20 +6752,20 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Justin Jefferson (MIN)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
+          <t>Zay Flowers (BAL)</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>4.05</t>
         </is>
       </c>
     </row>
@@ -6775,20 +6775,20 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>A.J. Brown (NE)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
+          <t>Malik Nabers (NYG)</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -6798,20 +6798,20 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Chris Olave (NO)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
+          <t>DeVonta Smith (PHI)</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.12</t>
         </is>
       </c>
     </row>
@@ -6821,20 +6821,20 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Brock Bowers (LV)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tetairoa McMillan (CAR)</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>4.01</t>
         </is>
       </c>
     </row>
@@ -6844,20 +6844,20 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Nico Collins (HOU)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
+          <t>Emeka Egbuka (TB)</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.03</t>
         </is>
       </c>
     </row>
@@ -6867,20 +6867,20 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Trey McBride (ARI)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Davante Adams (LAR)</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>5.02</t>
         </is>
       </c>
     </row>
@@ -6890,20 +6890,20 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Garrett Wilson (NYJ)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
+          <t>Tee Higgins (CIN)</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.11</t>
         </is>
       </c>
     </row>
@@ -6913,20 +6913,20 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Drake London (ATL)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
+          <t>Ladd McConkey (LAC)</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>4.02</t>
         </is>
       </c>
     </row>
@@ -6936,20 +6936,20 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>George Pickens (DAL)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
+          <t>Jameson Williams (DET)</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -6959,20 +6959,20 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Rashee Rice (KC)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
+          <t>Jaylen Waddle (DEN)</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Omarion Hampton (LAC)</t>
+          <t>Terry McLaurin (WAS)</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -7005,20 +7005,20 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Ashton Jeanty (LV)</t>
+          <t>DJ Moore (BUF)</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>5.09</t>
         </is>
       </c>
     </row>
@@ -7028,20 +7028,20 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Malik Nabers (NYG)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
+          <t>Luther Burden III (CHI)</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -7051,12 +7051,12 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Saquon Barkley (PHI)</t>
+          <t>Rome Odunze (CHI)</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>6.05</t>
         </is>
       </c>
     </row>
@@ -7074,20 +7074,20 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Zay Flowers (BAL)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
+          <t>Mike Evans (SF)</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Derrick Henry (BAL)</t>
+          <t>Marvin Harrison Jr. (ARI)</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -7120,10 +7120,10 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>DeVonta Smith (PHI)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
+          <t>Courtland Sutton (DEN)</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>7.09</t>
         </is>
       </c>
     </row>
@@ -7143,20 +7143,20 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Waddle (DEN)</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
+          <t>DK Metcalf (PIT)</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -7166,20 +7166,20 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>Jeremiyah Love (ARI)</t>
+          <t>Christian Watson (GB)</t>
         </is>
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -7189,20 +7189,20 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Kyren Williams (LAR)</t>
+          <t>Alec Pierce (IND)</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D36" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>9.05</t>
         </is>
       </c>
     </row>
@@ -7212,20 +7212,20 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Ladd McConkey (LAC)</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
+          <t>Michael Pittman Jr. (PIT)</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>9.07</t>
         </is>
       </c>
     </row>
@@ -7235,20 +7235,20 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Breece Hall (NYJ)</t>
+          <t>Parker Washington (JAX)</t>
         </is>
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>7.04</t>
         </is>
       </c>
     </row>
@@ -7258,20 +7258,20 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Emeka Egbuka (TB)</t>
-        </is>
-      </c>
-      <c r="C39" s="17" t="inlineStr">
+          <t>Brian Thomas Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>7.02</t>
         </is>
       </c>
     </row>
@@ -7281,20 +7281,20 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>D'Andre Swift (CHI)</t>
+          <t>Wan'Dale Robinson (TEN)</t>
         </is>
       </c>
       <c r="C40" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D40" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>10.09</t>
         </is>
       </c>
     </row>
@@ -7304,20 +7304,20 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan (CAR)</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="inlineStr">
+          <t>Jakobi Meyers (JAX)</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>10.1</t>
         </is>
       </c>
     </row>
@@ -7327,20 +7327,20 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Tee Higgins (CIN)</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="inlineStr">
+          <t>Carnell Tate (TEN)</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D42" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -7350,20 +7350,20 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Carnell Tate (TEN)</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
+          <t>Michael Wilson (ARI)</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>7.11</t>
         </is>
       </c>
     </row>
@@ -7373,20 +7373,20 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Javonte Williams (DAL)</t>
+          <t>Jayden Reed (GB)</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -7396,20 +7396,20 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Josh Allen (BUF)</t>
-        </is>
-      </c>
-      <c r="C45" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Chris Godwin Jr. (TB)</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>8.12</t>
         </is>
       </c>
     </row>
@@ -7419,20 +7419,20 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>Luther Burden III (CHI)</t>
-        </is>
-      </c>
-      <c r="C46" s="17" t="inlineStr">
+          <t>KC Concepcion (CLE)</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D46" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>11.01</t>
         </is>
       </c>
     </row>
@@ -7442,20 +7442,20 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Christian Watson (GB)</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="inlineStr">
+          <t>Quentin Johnston (LAC)</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>10.05</t>
         </is>
       </c>
     </row>
@@ -7465,20 +7465,20 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Bucky Irving (TB)</t>
+          <t>Jordan Addison (MIN)</t>
         </is>
       </c>
       <c r="C48" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D48" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>9.09</t>
         </is>
       </c>
     </row>
@@ -7488,20 +7488,20 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>Parker Washington (JAX)</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="inlineStr">
+          <t>Xavier Worthy (KC)</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D49" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -7511,20 +7511,20 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr. (NO)</t>
+          <t>Stefon Diggs (WAS)</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>10.02</t>
         </is>
       </c>
     </row>
@@ -7534,20 +7534,20 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Cam Skattebo (NYG)</t>
+          <t>Khalil Shakir (BUF)</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D51" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>12.11</t>
         </is>
       </c>
     </row>
@@ -7557,20 +7557,20 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Terry McLaurin (WAS)</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="inlineStr">
+          <t>De'Zhaun Stribling (SF)</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D52" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>12.07</t>
         </is>
       </c>
     </row>
@@ -7580,20 +7580,20 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Jameson Williams (DET)</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
+          <t>Romeo Doubs (NE)</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -7603,20 +7603,20 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>DJ Moore (BUF)</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
+          <t>Josh Downs (IND)</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>10.01</t>
         </is>
       </c>
     </row>
@@ -7626,20 +7626,20 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten (JAX)</t>
+          <t>Deebo Samuel Sr. (SF)</t>
         </is>
       </c>
       <c r="C55" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>11.11</t>
         </is>
       </c>
     </row>
@@ -7649,10 +7649,10 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Davante Adams (LAR)</t>
-        </is>
-      </c>
-      <c r="C56" s="17" t="inlineStr">
+          <t>Matthew Golden (GB)</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>11.07</t>
         </is>
       </c>
     </row>
@@ -7672,20 +7672,20 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Mike Evans (SF)</t>
-        </is>
-      </c>
-      <c r="C57" s="17" t="inlineStr">
+          <t>Denzel Boston (CLE)</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D57" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -7695,20 +7695,20 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Rome Odunze (CHI)</t>
-        </is>
-      </c>
-      <c r="C58" s="17" t="inlineStr">
+          <t>Jalen Coker (CAR)</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D58" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>13.02</t>
         </is>
       </c>
     </row>
@@ -7718,20 +7718,20 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr. (ARI)</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
+          <t>Rashid Shaheed (SEA)</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D59" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>13.03</t>
         </is>
       </c>
     </row>
@@ -7741,20 +7741,20 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>DK Metcalf (PIT)</t>
-        </is>
-      </c>
-      <c r="C60" s="17" t="inlineStr">
+          <t>Jerry Jeudy (CLE)</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D60" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -7764,20 +7764,20 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Tyler Warren (IND)</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Makai Lemon (PHI)</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -7787,20 +7787,20 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Colston Loveland (CHI)</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Calvin Ridley (TEN)</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D62" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>22.01</t>
         </is>
       </c>
     </row>
@@ -7810,10 +7810,10 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Alec Pierce (IND)</t>
-        </is>
-      </c>
-      <c r="C63" s="17" t="inlineStr">
+          <t>Tre Tucker (LV)</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>17.1</t>
         </is>
       </c>
     </row>
@@ -7833,20 +7833,20 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
+          <t>Keenan Allen (IND)</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D64" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>17.07</t>
         </is>
       </c>
     </row>
@@ -7856,20 +7856,20 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Quinshon Judkins (CLE)</t>
+          <t>Kayshon Boutte (HOU)</t>
         </is>
       </c>
       <c r="C65" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D65" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>19.08</t>
         </is>
       </c>
     </row>
@@ -7879,20 +7879,20 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson (NE)</t>
+          <t>Rashod Bateman (BAL)</t>
         </is>
       </c>
       <c r="C66" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D66" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>20.05</t>
         </is>
       </c>
     </row>
@@ -7902,20 +7902,20 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>David Montgomery (HOU)</t>
+          <t>Ja'Kobi Lane (BAL)</t>
         </is>
       </c>
       <c r="C67" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D67" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>14.02</t>
         </is>
       </c>
     </row>
@@ -7925,12 +7925,12 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Lamar Jackson (BAL)</t>
-        </is>
-      </c>
-      <c r="C68" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jalen Nailor (LV)</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D68" s="14" t="n">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -7948,20 +7948,20 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr. (TB)</t>
-        </is>
-      </c>
-      <c r="C69" s="17" t="inlineStr">
+          <t>Devaughn Vele (NO)</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D69" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -7971,12 +7971,12 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Jadarian Price (SEA)</t>
+          <t>Cooper Kupp (SEA)</t>
         </is>
       </c>
       <c r="C70" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D70" s="14" t="n">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>19.05</t>
         </is>
       </c>
     </row>
@@ -7994,20 +7994,20 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd (GB)</t>
+          <t>Jaylin Noel (HOU)</t>
         </is>
       </c>
       <c r="C71" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>18.1</t>
         </is>
       </c>
     </row>
@@ -8017,20 +8017,20 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson (NE)</t>
+          <t>Adonai Mitchell (NYJ)</t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -8040,20 +8040,20 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Quentin Johnston (LAC)</t>
-        </is>
-      </c>
-      <c r="C73" s="17" t="inlineStr">
+          <t>Malik Washington (MIA)</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -8063,10 +8063,10 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Michael Pittman Jr. (PIT)</t>
-        </is>
-      </c>
-      <c r="C74" s="17" t="inlineStr">
+          <t>Germie Bernard (PIT)</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8076,7 +8076,7 @@
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -8086,20 +8086,20 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>Rico Dowdle (PIT)</t>
+          <t>Jordyn Tyson (NO)</t>
         </is>
       </c>
       <c r="C75" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>8.07</t>
         </is>
       </c>
     </row>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson (TEN)</t>
-        </is>
-      </c>
-      <c r="C76" s="17" t="inlineStr">
+          <t>Caleb Douglas (MIA)</t>
+        </is>
+      </c>
+      <c r="C76" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D76" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>18.09</t>
         </is>
       </c>
     </row>
@@ -8132,20 +8132,20 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>Harold Fannin Jr. (CLE)</t>
-        </is>
-      </c>
-      <c r="C77" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Omar Cooper Jr. (NYJ)</t>
+        </is>
+      </c>
+      <c r="C77" s="16" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D77" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>17.02</t>
         </is>
       </c>
     </row>
@@ -8155,20 +8155,20 @@
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Michael Wilson (ARI)</t>
-        </is>
-      </c>
-      <c r="C78" s="17" t="inlineStr">
+          <t>Travis Hunter (JAX)</t>
+        </is>
+      </c>
+      <c r="C78" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D78" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -8178,20 +8178,20 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>Stefon Diggs (WAS)</t>
-        </is>
-      </c>
-      <c r="C79" s="17" t="inlineStr">
+          <t>Dontayvion Wicks (PHI)</t>
+        </is>
+      </c>
+      <c r="C79" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D79" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8201,20 +8201,20 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Courtland Sutton (DEN)</t>
-        </is>
-      </c>
-      <c r="C80" s="17" t="inlineStr">
+          <t>Darius Slayton (NYG)</t>
+        </is>
+      </c>
+      <c r="C80" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D80" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8224,20 +8224,20 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt (WAS)</t>
+          <t>Tory Horton (SEA)</t>
         </is>
       </c>
       <c r="C81" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D81" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -8247,20 +8247,20 @@
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Kenny Gainwell (TB)</t>
+          <t>Tre' Harris (LAC)</t>
         </is>
       </c>
       <c r="C82" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D82" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -8270,20 +8270,20 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Warren (PIT)</t>
+          <t>Jalen Tolbert (MIA)</t>
         </is>
       </c>
       <c r="C83" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D83" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8293,20 +8293,20 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Jordan Addison (MIN)</t>
-        </is>
-      </c>
-      <c r="C84" s="17" t="inlineStr">
+          <t>Ryan Flournoy (DAL)</t>
+        </is>
+      </c>
+      <c r="C84" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D84" s="14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -8316,10 +8316,10 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling (SF)</t>
-        </is>
-      </c>
-      <c r="C85" s="17" t="inlineStr">
+          <t>Malachi Fields (NYG)</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8329,7 +8329,7 @@
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>19.04</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Tucker Kraft (GB)</t>
-        </is>
-      </c>
-      <c r="C86" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>DeMario Douglas (NE)</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D86" s="14" t="n">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8362,20 +8362,20 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>Jalen Hurts (PHI)</t>
-        </is>
-      </c>
-      <c r="C87" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Zachariah Branch (ATL)</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D87" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -8385,20 +8385,20 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Jayden Reed (GB)</t>
-        </is>
-      </c>
-      <c r="C88" s="17" t="inlineStr">
+          <t>Keon Coleman (BUF)</t>
+        </is>
+      </c>
+      <c r="C88" s="16" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D88" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>20.07</t>
         </is>
       </c>
     </row>
@@ -8408,20 +8408,20 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>Jayden Daniels (WAS)</t>
-        </is>
-      </c>
-      <c r="C89" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Pat Bryant (DEN)</t>
+        </is>
+      </c>
+      <c r="C89" s="16" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D89" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>19.11</t>
         </is>
       </c>
     </row>
@@ -8431,20 +8431,20 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Joe Burrow (CIN)</t>
-        </is>
-      </c>
-      <c r="C90" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tank Dell (HOU)</t>
+        </is>
+      </c>
+      <c r="C90" s="16" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D90" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -8454,20 +8454,20 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>George Kittle (SF)</t>
-        </is>
-      </c>
-      <c r="C91" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Cyrus Allen (KC)</t>
+        </is>
+      </c>
+      <c r="C91" s="16" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -8477,20 +8477,20 @@
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>Chuba Hubbard (CAR)</t>
+          <t>Kyle Williams (NE)</t>
         </is>
       </c>
       <c r="C92" s="16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D92" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>19.06</t>
         </is>
       </c>
     </row>
@@ -8500,20 +8500,20 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>J.K. Dobbins (DEN)</t>
-        </is>
-      </c>
-      <c r="C93" s="16" t="inlineStr">
+          <t>Jahmyr Gibbs (DET)</t>
+        </is>
+      </c>
+      <c r="C93" s="17" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D93" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>1.02</t>
         </is>
       </c>
     </row>
@@ -8523,20 +8523,20 @@
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>Tony Pollard (TEN)</t>
-        </is>
-      </c>
-      <c r="C94" s="16" t="inlineStr">
+          <t>Bijan Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D94" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>1.03</t>
         </is>
       </c>
     </row>
@@ -8546,20 +8546,20 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>Josh Downs (IND)</t>
+          <t>Christian McCaffrey (SF)</t>
         </is>
       </c>
       <c r="C95" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D95" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>1.06</t>
         </is>
       </c>
     </row>
@@ -8569,20 +8569,20 @@
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Jonathon Brooks (CAR)</t>
-        </is>
-      </c>
-      <c r="C96" s="16" t="inlineStr">
+          <t>Jonathan Taylor (IND)</t>
+        </is>
+      </c>
+      <c r="C96" s="17" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D96" s="14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -8592,12 +8592,12 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>Jakobi Meyers (JAX)</t>
+          <t>James Cook III (BUF)</t>
         </is>
       </c>
       <c r="C97" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>1.11</t>
         </is>
       </c>
     </row>
@@ -8615,20 +8615,20 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>Romeo Doubs (NE)</t>
+          <t>De'Von Achane (MIA)</t>
         </is>
       </c>
       <c r="C98" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D98" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -8638,20 +8638,20 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>Sam LaPorta (DET)</t>
-        </is>
-      </c>
-      <c r="C99" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kenneth Walker (KC)</t>
+        </is>
+      </c>
+      <c r="C99" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -8661,20 +8661,20 @@
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>Khalil Shakir (BUF)</t>
+          <t>Chase Brown (CIN)</t>
         </is>
       </c>
       <c r="C100" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D100" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -8684,20 +8684,20 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>Kyle Monangai (CHI)</t>
-        </is>
-      </c>
-      <c r="C101" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Brock Bowers (LV)</t>
+        </is>
+      </c>
+      <c r="C101" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -8707,20 +8707,20 @@
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Makai Lemon (PHI)</t>
-        </is>
-      </c>
-      <c r="C102" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Trey McBride (ARI)</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D102" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -8730,20 +8730,20 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>Xavier Worthy (KC)</t>
+          <t>Omarion Hampton (LAC)</t>
         </is>
       </c>
       <c r="C103" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -8753,20 +8753,20 @@
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>Malik Washington (MIA)</t>
+          <t>Ashton Jeanty (LV)</t>
         </is>
       </c>
       <c r="C104" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D104" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -8776,20 +8776,20 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>Jordan Mason (MIN)</t>
-        </is>
-      </c>
-      <c r="C105" s="16" t="inlineStr">
+          <t>Saquon Barkley (PHI)</t>
+        </is>
+      </c>
+      <c r="C105" s="17" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -8799,20 +8799,20 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>Jalen Coker (CAR)</t>
+          <t>Derrick Henry (BAL)</t>
         </is>
       </c>
       <c r="C106" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D106" s="14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>2.08</t>
         </is>
       </c>
     </row>
@@ -8822,20 +8822,20 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Rashid Shaheed (SEA)</t>
+          <t>Jeremiyah Love (ARI)</t>
         </is>
       </c>
       <c r="C107" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -8845,12 +8845,12 @@
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>KC Concepcion (CLE)</t>
+          <t>Kyren Williams (LAR)</t>
         </is>
       </c>
       <c r="C108" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D108" s="14" t="n">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
@@ -8868,20 +8868,20 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>Kayshon Boutte (HOU)</t>
+          <t>Breece Hall (NYJ)</t>
         </is>
       </c>
       <c r="C109" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -8891,20 +8891,20 @@
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>Drake Maye (NE)</t>
-        </is>
-      </c>
-      <c r="C110" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>D'Andre Swift (CHI)</t>
+        </is>
+      </c>
+      <c r="C110" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D110" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -8914,20 +8914,20 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>Rachaad White (WAS)</t>
-        </is>
-      </c>
-      <c r="C111" s="16" t="inlineStr">
+          <t>Javonte Williams (DAL)</t>
+        </is>
+      </c>
+      <c r="C111" s="17" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -8937,20 +8937,20 @@
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Matthew Golden (GB)</t>
-        </is>
-      </c>
-      <c r="C112" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Josh Allen (BUF)</t>
+        </is>
+      </c>
+      <c r="C112" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D112" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>2.09</t>
         </is>
       </c>
     </row>
@@ -8960,20 +8960,20 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>Jaxson Dart (NYG)</t>
-        </is>
-      </c>
-      <c r="C113" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Bucky Irving (TB)</t>
+        </is>
+      </c>
+      <c r="C113" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>4.06</t>
         </is>
       </c>
     </row>
@@ -8983,20 +8983,20 @@
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Kyle Pitts Sr. (ATL)</t>
-        </is>
-      </c>
-      <c r="C114" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Travis Etienne Jr. (NO)</t>
+        </is>
+      </c>
+      <c r="C114" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D114" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.09</t>
         </is>
       </c>
     </row>
@@ -9006,20 +9006,20 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>Keenan Allen (IND)</t>
+          <t>Cam Skattebo (NYG)</t>
         </is>
       </c>
       <c r="C115" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>4.08</t>
         </is>
       </c>
     </row>
@@ -9029,20 +9029,20 @@
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>Caleb Williams (CHI)</t>
-        </is>
-      </c>
-      <c r="C116" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Bhayshul Tuten (JAX)</t>
+        </is>
+      </c>
+      <c r="C116" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D116" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -9052,20 +9052,20 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>Trevor Lawrence (JAX)</t>
-        </is>
-      </c>
-      <c r="C117" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tyler Warren (IND)</t>
+        </is>
+      </c>
+      <c r="C117" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>4.11</t>
         </is>
       </c>
     </row>
@@ -9075,20 +9075,20 @@
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>Blake Corum (LAR)</t>
-        </is>
-      </c>
-      <c r="C118" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Colston Loveland (CHI)</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D118" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>4.04</t>
         </is>
       </c>
     </row>
@@ -9098,20 +9098,20 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>RJ Harvey (DEN)</t>
-        </is>
-      </c>
-      <c r="C119" s="16" t="inlineStr">
+          <t>Quinshon Judkins (CLE)</t>
+        </is>
+      </c>
+      <c r="C119" s="17" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Juwan Johnson (NO)</t>
-        </is>
-      </c>
-      <c r="C120" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>TreVeyon Henderson (NE)</t>
+        </is>
+      </c>
+      <c r="C120" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D120" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -9144,12 +9144,12 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>Jordyn Tyson (NO)</t>
+          <t>David Montgomery (HOU)</t>
         </is>
       </c>
       <c r="C121" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D121" s="14" t="n">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -9167,20 +9167,20 @@
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>Dalton Schultz (HOU)</t>
-        </is>
-      </c>
-      <c r="C122" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Lamar Jackson (BAL)</t>
+        </is>
+      </c>
+      <c r="C122" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>3.09</t>
         </is>
       </c>
     </row>
@@ -9190,20 +9190,20 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>Travis Kelce (KC)</t>
-        </is>
-      </c>
-      <c r="C123" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jadarian Price (SEA)</t>
+        </is>
+      </c>
+      <c r="C123" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -9213,20 +9213,20 @@
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>Tre Tucker (LV)</t>
+          <t>MarShawn Lloyd (GB)</t>
         </is>
       </c>
       <c r="C124" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D124" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>15.06</t>
         </is>
       </c>
     </row>
@@ -9236,20 +9236,20 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr. (MIN)</t>
-        </is>
-      </c>
-      <c r="C125" s="16" t="inlineStr">
+          <t>Rhamondre Stevenson (NE)</t>
+        </is>
+      </c>
+      <c r="C125" s="17" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -9259,20 +9259,20 @@
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>Jake Ferguson (DAL)</t>
-        </is>
-      </c>
-      <c r="C126" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Rico Dowdle (PIT)</t>
+        </is>
+      </c>
+      <c r="C126" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>8.01</t>
         </is>
       </c>
     </row>
@@ -9282,20 +9282,20 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>Dak Prescott (DAL)</t>
-        </is>
-      </c>
-      <c r="C127" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Harold Fannin Jr. (CLE)</t>
+        </is>
+      </c>
+      <c r="C127" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -9305,12 +9305,12 @@
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>Dalton Kincaid (BUF)</t>
-        </is>
-      </c>
-      <c r="C128" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jacory Croskey-Merritt (WAS)</t>
+        </is>
+      </c>
+      <c r="C128" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D128" s="14" t="n">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>10.06</t>
         </is>
       </c>
     </row>
@@ -9328,20 +9328,20 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>Isaiah Likely (NYG)</t>
-        </is>
-      </c>
-      <c r="C129" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kenny Gainwell (TB)</t>
+        </is>
+      </c>
+      <c r="C129" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D129" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -9351,10 +9351,10 @@
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>Tyjae Spears (TEN)</t>
-        </is>
-      </c>
-      <c r="C130" s="16" t="inlineStr">
+          <t>Jaylen Warren (PIT)</t>
+        </is>
+      </c>
+      <c r="C130" s="17" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -9374,20 +9374,20 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>Justin Herbert (LAC)</t>
-        </is>
-      </c>
-      <c r="C131" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tucker Kraft (GB)</t>
+        </is>
+      </c>
+      <c r="C131" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -9397,12 +9397,12 @@
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>Dallas Goedert (PHI)</t>
-        </is>
-      </c>
-      <c r="C132" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jalen Hurts (PHI)</t>
+        </is>
+      </c>
+      <c r="C132" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D132" s="14" t="n">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>5.12</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>Bo Nix (DEN)</t>
+          <t>Jayden Daniels (WAS)</t>
         </is>
       </c>
       <c r="C133" s="19" t="inlineStr">
@@ -9429,11 +9429,11 @@
         </is>
       </c>
       <c r="D133" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>6.04</t>
         </is>
       </c>
     </row>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Brock Purdy (SF)</t>
+          <t>Joe Burrow (CIN)</t>
         </is>
       </c>
       <c r="C134" s="19" t="inlineStr">
@@ -9452,11 +9452,11 @@
         </is>
       </c>
       <c r="D134" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -9466,20 +9466,20 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>Omar Cooper Jr. (NYJ)</t>
-        </is>
-      </c>
-      <c r="C135" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>George Kittle (SF)</t>
+        </is>
+      </c>
+      <c r="C135" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -9489,20 +9489,20 @@
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>Jared Goff (DET)</t>
-        </is>
-      </c>
-      <c r="C136" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Chuba Hubbard (CAR)</t>
+        </is>
+      </c>
+      <c r="C136" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D136" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>7.05</t>
         </is>
       </c>
     </row>
@@ -9512,20 +9512,20 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>Deebo Samuel Sr. (SF)</t>
+          <t>J.K. Dobbins (DEN)</t>
         </is>
       </c>
       <c r="C137" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>8.1</t>
         </is>
       </c>
     </row>
@@ -9535,20 +9535,20 @@
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>Tyler Shough (NO)</t>
-        </is>
-      </c>
-      <c r="C138" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tony Pollard (TEN)</t>
+        </is>
+      </c>
+      <c r="C138" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>7.12</t>
         </is>
       </c>
     </row>
@@ -9558,20 +9558,20 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>Matthew Stafford (LAR)</t>
-        </is>
-      </c>
-      <c r="C139" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jonathon Brooks (CAR)</t>
+        </is>
+      </c>
+      <c r="C139" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>9.1</t>
         </is>
       </c>
     </row>
@@ -9581,12 +9581,12 @@
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>Kyler Murray (MIN)</t>
-        </is>
-      </c>
-      <c r="C140" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Sam LaPorta (DET)</t>
+        </is>
+      </c>
+      <c r="C140" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D140" s="14" t="n">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -9604,20 +9604,20 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>Jordan Love (GB)</t>
-        </is>
-      </c>
-      <c r="C141" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Kyle Monangai (CHI)</t>
+        </is>
+      </c>
+      <c r="C141" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -9627,20 +9627,20 @@
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>Baker Mayfield (TB)</t>
-        </is>
-      </c>
-      <c r="C142" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jordan Mason (MIN)</t>
+        </is>
+      </c>
+      <c r="C142" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>10.07</t>
         </is>
       </c>
     </row>
@@ -9650,12 +9650,12 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>Denzel Boston (CLE)</t>
-        </is>
-      </c>
-      <c r="C143" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Drake Maye (NE)</t>
+        </is>
+      </c>
+      <c r="C143" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -9673,20 +9673,20 @@
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>Patrick Mahomes (KC)</t>
-        </is>
-      </c>
-      <c r="C144" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Rachaad White (WAS)</t>
+        </is>
+      </c>
+      <c r="C144" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -9696,20 +9696,20 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>Brenton Strange (JAX)</t>
-        </is>
-      </c>
-      <c r="C145" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jaxson Dart (NYG)</t>
+        </is>
+      </c>
+      <c r="C145" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -9719,20 +9719,20 @@
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks (PHI)</t>
-        </is>
-      </c>
-      <c r="C146" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kyle Pitts Sr. (ATL)</t>
+        </is>
+      </c>
+      <c r="C146" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.1</t>
         </is>
       </c>
     </row>
@@ -9742,20 +9742,20 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Mark Andrews (BAL)</t>
-        </is>
-      </c>
-      <c r="C147" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Caleb Williams (CHI)</t>
+        </is>
+      </c>
+      <c r="C147" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -9765,20 +9765,20 @@
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>Pat Bryant (DEN)</t>
-        </is>
-      </c>
-      <c r="C148" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Trevor Lawrence (JAX)</t>
+        </is>
+      </c>
+      <c r="C148" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -9788,20 +9788,20 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>Malik Willis (MIA)</t>
-        </is>
-      </c>
-      <c r="C149" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Blake Corum (LAR)</t>
+        </is>
+      </c>
+      <c r="C149" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>9.08</t>
         </is>
       </c>
     </row>
@@ -9811,20 +9811,20 @@
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>Jalen Nailor (LV)</t>
+          <t>RJ Harvey (DEN)</t>
         </is>
       </c>
       <c r="C150" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>7.08</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Woody Marks (HOU)</t>
-        </is>
-      </c>
-      <c r="C151" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Juwan Johnson (NO)</t>
+        </is>
+      </c>
+      <c r="C151" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D151" s="14" t="n">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9857,7 +9857,7 @@
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Hunter Henry (NE)</t>
+          <t>Dalton Schultz (HOU)</t>
         </is>
       </c>
       <c r="C152" s="18" t="inlineStr">
@@ -9866,11 +9866,11 @@
         </is>
       </c>
       <c r="D152" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>17.01</t>
         </is>
       </c>
     </row>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>Chig Okonkwo (WAS)</t>
+          <t>Travis Kelce (KC)</t>
         </is>
       </c>
       <c r="C153" s="18" t="inlineStr">
@@ -9889,11 +9889,11 @@
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>8.08</t>
         </is>
       </c>
     </row>
@@ -9903,20 +9903,20 @@
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>Chris Rodriguez Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C154" s="16" t="inlineStr">
+          <t>Aaron Jones Sr. (MIN)</t>
+        </is>
+      </c>
+      <c r="C154" s="17" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -9926,20 +9926,20 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>Travis Hunter (JAX)</t>
-        </is>
-      </c>
-      <c r="C155" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jake Ferguson (DAL)</t>
+        </is>
+      </c>
+      <c r="C155" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>9.02</t>
         </is>
       </c>
     </row>
@@ -9949,20 +9949,20 @@
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Cooper Kupp (SEA)</t>
-        </is>
-      </c>
-      <c r="C156" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dak Prescott (DAL)</t>
+        </is>
+      </c>
+      <c r="C156" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>7.07</t>
         </is>
       </c>
     </row>
@@ -9972,20 +9972,20 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Jerry Jeudy (CLE)</t>
-        </is>
-      </c>
-      <c r="C157" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dalton Kincaid (BUF)</t>
+        </is>
+      </c>
+      <c r="C157" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D157" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E157" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -9995,20 +9995,20 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Cam Ward (TEN)</t>
-        </is>
-      </c>
-      <c r="C158" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Isaiah Likely (NYG)</t>
+        </is>
+      </c>
+      <c r="C158" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -10018,20 +10018,20 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Isiah Pacheco (DET)</t>
-        </is>
-      </c>
-      <c r="C159" s="16" t="inlineStr">
+          <t>Tyjae Spears (TEN)</t>
+        </is>
+      </c>
+      <c r="C159" s="17" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E159" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -10041,7 +10041,7 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>C.J. Stroud (HOU)</t>
+          <t>Justin Herbert (LAC)</t>
         </is>
       </c>
       <c r="C160" s="19" t="inlineStr">
@@ -10050,11 +10050,11 @@
         </is>
       </c>
       <c r="D160" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -10064,20 +10064,20 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>DeMario Douglas (NE)</t>
-        </is>
-      </c>
-      <c r="C161" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dallas Goedert (PHI)</t>
+        </is>
+      </c>
+      <c r="C161" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E161" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -10087,20 +10087,20 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Malachi Fields (NYG)</t>
-        </is>
-      </c>
-      <c r="C162" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Bo Nix (DEN)</t>
+        </is>
+      </c>
+      <c r="C162" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D162" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>10.12</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>Sam Darnold (SEA)</t>
+          <t>Brock Purdy (SF)</t>
         </is>
       </c>
       <c r="C163" s="19" t="inlineStr">
@@ -10119,11 +10119,11 @@
         </is>
       </c>
       <c r="D163" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E163" s="14" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>11.02</t>
         </is>
       </c>
     </row>
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Keaton Mitchell (LAC)</t>
-        </is>
-      </c>
-      <c r="C164" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jared Goff (DET)</t>
+        </is>
+      </c>
+      <c r="C164" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>12.03</t>
         </is>
       </c>
     </row>
@@ -10156,20 +10156,20 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>Adonai Mitchell (NYJ)</t>
-        </is>
-      </c>
-      <c r="C165" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyler Shough (NO)</t>
+        </is>
+      </c>
+      <c r="C165" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E165" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>16.07</t>
         </is>
       </c>
     </row>
@@ -10179,20 +10179,20 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane (BAL)</t>
-        </is>
-      </c>
-      <c r="C166" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Matthew Stafford (LAR)</t>
+        </is>
+      </c>
+      <c r="C166" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>9.01</t>
         </is>
       </c>
     </row>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>Daniel Jones (IND)</t>
+          <t>Kyler Murray (MIN)</t>
         </is>
       </c>
       <c r="C167" s="19" t="inlineStr">
@@ -10211,11 +10211,11 @@
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E167" s="14" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>14.03</t>
         </is>
       </c>
     </row>
@@ -10225,20 +10225,20 @@
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>Tank Dell (HOU)</t>
-        </is>
-      </c>
-      <c r="C168" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jordan Love (GB)</t>
+        </is>
+      </c>
+      <c r="C168" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>13.05</t>
         </is>
       </c>
     </row>
@@ -10248,20 +10248,20 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>Germie Bernard (PIT)</t>
-        </is>
-      </c>
-      <c r="C169" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Baker Mayfield (TB)</t>
+        </is>
+      </c>
+      <c r="C169" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E169" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -10271,20 +10271,20 @@
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Zach Charbonnet (SEA)</t>
-        </is>
-      </c>
-      <c r="C170" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Patrick Mahomes (KC)</t>
+        </is>
+      </c>
+      <c r="C170" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -10294,20 +10294,20 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>Cyrus Allen (KC)</t>
-        </is>
-      </c>
-      <c r="C171" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brenton Strange (JAX)</t>
+        </is>
+      </c>
+      <c r="C171" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>13.08</t>
         </is>
       </c>
     </row>
@@ -10317,20 +10317,20 @@
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Tyler Allgeier (ARI)</t>
-        </is>
-      </c>
-      <c r="C172" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Mark Andrews (BAL)</t>
+        </is>
+      </c>
+      <c r="C172" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>11.09</t>
         </is>
       </c>
     </row>
@@ -10340,20 +10340,20 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>Dylan Sampson (CLE)</t>
-        </is>
-      </c>
-      <c r="C173" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Malik Willis (MIA)</t>
+        </is>
+      </c>
+      <c r="C173" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -10363,20 +10363,20 @@
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Kyle Williams (NE)</t>
+          <t>Woody Marks (HOU)</t>
         </is>
       </c>
       <c r="C174" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>14.04</t>
         </is>
       </c>
     </row>
@@ -10386,20 +10386,20 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>Calvin Ridley (TEN)</t>
-        </is>
-      </c>
-      <c r="C175" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Hunter Henry (NE)</t>
+        </is>
+      </c>
+      <c r="C175" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E175" s="14" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>T.J. Hockenson (MIN)</t>
+          <t>Chig Okonkwo (WAS)</t>
         </is>
       </c>
       <c r="C176" s="18" t="inlineStr">
@@ -10418,11 +10418,11 @@
         </is>
       </c>
       <c r="D176" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -10432,20 +10432,20 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Mike Washington Jr. (LV)</t>
-        </is>
-      </c>
-      <c r="C177" s="16" t="inlineStr">
+          <t>Chris Rodriguez Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C177" s="17" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E177" s="14" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>12.08</t>
         </is>
       </c>
     </row>
@@ -10455,20 +10455,20 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Greg Dulcich (MIA)</t>
-        </is>
-      </c>
-      <c r="C178" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Cam Ward (TEN)</t>
+        </is>
+      </c>
+      <c r="C178" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10478,20 +10478,20 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq (NYJ)</t>
-        </is>
-      </c>
-      <c r="C179" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Isiah Pacheco (DET)</t>
+        </is>
+      </c>
+      <c r="C179" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E179" s="14" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -10501,20 +10501,20 @@
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Jonah Coleman (DEN)</t>
-        </is>
-      </c>
-      <c r="C180" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>C.J. Stroud (HOU)</t>
+        </is>
+      </c>
+      <c r="C180" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>18.01</t>
         </is>
       </c>
     </row>
@@ -10524,20 +10524,20 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>Tre' Harris (LAC)</t>
-        </is>
-      </c>
-      <c r="C181" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Sam Darnold (SEA)</t>
+        </is>
+      </c>
+      <c r="C181" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>14.05</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Keon Coleman (BUF)</t>
+          <t>Keaton Mitchell (LAC)</t>
         </is>
       </c>
       <c r="C182" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D182" s="14" t="n">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10570,20 +10570,20 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr. (NYG)</t>
-        </is>
-      </c>
-      <c r="C183" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Daniel Jones (IND)</t>
+        </is>
+      </c>
+      <c r="C183" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D183" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E183" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>17.11</t>
         </is>
       </c>
     </row>
@@ -10593,20 +10593,20 @@
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>Pat Freiermuth (PIT)</t>
-        </is>
-      </c>
-      <c r="C184" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Zach Charbonnet (SEA)</t>
+        </is>
+      </c>
+      <c r="C184" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D184" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>13.04</t>
         </is>
       </c>
     </row>
@@ -10616,20 +10616,20 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Aaron Rodgers (PIT)</t>
-        </is>
-      </c>
-      <c r="C185" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tyler Allgeier (ARI)</t>
+        </is>
+      </c>
+      <c r="C185" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E185" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -10639,20 +10639,20 @@
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Bryce Young (CAR)</t>
-        </is>
-      </c>
-      <c r="C186" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Dylan Sampson (CLE)</t>
+        </is>
+      </c>
+      <c r="C186" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D186" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -10662,20 +10662,20 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>Zachariah Branch (ATL)</t>
-        </is>
-      </c>
-      <c r="C187" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>T.J. Hockenson (MIN)</t>
+        </is>
+      </c>
+      <c r="C187" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D187" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E187" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -10685,20 +10685,20 @@
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Ryan Flournoy (DAL)</t>
+          <t>Mike Washington Jr. (LV)</t>
         </is>
       </c>
       <c r="C188" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D188" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>15.05</t>
         </is>
       </c>
     </row>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Cade Otton (TB)</t>
+          <t>Greg Dulcich (MIA)</t>
         </is>
       </c>
       <c r="C189" s="18" t="inlineStr">
@@ -10717,11 +10717,11 @@
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E189" s="14" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10731,20 +10731,20 @@
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Tank Bigsby (PHI)</t>
-        </is>
-      </c>
-      <c r="C190" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kenyon Sadiq (NYJ)</t>
+        </is>
+      </c>
+      <c r="C190" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D190" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E190" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>13.1</t>
         </is>
       </c>
     </row>
@@ -10754,20 +10754,20 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>Alvin Kamara (NO)</t>
-        </is>
-      </c>
-      <c r="C191" s="16" t="inlineStr">
+          <t>Jonah Coleman (DEN)</t>
+        </is>
+      </c>
+      <c r="C191" s="17" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E191" s="14" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>15.03</t>
         </is>
       </c>
     </row>
@@ -10777,20 +10777,20 @@
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Caleb Douglas (MIA)</t>
+          <t>Tyrone Tracy Jr. (NYG)</t>
         </is>
       </c>
       <c r="C192" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D192" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10800,20 +10800,20 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Geno Smith (NYJ)</t>
-        </is>
-      </c>
-      <c r="C193" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Pat Freiermuth (PIT)</t>
+        </is>
+      </c>
+      <c r="C193" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10823,20 +10823,20 @@
       </c>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>Najee Harris (NYG)</t>
-        </is>
-      </c>
-      <c r="C194" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Aaron Rodgers (PIT)</t>
+        </is>
+      </c>
+      <c r="C194" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D194" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E194" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10846,20 +10846,20 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Brian Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C195" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Bryce Young (CAR)</t>
+        </is>
+      </c>
+      <c r="C195" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E195" s="14" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>19.12</t>
         </is>
       </c>
     </row>
@@ -10869,20 +10869,20 @@
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>Devaughn Vele (NO)</t>
-        </is>
-      </c>
-      <c r="C196" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Cade Otton (TB)</t>
+        </is>
+      </c>
+      <c r="C196" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D196" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E196" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.06</t>
         </is>
       </c>
     </row>
@@ -10892,20 +10892,20 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>AJ Barner (SEA)</t>
-        </is>
-      </c>
-      <c r="C197" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tank Bigsby (PHI)</t>
+        </is>
+      </c>
+      <c r="C197" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D197" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E197" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10915,12 +10915,12 @@
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Jaylin Noel (HOU)</t>
+          <t>Alvin Kamara (NO)</t>
         </is>
       </c>
       <c r="C198" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D198" s="14" t="n">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>14.07</t>
         </is>
       </c>
     </row>
@@ -10938,16 +10938,16 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>Darius Slayton (NYG)</t>
-        </is>
-      </c>
-      <c r="C199" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Geno Smith (NYJ)</t>
+        </is>
+      </c>
+      <c r="C199" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E199" s="14" t="inlineStr">
         <is>
@@ -10961,20 +10961,20 @@
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Oronde Gadsden (LAC)</t>
-        </is>
-      </c>
-      <c r="C200" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Najee Harris (NYG)</t>
+        </is>
+      </c>
+      <c r="C200" s="17" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D200" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10984,20 +10984,20 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>Rashod Bateman (BAL)</t>
+          <t>Brian Robinson (ATL)</t>
         </is>
       </c>
       <c r="C201" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D201" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>13.12</t>
         </is>
       </c>
     </row>
@@ -11007,20 +11007,20 @@
       </c>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>Jalen Tolbert (MIA)</t>
-        </is>
-      </c>
-      <c r="C202" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>AJ Barner (SEA)</t>
+        </is>
+      </c>
+      <c r="C202" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D202" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E202" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -11030,20 +11030,20 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>Tory Horton (SEA)</t>
-        </is>
-      </c>
-      <c r="C203" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Oronde Gadsden (LAC)</t>
+        </is>
+      </c>
+      <c r="C203" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D203" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>

--- a/assets/data/12guys1cup-cheat-sheet.xlsx
+++ b/assets/data/12guys1cup-cheat-sheet.xlsx
@@ -56,13 +56,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001565C0"/>
+      <color rgb="002E7D32"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="002E7D32"/>
+      <color rgb="00B8386B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -74,7 +74,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00B8386B"/>
+      <color rgb="001565C0"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -120,12 +120,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4E4F7"/>
+        <fgColor rgb="00D5ECD5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5ECD5"/>
+        <fgColor rgb="00F8D7E8"/>
       </patternFill>
     </fill>
     <fill>
@@ -135,7 +135,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7E8"/>
+        <fgColor rgb="00D4E4F7"/>
       </patternFill>
     </fill>
   </fills>
@@ -6453,20 +6453,20 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>Puka Nacua (LAR)</t>
+          <t>Jahmyr Gibbs (DET)</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D4" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.02</t>
         </is>
       </c>
     </row>
@@ -6476,20 +6476,20 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase (CIN)</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Josh Allen (BUF)</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>2.09</t>
         </is>
       </c>
     </row>
@@ -6499,12 +6499,12 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba (SEA)</t>
+          <t>Bijan Robinson (ATL)</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.03</t>
         </is>
       </c>
     </row>
@@ -6522,20 +6522,20 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown (DET)</t>
+          <t>Christian McCaffrey (SF)</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.06</t>
         </is>
       </c>
     </row>
@@ -6545,20 +6545,20 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Drake London (ATL)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Lamar Jackson (BAL)</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>3.09</t>
         </is>
       </c>
     </row>
@@ -6568,20 +6568,20 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Justin Jefferson (MIN)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jayden Daniels (WAS)</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>6.04</t>
         </is>
       </c>
     </row>
@@ -6591,20 +6591,20 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>CeeDee Lamb (DAL)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Drake Maye (NE)</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -6614,20 +6614,20 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Rashee Rice (KC)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jalen Hurts (PHI)</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>5.12</t>
         </is>
       </c>
     </row>
@@ -6637,20 +6637,20 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Chris Olave (NO)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Joe Burrow (CIN)</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -6660,20 +6660,20 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>A.J. Brown (NE)</t>
+          <t>Jonathan Taylor (IND)</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6683,20 +6683,20 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>George Pickens (DAL)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jaxson Dart (NYG)</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -6706,20 +6706,20 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Nico Collins (HOU)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Trevor Lawrence (JAX)</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -6729,20 +6729,20 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Garrett Wilson (NYJ)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brock Purdy (SF)</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>11.02</t>
         </is>
       </c>
     </row>
@@ -6752,20 +6752,20 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Zay Flowers (BAL)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dak Prescott (DAL)</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>7.07</t>
         </is>
       </c>
     </row>
@@ -6775,20 +6775,20 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Malik Nabers (NYG)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Caleb Williams (CHI)</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -6798,20 +6798,20 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>DeVonta Smith (PHI)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Justin Herbert (LAC)</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -6821,20 +6821,20 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan (CAR)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Bo Nix (DEN)</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>10.12</t>
         </is>
       </c>
     </row>
@@ -6844,20 +6844,20 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Emeka Egbuka (TB)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Matthew Stafford (LAR)</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>9.01</t>
         </is>
       </c>
     </row>
@@ -6867,20 +6867,20 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Davante Adams (LAR)</t>
+          <t>De'Von Achane (MIA)</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6890,12 +6890,12 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Tee Higgins (CIN)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kyler Murray (MIN)</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>14.03</t>
         </is>
       </c>
     </row>
@@ -6913,20 +6913,20 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Ladd McConkey (LAC)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jared Goff (DET)</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>12.03</t>
         </is>
       </c>
     </row>
@@ -6936,20 +6936,20 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Jameson Williams (DET)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyler Shough (NO)</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>16.07</t>
         </is>
       </c>
     </row>
@@ -6959,12 +6959,12 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Waddle (DEN)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Baker Mayfield (TB)</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -6982,20 +6982,20 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Terry McLaurin (WAS)</t>
+          <t>Chase Brown (CIN)</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7005,20 +7005,20 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>DJ Moore (BUF)</t>
+          <t>Derrick Henry (BAL)</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>2.08</t>
         </is>
       </c>
     </row>
@@ -7028,20 +7028,20 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Luther Burden III (CHI)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Daniel Jones (IND)</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>17.11</t>
         </is>
       </c>
     </row>
@@ -7051,20 +7051,20 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Rome Odunze (CHI)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Malik Willis (MIA)</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -7074,20 +7074,20 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Mike Evans (SF)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jordan Love (GB)</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>13.05</t>
         </is>
       </c>
     </row>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr. (ARI)</t>
+          <t>James Cook III (BUF)</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>1.11</t>
         </is>
       </c>
     </row>
@@ -7120,20 +7120,20 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Courtland Sutton (DEN)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Sam Darnold (SEA)</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>14.05</t>
         </is>
       </c>
     </row>
@@ -7143,20 +7143,20 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>DK Metcalf (PIT)</t>
+          <t>Saquon Barkley (PHI)</t>
         </is>
       </c>
       <c r="C34" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -7166,20 +7166,20 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>Christian Watson (GB)</t>
+          <t>Ashton Jeanty (LV)</t>
         </is>
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -7189,20 +7189,20 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Alec Pierce (IND)</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>C.J. Stroud (HOU)</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D36" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>18.01</t>
         </is>
       </c>
     </row>
@@ -7212,20 +7212,20 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Michael Pittman Jr. (PIT)</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Trey McBride (ARI)</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -7235,20 +7235,20 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Parker Washington (JAX)</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Bryce Young (CAR)</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>19.12</t>
         </is>
       </c>
     </row>
@@ -7258,12 +7258,12 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr. (JAX)</t>
+          <t>Omarion Hampton (LAC)</t>
         </is>
       </c>
       <c r="C39" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D39" s="14" t="n">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7281,20 +7281,20 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson (TEN)</t>
+          <t>Jeremiyah Love (ARI)</t>
         </is>
       </c>
       <c r="C40" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D40" s="14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7304,20 +7304,20 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Jakobi Meyers (JAX)</t>
+          <t>Breece Hall (NYJ)</t>
         </is>
       </c>
       <c r="C41" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7327,20 +7327,20 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Carnell Tate (TEN)</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brock Bowers (LV)</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D42" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Michael Wilson (ARI)</t>
+          <t>Javonte Williams (DAL)</t>
         </is>
       </c>
       <c r="C43" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D43" s="14" t="n">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7373,20 +7373,20 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Jayden Reed (GB)</t>
+          <t>Travis Etienne Jr. (NO)</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>4.09</t>
         </is>
       </c>
     </row>
@@ -7396,20 +7396,20 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr. (TB)</t>
+          <t>Kyren Williams (LAR)</t>
         </is>
       </c>
       <c r="C45" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
@@ -7419,20 +7419,20 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>KC Concepcion (CLE)</t>
+          <t>Cam Skattebo (NYG)</t>
         </is>
       </c>
       <c r="C46" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D46" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>4.08</t>
         </is>
       </c>
     </row>
@@ -7442,20 +7442,20 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Quentin Johnston (LAC)</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Geno Smith (NYJ)</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7465,20 +7465,20 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Jordan Addison (MIN)</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Cam Ward (TEN)</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D48" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -7488,20 +7488,20 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>Xavier Worthy (KC)</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Aaron Rodgers (PIT)</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D49" s="14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -7511,20 +7511,20 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Stefon Diggs (WAS)</t>
+          <t>D'Andre Swift (CHI)</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -7534,20 +7534,20 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Khalil Shakir (BUF)</t>
+          <t>Bucky Irving (TB)</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D51" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>4.06</t>
         </is>
       </c>
     </row>
@@ -7557,20 +7557,20 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling (SF)</t>
+          <t>Quinshon Judkins (CLE)</t>
         </is>
       </c>
       <c r="C52" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D52" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -7580,20 +7580,20 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Romeo Doubs (NE)</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Colston Loveland (CHI)</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>4.04</t>
         </is>
       </c>
     </row>
@@ -7603,20 +7603,20 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>Josh Downs (IND)</t>
+          <t>Bhayshul Tuten (JAX)</t>
         </is>
       </c>
       <c r="C54" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -7626,20 +7626,20 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Deebo Samuel Sr. (SF)</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyler Warren (IND)</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>4.11</t>
         </is>
       </c>
     </row>
@@ -7649,12 +7649,12 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Matthew Golden (GB)</t>
-        </is>
-      </c>
-      <c r="C56" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Harold Fannin Jr. (CLE)</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -7672,20 +7672,20 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Denzel Boston (CLE)</t>
+          <t>David Montgomery (HOU)</t>
         </is>
       </c>
       <c r="C57" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D57" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -7695,20 +7695,20 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Jalen Coker (CAR)</t>
+          <t>Jaylen Warren (PIT)</t>
         </is>
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D58" s="14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Rashid Shaheed (SEA)</t>
+          <t>TreVeyon Henderson (NE)</t>
         </is>
       </c>
       <c r="C59" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D59" s="14" t="n">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -7741,12 +7741,12 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>Jerry Jeudy (CLE)</t>
+          <t>Rhamondre Stevenson (NE)</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D60" s="14" t="n">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -7764,20 +7764,20 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Makai Lemon (PHI)</t>
-        </is>
-      </c>
-      <c r="C61" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>George Kittle (SF)</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -7787,20 +7787,20 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Calvin Ridley (TEN)</t>
-        </is>
-      </c>
-      <c r="C62" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kyle Pitts Sr. (ATL)</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D62" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>6.1</t>
         </is>
       </c>
     </row>
@@ -7810,20 +7810,20 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Tre Tucker (LV)</t>
+          <t>Tony Pollard (TEN)</t>
         </is>
       </c>
       <c r="C63" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D63" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>7.12</t>
         </is>
       </c>
     </row>
@@ -7833,20 +7833,20 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Keenan Allen (IND)</t>
+          <t>Jadarian Price (SEA)</t>
         </is>
       </c>
       <c r="C64" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D64" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -7856,20 +7856,20 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Kayshon Boutte (HOU)</t>
-        </is>
-      </c>
-      <c r="C65" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Sam LaPorta (DET)</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D65" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -7879,20 +7879,20 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>Rashod Bateman (BAL)</t>
-        </is>
-      </c>
-      <c r="C66" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Travis Kelce (KC)</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D66" s="14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>8.08</t>
         </is>
       </c>
     </row>
@@ -7902,20 +7902,20 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane (BAL)</t>
+          <t>Rico Dowdle (PIT)</t>
         </is>
       </c>
       <c r="C67" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D67" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>8.01</t>
         </is>
       </c>
     </row>
@@ -7925,20 +7925,20 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Jalen Nailor (LV)</t>
-        </is>
-      </c>
-      <c r="C68" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dallas Goedert (PHI)</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D68" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -7948,20 +7948,20 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Devaughn Vele (NO)</t>
+          <t>J.K. Dobbins (DEN)</t>
         </is>
       </c>
       <c r="C69" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D69" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>8.1</t>
         </is>
       </c>
     </row>
@@ -7971,20 +7971,20 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Cooper Kupp (SEA)</t>
+          <t>Chuba Hubbard (CAR)</t>
         </is>
       </c>
       <c r="C70" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D70" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>7.05</t>
         </is>
       </c>
     </row>
@@ -7994,20 +7994,20 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>Jaylin Noel (HOU)</t>
-        </is>
-      </c>
-      <c r="C71" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tucker Kraft (GB)</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8017,20 +8017,20 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Adonai Mitchell (NYJ)</t>
+          <t>Kenny Gainwell (TB)</t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8040,20 +8040,20 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Malik Washington (MIA)</t>
+          <t>Jonathon Brooks (CAR)</t>
         </is>
       </c>
       <c r="C73" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>9.1</t>
         </is>
       </c>
     </row>
@@ -8063,20 +8063,20 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Germie Bernard (PIT)</t>
-        </is>
-      </c>
-      <c r="C74" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jake Ferguson (DAL)</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D74" s="14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>9.02</t>
         </is>
       </c>
     </row>
@@ -8086,20 +8086,20 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>Jordyn Tyson (NO)</t>
-        </is>
-      </c>
-      <c r="C75" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Mark Andrews (BAL)</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>11.09</t>
         </is>
       </c>
     </row>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Caleb Douglas (MIA)</t>
-        </is>
-      </c>
-      <c r="C76" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Isaiah Likely (NYG)</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D76" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -8132,20 +8132,20 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>Omar Cooper Jr. (NYJ)</t>
+          <t>RJ Harvey (DEN)</t>
         </is>
       </c>
       <c r="C77" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D77" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>7.08</t>
         </is>
       </c>
     </row>
@@ -8155,20 +8155,20 @@
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Travis Hunter (JAX)</t>
+          <t>Aaron Jones Sr. (MIN)</t>
         </is>
       </c>
       <c r="C78" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D78" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -8178,20 +8178,20 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks (PHI)</t>
+          <t>Rachaad White (WAS)</t>
         </is>
       </c>
       <c r="C79" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D79" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -8201,20 +8201,20 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Darius Slayton (NYG)</t>
-        </is>
-      </c>
-      <c r="C80" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dalton Kincaid (BUF)</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D80" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -8224,20 +8224,20 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>Tory Horton (SEA)</t>
+          <t>Kyle Monangai (CHI)</t>
         </is>
       </c>
       <c r="C81" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D81" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -8247,20 +8247,20 @@
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Tre' Harris (LAC)</t>
-        </is>
-      </c>
-      <c r="C82" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Juwan Johnson (NO)</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D82" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -8270,20 +8270,20 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>Jalen Tolbert (MIA)</t>
-        </is>
-      </c>
-      <c r="C83" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Hunter Henry (NE)</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D83" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -8293,20 +8293,20 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Ryan Flournoy (DAL)</t>
+          <t>MarShawn Lloyd (GB)</t>
         </is>
       </c>
       <c r="C84" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D84" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>15.06</t>
         </is>
       </c>
     </row>
@@ -8316,20 +8316,20 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>Malachi Fields (NYG)</t>
-        </is>
-      </c>
-      <c r="C85" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brenton Strange (JAX)</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D85" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>13.08</t>
         </is>
       </c>
     </row>
@@ -8339,20 +8339,20 @@
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>DeMario Douglas (NE)</t>
-        </is>
-      </c>
-      <c r="C86" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dalton Schultz (HOU)</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D86" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17.01</t>
         </is>
       </c>
     </row>
@@ -8362,20 +8362,20 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>Zachariah Branch (ATL)</t>
+          <t>Jacory Croskey-Merritt (WAS)</t>
         </is>
       </c>
       <c r="C87" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D87" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>10.06</t>
         </is>
       </c>
     </row>
@@ -8385,20 +8385,20 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Keon Coleman (BUF)</t>
+          <t>Jordan Mason (MIN)</t>
         </is>
       </c>
       <c r="C88" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D88" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>10.07</t>
         </is>
       </c>
     </row>
@@ -8408,20 +8408,20 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>Pat Bryant (DEN)</t>
-        </is>
-      </c>
-      <c r="C89" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>T.J. Hockenson (MIN)</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D89" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -8431,20 +8431,20 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Tank Dell (HOU)</t>
+          <t>Blake Corum (LAR)</t>
         </is>
       </c>
       <c r="C90" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D90" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>9.08</t>
         </is>
       </c>
     </row>
@@ -8454,20 +8454,20 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>Cyrus Allen (KC)</t>
+          <t>Tyjae Spears (TEN)</t>
         </is>
       </c>
       <c r="C91" s="16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -8477,20 +8477,20 @@
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>Kyle Williams (NE)</t>
-        </is>
-      </c>
-      <c r="C92" s="16" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Pat Freiermuth (PIT)</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D92" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -8500,12 +8500,12 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>Jahmyr Gibbs (DET)</t>
-        </is>
-      </c>
-      <c r="C93" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Greg Dulcich (MIA)</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D93" s="14" t="n">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -8523,20 +8523,20 @@
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>Bijan Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C94" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Cade Otton (TB)</t>
+        </is>
+      </c>
+      <c r="C94" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D94" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>20.06</t>
         </is>
       </c>
     </row>
@@ -8546,20 +8546,20 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>Christian McCaffrey (SF)</t>
-        </is>
-      </c>
-      <c r="C95" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Chig Okonkwo (WAS)</t>
+        </is>
+      </c>
+      <c r="C95" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D95" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -8569,20 +8569,20 @@
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Jonathan Taylor (IND)</t>
-        </is>
-      </c>
-      <c r="C96" s="17" t="inlineStr">
+          <t>Woody Marks (HOU)</t>
+        </is>
+      </c>
+      <c r="C96" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D96" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>14.04</t>
         </is>
       </c>
     </row>
@@ -8592,20 +8592,20 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>James Cook III (BUF)</t>
-        </is>
-      </c>
-      <c r="C97" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kenyon Sadiq (NYJ)</t>
+        </is>
+      </c>
+      <c r="C97" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>13.1</t>
         </is>
       </c>
     </row>
@@ -8615,20 +8615,20 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>De'Von Achane (MIA)</t>
-        </is>
-      </c>
-      <c r="C98" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>AJ Barner (SEA)</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D98" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -8638,20 +8638,20 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>Kenneth Walker (KC)</t>
-        </is>
-      </c>
-      <c r="C99" s="17" t="inlineStr">
+          <t>Zach Charbonnet (SEA)</t>
+        </is>
+      </c>
+      <c r="C99" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>13.04</t>
         </is>
       </c>
     </row>
@@ -8661,20 +8661,20 @@
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>Chase Brown (CIN)</t>
-        </is>
-      </c>
-      <c r="C100" s="17" t="inlineStr">
+          <t>Alvin Kamara (NO)</t>
+        </is>
+      </c>
+      <c r="C100" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D100" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>14.07</t>
         </is>
       </c>
     </row>
@@ -8684,20 +8684,20 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>Brock Bowers (LV)</t>
-        </is>
-      </c>
-      <c r="C101" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Isiah Pacheco (DET)</t>
+        </is>
+      </c>
+      <c r="C101" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -8707,20 +8707,20 @@
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Trey McBride (ARI)</t>
-        </is>
-      </c>
-      <c r="C102" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Dylan Sampson (CLE)</t>
+        </is>
+      </c>
+      <c r="C102" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D102" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -8730,20 +8730,20 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>Omarion Hampton (LAC)</t>
-        </is>
-      </c>
-      <c r="C103" s="17" t="inlineStr">
+          <t>Mike Washington Jr. (LV)</t>
+        </is>
+      </c>
+      <c r="C103" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>15.05</t>
         </is>
       </c>
     </row>
@@ -8753,20 +8753,20 @@
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>Ashton Jeanty (LV)</t>
-        </is>
-      </c>
-      <c r="C104" s="17" t="inlineStr">
+          <t>Chris Rodriguez Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C104" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D104" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>12.08</t>
         </is>
       </c>
     </row>
@@ -8776,20 +8776,20 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>Saquon Barkley (PHI)</t>
-        </is>
-      </c>
-      <c r="C105" s="17" t="inlineStr">
+          <t>Tyler Allgeier (ARI)</t>
+        </is>
+      </c>
+      <c r="C105" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -8799,20 +8799,20 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>Derrick Henry (BAL)</t>
-        </is>
-      </c>
-      <c r="C106" s="17" t="inlineStr">
+          <t>Keaton Mitchell (LAC)</t>
+        </is>
+      </c>
+      <c r="C106" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D106" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -8822,20 +8822,20 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Jeremiyah Love (ARI)</t>
-        </is>
-      </c>
-      <c r="C107" s="17" t="inlineStr">
+          <t>Tyrone Tracy Jr. (NYG)</t>
+        </is>
+      </c>
+      <c r="C107" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -8845,20 +8845,20 @@
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>Kyren Williams (LAR)</t>
-        </is>
-      </c>
-      <c r="C108" s="17" t="inlineStr">
+          <t>Tank Bigsby (PHI)</t>
+        </is>
+      </c>
+      <c r="C108" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D108" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -8868,20 +8868,20 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>Breece Hall (NYJ)</t>
-        </is>
-      </c>
-      <c r="C109" s="17" t="inlineStr">
+          <t>Najee Harris (NYG)</t>
+        </is>
+      </c>
+      <c r="C109" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -8891,10 +8891,10 @@
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>D'Andre Swift (CHI)</t>
-        </is>
-      </c>
-      <c r="C110" s="17" t="inlineStr">
+          <t>Jonah Coleman (DEN)</t>
+        </is>
+      </c>
+      <c r="C110" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>15.03</t>
         </is>
       </c>
     </row>
@@ -8914,20 +8914,20 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>Javonte Williams (DAL)</t>
-        </is>
-      </c>
-      <c r="C111" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ja'Marr Chase (CIN)</t>
+        </is>
+      </c>
+      <c r="C111" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>
@@ -8937,20 +8937,20 @@
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Josh Allen (BUF)</t>
+          <t>Puka Nacua (LAR)</t>
         </is>
       </c>
       <c r="C112" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D112" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.05</t>
         </is>
       </c>
     </row>
@@ -8960,20 +8960,20 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>Bucky Irving (TB)</t>
-        </is>
-      </c>
-      <c r="C113" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jaxon Smith-Njigba (SEA)</t>
+        </is>
+      </c>
+      <c r="C113" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -8983,20 +8983,20 @@
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr. (NO)</t>
-        </is>
-      </c>
-      <c r="C114" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Amon-Ra St. Brown (DET)</t>
+        </is>
+      </c>
+      <c r="C114" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D114" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -9006,20 +9006,20 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>Cam Skattebo (NYG)</t>
-        </is>
-      </c>
-      <c r="C115" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>CeeDee Lamb (DAL)</t>
+        </is>
+      </c>
+      <c r="C115" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -9029,20 +9029,20 @@
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten (JAX)</t>
-        </is>
-      </c>
-      <c r="C116" s="17" t="inlineStr">
+          <t>Kenneth Walker (KC)</t>
+        </is>
+      </c>
+      <c r="C116" s="16" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
       <c r="D116" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -9052,20 +9052,20 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>Tyler Warren (IND)</t>
-        </is>
-      </c>
-      <c r="C117" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Justin Jefferson (MIN)</t>
+        </is>
+      </c>
+      <c r="C117" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -9075,20 +9075,20 @@
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>Colston Loveland (CHI)</t>
-        </is>
-      </c>
-      <c r="C118" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>A.J. Brown (NE)</t>
+        </is>
+      </c>
+      <c r="C118" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D118" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -9098,20 +9098,20 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>Quinshon Judkins (CLE)</t>
-        </is>
-      </c>
-      <c r="C119" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Chris Olave (NO)</t>
+        </is>
+      </c>
+      <c r="C119" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>3.07</t>
         </is>
       </c>
     </row>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson (NE)</t>
-        </is>
-      </c>
-      <c r="C120" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Nico Collins (HOU)</t>
+        </is>
+      </c>
+      <c r="C120" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D120" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -9144,20 +9144,20 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>David Montgomery (HOU)</t>
-        </is>
-      </c>
-      <c r="C121" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Garrett Wilson (NYJ)</t>
+        </is>
+      </c>
+      <c r="C121" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D121" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -9167,20 +9167,20 @@
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>Lamar Jackson (BAL)</t>
+          <t>Drake London (ATL)</t>
         </is>
       </c>
       <c r="C122" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -9190,20 +9190,20 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>Jadarian Price (SEA)</t>
-        </is>
-      </c>
-      <c r="C123" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>George Pickens (DAL)</t>
+        </is>
+      </c>
+      <c r="C123" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -9213,20 +9213,20 @@
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd (GB)</t>
-        </is>
-      </c>
-      <c r="C124" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rashee Rice (KC)</t>
+        </is>
+      </c>
+      <c r="C124" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D124" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -9236,20 +9236,20 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson (NE)</t>
-        </is>
-      </c>
-      <c r="C125" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Malik Nabers (NYG)</t>
+        </is>
+      </c>
+      <c r="C125" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -9259,20 +9259,20 @@
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>Rico Dowdle (PIT)</t>
-        </is>
-      </c>
-      <c r="C126" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Zay Flowers (BAL)</t>
+        </is>
+      </c>
+      <c r="C126" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>4.05</t>
         </is>
       </c>
     </row>
@@ -9282,20 +9282,20 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>Harold Fannin Jr. (CLE)</t>
-        </is>
-      </c>
-      <c r="C127" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>DeVonta Smith (PHI)</t>
+        </is>
+      </c>
+      <c r="C127" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>3.12</t>
         </is>
       </c>
     </row>
@@ -9305,20 +9305,20 @@
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt (WAS)</t>
-        </is>
-      </c>
-      <c r="C128" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jaylen Waddle (DEN)</t>
+        </is>
+      </c>
+      <c r="C128" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D128" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -9328,20 +9328,20 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>Kenny Gainwell (TB)</t>
-        </is>
-      </c>
-      <c r="C129" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ladd McConkey (LAC)</t>
+        </is>
+      </c>
+      <c r="C129" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D129" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>4.02</t>
         </is>
       </c>
     </row>
@@ -9351,20 +9351,20 @@
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Warren (PIT)</t>
-        </is>
-      </c>
-      <c r="C130" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Emeka Egbuka (TB)</t>
+        </is>
+      </c>
+      <c r="C130" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D130" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>4.03</t>
         </is>
       </c>
     </row>
@@ -9374,20 +9374,20 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>Tucker Kraft (GB)</t>
-        </is>
-      </c>
-      <c r="C131" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tetairoa McMillan (CAR)</t>
+        </is>
+      </c>
+      <c r="C131" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>4.01</t>
         </is>
       </c>
     </row>
@@ -9397,20 +9397,20 @@
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>Jalen Hurts (PHI)</t>
+          <t>Tee Higgins (CIN)</t>
         </is>
       </c>
       <c r="C132" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D132" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>3.11</t>
         </is>
       </c>
     </row>
@@ -9420,20 +9420,20 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>Jayden Daniels (WAS)</t>
+          <t>Carnell Tate (TEN)</t>
         </is>
       </c>
       <c r="C133" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D133" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -9443,16 +9443,16 @@
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Joe Burrow (CIN)</t>
+          <t>Luther Burden III (CHI)</t>
         </is>
       </c>
       <c r="C134" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D134" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
@@ -9466,20 +9466,20 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>George Kittle (SF)</t>
-        </is>
-      </c>
-      <c r="C135" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Christian Watson (GB)</t>
+        </is>
+      </c>
+      <c r="C135" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -9489,20 +9489,20 @@
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>Chuba Hubbard (CAR)</t>
-        </is>
-      </c>
-      <c r="C136" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Parker Washington (JAX)</t>
+        </is>
+      </c>
+      <c r="C136" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D136" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>7.04</t>
         </is>
       </c>
     </row>
@@ -9512,20 +9512,20 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>J.K. Dobbins (DEN)</t>
-        </is>
-      </c>
-      <c r="C137" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Terry McLaurin (WAS)</t>
+        </is>
+      </c>
+      <c r="C137" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -9535,20 +9535,20 @@
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>Tony Pollard (TEN)</t>
-        </is>
-      </c>
-      <c r="C138" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jameson Williams (DET)</t>
+        </is>
+      </c>
+      <c r="C138" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -9558,20 +9558,20 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>Jonathon Brooks (CAR)</t>
-        </is>
-      </c>
-      <c r="C139" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DJ Moore (BUF)</t>
+        </is>
+      </c>
+      <c r="C139" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>5.09</t>
         </is>
       </c>
     </row>
@@ -9581,20 +9581,20 @@
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>Sam LaPorta (DET)</t>
-        </is>
-      </c>
-      <c r="C140" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Davante Adams (LAR)</t>
+        </is>
+      </c>
+      <c r="C140" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D140" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.02</t>
         </is>
       </c>
     </row>
@@ -9604,20 +9604,20 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>Kyle Monangai (CHI)</t>
-        </is>
-      </c>
-      <c r="C141" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Mike Evans (SF)</t>
+        </is>
+      </c>
+      <c r="C141" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -9627,20 +9627,20 @@
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>Jordan Mason (MIN)</t>
-        </is>
-      </c>
-      <c r="C142" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rome Odunze (CHI)</t>
+        </is>
+      </c>
+      <c r="C142" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>6.05</t>
         </is>
       </c>
     </row>
@@ -9650,20 +9650,20 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>Drake Maye (NE)</t>
+          <t>Marvin Harrison Jr. (ARI)</t>
         </is>
       </c>
       <c r="C143" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -9673,20 +9673,20 @@
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>Rachaad White (WAS)</t>
-        </is>
-      </c>
-      <c r="C144" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DK Metcalf (PIT)</t>
+        </is>
+      </c>
+      <c r="C144" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -9696,20 +9696,20 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>Jaxson Dart (NYG)</t>
+          <t>Alec Pierce (IND)</t>
         </is>
       </c>
       <c r="C145" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>9.05</t>
         </is>
       </c>
     </row>
@@ -9719,20 +9719,20 @@
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>Kyle Pitts Sr. (ATL)</t>
-        </is>
-      </c>
-      <c r="C146" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Brian Thomas Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C146" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>7.02</t>
         </is>
       </c>
     </row>
@@ -9742,12 +9742,12 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Caleb Williams (CHI)</t>
+          <t>Chris Godwin Jr. (TB)</t>
         </is>
       </c>
       <c r="C147" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>8.12</t>
         </is>
       </c>
     </row>
@@ -9765,12 +9765,12 @@
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>Trevor Lawrence (JAX)</t>
+          <t>Quentin Johnston (LAC)</t>
         </is>
       </c>
       <c r="C148" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D148" s="14" t="n">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>10.05</t>
         </is>
       </c>
     </row>
@@ -9788,20 +9788,20 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>Blake Corum (LAR)</t>
-        </is>
-      </c>
-      <c r="C149" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Michael Pittman Jr. (PIT)</t>
+        </is>
+      </c>
+      <c r="C149" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>9.07</t>
         </is>
       </c>
     </row>
@@ -9811,20 +9811,20 @@
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>RJ Harvey (DEN)</t>
-        </is>
-      </c>
-      <c r="C150" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Wan'Dale Robinson (TEN)</t>
+        </is>
+      </c>
+      <c r="C150" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>10.09</t>
         </is>
       </c>
     </row>
@@ -9834,20 +9834,20 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Juwan Johnson (NO)</t>
-        </is>
-      </c>
-      <c r="C151" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Michael Wilson (ARI)</t>
+        </is>
+      </c>
+      <c r="C151" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D151" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>7.11</t>
         </is>
       </c>
     </row>
@@ -9857,20 +9857,20 @@
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Dalton Schultz (HOU)</t>
-        </is>
-      </c>
-      <c r="C152" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Stefon Diggs (WAS)</t>
+        </is>
+      </c>
+      <c r="C152" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>10.02</t>
         </is>
       </c>
     </row>
@@ -9880,20 +9880,20 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>Travis Kelce (KC)</t>
-        </is>
-      </c>
-      <c r="C153" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Courtland Sutton (DEN)</t>
+        </is>
+      </c>
+      <c r="C153" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>7.09</t>
         </is>
       </c>
     </row>
@@ -9903,12 +9903,12 @@
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr. (MIN)</t>
-        </is>
-      </c>
-      <c r="C154" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jordan Addison (MIN)</t>
+        </is>
+      </c>
+      <c r="C154" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D154" s="14" t="n">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>9.09</t>
         </is>
       </c>
     </row>
@@ -9926,20 +9926,20 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>Jake Ferguson (DAL)</t>
-        </is>
-      </c>
-      <c r="C155" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>De'Zhaun Stribling (SF)</t>
+        </is>
+      </c>
+      <c r="C155" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>12.07</t>
         </is>
       </c>
     </row>
@@ -9949,20 +9949,20 @@
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Dak Prescott (DAL)</t>
+          <t>Jayden Reed (GB)</t>
         </is>
       </c>
       <c r="C156" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -9972,20 +9972,20 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Dalton Kincaid (BUF)</t>
-        </is>
-      </c>
-      <c r="C157" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Josh Downs (IND)</t>
+        </is>
+      </c>
+      <c r="C157" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D157" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E157" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>10.01</t>
         </is>
       </c>
     </row>
@@ -9995,20 +9995,20 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Isaiah Likely (NYG)</t>
-        </is>
-      </c>
-      <c r="C158" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jakobi Meyers (JAX)</t>
+        </is>
+      </c>
+      <c r="C158" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>10.1</t>
         </is>
       </c>
     </row>
@@ -10018,20 +10018,20 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Tyjae Spears (TEN)</t>
-        </is>
-      </c>
-      <c r="C159" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Romeo Doubs (NE)</t>
+        </is>
+      </c>
+      <c r="C159" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E159" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -10041,12 +10041,12 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>Justin Herbert (LAC)</t>
+          <t>Khalil Shakir (BUF)</t>
         </is>
       </c>
       <c r="C160" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>12.11</t>
         </is>
       </c>
     </row>
@@ -10064,12 +10064,12 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>Dallas Goedert (PHI)</t>
-        </is>
-      </c>
-      <c r="C161" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Makai Lemon (PHI)</t>
+        </is>
+      </c>
+      <c r="C161" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="E161" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -10087,20 +10087,20 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Bo Nix (DEN)</t>
+          <t>Xavier Worthy (KC)</t>
         </is>
       </c>
       <c r="C162" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D162" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -10110,20 +10110,20 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>Brock Purdy (SF)</t>
+          <t>Malik Washington (MIA)</t>
         </is>
       </c>
       <c r="C163" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E163" s="14" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Jared Goff (DET)</t>
+          <t>Jalen Coker (CAR)</t>
         </is>
       </c>
       <c r="C164" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>13.02</t>
         </is>
       </c>
     </row>
@@ -10156,20 +10156,20 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>Tyler Shough (NO)</t>
+          <t>Rashid Shaheed (SEA)</t>
         </is>
       </c>
       <c r="C165" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E165" s="14" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>13.03</t>
         </is>
       </c>
     </row>
@@ -10179,12 +10179,12 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Matthew Stafford (LAR)</t>
+          <t>KC Concepcion (CLE)</t>
         </is>
       </c>
       <c r="C166" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>11.01</t>
         </is>
       </c>
     </row>
@@ -10202,20 +10202,20 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>Kyler Murray (MIN)</t>
+          <t>Kayshon Boutte (HOU)</t>
         </is>
       </c>
       <c r="C167" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E167" s="14" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>19.08</t>
         </is>
       </c>
     </row>
@@ -10225,12 +10225,12 @@
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>Jordan Love (GB)</t>
+          <t>Matthew Golden (GB)</t>
         </is>
       </c>
       <c r="C168" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>11.07</t>
         </is>
       </c>
     </row>
@@ -10248,20 +10248,20 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>Baker Mayfield (TB)</t>
+          <t>Keenan Allen (IND)</t>
         </is>
       </c>
       <c r="C169" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E169" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>17.07</t>
         </is>
       </c>
     </row>
@@ -10271,20 +10271,20 @@
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Patrick Mahomes (KC)</t>
+          <t>Jordyn Tyson (NO)</t>
         </is>
       </c>
       <c r="C170" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>8.07</t>
         </is>
       </c>
     </row>
@@ -10294,20 +10294,20 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>Brenton Strange (JAX)</t>
-        </is>
-      </c>
-      <c r="C171" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tre Tucker (LV)</t>
+        </is>
+      </c>
+      <c r="C171" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>17.1</t>
         </is>
       </c>
     </row>
@@ -10317,12 +10317,12 @@
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Mark Andrews (BAL)</t>
-        </is>
-      </c>
-      <c r="C172" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Omar Cooper Jr. (NYJ)</t>
+        </is>
+      </c>
+      <c r="C172" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D172" s="14" t="n">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>17.02</t>
         </is>
       </c>
     </row>
@@ -10340,20 +10340,20 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>Malik Willis (MIA)</t>
+          <t>Deebo Samuel Sr. (SF)</t>
         </is>
       </c>
       <c r="C173" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>11.11</t>
         </is>
       </c>
     </row>
@@ -10363,20 +10363,20 @@
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Woody Marks (HOU)</t>
-        </is>
-      </c>
-      <c r="C174" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Denzel Boston (CLE)</t>
+        </is>
+      </c>
+      <c r="C174" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10386,20 +10386,20 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>Hunter Henry (NE)</t>
-        </is>
-      </c>
-      <c r="C175" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Patrick Mahomes (KC)</t>
+        </is>
+      </c>
+      <c r="C175" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E175" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -10409,20 +10409,20 @@
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>Chig Okonkwo (WAS)</t>
-        </is>
-      </c>
-      <c r="C176" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Dontayvion Wicks (PHI)</t>
+        </is>
+      </c>
+      <c r="C176" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D176" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10432,20 +10432,20 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Chris Rodriguez Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C177" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Pat Bryant (DEN)</t>
+        </is>
+      </c>
+      <c r="C177" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E177" s="14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>19.11</t>
         </is>
       </c>
     </row>
@@ -10455,20 +10455,20 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Cam Ward (TEN)</t>
+          <t>Jalen Nailor (LV)</t>
         </is>
       </c>
       <c r="C178" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -10478,20 +10478,20 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Isiah Pacheco (DET)</t>
-        </is>
-      </c>
-      <c r="C179" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Travis Hunter (JAX)</t>
+        </is>
+      </c>
+      <c r="C179" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E179" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10501,20 +10501,20 @@
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>C.J. Stroud (HOU)</t>
+          <t>Cooper Kupp (SEA)</t>
         </is>
       </c>
       <c r="C180" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>19.05</t>
         </is>
       </c>
     </row>
@@ -10524,12 +10524,12 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>Sam Darnold (SEA)</t>
+          <t>Jerry Jeudy (CLE)</t>
         </is>
       </c>
       <c r="C181" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -10547,20 +10547,20 @@
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Keaton Mitchell (LAC)</t>
-        </is>
-      </c>
-      <c r="C182" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DeMario Douglas (NE)</t>
+        </is>
+      </c>
+      <c r="C182" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D182" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10570,20 +10570,20 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>Daniel Jones (IND)</t>
+          <t>Malachi Fields (NYG)</t>
         </is>
       </c>
       <c r="C183" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D183" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E183" s="14" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>19.04</t>
         </is>
       </c>
     </row>
@@ -10593,20 +10593,20 @@
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>Zach Charbonnet (SEA)</t>
-        </is>
-      </c>
-      <c r="C184" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Adonai Mitchell (NYJ)</t>
+        </is>
+      </c>
+      <c r="C184" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D184" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10616,20 +10616,20 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Tyler Allgeier (ARI)</t>
-        </is>
-      </c>
-      <c r="C185" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ja'Kobi Lane (BAL)</t>
+        </is>
+      </c>
+      <c r="C185" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E185" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>14.02</t>
         </is>
       </c>
     </row>
@@ -10639,20 +10639,20 @@
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Dylan Sampson (CLE)</t>
-        </is>
-      </c>
-      <c r="C186" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tank Dell (HOU)</t>
+        </is>
+      </c>
+      <c r="C186" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D186" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10662,20 +10662,20 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>T.J. Hockenson (MIN)</t>
-        </is>
-      </c>
-      <c r="C187" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Germie Bernard (PIT)</t>
+        </is>
+      </c>
+      <c r="C187" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D187" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E187" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10685,20 +10685,20 @@
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Mike Washington Jr. (LV)</t>
-        </is>
-      </c>
-      <c r="C188" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Cyrus Allen (KC)</t>
+        </is>
+      </c>
+      <c r="C188" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D188" s="14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -10708,20 +10708,20 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Greg Dulcich (MIA)</t>
-        </is>
-      </c>
-      <c r="C189" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kyle Williams (NE)</t>
+        </is>
+      </c>
+      <c r="C189" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E189" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>19.06</t>
         </is>
       </c>
     </row>
@@ -10731,20 +10731,20 @@
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq (NYJ)</t>
-        </is>
-      </c>
-      <c r="C190" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Calvin Ridley (TEN)</t>
+        </is>
+      </c>
+      <c r="C190" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D190" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E190" s="14" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>22.01</t>
         </is>
       </c>
     </row>
@@ -10754,20 +10754,20 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>Jonah Coleman (DEN)</t>
-        </is>
-      </c>
-      <c r="C191" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tre' Harris (LAC)</t>
+        </is>
+      </c>
+      <c r="C191" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E191" s="14" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10777,20 +10777,20 @@
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr. (NYG)</t>
-        </is>
-      </c>
-      <c r="C192" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Keon Coleman (BUF)</t>
+        </is>
+      </c>
+      <c r="C192" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D192" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>20.07</t>
         </is>
       </c>
     </row>
@@ -10800,20 +10800,20 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Pat Freiermuth (PIT)</t>
-        </is>
-      </c>
-      <c r="C193" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Zachariah Branch (ATL)</t>
+        </is>
+      </c>
+      <c r="C193" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -10823,20 +10823,20 @@
       </c>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>Aaron Rodgers (PIT)</t>
+          <t>Ryan Flournoy (DAL)</t>
         </is>
       </c>
       <c r="C194" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D194" s="14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E194" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10846,20 +10846,20 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Bryce Young (CAR)</t>
+          <t>Caleb Douglas (MIA)</t>
         </is>
       </c>
       <c r="C195" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E195" s="14" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>18.09</t>
         </is>
       </c>
     </row>
@@ -10869,20 +10869,20 @@
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>Cade Otton (TB)</t>
-        </is>
-      </c>
-      <c r="C196" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Brian Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C196" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D196" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E196" s="14" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>13.12</t>
         </is>
       </c>
     </row>
@@ -10892,20 +10892,20 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>Tank Bigsby (PHI)</t>
-        </is>
-      </c>
-      <c r="C197" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Devaughn Vele (NO)</t>
+        </is>
+      </c>
+      <c r="C197" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D197" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E197" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10915,12 +10915,12 @@
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Alvin Kamara (NO)</t>
-        </is>
-      </c>
-      <c r="C198" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jaylin Noel (HOU)</t>
+        </is>
+      </c>
+      <c r="C198" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D198" s="14" t="n">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>18.1</t>
         </is>
       </c>
     </row>
@@ -10938,16 +10938,16 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>Geno Smith (NYJ)</t>
+          <t>Darius Slayton (NYG)</t>
         </is>
       </c>
       <c r="C199" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E199" s="14" t="inlineStr">
         <is>
@@ -10961,20 +10961,20 @@
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Najee Harris (NYG)</t>
-        </is>
-      </c>
-      <c r="C200" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Oronde Gadsden (LAC)</t>
+        </is>
+      </c>
+      <c r="C200" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D200" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
@@ -10984,20 +10984,20 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>Brian Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C201" s="17" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rashod Bateman (BAL)</t>
+        </is>
+      </c>
+      <c r="C201" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D201" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>20.05</t>
         </is>
       </c>
     </row>
@@ -11007,20 +11007,20 @@
       </c>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>AJ Barner (SEA)</t>
-        </is>
-      </c>
-      <c r="C202" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jalen Tolbert (MIA)</t>
+        </is>
+      </c>
+      <c r="C202" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D202" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E202" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11030,20 +11030,20 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>Oronde Gadsden (LAC)</t>
-        </is>
-      </c>
-      <c r="C203" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tory Horton (SEA)</t>
+        </is>
+      </c>
+      <c r="C203" s="19" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D203" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>

--- a/assets/data/12guys1cup-cheat-sheet.xlsx
+++ b/assets/data/12guys1cup-cheat-sheet.xlsx
@@ -68,13 +68,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00E65100"/>
+      <color rgb="001565C0"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001565C0"/>
+      <color rgb="00E65100"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -130,12 +130,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00D4E4F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4E4F7"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -6522,20 +6522,20 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Christian McCaffrey (SF)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Puka Nacua (LAR)</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
     </row>
@@ -6545,20 +6545,20 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Lamar Jackson (BAL)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Ja'Marr Chase (CIN)</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>
@@ -6568,20 +6568,20 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Jayden Daniels (WAS)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Christian McCaffrey (SF)</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>1.06</t>
         </is>
       </c>
     </row>
@@ -6591,12 +6591,12 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Drake Maye (NE)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jaxon Smith-Njigba (SEA)</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Jalen Hurts (PHI)</t>
+          <t>Lamar Jackson (BAL)</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
@@ -6623,11 +6623,11 @@
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>3.09</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Joe Burrow (CIN)</t>
+          <t>Jayden Daniels (WAS)</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
@@ -6646,11 +6646,11 @@
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>6.04</t>
         </is>
       </c>
     </row>
@@ -6660,20 +6660,20 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Jonathan Taylor (IND)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Drake Maye (NE)</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Jaxson Dart (NYG)</t>
+          <t>Jalen Hurts (PHI)</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
@@ -6692,11 +6692,11 @@
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>5.12</t>
         </is>
       </c>
     </row>
@@ -6706,20 +6706,20 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Trevor Lawrence (JAX)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Amon-Ra St. Brown (DET)</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Brock Purdy (SF)</t>
+          <t>Joe Burrow (CIN)</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
@@ -6738,11 +6738,11 @@
         </is>
       </c>
       <c r="D16" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -6752,20 +6752,20 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Dak Prescott (DAL)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jonathan Taylor (IND)</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Caleb Williams (CHI)</t>
+          <t>Jaxson Dart (NYG)</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
@@ -6784,11 +6784,11 @@
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Justin Herbert (LAC)</t>
+          <t>Trevor Lawrence (JAX)</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Bo Nix (DEN)</t>
+          <t>Brock Purdy (SF)</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
@@ -6830,11 +6830,11 @@
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>11.02</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Matthew Stafford (LAR)</t>
+          <t>Dak Prescott (DAL)</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
@@ -6853,11 +6853,11 @@
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>7.07</t>
         </is>
       </c>
     </row>
@@ -6867,20 +6867,20 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>De'Von Achane (MIA)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Caleb Williams (CHI)</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Kyler Murray (MIN)</t>
+          <t>Justin Herbert (LAC)</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
@@ -6899,11 +6899,11 @@
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Jared Goff (DET)</t>
+          <t>Bo Nix (DEN)</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
@@ -6922,11 +6922,11 @@
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>10.12</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Tyler Shough (NO)</t>
+          <t>Matthew Stafford (LAR)</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
@@ -6945,11 +6945,11 @@
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>9.01</t>
         </is>
       </c>
     </row>
@@ -6959,20 +6959,20 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Baker Mayfield (TB)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>De'Von Achane (MIA)</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Chase Brown (CIN)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kyler Murray (MIN)</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>14.03</t>
         </is>
       </c>
     </row>
@@ -7005,20 +7005,20 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Derrick Henry (BAL)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jared Goff (DET)</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>12.03</t>
         </is>
       </c>
     </row>
@@ -7028,7 +7028,7 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Daniel Jones (IND)</t>
+          <t>Tyler Shough (NO)</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
@@ -7037,11 +7037,11 @@
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>16.07</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Malik Willis (MIA)</t>
+          <t>Baker Mayfield (TB)</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
@@ -7060,11 +7060,11 @@
         </is>
       </c>
       <c r="D30" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -7074,20 +7074,20 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Jordan Love (GB)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Chase Brown (CIN)</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>James Cook III (BUF)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Drake London (ATL)</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -7120,20 +7120,20 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Sam Darnold (SEA)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Derrick Henry (BAL)</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>2.08</t>
         </is>
       </c>
     </row>
@@ -7143,20 +7143,20 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Saquon Barkley (PHI)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Daniel Jones (IND)</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>17.11</t>
         </is>
       </c>
     </row>
@@ -7166,20 +7166,20 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>Ashton Jeanty (LV)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>CeeDee Lamb (DAL)</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>C.J. Stroud (HOU)</t>
+          <t>Malik Willis (MIA)</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
@@ -7198,11 +7198,11 @@
         </is>
       </c>
       <c r="D36" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -7212,20 +7212,20 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Trey McBride (ARI)</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jordan Love (GB)</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>13.05</t>
         </is>
       </c>
     </row>
@@ -7235,20 +7235,20 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Bryce Young (CAR)</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Justin Jefferson (MIN)</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Omarion Hampton (LAC)</t>
+          <t>James Cook III (BUF)</t>
         </is>
       </c>
       <c r="C39" s="16" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.11</t>
         </is>
       </c>
     </row>
@@ -7281,20 +7281,20 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>Jeremiyah Love (ARI)</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rashee Rice (KC)</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D40" s="14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -7304,20 +7304,20 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Breece Hall (NYJ)</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Sam Darnold (SEA)</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>14.05</t>
         </is>
       </c>
     </row>
@@ -7327,20 +7327,20 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Brock Bowers (LV)</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Saquon Barkley (PHI)</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D42" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -7350,20 +7350,20 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Javonte Williams (DAL)</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Chris Olave (NO)</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.07</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr. (NO)</t>
+          <t>Ashton Jeanty (LV)</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
@@ -7382,11 +7382,11 @@
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -7396,20 +7396,20 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Kyren Williams (LAR)</t>
-        </is>
-      </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>C.J. Stroud (HOU)</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>18.01</t>
         </is>
       </c>
     </row>
@@ -7419,20 +7419,20 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>Cam Skattebo (NYG)</t>
-        </is>
-      </c>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>A.J. Brown (NE)</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D46" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -7442,20 +7442,20 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Geno Smith (NYJ)</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Trey McBride (ARI)</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -7465,7 +7465,7 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Cam Ward (TEN)</t>
+          <t>Bryce Young (CAR)</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
@@ -7474,11 +7474,11 @@
         </is>
       </c>
       <c r="D48" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>19.12</t>
         </is>
       </c>
     </row>
@@ -7488,20 +7488,20 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>Aaron Rodgers (PIT)</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Omarion Hampton (LAC)</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D49" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>D'Andre Swift (CHI)</t>
+          <t>Jeremiyah Love (ARI)</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
@@ -7520,11 +7520,11 @@
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7534,20 +7534,20 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Bucky Irving (TB)</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>George Pickens (DAL)</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D51" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -7557,20 +7557,20 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Quinshon Judkins (CLE)</t>
-        </is>
-      </c>
-      <c r="C52" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Nico Collins (HOU)</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D52" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7580,20 +7580,20 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Colston Loveland (CHI)</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Breece Hall (NYJ)</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7603,20 +7603,20 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten (JAX)</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Brock Bowers (LV)</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -7626,12 +7626,12 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Tyler Warren (IND)</t>
+          <t>Garrett Wilson (NYJ)</t>
         </is>
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -7649,20 +7649,20 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Harold Fannin Jr. (CLE)</t>
+          <t>Zay Flowers (BAL)</t>
         </is>
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>4.05</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>David Montgomery (HOU)</t>
-        </is>
-      </c>
-      <c r="C57" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Malik Nabers (NYG)</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D57" s="14" t="n">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Warren (PIT)</t>
+          <t>Javonte Williams (DAL)</t>
         </is>
       </c>
       <c r="C58" s="16" t="inlineStr">
@@ -7704,11 +7704,11 @@
         </is>
       </c>
       <c r="D58" s="14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7718,20 +7718,20 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson (NE)</t>
-        </is>
-      </c>
-      <c r="C59" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DeVonta Smith (PHI)</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D59" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>3.12</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson (NE)</t>
+          <t>Travis Etienne Jr. (NO)</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr">
@@ -7750,11 +7750,11 @@
         </is>
       </c>
       <c r="D60" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.09</t>
         </is>
       </c>
     </row>
@@ -7764,20 +7764,20 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>George Kittle (SF)</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kyren Williams (LAR)</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
@@ -7787,20 +7787,20 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Kyle Pitts Sr. (ATL)</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Cam Skattebo (NYG)</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D62" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.08</t>
         </is>
       </c>
     </row>
@@ -7810,20 +7810,20 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Tony Pollard (TEN)</t>
-        </is>
-      </c>
-      <c r="C63" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Geno Smith (NYJ)</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D63" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7833,20 +7833,20 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Jadarian Price (SEA)</t>
-        </is>
-      </c>
-      <c r="C64" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tetairoa McMillan (CAR)</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D64" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>4.01</t>
         </is>
       </c>
     </row>
@@ -7856,20 +7856,20 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Sam LaPorta (DET)</t>
-        </is>
-      </c>
-      <c r="C65" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Cam Ward (TEN)</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D65" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -7879,20 +7879,20 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>Travis Kelce (KC)</t>
+          <t>Emeka Egbuka (TB)</t>
         </is>
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D66" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>4.03</t>
         </is>
       </c>
     </row>
@@ -7902,12 +7902,12 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>Rico Dowdle (PIT)</t>
-        </is>
-      </c>
-      <c r="C67" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Aaron Rodgers (PIT)</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D67" s="14" t="n">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -7925,12 +7925,12 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Dallas Goedert (PHI)</t>
-        </is>
-      </c>
-      <c r="C68" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>D'Andre Swift (CHI)</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D68" s="14" t="n">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -7948,20 +7948,20 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>J.K. Dobbins (DEN)</t>
-        </is>
-      </c>
-      <c r="C69" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Davante Adams (LAR)</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D69" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.02</t>
         </is>
       </c>
     </row>
@@ -7971,20 +7971,20 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Chuba Hubbard (CAR)</t>
-        </is>
-      </c>
-      <c r="C70" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tee Higgins (CIN)</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D70" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>3.11</t>
         </is>
       </c>
     </row>
@@ -7994,20 +7994,20 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>Tucker Kraft (GB)</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Bucky Irving (TB)</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>4.06</t>
         </is>
       </c>
     </row>
@@ -8017,20 +8017,20 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Kenny Gainwell (TB)</t>
-        </is>
-      </c>
-      <c r="C72" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ladd McConkey (LAC)</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>4.02</t>
         </is>
       </c>
     </row>
@@ -8040,20 +8040,20 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Jonathon Brooks (CAR)</t>
-        </is>
-      </c>
-      <c r="C73" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jameson Williams (DET)</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -8063,20 +8063,20 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Jake Ferguson (DAL)</t>
-        </is>
-      </c>
-      <c r="C74" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Quinshon Judkins (CLE)</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D74" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -8086,20 +8086,20 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>Mark Andrews (BAL)</t>
-        </is>
-      </c>
-      <c r="C75" s="18" t="inlineStr">
+          <t>Colston Loveland (CHI)</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>4.04</t>
         </is>
       </c>
     </row>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Isaiah Likely (NYG)</t>
+          <t>Jaylen Waddle (DEN)</t>
         </is>
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D76" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>RJ Harvey (DEN)</t>
+          <t>Bhayshul Tuten (JAX)</t>
         </is>
       </c>
       <c r="C77" s="16" t="inlineStr">
@@ -8141,11 +8141,11 @@
         </is>
       </c>
       <c r="D77" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8155,20 +8155,20 @@
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr. (MIN)</t>
-        </is>
-      </c>
-      <c r="C78" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Terry McLaurin (WAS)</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D78" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>Rachaad White (WAS)</t>
-        </is>
-      </c>
-      <c r="C79" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DJ Moore (BUF)</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D79" s="14" t="n">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>5.09</t>
         </is>
       </c>
     </row>
@@ -8201,20 +8201,20 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Dalton Kincaid (BUF)</t>
+          <t>Luther Burden III (CHI)</t>
         </is>
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D80" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -8224,12 +8224,12 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>Kyle Monangai (CHI)</t>
-        </is>
-      </c>
-      <c r="C81" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rome Odunze (CHI)</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D81" s="14" t="n">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>6.05</t>
         </is>
       </c>
     </row>
@@ -8247,20 +8247,20 @@
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Juwan Johnson (NO)</t>
-        </is>
-      </c>
-      <c r="C82" s="18" t="inlineStr">
+          <t>Tyler Warren (IND)</t>
+        </is>
+      </c>
+      <c r="C82" s="19" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D82" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>4.11</t>
         </is>
       </c>
     </row>
@@ -8270,10 +8270,10 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>Hunter Henry (NE)</t>
-        </is>
-      </c>
-      <c r="C83" s="18" t="inlineStr">
+          <t>Harold Fannin Jr. (CLE)</t>
+        </is>
+      </c>
+      <c r="C83" s="19" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -8293,20 +8293,20 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd (GB)</t>
-        </is>
-      </c>
-      <c r="C84" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Courtland Sutton (DEN)</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D84" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>7.09</t>
         </is>
       </c>
     </row>
@@ -8316,20 +8316,20 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>Brenton Strange (JAX)</t>
-        </is>
-      </c>
-      <c r="C85" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>David Montgomery (HOU)</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D85" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -8339,20 +8339,20 @@
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Dalton Schultz (HOU)</t>
+          <t>Christian Watson (GB)</t>
         </is>
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D86" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -8362,20 +8362,20 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt (WAS)</t>
-        </is>
-      </c>
-      <c r="C87" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Marvin Harrison Jr. (ARI)</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D87" s="14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8385,7 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Jordan Mason (MIN)</t>
+          <t>Jaylen Warren (PIT)</t>
         </is>
       </c>
       <c r="C88" s="16" t="inlineStr">
@@ -8394,11 +8394,11 @@
         </is>
       </c>
       <c r="D88" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -8408,20 +8408,20 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>T.J. Hockenson (MIN)</t>
+          <t>DK Metcalf (PIT)</t>
         </is>
       </c>
       <c r="C89" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D89" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -8431,20 +8431,20 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Blake Corum (LAR)</t>
-        </is>
-      </c>
-      <c r="C90" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Mike Evans (SF)</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D90" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8454,20 +8454,20 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>Tyjae Spears (TEN)</t>
-        </is>
-      </c>
-      <c r="C91" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Alec Pierce (IND)</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>9.05</t>
         </is>
       </c>
     </row>
@@ -8477,20 +8477,20 @@
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>Pat Freiermuth (PIT)</t>
-        </is>
-      </c>
-      <c r="C92" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>TreVeyon Henderson (NE)</t>
+        </is>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D92" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -8500,20 +8500,20 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>Greg Dulcich (MIA)</t>
-        </is>
-      </c>
-      <c r="C93" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Rhamondre Stevenson (NE)</t>
+        </is>
+      </c>
+      <c r="C93" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D93" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -8523,20 +8523,20 @@
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>Cade Otton (TB)</t>
+          <t>Michael Pittman Jr. (PIT)</t>
         </is>
       </c>
       <c r="C94" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D94" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>9.07</t>
         </is>
       </c>
     </row>
@@ -8546,20 +8546,20 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>Chig Okonkwo (WAS)</t>
-        </is>
-      </c>
-      <c r="C95" s="18" t="inlineStr">
+          <t>George Kittle (SF)</t>
+        </is>
+      </c>
+      <c r="C95" s="19" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D95" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -8569,20 +8569,20 @@
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Woody Marks (HOU)</t>
-        </is>
-      </c>
-      <c r="C96" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kyle Pitts Sr. (ATL)</t>
+        </is>
+      </c>
+      <c r="C96" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D96" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>6.1</t>
         </is>
       </c>
     </row>
@@ -8592,20 +8592,20 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq (NYJ)</t>
-        </is>
-      </c>
-      <c r="C97" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tony Pollard (TEN)</t>
+        </is>
+      </c>
+      <c r="C97" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>7.12</t>
         </is>
       </c>
     </row>
@@ -8615,12 +8615,12 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>AJ Barner (SEA)</t>
-        </is>
-      </c>
-      <c r="C98" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jadarian Price (SEA)</t>
+        </is>
+      </c>
+      <c r="C98" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D98" s="14" t="n">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -8638,20 +8638,20 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>Zach Charbonnet (SEA)</t>
-        </is>
-      </c>
-      <c r="C99" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Parker Washington (JAX)</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>7.04</t>
         </is>
       </c>
     </row>
@@ -8661,20 +8661,20 @@
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>Alvin Kamara (NO)</t>
-        </is>
-      </c>
-      <c r="C100" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Sam LaPorta (DET)</t>
+        </is>
+      </c>
+      <c r="C100" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D100" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -8684,20 +8684,20 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>Isiah Pacheco (DET)</t>
-        </is>
-      </c>
-      <c r="C101" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Travis Kelce (KC)</t>
+        </is>
+      </c>
+      <c r="C101" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>8.08</t>
         </is>
       </c>
     </row>
@@ -8707,20 +8707,20 @@
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Dylan Sampson (CLE)</t>
-        </is>
-      </c>
-      <c r="C102" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Brian Thomas Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D102" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>7.02</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>Mike Washington Jr. (LV)</t>
+          <t>Rico Dowdle (PIT)</t>
         </is>
       </c>
       <c r="C103" s="16" t="inlineStr">
@@ -8739,11 +8739,11 @@
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>8.01</t>
         </is>
       </c>
     </row>
@@ -8753,20 +8753,20 @@
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>Chris Rodriguez Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C104" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dallas Goedert (PHI)</t>
+        </is>
+      </c>
+      <c r="C104" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D104" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -8776,20 +8776,20 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>Tyler Allgeier (ARI)</t>
-        </is>
-      </c>
-      <c r="C105" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Wan'Dale Robinson (TEN)</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>10.09</t>
         </is>
       </c>
     </row>
@@ -8799,12 +8799,12 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>Keaton Mitchell (LAC)</t>
-        </is>
-      </c>
-      <c r="C106" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jakobi Meyers (JAX)</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D106" s="14" t="n">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>10.1</t>
         </is>
       </c>
     </row>
@@ -8822,20 +8822,20 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr. (NYG)</t>
-        </is>
-      </c>
-      <c r="C107" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Carnell Tate (TEN)</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -8845,20 +8845,20 @@
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>Tank Bigsby (PHI)</t>
-        </is>
-      </c>
-      <c r="C108" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Michael Wilson (ARI)</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D108" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>7.11</t>
         </is>
       </c>
     </row>
@@ -8868,20 +8868,20 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>Najee Harris (NYG)</t>
-        </is>
-      </c>
-      <c r="C109" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jayden Reed (GB)</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>Jonah Coleman (DEN)</t>
+          <t>J.K. Dobbins (DEN)</t>
         </is>
       </c>
       <c r="C110" s="16" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>8.1</t>
         </is>
       </c>
     </row>
@@ -8914,20 +8914,20 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase (CIN)</t>
-        </is>
-      </c>
-      <c r="C111" s="19" t="inlineStr">
+          <t>Chris Godwin Jr. (TB)</t>
+        </is>
+      </c>
+      <c r="C111" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>8.12</t>
         </is>
       </c>
     </row>
@@ -8937,20 +8937,20 @@
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Puka Nacua (LAR)</t>
-        </is>
-      </c>
-      <c r="C112" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chuba Hubbard (CAR)</t>
+        </is>
+      </c>
+      <c r="C112" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D112" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>7.05</t>
         </is>
       </c>
     </row>
@@ -8960,12 +8960,12 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba (SEA)</t>
+          <t>Tucker Kraft (GB)</t>
         </is>
       </c>
       <c r="C113" s="19" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D113" s="14" t="n">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8983,20 +8983,20 @@
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown (DET)</t>
-        </is>
-      </c>
-      <c r="C114" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kenny Gainwell (TB)</t>
+        </is>
+      </c>
+      <c r="C114" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D114" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -9006,20 +9006,20 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>CeeDee Lamb (DAL)</t>
-        </is>
-      </c>
-      <c r="C115" s="19" t="inlineStr">
+          <t>Quentin Johnston (LAC)</t>
+        </is>
+      </c>
+      <c r="C115" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>10.05</t>
         </is>
       </c>
     </row>
@@ -9029,20 +9029,20 @@
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>Kenneth Walker (KC)</t>
-        </is>
-      </c>
-      <c r="C116" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jordan Addison (MIN)</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D116" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>9.09</t>
         </is>
       </c>
     </row>
@@ -9052,20 +9052,20 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>Justin Jefferson (MIN)</t>
-        </is>
-      </c>
-      <c r="C117" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonathon Brooks (CAR)</t>
+        </is>
+      </c>
+      <c r="C117" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>9.1</t>
         </is>
       </c>
     </row>
@@ -9075,20 +9075,20 @@
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>A.J. Brown (NE)</t>
-        </is>
-      </c>
-      <c r="C118" s="19" t="inlineStr">
+          <t>Xavier Worthy (KC)</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D118" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -9098,20 +9098,20 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>Chris Olave (NO)</t>
+          <t>Jake Ferguson (DAL)</t>
         </is>
       </c>
       <c r="C119" s="19" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>9.02</t>
         </is>
       </c>
     </row>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Nico Collins (HOU)</t>
+          <t>Mark Andrews (BAL)</t>
         </is>
       </c>
       <c r="C120" s="19" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D120" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>11.09</t>
         </is>
       </c>
     </row>
@@ -9144,20 +9144,20 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>Garrett Wilson (NYJ)</t>
-        </is>
-      </c>
-      <c r="C121" s="19" t="inlineStr">
+          <t>Stefon Diggs (WAS)</t>
+        </is>
+      </c>
+      <c r="C121" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D121" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>10.02</t>
         </is>
       </c>
     </row>
@@ -9167,20 +9167,20 @@
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>Drake London (ATL)</t>
-        </is>
-      </c>
-      <c r="C122" s="19" t="inlineStr">
+          <t>De'Zhaun Stribling (SF)</t>
+        </is>
+      </c>
+      <c r="C122" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>12.07</t>
         </is>
       </c>
     </row>
@@ -9190,20 +9190,20 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>George Pickens (DAL)</t>
+          <t>Isaiah Likely (NYG)</t>
         </is>
       </c>
       <c r="C123" s="19" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -9213,20 +9213,20 @@
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>Rashee Rice (KC)</t>
-        </is>
-      </c>
-      <c r="C124" s="19" t="inlineStr">
+          <t>Matthew Golden (GB)</t>
+        </is>
+      </c>
+      <c r="C124" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D124" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>11.07</t>
         </is>
       </c>
     </row>
@@ -9236,20 +9236,20 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>Malik Nabers (NYG)</t>
-        </is>
-      </c>
-      <c r="C125" s="19" t="inlineStr">
+          <t>Khalil Shakir (BUF)</t>
+        </is>
+      </c>
+      <c r="C125" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>12.11</t>
         </is>
       </c>
     </row>
@@ -9259,20 +9259,20 @@
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>Zay Flowers (BAL)</t>
-        </is>
-      </c>
-      <c r="C126" s="19" t="inlineStr">
+          <t>KC Concepcion (CLE)</t>
+        </is>
+      </c>
+      <c r="C126" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>11.01</t>
         </is>
       </c>
     </row>
@@ -9282,20 +9282,20 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>DeVonta Smith (PHI)</t>
-        </is>
-      </c>
-      <c r="C127" s="19" t="inlineStr">
+          <t>Josh Downs (IND)</t>
+        </is>
+      </c>
+      <c r="C127" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>10.01</t>
         </is>
       </c>
     </row>
@@ -9305,20 +9305,20 @@
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Waddle (DEN)</t>
-        </is>
-      </c>
-      <c r="C128" s="19" t="inlineStr">
+          <t>Romeo Doubs (NE)</t>
+        </is>
+      </c>
+      <c r="C128" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D128" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -9328,20 +9328,20 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>Ladd McConkey (LAC)</t>
-        </is>
-      </c>
-      <c r="C129" s="19" t="inlineStr">
+          <t>Deebo Samuel Sr. (SF)</t>
+        </is>
+      </c>
+      <c r="C129" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D129" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>11.11</t>
         </is>
       </c>
     </row>
@@ -9351,12 +9351,12 @@
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>Emeka Egbuka (TB)</t>
-        </is>
-      </c>
-      <c r="C130" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>RJ Harvey (DEN)</t>
+        </is>
+      </c>
+      <c r="C130" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D130" s="14" t="n">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>7.08</t>
         </is>
       </c>
     </row>
@@ -9374,20 +9374,20 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan (CAR)</t>
-        </is>
-      </c>
-      <c r="C131" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Aaron Jones Sr. (MIN)</t>
+        </is>
+      </c>
+      <c r="C131" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -9397,20 +9397,20 @@
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>Tee Higgins (CIN)</t>
-        </is>
-      </c>
-      <c r="C132" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rachaad White (WAS)</t>
+        </is>
+      </c>
+      <c r="C132" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D132" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -9420,20 +9420,20 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>Carnell Tate (TEN)</t>
+          <t>Dalton Kincaid (BUF)</t>
         </is>
       </c>
       <c r="C133" s="19" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D133" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -9443,20 +9443,20 @@
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Luther Burden III (CHI)</t>
-        </is>
-      </c>
-      <c r="C134" s="19" t="inlineStr">
+          <t>Jalen Coker (CAR)</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D134" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>13.02</t>
         </is>
       </c>
     </row>
@@ -9466,10 +9466,10 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>Christian Watson (GB)</t>
-        </is>
-      </c>
-      <c r="C135" s="19" t="inlineStr">
+          <t>Rashid Shaheed (SEA)</t>
+        </is>
+      </c>
+      <c r="C135" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>13.03</t>
         </is>
       </c>
     </row>
@@ -9489,20 +9489,20 @@
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>Parker Washington (JAX)</t>
-        </is>
-      </c>
-      <c r="C136" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kyle Monangai (CHI)</t>
+        </is>
+      </c>
+      <c r="C136" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D136" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -9512,20 +9512,20 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>Terry McLaurin (WAS)</t>
-        </is>
-      </c>
-      <c r="C137" s="19" t="inlineStr">
+          <t>Jerry Jeudy (CLE)</t>
+        </is>
+      </c>
+      <c r="C137" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -9535,20 +9535,20 @@
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>Jameson Williams (DET)</t>
+          <t>Juwan Johnson (NO)</t>
         </is>
       </c>
       <c r="C138" s="19" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9558,20 +9558,20 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>DJ Moore (BUF)</t>
+          <t>Hunter Henry (NE)</t>
         </is>
       </c>
       <c r="C139" s="19" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -9581,12 +9581,12 @@
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>Davante Adams (LAR)</t>
-        </is>
-      </c>
-      <c r="C140" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>MarShawn Lloyd (GB)</t>
+        </is>
+      </c>
+      <c r="C140" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D140" s="14" t="n">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>15.06</t>
         </is>
       </c>
     </row>
@@ -9604,20 +9604,20 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>Mike Evans (SF)</t>
+          <t>Brenton Strange (JAX)</t>
         </is>
       </c>
       <c r="C141" s="19" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>13.08</t>
         </is>
       </c>
     </row>
@@ -9627,20 +9627,20 @@
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>Rome Odunze (CHI)</t>
-        </is>
-      </c>
-      <c r="C142" s="19" t="inlineStr">
+          <t>Denzel Boston (CLE)</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9650,20 +9650,20 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr. (ARI)</t>
-        </is>
-      </c>
-      <c r="C143" s="19" t="inlineStr">
+          <t>Makai Lemon (PHI)</t>
+        </is>
+      </c>
+      <c r="C143" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -9673,20 +9673,20 @@
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>DK Metcalf (PIT)</t>
+          <t>Dalton Schultz (HOU)</t>
         </is>
       </c>
       <c r="C144" s="19" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>17.01</t>
         </is>
       </c>
     </row>
@@ -9696,20 +9696,20 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>Alec Pierce (IND)</t>
-        </is>
-      </c>
-      <c r="C145" s="19" t="inlineStr">
+          <t>Calvin Ridley (TEN)</t>
+        </is>
+      </c>
+      <c r="C145" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>22.01</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C146" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jacory Croskey-Merritt (WAS)</t>
+        </is>
+      </c>
+      <c r="C146" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D146" s="14" t="n">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>10.06</t>
         </is>
       </c>
     </row>
@@ -9742,20 +9742,20 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr. (TB)</t>
-        </is>
-      </c>
-      <c r="C147" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jordan Mason (MIN)</t>
+        </is>
+      </c>
+      <c r="C147" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>10.07</t>
         </is>
       </c>
     </row>
@@ -9765,20 +9765,20 @@
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>Quentin Johnston (LAC)</t>
-        </is>
-      </c>
-      <c r="C148" s="19" t="inlineStr">
+          <t>Tre Tucker (LV)</t>
+        </is>
+      </c>
+      <c r="C148" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>17.1</t>
         </is>
       </c>
     </row>
@@ -9788,20 +9788,20 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>Michael Pittman Jr. (PIT)</t>
-        </is>
-      </c>
-      <c r="C149" s="19" t="inlineStr">
+          <t>Keenan Allen (IND)</t>
+        </is>
+      </c>
+      <c r="C149" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>17.07</t>
         </is>
       </c>
     </row>
@@ -9811,20 +9811,20 @@
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson (TEN)</t>
+          <t>T.J. Hockenson (MIN)</t>
         </is>
       </c>
       <c r="C150" s="19" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -9834,20 +9834,20 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Michael Wilson (ARI)</t>
-        </is>
-      </c>
-      <c r="C151" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Blake Corum (LAR)</t>
+        </is>
+      </c>
+      <c r="C151" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D151" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>9.08</t>
         </is>
       </c>
     </row>
@@ -9857,20 +9857,20 @@
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Stefon Diggs (WAS)</t>
-        </is>
-      </c>
-      <c r="C152" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyjae Spears (TEN)</t>
+        </is>
+      </c>
+      <c r="C152" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -9880,20 +9880,20 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>Courtland Sutton (DEN)</t>
-        </is>
-      </c>
-      <c r="C153" s="19" t="inlineStr">
+          <t>Kayshon Boutte (HOU)</t>
+        </is>
+      </c>
+      <c r="C153" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>19.08</t>
         </is>
       </c>
     </row>
@@ -9903,20 +9903,20 @@
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>Jordan Addison (MIN)</t>
-        </is>
-      </c>
-      <c r="C154" s="19" t="inlineStr">
+          <t>Rashod Bateman (BAL)</t>
+        </is>
+      </c>
+      <c r="C154" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>20.05</t>
         </is>
       </c>
     </row>
@@ -9926,20 +9926,20 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling (SF)</t>
+          <t>Pat Freiermuth (PIT)</t>
         </is>
       </c>
       <c r="C155" s="19" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -9949,20 +9949,20 @@
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Jayden Reed (GB)</t>
+          <t>Greg Dulcich (MIA)</t>
         </is>
       </c>
       <c r="C156" s="19" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -9972,10 +9972,10 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Josh Downs (IND)</t>
-        </is>
-      </c>
-      <c r="C157" s="19" t="inlineStr">
+          <t>Ja'Kobi Lane (BAL)</t>
+        </is>
+      </c>
+      <c r="C157" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -9985,7 +9985,7 @@
       </c>
       <c r="E157" s="14" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>14.02</t>
         </is>
       </c>
     </row>
@@ -9995,20 +9995,20 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Jakobi Meyers (JAX)</t>
+          <t>Cade Otton (TB)</t>
         </is>
       </c>
       <c r="C158" s="19" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>20.06</t>
         </is>
       </c>
     </row>
@@ -10018,20 +10018,20 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Romeo Doubs (NE)</t>
-        </is>
-      </c>
-      <c r="C159" s="19" t="inlineStr">
+          <t>Jalen Nailor (LV)</t>
+        </is>
+      </c>
+      <c r="C159" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E159" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -10041,12 +10041,12 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>Khalil Shakir (BUF)</t>
+          <t>Chig Okonkwo (WAS)</t>
         </is>
       </c>
       <c r="C160" s="19" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -10064,20 +10064,20 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>Makai Lemon (PHI)</t>
-        </is>
-      </c>
-      <c r="C161" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Woody Marks (HOU)</t>
+        </is>
+      </c>
+      <c r="C161" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E161" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>14.04</t>
         </is>
       </c>
     </row>
@@ -10087,20 +10087,20 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Xavier Worthy (KC)</t>
-        </is>
-      </c>
-      <c r="C162" s="19" t="inlineStr">
+          <t>Devaughn Vele (NO)</t>
+        </is>
+      </c>
+      <c r="C162" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D162" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10110,20 +10110,20 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>Malik Washington (MIA)</t>
+          <t>Kenyon Sadiq (NYJ)</t>
         </is>
       </c>
       <c r="C163" s="19" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E163" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>13.1</t>
         </is>
       </c>
     </row>
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Jalen Coker (CAR)</t>
-        </is>
-      </c>
-      <c r="C164" s="19" t="inlineStr">
+          <t>Cooper Kupp (SEA)</t>
+        </is>
+      </c>
+      <c r="C164" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>19.05</t>
         </is>
       </c>
     </row>
@@ -10156,12 +10156,12 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>Rashid Shaheed (SEA)</t>
+          <t>AJ Barner (SEA)</t>
         </is>
       </c>
       <c r="C165" s="19" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D165" s="14" t="n">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="E165" s="14" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10179,20 +10179,20 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>KC Concepcion (CLE)</t>
-        </is>
-      </c>
-      <c r="C166" s="19" t="inlineStr">
+          <t>Jaylin Noel (HOU)</t>
+        </is>
+      </c>
+      <c r="C166" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>18.1</t>
         </is>
       </c>
     </row>
@@ -10202,20 +10202,20 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>Kayshon Boutte (HOU)</t>
-        </is>
-      </c>
-      <c r="C167" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Zach Charbonnet (SEA)</t>
+        </is>
+      </c>
+      <c r="C167" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E167" s="14" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>13.04</t>
         </is>
       </c>
     </row>
@@ -10225,20 +10225,20 @@
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>Matthew Golden (GB)</t>
-        </is>
-      </c>
-      <c r="C168" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Alvin Kamara (NO)</t>
+        </is>
+      </c>
+      <c r="C168" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>14.07</t>
         </is>
       </c>
     </row>
@@ -10248,10 +10248,10 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>Keenan Allen (IND)</t>
-        </is>
-      </c>
-      <c r="C169" s="19" t="inlineStr">
+          <t>Adonai Mitchell (NYJ)</t>
+        </is>
+      </c>
+      <c r="C169" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="E169" s="14" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10271,20 +10271,20 @@
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Jordyn Tyson (NO)</t>
-        </is>
-      </c>
-      <c r="C170" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Isiah Pacheco (DET)</t>
+        </is>
+      </c>
+      <c r="C170" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -10294,20 +10294,20 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>Tre Tucker (LV)</t>
-        </is>
-      </c>
-      <c r="C171" s="19" t="inlineStr">
+          <t>Malik Washington (MIA)</t>
+        </is>
+      </c>
+      <c r="C171" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -10317,20 +10317,20 @@
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Omar Cooper Jr. (NYJ)</t>
-        </is>
-      </c>
-      <c r="C172" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dylan Sampson (CLE)</t>
+        </is>
+      </c>
+      <c r="C172" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -10340,20 +10340,20 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>Deebo Samuel Sr. (SF)</t>
-        </is>
-      </c>
-      <c r="C173" s="19" t="inlineStr">
+          <t>Germie Bernard (PIT)</t>
+        </is>
+      </c>
+      <c r="C173" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10363,20 +10363,20 @@
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Denzel Boston (CLE)</t>
-        </is>
-      </c>
-      <c r="C174" s="19" t="inlineStr">
+          <t>Jordyn Tyson (NO)</t>
+        </is>
+      </c>
+      <c r="C174" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>8.07</t>
         </is>
       </c>
     </row>
@@ -10386,20 +10386,20 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>Patrick Mahomes (KC)</t>
-        </is>
-      </c>
-      <c r="C175" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Caleb Douglas (MIA)</t>
+        </is>
+      </c>
+      <c r="C175" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E175" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>18.09</t>
         </is>
       </c>
     </row>
@@ -10409,20 +10409,20 @@
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks (PHI)</t>
-        </is>
-      </c>
-      <c r="C176" s="19" t="inlineStr">
+          <t>Omar Cooper Jr. (NYJ)</t>
+        </is>
+      </c>
+      <c r="C176" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D176" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17.02</t>
         </is>
       </c>
     </row>
@@ -10432,20 +10432,20 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Pat Bryant (DEN)</t>
-        </is>
-      </c>
-      <c r="C177" s="19" t="inlineStr">
+          <t>Travis Hunter (JAX)</t>
+        </is>
+      </c>
+      <c r="C177" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E177" s="14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10455,20 +10455,20 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Jalen Nailor (LV)</t>
-        </is>
-      </c>
-      <c r="C178" s="19" t="inlineStr">
+          <t>Dontayvion Wicks (PHI)</t>
+        </is>
+      </c>
+      <c r="C178" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10478,20 +10478,20 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Travis Hunter (JAX)</t>
-        </is>
-      </c>
-      <c r="C179" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Mike Washington Jr. (LV)</t>
+        </is>
+      </c>
+      <c r="C179" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E179" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>15.05</t>
         </is>
       </c>
     </row>
@@ -10501,20 +10501,20 @@
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Cooper Kupp (SEA)</t>
-        </is>
-      </c>
-      <c r="C180" s="19" t="inlineStr">
+          <t>Darius Slayton (NYG)</t>
+        </is>
+      </c>
+      <c r="C180" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10524,20 +10524,20 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>Jerry Jeudy (CLE)</t>
-        </is>
-      </c>
-      <c r="C181" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chris Rodriguez Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C181" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>12.08</t>
         </is>
       </c>
     </row>
@@ -10547,10 +10547,10 @@
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>DeMario Douglas (NE)</t>
-        </is>
-      </c>
-      <c r="C182" s="19" t="inlineStr">
+          <t>Tory Horton (SEA)</t>
+        </is>
+      </c>
+      <c r="C182" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10570,20 +10570,20 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>Malachi Fields (NYG)</t>
-        </is>
-      </c>
-      <c r="C183" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyler Allgeier (ARI)</t>
+        </is>
+      </c>
+      <c r="C183" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D183" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E183" s="14" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -10593,20 +10593,20 @@
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>Adonai Mitchell (NYJ)</t>
-        </is>
-      </c>
-      <c r="C184" s="19" t="inlineStr">
+          <t>Tre' Harris (LAC)</t>
+        </is>
+      </c>
+      <c r="C184" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D184" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10616,20 +10616,20 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane (BAL)</t>
-        </is>
-      </c>
-      <c r="C185" s="19" t="inlineStr">
+          <t>Jalen Tolbert (MIA)</t>
+        </is>
+      </c>
+      <c r="C185" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E185" s="14" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10639,20 +10639,20 @@
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Tank Dell (HOU)</t>
-        </is>
-      </c>
-      <c r="C186" s="19" t="inlineStr">
+          <t>Ryan Flournoy (DAL)</t>
+        </is>
+      </c>
+      <c r="C186" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D186" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10662,20 +10662,20 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>Germie Bernard (PIT)</t>
-        </is>
-      </c>
-      <c r="C187" s="19" t="inlineStr">
+          <t>Malachi Fields (NYG)</t>
+        </is>
+      </c>
+      <c r="C187" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D187" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E187" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>19.04</t>
         </is>
       </c>
     </row>
@@ -10685,20 +10685,20 @@
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Cyrus Allen (KC)</t>
-        </is>
-      </c>
-      <c r="C188" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Keaton Mitchell (LAC)</t>
+        </is>
+      </c>
+      <c r="C188" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D188" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10708,20 +10708,20 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Kyle Williams (NE)</t>
-        </is>
-      </c>
-      <c r="C189" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyrone Tracy Jr. (NYG)</t>
+        </is>
+      </c>
+      <c r="C189" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E189" s="14" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10731,20 +10731,20 @@
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Calvin Ridley (TEN)</t>
-        </is>
-      </c>
-      <c r="C190" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tank Bigsby (PHI)</t>
+        </is>
+      </c>
+      <c r="C190" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D190" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E190" s="14" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10754,20 +10754,20 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>Tre' Harris (LAC)</t>
-        </is>
-      </c>
-      <c r="C191" s="19" t="inlineStr">
+          <t>DeMario Douglas (NE)</t>
+        </is>
+      </c>
+      <c r="C191" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E191" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10777,20 +10777,20 @@
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Keon Coleman (BUF)</t>
-        </is>
-      </c>
-      <c r="C192" s="19" t="inlineStr">
+          <t>Zachariah Branch (ATL)</t>
+        </is>
+      </c>
+      <c r="C192" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D192" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -10800,20 +10800,20 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Zachariah Branch (ATL)</t>
-        </is>
-      </c>
-      <c r="C193" s="19" t="inlineStr">
+          <t>Keon Coleman (BUF)</t>
+        </is>
+      </c>
+      <c r="C193" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>20.07</t>
         </is>
       </c>
     </row>
@@ -10823,20 +10823,20 @@
       </c>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>Ryan Flournoy (DAL)</t>
-        </is>
-      </c>
-      <c r="C194" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Najee Harris (NYG)</t>
+        </is>
+      </c>
+      <c r="C194" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D194" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E194" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10846,20 +10846,20 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Caleb Douglas (MIA)</t>
-        </is>
-      </c>
-      <c r="C195" s="19" t="inlineStr">
+          <t>Pat Bryant (DEN)</t>
+        </is>
+      </c>
+      <c r="C195" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E195" s="14" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>19.11</t>
         </is>
       </c>
     </row>
@@ -10869,20 +10869,20 @@
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>Brian Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C196" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tank Dell (HOU)</t>
+        </is>
+      </c>
+      <c r="C196" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D196" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E196" s="14" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10892,20 +10892,20 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>Devaughn Vele (NO)</t>
-        </is>
-      </c>
-      <c r="C197" s="19" t="inlineStr">
+          <t>Cyrus Allen (KC)</t>
+        </is>
+      </c>
+      <c r="C197" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D197" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E197" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -10915,20 +10915,20 @@
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Jaylin Noel (HOU)</t>
-        </is>
-      </c>
-      <c r="C198" s="19" t="inlineStr">
+          <t>Kyle Williams (NE)</t>
+        </is>
+      </c>
+      <c r="C198" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D198" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>19.06</t>
         </is>
       </c>
     </row>
@@ -10938,20 +10938,20 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>Darius Slayton (NYG)</t>
-        </is>
-      </c>
-      <c r="C199" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonah Coleman (DEN)</t>
+        </is>
+      </c>
+      <c r="C199" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E199" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.03</t>
         </is>
       </c>
     </row>
@@ -10961,20 +10961,20 @@
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Oronde Gadsden (LAC)</t>
-        </is>
-      </c>
-      <c r="C200" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kenneth Walker (KC)</t>
+        </is>
+      </c>
+      <c r="C200" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D200" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -10984,20 +10984,20 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>Rashod Bateman (BAL)</t>
-        </is>
-      </c>
-      <c r="C201" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Patrick Mahomes (KC)</t>
+        </is>
+      </c>
+      <c r="C201" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D201" s="14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -11007,20 +11007,20 @@
       </c>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>Jalen Tolbert (MIA)</t>
-        </is>
-      </c>
-      <c r="C202" s="19" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brian Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C202" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D202" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E202" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.12</t>
         </is>
       </c>
     </row>
@@ -11030,20 +11030,20 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>Tory Horton (SEA)</t>
+          <t>Oronde Gadsden (LAC)</t>
         </is>
       </c>
       <c r="C203" s="19" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D203" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>

--- a/assets/data/12guys1cup-cheat-sheet.xlsx
+++ b/assets/data/12guys1cup-cheat-sheet.xlsx
@@ -62,12 +62,6 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00B8386B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="001565C0"/>
       <sz val="10"/>
     </font>
@@ -75,6 +69,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00E65100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00B8386B"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -125,17 +125,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D4E4F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -6476,20 +6476,20 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Josh Allen (BUF)</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Bijan Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.03</t>
         </is>
       </c>
     </row>
@@ -6499,20 +6499,20 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Bijan Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ja'Marr Chase (CIN)</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>
@@ -6525,7 +6525,7 @@
           <t>Puka Nacua (LAR)</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6545,20 +6545,20 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase (CIN)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Christian McCaffrey (SF)</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
     </row>
@@ -6568,20 +6568,20 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Christian McCaffrey (SF)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jaxon Smith-Njigba (SEA)</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6591,20 +6591,20 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba (SEA)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
+          <t>Amon-Ra St. Brown (DET)</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6614,20 +6614,20 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Lamar Jackson (BAL)</t>
+          <t>CeeDee Lamb (DAL)</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6637,20 +6637,20 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Jayden Daniels (WAS)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jonathan Taylor (IND)</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6660,20 +6660,20 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Drake Maye (NE)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>James Cook III (BUF)</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>1.11</t>
         </is>
       </c>
     </row>
@@ -6683,20 +6683,20 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Jalen Hurts (PHI)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>De'Von Achane (MIA)</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6706,20 +6706,20 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown (DET)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kenneth Walker (KC)</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -6729,12 +6729,12 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Joe Burrow (CIN)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Chase Brown (CIN)</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -6752,20 +6752,20 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Jonathan Taylor (IND)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Justin Jefferson (MIN)</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6775,20 +6775,20 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Jaxson Dart (NYG)</t>
+          <t>A.J. Brown (NE)</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -6798,20 +6798,20 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Trevor Lawrence (JAX)</t>
+          <t>Chris Olave (NO)</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>3.07</t>
         </is>
       </c>
     </row>
@@ -6821,20 +6821,20 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Brock Purdy (SF)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Brock Bowers (LV)</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -6844,20 +6844,20 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Dak Prescott (DAL)</t>
+          <t>Nico Collins (HOU)</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -6867,20 +6867,20 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Caleb Williams (CHI)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Trey McBride (ARI)</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -6890,20 +6890,20 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Justin Herbert (LAC)</t>
+          <t>Garrett Wilson (NYJ)</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -6913,20 +6913,20 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Bo Nix (DEN)</t>
+          <t>Drake London (ATL)</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -6936,20 +6936,20 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Matthew Stafford (LAR)</t>
+          <t>George Pickens (DAL)</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -6959,20 +6959,20 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>De'Von Achane (MIA)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rashee Rice (KC)</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -6982,20 +6982,20 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Kyler Murray (MIN)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Omarion Hampton (LAC)</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7005,20 +7005,20 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Jared Goff (DET)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Ashton Jeanty (LV)</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -7028,12 +7028,12 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Tyler Shough (NO)</t>
+          <t>Malik Nabers (NYG)</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -7051,12 +7051,12 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Baker Mayfield (TB)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Saquon Barkley (PHI)</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -7074,20 +7074,20 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Chase Brown (CIN)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Zay Flowers (BAL)</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>4.05</t>
         </is>
       </c>
     </row>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Drake London (ATL)</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Derrick Henry (BAL)</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.08</t>
         </is>
       </c>
     </row>
@@ -7120,20 +7120,20 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Derrick Henry (BAL)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DeVonta Smith (PHI)</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.12</t>
         </is>
       </c>
     </row>
@@ -7143,20 +7143,20 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Daniel Jones (IND)</t>
+          <t>Jaylen Waddle (DEN)</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -7166,12 +7166,12 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>CeeDee Lamb (DAL)</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jeremiyah Love (ARI)</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7189,20 +7189,20 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Malik Willis (MIA)</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Kyren Williams (LAR)</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D36" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
@@ -7212,20 +7212,20 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Jordan Love (GB)</t>
+          <t>Ladd McConkey (LAC)</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>4.02</t>
         </is>
       </c>
     </row>
@@ -7235,20 +7235,20 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Justin Jefferson (MIN)</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Breece Hall (NYJ)</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7258,20 +7258,20 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>James Cook III (BUF)</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Emeka Egbuka (TB)</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>4.03</t>
         </is>
       </c>
     </row>
@@ -7281,20 +7281,20 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>Rashee Rice (KC)</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>D'Andre Swift (CHI)</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D40" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -7304,20 +7304,20 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Sam Darnold (SEA)</t>
+          <t>Tetairoa McMillan (CAR)</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>4.01</t>
         </is>
       </c>
     </row>
@@ -7327,20 +7327,20 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Saquon Barkley (PHI)</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tee Higgins (CIN)</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D42" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>3.11</t>
         </is>
       </c>
     </row>
@@ -7350,20 +7350,20 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Chris Olave (NO)</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
+          <t>Carnell Tate (TEN)</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Ashton Jeanty (LV)</t>
+          <t>Javonte Williams (DAL)</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
@@ -7382,11 +7382,11 @@
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7396,20 +7396,20 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>C.J. Stroud (HOU)</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="inlineStr">
+          <t>Josh Allen (BUF)</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>2.09</t>
         </is>
       </c>
     </row>
@@ -7419,20 +7419,20 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>A.J. Brown (NE)</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="inlineStr">
+          <t>Luther Burden III (CHI)</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D46" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -7442,20 +7442,20 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Trey McBride (ARI)</t>
-        </is>
-      </c>
-      <c r="C47" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Christian Watson (GB)</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -7465,20 +7465,20 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Bryce Young (CAR)</t>
-        </is>
-      </c>
-      <c r="C48" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Bucky Irving (TB)</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D48" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>4.06</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>Omarion Hampton (LAC)</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Parker Washington (JAX)</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D49" s="14" t="n">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>7.04</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Jeremiyah Love (ARI)</t>
+          <t>Travis Etienne Jr. (NO)</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
@@ -7520,11 +7520,11 @@
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.09</t>
         </is>
       </c>
     </row>
@@ -7534,20 +7534,20 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>George Pickens (DAL)</t>
-        </is>
-      </c>
-      <c r="C51" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Cam Skattebo (NYG)</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D51" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>4.08</t>
         </is>
       </c>
     </row>
@@ -7557,20 +7557,20 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Nico Collins (HOU)</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="inlineStr">
+          <t>Terry McLaurin (WAS)</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D52" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -7580,20 +7580,20 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Breece Hall (NYJ)</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jameson Williams (DET)</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -7603,20 +7603,20 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>Brock Bowers (LV)</t>
-        </is>
-      </c>
-      <c r="C54" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>DJ Moore (BUF)</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>5.09</t>
         </is>
       </c>
     </row>
@@ -7626,20 +7626,20 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Garrett Wilson (NYJ)</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Bhayshul Tuten (JAX)</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -7649,20 +7649,20 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Zay Flowers (BAL)</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="inlineStr">
+          <t>Davante Adams (LAR)</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>5.02</t>
         </is>
       </c>
     </row>
@@ -7672,10 +7672,10 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Malik Nabers (NYG)</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="inlineStr">
+          <t>Mike Evans (SF)</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -7695,20 +7695,20 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Javonte Williams (DAL)</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rome Odunze (CHI)</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D58" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>6.05</t>
         </is>
       </c>
     </row>
@@ -7718,20 +7718,20 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>DeVonta Smith (PHI)</t>
-        </is>
-      </c>
-      <c r="C59" s="18" t="inlineStr">
+          <t>Marvin Harrison Jr. (ARI)</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D59" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -7741,20 +7741,20 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr. (NO)</t>
-        </is>
-      </c>
-      <c r="C60" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DK Metcalf (PIT)</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D60" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -7764,20 +7764,20 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Kyren Williams (LAR)</t>
-        </is>
-      </c>
-      <c r="C61" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tyler Warren (IND)</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>4.11</t>
         </is>
       </c>
     </row>
@@ -7787,20 +7787,20 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Cam Skattebo (NYG)</t>
-        </is>
-      </c>
-      <c r="C62" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Colston Loveland (CHI)</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D62" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.04</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Geno Smith (NYJ)</t>
+          <t>Alec Pierce (IND)</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D63" s="14" t="n">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.05</t>
         </is>
       </c>
     </row>
@@ -7833,20 +7833,20 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan (CAR)</t>
-        </is>
-      </c>
-      <c r="C64" s="18" t="inlineStr">
+          <t>Brian Thomas Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D64" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>7.02</t>
         </is>
       </c>
     </row>
@@ -7856,20 +7856,20 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Cam Ward (TEN)</t>
-        </is>
-      </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Quinshon Judkins (CLE)</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D65" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -7879,20 +7879,20 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>Emeka Egbuka (TB)</t>
-        </is>
-      </c>
-      <c r="C66" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>TreVeyon Henderson (NE)</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D66" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -7902,20 +7902,20 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>Aaron Rodgers (PIT)</t>
-        </is>
-      </c>
-      <c r="C67" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>David Montgomery (HOU)</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D67" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -7925,20 +7925,20 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>D'Andre Swift (CHI)</t>
-        </is>
-      </c>
-      <c r="C68" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Lamar Jackson (BAL)</t>
+        </is>
+      </c>
+      <c r="C68" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D68" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>3.09</t>
         </is>
       </c>
     </row>
@@ -7948,20 +7948,20 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Davante Adams (LAR)</t>
-        </is>
-      </c>
-      <c r="C69" s="18" t="inlineStr">
+          <t>Chris Godwin Jr. (TB)</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D69" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>8.12</t>
         </is>
       </c>
     </row>
@@ -7971,20 +7971,20 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Tee Higgins (CIN)</t>
-        </is>
-      </c>
-      <c r="C70" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jadarian Price (SEA)</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D70" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>Bucky Irving (TB)</t>
+          <t>MarShawn Lloyd (GB)</t>
         </is>
       </c>
       <c r="C71" s="16" t="inlineStr">
@@ -8003,11 +8003,11 @@
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>15.06</t>
         </is>
       </c>
     </row>
@@ -8017,20 +8017,20 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Ladd McConkey (LAC)</t>
-        </is>
-      </c>
-      <c r="C72" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rhamondre Stevenson (NE)</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -8040,20 +8040,20 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Jameson Williams (DET)</t>
-        </is>
-      </c>
-      <c r="C73" s="18" t="inlineStr">
+          <t>Quentin Johnston (LAC)</t>
+        </is>
+      </c>
+      <c r="C73" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>10.05</t>
         </is>
       </c>
     </row>
@@ -8063,20 +8063,20 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Quinshon Judkins (CLE)</t>
-        </is>
-      </c>
-      <c r="C74" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Michael Pittman Jr. (PIT)</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D74" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>9.07</t>
         </is>
       </c>
     </row>
@@ -8086,20 +8086,20 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>Colston Loveland (CHI)</t>
-        </is>
-      </c>
-      <c r="C75" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Rico Dowdle (PIT)</t>
+        </is>
+      </c>
+      <c r="C75" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>8.01</t>
         </is>
       </c>
     </row>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Waddle (DEN)</t>
-        </is>
-      </c>
-      <c r="C76" s="18" t="inlineStr">
+          <t>Wan'Dale Robinson (TEN)</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D76" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>10.09</t>
         </is>
       </c>
     </row>
@@ -8132,20 +8132,20 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten (JAX)</t>
-        </is>
-      </c>
-      <c r="C77" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Harold Fannin Jr. (CLE)</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D77" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -8155,20 +8155,20 @@
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Terry McLaurin (WAS)</t>
-        </is>
-      </c>
-      <c r="C78" s="18" t="inlineStr">
+          <t>Michael Wilson (ARI)</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D78" s="14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>7.11</t>
         </is>
       </c>
     </row>
@@ -8178,10 +8178,10 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>DJ Moore (BUF)</t>
-        </is>
-      </c>
-      <c r="C79" s="18" t="inlineStr">
+          <t>Stefon Diggs (WAS)</t>
+        </is>
+      </c>
+      <c r="C79" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>10.02</t>
         </is>
       </c>
     </row>
@@ -8201,10 +8201,10 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Luther Burden III (CHI)</t>
-        </is>
-      </c>
-      <c r="C80" s="18" t="inlineStr">
+          <t>Courtland Sutton (DEN)</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8214,7 +8214,7 @@
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>7.09</t>
         </is>
       </c>
     </row>
@@ -8224,20 +8224,20 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>Rome Odunze (CHI)</t>
-        </is>
-      </c>
-      <c r="C81" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jacory Croskey-Merritt (WAS)</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D81" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>10.06</t>
         </is>
       </c>
     </row>
@@ -8247,20 +8247,20 @@
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Tyler Warren (IND)</t>
-        </is>
-      </c>
-      <c r="C82" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kenny Gainwell (TB)</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D82" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8270,20 +8270,20 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>Harold Fannin Jr. (CLE)</t>
-        </is>
-      </c>
-      <c r="C83" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jaylen Warren (PIT)</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D83" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -8293,20 +8293,20 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Courtland Sutton (DEN)</t>
-        </is>
-      </c>
-      <c r="C84" s="18" t="inlineStr">
+          <t>Jordan Addison (MIN)</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D84" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>9.09</t>
         </is>
       </c>
     </row>
@@ -8316,12 +8316,12 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>David Montgomery (HOU)</t>
-        </is>
-      </c>
-      <c r="C85" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>De'Zhaun Stribling (SF)</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D85" s="14" t="n">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>12.07</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Christian Watson (GB)</t>
+          <t>Tucker Kraft (GB)</t>
         </is>
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D86" s="14" t="n">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8362,20 +8362,20 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr. (ARI)</t>
-        </is>
-      </c>
-      <c r="C87" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jalen Hurts (PHI)</t>
+        </is>
+      </c>
+      <c r="C87" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D87" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>5.12</t>
         </is>
       </c>
     </row>
@@ -8385,20 +8385,20 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Warren (PIT)</t>
-        </is>
-      </c>
-      <c r="C88" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jayden Reed (GB)</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D88" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8408,20 +8408,20 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>DK Metcalf (PIT)</t>
-        </is>
-      </c>
-      <c r="C89" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jayden Daniels (WAS)</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D89" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>6.04</t>
         </is>
       </c>
     </row>
@@ -8431,20 +8431,20 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Mike Evans (SF)</t>
-        </is>
-      </c>
-      <c r="C90" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Joe Burrow (CIN)</t>
+        </is>
+      </c>
+      <c r="C90" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D90" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -8454,20 +8454,20 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>Alec Pierce (IND)</t>
+          <t>George Kittle (SF)</t>
         </is>
       </c>
       <c r="C91" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson (NE)</t>
+          <t>Chuba Hubbard (CAR)</t>
         </is>
       </c>
       <c r="C92" s="16" t="inlineStr">
@@ -8486,11 +8486,11 @@
         </is>
       </c>
       <c r="D92" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>7.05</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson (NE)</t>
+          <t>J.K. Dobbins (DEN)</t>
         </is>
       </c>
       <c r="C93" s="16" t="inlineStr">
@@ -8509,11 +8509,11 @@
         </is>
       </c>
       <c r="D93" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>8.1</t>
         </is>
       </c>
     </row>
@@ -8523,12 +8523,12 @@
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>Michael Pittman Jr. (PIT)</t>
-        </is>
-      </c>
-      <c r="C94" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tony Pollard (TEN)</t>
+        </is>
+      </c>
+      <c r="C94" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D94" s="14" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>7.12</t>
         </is>
       </c>
     </row>
@@ -8546,20 +8546,20 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>George Kittle (SF)</t>
-        </is>
-      </c>
-      <c r="C95" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Josh Downs (IND)</t>
+        </is>
+      </c>
+      <c r="C95" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D95" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>10.01</t>
         </is>
       </c>
     </row>
@@ -8569,20 +8569,20 @@
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Kyle Pitts Sr. (ATL)</t>
-        </is>
-      </c>
-      <c r="C96" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jonathon Brooks (CAR)</t>
+        </is>
+      </c>
+      <c r="C96" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D96" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>9.1</t>
         </is>
       </c>
     </row>
@@ -8592,20 +8592,20 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>Tony Pollard (TEN)</t>
-        </is>
-      </c>
-      <c r="C97" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jakobi Meyers (JAX)</t>
+        </is>
+      </c>
+      <c r="C97" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>10.1</t>
         </is>
       </c>
     </row>
@@ -8615,12 +8615,12 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>Jadarian Price (SEA)</t>
-        </is>
-      </c>
-      <c r="C98" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Romeo Doubs (NE)</t>
+        </is>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D98" s="14" t="n">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -8638,20 +8638,20 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>Parker Washington (JAX)</t>
+          <t>Sam LaPorta (DET)</t>
         </is>
       </c>
       <c r="C99" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -8661,20 +8661,20 @@
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>Sam LaPorta (DET)</t>
-        </is>
-      </c>
-      <c r="C100" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Khalil Shakir (BUF)</t>
+        </is>
+      </c>
+      <c r="C100" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D100" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>12.11</t>
         </is>
       </c>
     </row>
@@ -8684,20 +8684,20 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>Travis Kelce (KC)</t>
-        </is>
-      </c>
-      <c r="C101" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kyle Monangai (CHI)</t>
+        </is>
+      </c>
+      <c r="C101" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -8707,20 +8707,20 @@
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C102" s="18" t="inlineStr">
+          <t>Makai Lemon (PHI)</t>
+        </is>
+      </c>
+      <c r="C102" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D102" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -8730,20 +8730,20 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>Rico Dowdle (PIT)</t>
-        </is>
-      </c>
-      <c r="C103" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Xavier Worthy (KC)</t>
+        </is>
+      </c>
+      <c r="C103" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -8753,20 +8753,20 @@
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>Dallas Goedert (PHI)</t>
-        </is>
-      </c>
-      <c r="C104" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Malik Washington (MIA)</t>
+        </is>
+      </c>
+      <c r="C104" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D104" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -8776,20 +8776,20 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson (TEN)</t>
-        </is>
-      </c>
-      <c r="C105" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jordan Mason (MIN)</t>
+        </is>
+      </c>
+      <c r="C105" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.07</t>
         </is>
       </c>
     </row>
@@ -8799,20 +8799,20 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>Jakobi Meyers (JAX)</t>
-        </is>
-      </c>
-      <c r="C106" s="18" t="inlineStr">
+          <t>Jalen Coker (CAR)</t>
+        </is>
+      </c>
+      <c r="C106" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D106" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>13.02</t>
         </is>
       </c>
     </row>
@@ -8822,20 +8822,20 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Carnell Tate (TEN)</t>
-        </is>
-      </c>
-      <c r="C107" s="18" t="inlineStr">
+          <t>Rashid Shaheed (SEA)</t>
+        </is>
+      </c>
+      <c r="C107" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>13.03</t>
         </is>
       </c>
     </row>
@@ -8845,20 +8845,20 @@
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>Michael Wilson (ARI)</t>
-        </is>
-      </c>
-      <c r="C108" s="18" t="inlineStr">
+          <t>KC Concepcion (CLE)</t>
+        </is>
+      </c>
+      <c r="C108" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D108" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>11.01</t>
         </is>
       </c>
     </row>
@@ -8868,20 +8868,20 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>Jayden Reed (GB)</t>
-        </is>
-      </c>
-      <c r="C109" s="18" t="inlineStr">
+          <t>Kayshon Boutte (HOU)</t>
+        </is>
+      </c>
+      <c r="C109" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>19.08</t>
         </is>
       </c>
     </row>
@@ -8891,20 +8891,20 @@
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>J.K. Dobbins (DEN)</t>
-        </is>
-      </c>
-      <c r="C110" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Drake Maye (NE)</t>
+        </is>
+      </c>
+      <c r="C110" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D110" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -8914,20 +8914,20 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr. (TB)</t>
-        </is>
-      </c>
-      <c r="C111" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rachaad White (WAS)</t>
+        </is>
+      </c>
+      <c r="C111" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -8937,20 +8937,20 @@
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Chuba Hubbard (CAR)</t>
-        </is>
-      </c>
-      <c r="C112" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Matthew Golden (GB)</t>
+        </is>
+      </c>
+      <c r="C112" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D112" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>11.07</t>
         </is>
       </c>
     </row>
@@ -8960,20 +8960,20 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>Tucker Kraft (GB)</t>
+          <t>Jaxson Dart (NYG)</t>
         </is>
       </c>
       <c r="C113" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -8983,20 +8983,20 @@
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Kenny Gainwell (TB)</t>
-        </is>
-      </c>
-      <c r="C114" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kyle Pitts Sr. (ATL)</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D114" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>6.1</t>
         </is>
       </c>
     </row>
@@ -9006,20 +9006,20 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>Quentin Johnston (LAC)</t>
-        </is>
-      </c>
-      <c r="C115" s="18" t="inlineStr">
+          <t>Keenan Allen (IND)</t>
+        </is>
+      </c>
+      <c r="C115" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>17.07</t>
         </is>
       </c>
     </row>
@@ -9029,20 +9029,20 @@
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>Jordan Addison (MIN)</t>
-        </is>
-      </c>
-      <c r="C116" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Caleb Williams (CHI)</t>
+        </is>
+      </c>
+      <c r="C116" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D116" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -9052,20 +9052,20 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>Jonathon Brooks (CAR)</t>
-        </is>
-      </c>
-      <c r="C117" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Trevor Lawrence (JAX)</t>
+        </is>
+      </c>
+      <c r="C117" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -9075,20 +9075,20 @@
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>Xavier Worthy (KC)</t>
-        </is>
-      </c>
-      <c r="C118" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Blake Corum (LAR)</t>
+        </is>
+      </c>
+      <c r="C118" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D118" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>9.08</t>
         </is>
       </c>
     </row>
@@ -9098,20 +9098,20 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>Jake Ferguson (DAL)</t>
-        </is>
-      </c>
-      <c r="C119" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>RJ Harvey (DEN)</t>
+        </is>
+      </c>
+      <c r="C119" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>7.08</t>
         </is>
       </c>
     </row>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Mark Andrews (BAL)</t>
-        </is>
-      </c>
-      <c r="C120" s="19" t="inlineStr">
+          <t>Juwan Johnson (NO)</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D120" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9144,20 +9144,20 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>Stefon Diggs (WAS)</t>
-        </is>
-      </c>
-      <c r="C121" s="18" t="inlineStr">
+          <t>Jordyn Tyson (NO)</t>
+        </is>
+      </c>
+      <c r="C121" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D121" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>8.07</t>
         </is>
       </c>
     </row>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling (SF)</t>
+          <t>Dalton Schultz (HOU)</t>
         </is>
       </c>
       <c r="C122" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>17.01</t>
         </is>
       </c>
     </row>
@@ -9190,20 +9190,20 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>Isaiah Likely (NYG)</t>
-        </is>
-      </c>
-      <c r="C123" s="19" t="inlineStr">
+          <t>Travis Kelce (KC)</t>
+        </is>
+      </c>
+      <c r="C123" s="18" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>8.08</t>
         </is>
       </c>
     </row>
@@ -9213,20 +9213,20 @@
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>Matthew Golden (GB)</t>
-        </is>
-      </c>
-      <c r="C124" s="18" t="inlineStr">
+          <t>Tre Tucker (LV)</t>
+        </is>
+      </c>
+      <c r="C124" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D124" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>17.1</t>
         </is>
       </c>
     </row>
@@ -9236,20 +9236,20 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>Khalil Shakir (BUF)</t>
-        </is>
-      </c>
-      <c r="C125" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Aaron Jones Sr. (MIN)</t>
+        </is>
+      </c>
+      <c r="C125" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -9259,20 +9259,20 @@
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>KC Concepcion (CLE)</t>
+          <t>Jake Ferguson (DAL)</t>
         </is>
       </c>
       <c r="C126" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>9.02</t>
         </is>
       </c>
     </row>
@@ -9282,20 +9282,20 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>Josh Downs (IND)</t>
-        </is>
-      </c>
-      <c r="C127" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dak Prescott (DAL)</t>
+        </is>
+      </c>
+      <c r="C127" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>7.07</t>
         </is>
       </c>
     </row>
@@ -9305,20 +9305,20 @@
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>Romeo Doubs (NE)</t>
+          <t>Dalton Kincaid (BUF)</t>
         </is>
       </c>
       <c r="C128" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D128" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -9328,12 +9328,12 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>Deebo Samuel Sr. (SF)</t>
+          <t>Isaiah Likely (NYG)</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D129" s="14" t="n">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>RJ Harvey (DEN)</t>
+          <t>Tyjae Spears (TEN)</t>
         </is>
       </c>
       <c r="C130" s="16" t="inlineStr">
@@ -9360,11 +9360,11 @@
         </is>
       </c>
       <c r="D130" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -9374,20 +9374,20 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr. (MIN)</t>
-        </is>
-      </c>
-      <c r="C131" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Justin Herbert (LAC)</t>
+        </is>
+      </c>
+      <c r="C131" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -9397,20 +9397,20 @@
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>Rachaad White (WAS)</t>
-        </is>
-      </c>
-      <c r="C132" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dallas Goedert (PHI)</t>
+        </is>
+      </c>
+      <c r="C132" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D132" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -9420,20 +9420,20 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>Dalton Kincaid (BUF)</t>
+          <t>Bo Nix (DEN)</t>
         </is>
       </c>
       <c r="C133" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D133" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>10.12</t>
         </is>
       </c>
     </row>
@@ -9443,20 +9443,20 @@
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Jalen Coker (CAR)</t>
-        </is>
-      </c>
-      <c r="C134" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brock Purdy (SF)</t>
+        </is>
+      </c>
+      <c r="C134" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D134" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>11.02</t>
         </is>
       </c>
     </row>
@@ -9466,20 +9466,20 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>Rashid Shaheed (SEA)</t>
-        </is>
-      </c>
-      <c r="C135" s="18" t="inlineStr">
+          <t>Omar Cooper Jr. (NYJ)</t>
+        </is>
+      </c>
+      <c r="C135" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>17.02</t>
         </is>
       </c>
     </row>
@@ -9489,20 +9489,20 @@
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>Kyle Monangai (CHI)</t>
-        </is>
-      </c>
-      <c r="C136" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jared Goff (DET)</t>
+        </is>
+      </c>
+      <c r="C136" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D136" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>12.03</t>
         </is>
       </c>
     </row>
@@ -9512,20 +9512,20 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>Jerry Jeudy (CLE)</t>
-        </is>
-      </c>
-      <c r="C137" s="18" t="inlineStr">
+          <t>Deebo Samuel Sr. (SF)</t>
+        </is>
+      </c>
+      <c r="C137" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>11.11</t>
         </is>
       </c>
     </row>
@@ -9535,12 +9535,12 @@
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>Juwan Johnson (NO)</t>
+          <t>Tyler Shough (NO)</t>
         </is>
       </c>
       <c r="C138" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>16.07</t>
         </is>
       </c>
     </row>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>Hunter Henry (NE)</t>
+          <t>Matthew Stafford (LAR)</t>
         </is>
       </c>
       <c r="C139" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>9.01</t>
         </is>
       </c>
     </row>
@@ -9581,20 +9581,20 @@
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd (GB)</t>
-        </is>
-      </c>
-      <c r="C140" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kyler Murray (MIN)</t>
+        </is>
+      </c>
+      <c r="C140" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D140" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>14.03</t>
         </is>
       </c>
     </row>
@@ -9604,20 +9604,20 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>Brenton Strange (JAX)</t>
+          <t>Jordan Love (GB)</t>
         </is>
       </c>
       <c r="C141" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>13.05</t>
         </is>
       </c>
     </row>
@@ -9627,20 +9627,20 @@
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>Denzel Boston (CLE)</t>
-        </is>
-      </c>
-      <c r="C142" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Baker Mayfield (TB)</t>
+        </is>
+      </c>
+      <c r="C142" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -9650,20 +9650,20 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>Makai Lemon (PHI)</t>
-        </is>
-      </c>
-      <c r="C143" s="18" t="inlineStr">
+          <t>Denzel Boston (CLE)</t>
+        </is>
+      </c>
+      <c r="C143" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9673,20 +9673,20 @@
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>Dalton Schultz (HOU)</t>
+          <t>Patrick Mahomes (KC)</t>
         </is>
       </c>
       <c r="C144" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -9696,20 +9696,20 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>Calvin Ridley (TEN)</t>
+          <t>Brenton Strange (JAX)</t>
         </is>
       </c>
       <c r="C145" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>13.08</t>
         </is>
       </c>
     </row>
@@ -9719,20 +9719,20 @@
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt (WAS)</t>
-        </is>
-      </c>
-      <c r="C146" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dontayvion Wicks (PHI)</t>
+        </is>
+      </c>
+      <c r="C146" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9742,20 +9742,20 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Jordan Mason (MIN)</t>
-        </is>
-      </c>
-      <c r="C147" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Mark Andrews (BAL)</t>
+        </is>
+      </c>
+      <c r="C147" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>11.09</t>
         </is>
       </c>
     </row>
@@ -9765,20 +9765,20 @@
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>Tre Tucker (LV)</t>
-        </is>
-      </c>
-      <c r="C148" s="18" t="inlineStr">
+          <t>Pat Bryant (DEN)</t>
+        </is>
+      </c>
+      <c r="C148" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>19.11</t>
         </is>
       </c>
     </row>
@@ -9788,20 +9788,20 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>Keenan Allen (IND)</t>
-        </is>
-      </c>
-      <c r="C149" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Malik Willis (MIA)</t>
+        </is>
+      </c>
+      <c r="C149" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -9811,20 +9811,20 @@
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>T.J. Hockenson (MIN)</t>
-        </is>
-      </c>
-      <c r="C150" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jalen Nailor (LV)</t>
+        </is>
+      </c>
+      <c r="C150" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Blake Corum (LAR)</t>
+          <t>Woody Marks (HOU)</t>
         </is>
       </c>
       <c r="C151" s="16" t="inlineStr">
@@ -9843,11 +9843,11 @@
         </is>
       </c>
       <c r="D151" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>14.04</t>
         </is>
       </c>
     </row>
@@ -9857,20 +9857,20 @@
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Tyjae Spears (TEN)</t>
-        </is>
-      </c>
-      <c r="C152" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Hunter Henry (NE)</t>
+        </is>
+      </c>
+      <c r="C152" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -9880,20 +9880,20 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>Kayshon Boutte (HOU)</t>
+          <t>Chig Okonkwo (WAS)</t>
         </is>
       </c>
       <c r="C153" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9903,20 +9903,20 @@
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>Rashod Bateman (BAL)</t>
-        </is>
-      </c>
-      <c r="C154" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chris Rodriguez Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C154" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>12.08</t>
         </is>
       </c>
     </row>
@@ -9926,20 +9926,20 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>Pat Freiermuth (PIT)</t>
-        </is>
-      </c>
-      <c r="C155" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Travis Hunter (JAX)</t>
+        </is>
+      </c>
+      <c r="C155" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9949,20 +9949,20 @@
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Greg Dulcich (MIA)</t>
-        </is>
-      </c>
-      <c r="C156" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Cooper Kupp (SEA)</t>
+        </is>
+      </c>
+      <c r="C156" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>19.05</t>
         </is>
       </c>
     </row>
@@ -9972,20 +9972,20 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane (BAL)</t>
-        </is>
-      </c>
-      <c r="C157" s="18" t="inlineStr">
+          <t>Jerry Jeudy (CLE)</t>
+        </is>
+      </c>
+      <c r="C157" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D157" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E157" s="14" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -9995,20 +9995,20 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Cade Otton (TB)</t>
+          <t>Cam Ward (TEN)</t>
         </is>
       </c>
       <c r="C158" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10018,16 +10018,16 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Jalen Nailor (LV)</t>
-        </is>
-      </c>
-      <c r="C159" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Isiah Pacheco (DET)</t>
+        </is>
+      </c>
+      <c r="C159" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E159" s="14" t="inlineStr">
         <is>
@@ -10041,20 +10041,20 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>Chig Okonkwo (WAS)</t>
+          <t>C.J. Stroud (HOU)</t>
         </is>
       </c>
       <c r="C160" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>18.01</t>
         </is>
       </c>
     </row>
@@ -10064,20 +10064,20 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>Woody Marks (HOU)</t>
-        </is>
-      </c>
-      <c r="C161" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DeMario Douglas (NE)</t>
+        </is>
+      </c>
+      <c r="C161" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E161" s="14" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10087,10 +10087,10 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Devaughn Vele (NO)</t>
-        </is>
-      </c>
-      <c r="C162" s="18" t="inlineStr">
+          <t>Malachi Fields (NYG)</t>
+        </is>
+      </c>
+      <c r="C162" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>19.04</t>
         </is>
       </c>
     </row>
@@ -10110,20 +10110,20 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq (NYJ)</t>
+          <t>Sam Darnold (SEA)</t>
         </is>
       </c>
       <c r="C163" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E163" s="14" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>14.05</t>
         </is>
       </c>
     </row>
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Cooper Kupp (SEA)</t>
-        </is>
-      </c>
-      <c r="C164" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Keaton Mitchell (LAC)</t>
+        </is>
+      </c>
+      <c r="C164" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10156,20 +10156,20 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>AJ Barner (SEA)</t>
-        </is>
-      </c>
-      <c r="C165" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Adonai Mitchell (NYJ)</t>
+        </is>
+      </c>
+      <c r="C165" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E165" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10179,20 +10179,20 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Jaylin Noel (HOU)</t>
-        </is>
-      </c>
-      <c r="C166" s="18" t="inlineStr">
+          <t>Ja'Kobi Lane (BAL)</t>
+        </is>
+      </c>
+      <c r="C166" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>14.02</t>
         </is>
       </c>
     </row>
@@ -10202,20 +10202,20 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>Zach Charbonnet (SEA)</t>
-        </is>
-      </c>
-      <c r="C167" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Daniel Jones (IND)</t>
+        </is>
+      </c>
+      <c r="C167" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E167" s="14" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>17.11</t>
         </is>
       </c>
     </row>
@@ -10225,12 +10225,12 @@
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>Alvin Kamara (NO)</t>
-        </is>
-      </c>
-      <c r="C168" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tank Dell (HOU)</t>
+        </is>
+      </c>
+      <c r="C168" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10248,20 +10248,20 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>Adonai Mitchell (NYJ)</t>
-        </is>
-      </c>
-      <c r="C169" s="18" t="inlineStr">
+          <t>Germie Bernard (PIT)</t>
+        </is>
+      </c>
+      <c r="C169" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E169" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Isiah Pacheco (DET)</t>
+          <t>Zach Charbonnet (SEA)</t>
         </is>
       </c>
       <c r="C170" s="16" t="inlineStr">
@@ -10280,11 +10280,11 @@
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>13.04</t>
         </is>
       </c>
     </row>
@@ -10294,16 +10294,16 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>Malik Washington (MIA)</t>
-        </is>
-      </c>
-      <c r="C171" s="18" t="inlineStr">
+          <t>Cyrus Allen (KC)</t>
+        </is>
+      </c>
+      <c r="C171" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Dylan Sampson (CLE)</t>
+          <t>Tyler Allgeier (ARI)</t>
         </is>
       </c>
       <c r="C172" s="16" t="inlineStr">
@@ -10326,11 +10326,11 @@
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -10340,20 +10340,20 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>Germie Bernard (PIT)</t>
-        </is>
-      </c>
-      <c r="C173" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dylan Sampson (CLE)</t>
+        </is>
+      </c>
+      <c r="C173" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -10363,20 +10363,20 @@
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Jordyn Tyson (NO)</t>
-        </is>
-      </c>
-      <c r="C174" s="18" t="inlineStr">
+          <t>Kyle Williams (NE)</t>
+        </is>
+      </c>
+      <c r="C174" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>19.06</t>
         </is>
       </c>
     </row>
@@ -10386,20 +10386,20 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>Caleb Douglas (MIA)</t>
-        </is>
-      </c>
-      <c r="C175" s="18" t="inlineStr">
+          <t>Calvin Ridley (TEN)</t>
+        </is>
+      </c>
+      <c r="C175" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E175" s="14" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>22.01</t>
         </is>
       </c>
     </row>
@@ -10409,20 +10409,20 @@
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>Omar Cooper Jr. (NYJ)</t>
+          <t>T.J. Hockenson (MIN)</t>
         </is>
       </c>
       <c r="C176" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D176" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -10432,20 +10432,20 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Travis Hunter (JAX)</t>
-        </is>
-      </c>
-      <c r="C177" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Mike Washington Jr. (LV)</t>
+        </is>
+      </c>
+      <c r="C177" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E177" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>15.05</t>
         </is>
       </c>
     </row>
@@ -10455,20 +10455,20 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks (PHI)</t>
+          <t>Greg Dulcich (MIA)</t>
         </is>
       </c>
       <c r="C178" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10478,12 +10478,12 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Mike Washington Jr. (LV)</t>
-        </is>
-      </c>
-      <c r="C179" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kenyon Sadiq (NYJ)</t>
+        </is>
+      </c>
+      <c r="C179" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="E179" s="14" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>13.1</t>
         </is>
       </c>
     </row>
@@ -10501,20 +10501,20 @@
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Darius Slayton (NYG)</t>
-        </is>
-      </c>
-      <c r="C180" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonah Coleman (DEN)</t>
+        </is>
+      </c>
+      <c r="C180" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.03</t>
         </is>
       </c>
     </row>
@@ -10524,12 +10524,12 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>Chris Rodriguez Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C181" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tre' Harris (LAC)</t>
+        </is>
+      </c>
+      <c r="C181" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10547,20 +10547,20 @@
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Tory Horton (SEA)</t>
-        </is>
-      </c>
-      <c r="C182" s="18" t="inlineStr">
+          <t>Keon Coleman (BUF)</t>
+        </is>
+      </c>
+      <c r="C182" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D182" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.07</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>Tyler Allgeier (ARI)</t>
+          <t>Tyrone Tracy Jr. (NYG)</t>
         </is>
       </c>
       <c r="C183" s="16" t="inlineStr">
@@ -10579,11 +10579,11 @@
         </is>
       </c>
       <c r="D183" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E183" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10593,20 +10593,20 @@
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>Tre' Harris (LAC)</t>
+          <t>Pat Freiermuth (PIT)</t>
         </is>
       </c>
       <c r="C184" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D184" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10616,20 +10616,20 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Jalen Tolbert (MIA)</t>
-        </is>
-      </c>
-      <c r="C185" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Aaron Rodgers (PIT)</t>
+        </is>
+      </c>
+      <c r="C185" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E185" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10639,20 +10639,20 @@
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Ryan Flournoy (DAL)</t>
-        </is>
-      </c>
-      <c r="C186" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Bryce Young (CAR)</t>
+        </is>
+      </c>
+      <c r="C186" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D186" s="14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>19.12</t>
         </is>
       </c>
     </row>
@@ -10662,20 +10662,20 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>Malachi Fields (NYG)</t>
-        </is>
-      </c>
-      <c r="C187" s="18" t="inlineStr">
+          <t>Zachariah Branch (ATL)</t>
+        </is>
+      </c>
+      <c r="C187" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D187" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E187" s="14" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -10685,20 +10685,20 @@
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Keaton Mitchell (LAC)</t>
-        </is>
-      </c>
-      <c r="C188" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ryan Flournoy (DAL)</t>
+        </is>
+      </c>
+      <c r="C188" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D188" s="14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10708,20 +10708,20 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr. (NYG)</t>
-        </is>
-      </c>
-      <c r="C189" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Cade Otton (TB)</t>
+        </is>
+      </c>
+      <c r="C189" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E189" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>20.06</t>
         </is>
       </c>
     </row>
@@ -10754,20 +10754,20 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>DeMario Douglas (NE)</t>
-        </is>
-      </c>
-      <c r="C191" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Alvin Kamara (NO)</t>
+        </is>
+      </c>
+      <c r="C191" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E191" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.07</t>
         </is>
       </c>
     </row>
@@ -10777,20 +10777,20 @@
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Zachariah Branch (ATL)</t>
-        </is>
-      </c>
-      <c r="C192" s="18" t="inlineStr">
+          <t>Caleb Douglas (MIA)</t>
+        </is>
+      </c>
+      <c r="C192" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D192" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>18.09</t>
         </is>
       </c>
     </row>
@@ -10800,20 +10800,20 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Keon Coleman (BUF)</t>
-        </is>
-      </c>
-      <c r="C193" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Geno Smith (NYJ)</t>
+        </is>
+      </c>
+      <c r="C193" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10846,20 +10846,20 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Pat Bryant (DEN)</t>
-        </is>
-      </c>
-      <c r="C195" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brian Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C195" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E195" s="14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>13.12</t>
         </is>
       </c>
     </row>
@@ -10869,10 +10869,10 @@
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>Tank Dell (HOU)</t>
-        </is>
-      </c>
-      <c r="C196" s="18" t="inlineStr">
+          <t>Devaughn Vele (NO)</t>
+        </is>
+      </c>
+      <c r="C196" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="E196" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10892,20 +10892,20 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>Cyrus Allen (KC)</t>
+          <t>AJ Barner (SEA)</t>
         </is>
       </c>
       <c r="C197" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D197" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E197" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10915,20 +10915,20 @@
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Kyle Williams (NE)</t>
-        </is>
-      </c>
-      <c r="C198" s="18" t="inlineStr">
+          <t>Jaylin Noel (HOU)</t>
+        </is>
+      </c>
+      <c r="C198" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D198" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>18.1</t>
         </is>
       </c>
     </row>
@@ -10938,20 +10938,20 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>Jonah Coleman (DEN)</t>
-        </is>
-      </c>
-      <c r="C199" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Darius Slayton (NYG)</t>
+        </is>
+      </c>
+      <c r="C199" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E199" s="14" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10961,20 +10961,20 @@
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Kenneth Walker (KC)</t>
-        </is>
-      </c>
-      <c r="C200" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Oronde Gadsden (LAC)</t>
+        </is>
+      </c>
+      <c r="C200" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D200" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
@@ -10984,20 +10984,20 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>Patrick Mahomes (KC)</t>
+          <t>Rashod Bateman (BAL)</t>
         </is>
       </c>
       <c r="C201" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D201" s="14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>20.05</t>
         </is>
       </c>
     </row>
@@ -11007,20 +11007,20 @@
       </c>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>Brian Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C202" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jalen Tolbert (MIA)</t>
+        </is>
+      </c>
+      <c r="C202" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D202" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E202" s="14" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11030,20 +11030,20 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>Oronde Gadsden (LAC)</t>
-        </is>
-      </c>
-      <c r="C203" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tory Horton (SEA)</t>
+        </is>
+      </c>
+      <c r="C203" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D203" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>

--- a/assets/data/12guys1cup-cheat-sheet.xlsx
+++ b/assets/data/12guys1cup-cheat-sheet.xlsx
@@ -62,6 +62,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00B8386B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001565C0"/>
       <sz val="10"/>
     </font>
@@ -69,12 +75,6 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00E65100"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00B8386B"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -125,17 +125,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F8D7E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D4E4F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -6476,20 +6476,20 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Bijan Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Josh Allen (BUF)</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>2.09</t>
         </is>
       </c>
     </row>
@@ -6499,20 +6499,20 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase (CIN)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Bijan Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
     </row>
@@ -6525,7 +6525,7 @@
           <t>Puka Nacua (LAR)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6545,20 +6545,20 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Christian McCaffrey (SF)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ja'Marr Chase (CIN)</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>
@@ -6568,20 +6568,20 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba (SEA)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Christian McCaffrey (SF)</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
     </row>
@@ -6591,20 +6591,20 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown (DET)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
+          <t>Jaxon Smith-Njigba (SEA)</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6614,20 +6614,20 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>CeeDee Lamb (DAL)</t>
+          <t>Lamar Jackson (BAL)</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>3.09</t>
         </is>
       </c>
     </row>
@@ -6637,20 +6637,20 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Jonathan Taylor (IND)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jayden Daniels (WAS)</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>6.04</t>
         </is>
       </c>
     </row>
@@ -6660,20 +6660,20 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>James Cook III (BUF)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Drake Maye (NE)</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -6683,20 +6683,20 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>De'Von Achane (MIA)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jalen Hurts (PHI)</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>5.12</t>
         </is>
       </c>
     </row>
@@ -6706,20 +6706,20 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Kenneth Walker (KC)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Amon-Ra St. Brown (DET)</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6729,12 +6729,12 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Chase Brown (CIN)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Joe Burrow (CIN)</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -6752,20 +6752,20 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Justin Jefferson (MIN)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonathan Taylor (IND)</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6775,20 +6775,20 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>A.J. Brown (NE)</t>
+          <t>Jaxson Dart (NYG)</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -6798,20 +6798,20 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Chris Olave (NO)</t>
+          <t>Trevor Lawrence (JAX)</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -6821,20 +6821,20 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Brock Bowers (LV)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Brock Purdy (SF)</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>11.02</t>
         </is>
       </c>
     </row>
@@ -6844,20 +6844,20 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Nico Collins (HOU)</t>
+          <t>Dak Prescott (DAL)</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.07</t>
         </is>
       </c>
     </row>
@@ -6867,20 +6867,20 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Trey McBride (ARI)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Caleb Williams (CHI)</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -6890,20 +6890,20 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Garrett Wilson (NYJ)</t>
+          <t>Justin Herbert (LAC)</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -6913,20 +6913,20 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Drake London (ATL)</t>
+          <t>Bo Nix (DEN)</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>10.12</t>
         </is>
       </c>
     </row>
@@ -6936,20 +6936,20 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>George Pickens (DAL)</t>
+          <t>Matthew Stafford (LAR)</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>9.01</t>
         </is>
       </c>
     </row>
@@ -6959,20 +6959,20 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Rashee Rice (KC)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>De'Von Achane (MIA)</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6982,20 +6982,20 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Omarion Hampton (LAC)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kyler Murray (MIN)</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>14.03</t>
         </is>
       </c>
     </row>
@@ -7005,20 +7005,20 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Ashton Jeanty (LV)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jared Goff (DET)</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>12.03</t>
         </is>
       </c>
     </row>
@@ -7028,12 +7028,12 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Malik Nabers (NYG)</t>
+          <t>Tyler Shough (NO)</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>16.07</t>
         </is>
       </c>
     </row>
@@ -7051,12 +7051,12 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Saquon Barkley (PHI)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Baker Mayfield (TB)</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -7074,20 +7074,20 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Zay Flowers (BAL)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chase Brown (CIN)</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Derrick Henry (BAL)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Drake London (ATL)</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -7120,20 +7120,20 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>DeVonta Smith (PHI)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Derrick Henry (BAL)</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.08</t>
         </is>
       </c>
     </row>
@@ -7143,20 +7143,20 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Waddle (DEN)</t>
+          <t>Daniel Jones (IND)</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>17.11</t>
         </is>
       </c>
     </row>
@@ -7166,12 +7166,12 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>Jeremiyah Love (ARI)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>CeeDee Lamb (DAL)</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -7189,12 +7189,12 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Kyren Williams (LAR)</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jordan Love (GB)</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D36" s="14" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>13.05</t>
         </is>
       </c>
     </row>
@@ -7212,20 +7212,20 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Ladd McConkey (LAC)</t>
+          <t>Malik Willis (MIA)</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -7235,20 +7235,20 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Breece Hall (NYJ)</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Justin Jefferson (MIN)</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -7258,20 +7258,20 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Emeka Egbuka (TB)</t>
-        </is>
-      </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>James Cook III (BUF)</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>1.11</t>
         </is>
       </c>
     </row>
@@ -7281,20 +7281,20 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>D'Andre Swift (CHI)</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rashee Rice (KC)</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D40" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -7304,20 +7304,20 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan (CAR)</t>
+          <t>Sam Darnold (SEA)</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>14.05</t>
         </is>
       </c>
     </row>
@@ -7327,20 +7327,20 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Tee Higgins (CIN)</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Saquon Barkley (PHI)</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D42" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -7350,20 +7350,20 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Carnell Tate (TEN)</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
+          <t>Chris Olave (NO)</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>3.07</t>
         </is>
       </c>
     </row>
@@ -7373,20 +7373,20 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Javonte Williams (DAL)</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>C.J. Stroud (HOU)</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>18.01</t>
         </is>
       </c>
     </row>
@@ -7396,20 +7396,20 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Josh Allen (BUF)</t>
-        </is>
-      </c>
-      <c r="C45" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Ashton Jeanty (LV)</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -7419,20 +7419,20 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>Luther Burden III (CHI)</t>
-        </is>
-      </c>
-      <c r="C46" s="17" t="inlineStr">
+          <t>A.J. Brown (NE)</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D46" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -7442,20 +7442,20 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Christian Watson (GB)</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Trey McBride (ARI)</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -7465,20 +7465,20 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Bucky Irving (TB)</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Bryce Young (CAR)</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D48" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>19.12</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>Parker Washington (JAX)</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Omarion Hampton (LAC)</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D49" s="14" t="n">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7511,20 +7511,20 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr. (NO)</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>George Pickens (DAL)</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Cam Skattebo (NYG)</t>
+          <t>Jeremiyah Love (ARI)</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr">
@@ -7543,11 +7543,11 @@
         </is>
       </c>
       <c r="D51" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7557,20 +7557,20 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Terry McLaurin (WAS)</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="inlineStr">
+          <t>Nico Collins (HOU)</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D52" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7580,20 +7580,20 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Jameson Williams (DET)</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Breece Hall (NYJ)</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7603,20 +7603,20 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>DJ Moore (BUF)</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brock Bowers (LV)</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -7626,20 +7626,20 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten (JAX)</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Garrett Wilson (NYJ)</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -7649,20 +7649,20 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Davante Adams (LAR)</t>
-        </is>
-      </c>
-      <c r="C56" s="17" t="inlineStr">
+          <t>Zay Flowers (BAL)</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.05</t>
         </is>
       </c>
     </row>
@@ -7672,10 +7672,10 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Mike Evans (SF)</t>
-        </is>
-      </c>
-      <c r="C57" s="17" t="inlineStr">
+          <t>Malik Nabers (NYG)</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -7695,20 +7695,20 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Rome Odunze (CHI)</t>
-        </is>
-      </c>
-      <c r="C58" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Javonte Williams (DAL)</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D58" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7718,20 +7718,20 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr. (ARI)</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
+          <t>DeVonta Smith (PHI)</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D59" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>3.12</t>
         </is>
       </c>
     </row>
@@ -7741,20 +7741,20 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>DK Metcalf (PIT)</t>
-        </is>
-      </c>
-      <c r="C60" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Travis Etienne Jr. (NO)</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D60" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>4.09</t>
         </is>
       </c>
     </row>
@@ -7764,20 +7764,20 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Tyler Warren (IND)</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kyren Williams (LAR)</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
@@ -7787,20 +7787,20 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Colston Loveland (CHI)</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Cam Skattebo (NYG)</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D62" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.08</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Alec Pierce (IND)</t>
+          <t>Geno Smith (NYJ)</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D63" s="14" t="n">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7833,20 +7833,20 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
+          <t>Tetairoa McMillan (CAR)</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D64" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>4.01</t>
         </is>
       </c>
     </row>
@@ -7856,20 +7856,20 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Quinshon Judkins (CLE)</t>
-        </is>
-      </c>
-      <c r="C65" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Cam Ward (TEN)</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D65" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -7879,20 +7879,20 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson (NE)</t>
-        </is>
-      </c>
-      <c r="C66" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Emeka Egbuka (TB)</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D66" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>4.03</t>
         </is>
       </c>
     </row>
@@ -7902,20 +7902,20 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>David Montgomery (HOU)</t>
-        </is>
-      </c>
-      <c r="C67" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Aaron Rodgers (PIT)</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D67" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -7925,20 +7925,20 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Lamar Jackson (BAL)</t>
-        </is>
-      </c>
-      <c r="C68" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>D'Andre Swift (CHI)</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D68" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -7948,20 +7948,20 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr. (TB)</t>
-        </is>
-      </c>
-      <c r="C69" s="17" t="inlineStr">
+          <t>Davante Adams (LAR)</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D69" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>5.02</t>
         </is>
       </c>
     </row>
@@ -7971,20 +7971,20 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Jadarian Price (SEA)</t>
-        </is>
-      </c>
-      <c r="C70" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tee Higgins (CIN)</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D70" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>3.11</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd (GB)</t>
+          <t>Bucky Irving (TB)</t>
         </is>
       </c>
       <c r="C71" s="16" t="inlineStr">
@@ -8003,11 +8003,11 @@
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>4.06</t>
         </is>
       </c>
     </row>
@@ -8017,20 +8017,20 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson (NE)</t>
-        </is>
-      </c>
-      <c r="C72" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ladd McConkey (LAC)</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.02</t>
         </is>
       </c>
     </row>
@@ -8040,20 +8040,20 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Quentin Johnston (LAC)</t>
-        </is>
-      </c>
-      <c r="C73" s="17" t="inlineStr">
+          <t>Jameson Williams (DET)</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -8063,20 +8063,20 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Michael Pittman Jr. (PIT)</t>
-        </is>
-      </c>
-      <c r="C74" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Quinshon Judkins (CLE)</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D74" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -8086,20 +8086,20 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>Rico Dowdle (PIT)</t>
-        </is>
-      </c>
-      <c r="C75" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Colston Loveland (CHI)</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>4.04</t>
         </is>
       </c>
     </row>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson (TEN)</t>
-        </is>
-      </c>
-      <c r="C76" s="17" t="inlineStr">
+          <t>Jaylen Waddle (DEN)</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D76" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -8132,20 +8132,20 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>Harold Fannin Jr. (CLE)</t>
-        </is>
-      </c>
-      <c r="C77" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Bhayshul Tuten (JAX)</t>
+        </is>
+      </c>
+      <c r="C77" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D77" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8155,20 +8155,20 @@
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Michael Wilson (ARI)</t>
-        </is>
-      </c>
-      <c r="C78" s="17" t="inlineStr">
+          <t>Terry McLaurin (WAS)</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D78" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -8178,10 +8178,10 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>Stefon Diggs (WAS)</t>
-        </is>
-      </c>
-      <c r="C79" s="17" t="inlineStr">
+          <t>DJ Moore (BUF)</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>5.09</t>
         </is>
       </c>
     </row>
@@ -8201,10 +8201,10 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Courtland Sutton (DEN)</t>
-        </is>
-      </c>
-      <c r="C80" s="17" t="inlineStr">
+          <t>Luther Burden III (CHI)</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8214,7 +8214,7 @@
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -8224,20 +8224,20 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt (WAS)</t>
-        </is>
-      </c>
-      <c r="C81" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rome Odunze (CHI)</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D81" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>6.05</t>
         </is>
       </c>
     </row>
@@ -8247,20 +8247,20 @@
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Kenny Gainwell (TB)</t>
-        </is>
-      </c>
-      <c r="C82" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tyler Warren (IND)</t>
+        </is>
+      </c>
+      <c r="C82" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D82" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>4.11</t>
         </is>
       </c>
     </row>
@@ -8270,20 +8270,20 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Warren (PIT)</t>
-        </is>
-      </c>
-      <c r="C83" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Harold Fannin Jr. (CLE)</t>
+        </is>
+      </c>
+      <c r="C83" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D83" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -8293,20 +8293,20 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Jordan Addison (MIN)</t>
-        </is>
-      </c>
-      <c r="C84" s="17" t="inlineStr">
+          <t>Courtland Sutton (DEN)</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D84" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>7.09</t>
         </is>
       </c>
     </row>
@@ -8316,12 +8316,12 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling (SF)</t>
-        </is>
-      </c>
-      <c r="C85" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>David Montgomery (HOU)</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D85" s="14" t="n">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Tucker Kraft (GB)</t>
+          <t>Christian Watson (GB)</t>
         </is>
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D86" s="14" t="n">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -8362,20 +8362,20 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>Jalen Hurts (PHI)</t>
-        </is>
-      </c>
-      <c r="C87" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Marvin Harrison Jr. (ARI)</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D87" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -8385,20 +8385,20 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Jayden Reed (GB)</t>
-        </is>
-      </c>
-      <c r="C88" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jaylen Warren (PIT)</t>
+        </is>
+      </c>
+      <c r="C88" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D88" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -8408,20 +8408,20 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>Jayden Daniels (WAS)</t>
-        </is>
-      </c>
-      <c r="C89" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Mike Evans (SF)</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D89" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8431,20 +8431,20 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Joe Burrow (CIN)</t>
-        </is>
-      </c>
-      <c r="C90" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>DK Metcalf (PIT)</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D90" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -8454,20 +8454,20 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>George Kittle (SF)</t>
+          <t>Alec Pierce (IND)</t>
         </is>
       </c>
       <c r="C91" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>9.05</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>Chuba Hubbard (CAR)</t>
+          <t>TreVeyon Henderson (NE)</t>
         </is>
       </c>
       <c r="C92" s="16" t="inlineStr">
@@ -8486,11 +8486,11 @@
         </is>
       </c>
       <c r="D92" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>J.K. Dobbins (DEN)</t>
+          <t>Rhamondre Stevenson (NE)</t>
         </is>
       </c>
       <c r="C93" s="16" t="inlineStr">
@@ -8509,11 +8509,11 @@
         </is>
       </c>
       <c r="D93" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -8523,12 +8523,12 @@
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>Tony Pollard (TEN)</t>
-        </is>
-      </c>
-      <c r="C94" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Michael Pittman Jr. (PIT)</t>
+        </is>
+      </c>
+      <c r="C94" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D94" s="14" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>9.07</t>
         </is>
       </c>
     </row>
@@ -8546,20 +8546,20 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>Josh Downs (IND)</t>
-        </is>
-      </c>
-      <c r="C95" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kyle Pitts Sr. (ATL)</t>
+        </is>
+      </c>
+      <c r="C95" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D95" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>6.1</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Jonathon Brooks (CAR)</t>
+          <t>Tony Pollard (TEN)</t>
         </is>
       </c>
       <c r="C96" s="16" t="inlineStr">
@@ -8578,11 +8578,11 @@
         </is>
       </c>
       <c r="D96" s="14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.12</t>
         </is>
       </c>
     </row>
@@ -8592,20 +8592,20 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>Jakobi Meyers (JAX)</t>
-        </is>
-      </c>
-      <c r="C97" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jadarian Price (SEA)</t>
+        </is>
+      </c>
+      <c r="C97" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -8615,20 +8615,20 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>Romeo Doubs (NE)</t>
-        </is>
-      </c>
-      <c r="C98" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>George Kittle (SF)</t>
+        </is>
+      </c>
+      <c r="C98" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D98" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -8638,20 +8638,20 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>Sam LaPorta (DET)</t>
+          <t>Parker Washington (JAX)</t>
         </is>
       </c>
       <c r="C99" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>7.04</t>
         </is>
       </c>
     </row>
@@ -8661,20 +8661,20 @@
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>Khalil Shakir (BUF)</t>
-        </is>
-      </c>
-      <c r="C100" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Sam LaPorta (DET)</t>
+        </is>
+      </c>
+      <c r="C100" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D100" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -8684,20 +8684,20 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>Kyle Monangai (CHI)</t>
-        </is>
-      </c>
-      <c r="C101" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Travis Kelce (KC)</t>
+        </is>
+      </c>
+      <c r="C101" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.08</t>
         </is>
       </c>
     </row>
@@ -8707,20 +8707,20 @@
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Makai Lemon (PHI)</t>
-        </is>
-      </c>
-      <c r="C102" s="17" t="inlineStr">
+          <t>Brian Thomas Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D102" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>7.02</t>
         </is>
       </c>
     </row>
@@ -8730,20 +8730,20 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>Xavier Worthy (KC)</t>
-        </is>
-      </c>
-      <c r="C103" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rico Dowdle (PIT)</t>
+        </is>
+      </c>
+      <c r="C103" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>8.01</t>
         </is>
       </c>
     </row>
@@ -8753,20 +8753,20 @@
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>Malik Washington (MIA)</t>
-        </is>
-      </c>
-      <c r="C104" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dallas Goedert (PHI)</t>
+        </is>
+      </c>
+      <c r="C104" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D104" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -8776,20 +8776,20 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>Jordan Mason (MIN)</t>
-        </is>
-      </c>
-      <c r="C105" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Wan'Dale Robinson (TEN)</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>10.09</t>
         </is>
       </c>
     </row>
@@ -8799,20 +8799,20 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>Jalen Coker (CAR)</t>
-        </is>
-      </c>
-      <c r="C106" s="17" t="inlineStr">
+          <t>Jakobi Meyers (JAX)</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D106" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>10.1</t>
         </is>
       </c>
     </row>
@@ -8822,20 +8822,20 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Rashid Shaheed (SEA)</t>
-        </is>
-      </c>
-      <c r="C107" s="17" t="inlineStr">
+          <t>Carnell Tate (TEN)</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -8845,20 +8845,20 @@
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>KC Concepcion (CLE)</t>
-        </is>
-      </c>
-      <c r="C108" s="17" t="inlineStr">
+          <t>Michael Wilson (ARI)</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D108" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>7.11</t>
         </is>
       </c>
     </row>
@@ -8868,20 +8868,20 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>Kayshon Boutte (HOU)</t>
-        </is>
-      </c>
-      <c r="C109" s="17" t="inlineStr">
+          <t>Jayden Reed (GB)</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8891,20 +8891,20 @@
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>Drake Maye (NE)</t>
-        </is>
-      </c>
-      <c r="C110" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>J.K. Dobbins (DEN)</t>
+        </is>
+      </c>
+      <c r="C110" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D110" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>8.1</t>
         </is>
       </c>
     </row>
@@ -8914,20 +8914,20 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>Rachaad White (WAS)</t>
-        </is>
-      </c>
-      <c r="C111" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Chris Godwin Jr. (TB)</t>
+        </is>
+      </c>
+      <c r="C111" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>8.12</t>
         </is>
       </c>
     </row>
@@ -8937,20 +8937,20 @@
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Matthew Golden (GB)</t>
-        </is>
-      </c>
-      <c r="C112" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chuba Hubbard (CAR)</t>
+        </is>
+      </c>
+      <c r="C112" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D112" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>7.05</t>
         </is>
       </c>
     </row>
@@ -8960,20 +8960,20 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>Jaxson Dart (NYG)</t>
+          <t>Tucker Kraft (GB)</t>
         </is>
       </c>
       <c r="C113" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8983,20 +8983,20 @@
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Kyle Pitts Sr. (ATL)</t>
-        </is>
-      </c>
-      <c r="C114" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kenny Gainwell (TB)</t>
+        </is>
+      </c>
+      <c r="C114" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D114" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -9006,20 +9006,20 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>Keenan Allen (IND)</t>
-        </is>
-      </c>
-      <c r="C115" s="17" t="inlineStr">
+          <t>Quentin Johnston (LAC)</t>
+        </is>
+      </c>
+      <c r="C115" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>10.05</t>
         </is>
       </c>
     </row>
@@ -9029,20 +9029,20 @@
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>Caleb Williams (CHI)</t>
-        </is>
-      </c>
-      <c r="C116" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Stefon Diggs (WAS)</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D116" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>10.02</t>
         </is>
       </c>
     </row>
@@ -9052,20 +9052,20 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>Trevor Lawrence (JAX)</t>
-        </is>
-      </c>
-      <c r="C117" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jordan Addison (MIN)</t>
+        </is>
+      </c>
+      <c r="C117" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9.09</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>Blake Corum (LAR)</t>
+          <t>Jonathon Brooks (CAR)</t>
         </is>
       </c>
       <c r="C118" s="16" t="inlineStr">
@@ -9084,11 +9084,11 @@
         </is>
       </c>
       <c r="D118" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>9.1</t>
         </is>
       </c>
     </row>
@@ -9098,20 +9098,20 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>RJ Harvey (DEN)</t>
-        </is>
-      </c>
-      <c r="C119" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Xavier Worthy (KC)</t>
+        </is>
+      </c>
+      <c r="C119" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Juwan Johnson (NO)</t>
-        </is>
-      </c>
-      <c r="C120" s="18" t="inlineStr">
+          <t>Jake Ferguson (DAL)</t>
+        </is>
+      </c>
+      <c r="C120" s="19" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D120" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>9.02</t>
         </is>
       </c>
     </row>
@@ -9144,20 +9144,20 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>Jordyn Tyson (NO)</t>
-        </is>
-      </c>
-      <c r="C121" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Mark Andrews (BAL)</t>
+        </is>
+      </c>
+      <c r="C121" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D121" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>11.09</t>
         </is>
       </c>
     </row>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>Dalton Schultz (HOU)</t>
+          <t>De'Zhaun Stribling (SF)</t>
         </is>
       </c>
       <c r="C122" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>12.07</t>
         </is>
       </c>
     </row>
@@ -9190,20 +9190,20 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>Travis Kelce (KC)</t>
+          <t>Matthew Golden (GB)</t>
         </is>
       </c>
       <c r="C123" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>11.07</t>
         </is>
       </c>
     </row>
@@ -9213,20 +9213,20 @@
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>Tre Tucker (LV)</t>
-        </is>
-      </c>
-      <c r="C124" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Isaiah Likely (NYG)</t>
+        </is>
+      </c>
+      <c r="C124" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D124" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -9236,20 +9236,20 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr. (MIN)</t>
-        </is>
-      </c>
-      <c r="C125" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Khalil Shakir (BUF)</t>
+        </is>
+      </c>
+      <c r="C125" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>12.11</t>
         </is>
       </c>
     </row>
@@ -9259,20 +9259,20 @@
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>Jake Ferguson (DAL)</t>
+          <t>KC Concepcion (CLE)</t>
         </is>
       </c>
       <c r="C126" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>11.01</t>
         </is>
       </c>
     </row>
@@ -9282,20 +9282,20 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>Dak Prescott (DAL)</t>
-        </is>
-      </c>
-      <c r="C127" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Josh Downs (IND)</t>
+        </is>
+      </c>
+      <c r="C127" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>10.01</t>
         </is>
       </c>
     </row>
@@ -9305,20 +9305,20 @@
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>Dalton Kincaid (BUF)</t>
+          <t>Romeo Doubs (NE)</t>
         </is>
       </c>
       <c r="C128" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D128" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -9328,12 +9328,12 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>Isaiah Likely (NYG)</t>
+          <t>Deebo Samuel Sr. (SF)</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D129" s="14" t="n">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>11.11</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>Tyjae Spears (TEN)</t>
+          <t>RJ Harvey (DEN)</t>
         </is>
       </c>
       <c r="C130" s="16" t="inlineStr">
@@ -9360,11 +9360,11 @@
         </is>
       </c>
       <c r="D130" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>7.08</t>
         </is>
       </c>
     </row>
@@ -9374,20 +9374,20 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>Justin Herbert (LAC)</t>
-        </is>
-      </c>
-      <c r="C131" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Aaron Jones Sr. (MIN)</t>
+        </is>
+      </c>
+      <c r="C131" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -9397,20 +9397,20 @@
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>Dallas Goedert (PHI)</t>
-        </is>
-      </c>
-      <c r="C132" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Rachaad White (WAS)</t>
+        </is>
+      </c>
+      <c r="C132" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D132" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -9420,20 +9420,20 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>Bo Nix (DEN)</t>
+          <t>Dalton Kincaid (BUF)</t>
         </is>
       </c>
       <c r="C133" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D133" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -9443,20 +9443,20 @@
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Brock Purdy (SF)</t>
-        </is>
-      </c>
-      <c r="C134" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jalen Coker (CAR)</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D134" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>13.02</t>
         </is>
       </c>
     </row>
@@ -9466,20 +9466,20 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>Omar Cooper Jr. (NYJ)</t>
-        </is>
-      </c>
-      <c r="C135" s="17" t="inlineStr">
+          <t>Rashid Shaheed (SEA)</t>
+        </is>
+      </c>
+      <c r="C135" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>13.03</t>
         </is>
       </c>
     </row>
@@ -9489,20 +9489,20 @@
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>Jared Goff (DET)</t>
-        </is>
-      </c>
-      <c r="C136" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>MarShawn Lloyd (GB)</t>
+        </is>
+      </c>
+      <c r="C136" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D136" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>15.06</t>
         </is>
       </c>
     </row>
@@ -9512,20 +9512,20 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>Deebo Samuel Sr. (SF)</t>
-        </is>
-      </c>
-      <c r="C137" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kyle Monangai (CHI)</t>
+        </is>
+      </c>
+      <c r="C137" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -9535,12 +9535,12 @@
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>Tyler Shough (NO)</t>
+          <t>Juwan Johnson (NO)</t>
         </is>
       </c>
       <c r="C138" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>Matthew Stafford (LAR)</t>
-        </is>
-      </c>
-      <c r="C139" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jerry Jeudy (CLE)</t>
+        </is>
+      </c>
+      <c r="C139" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -9581,20 +9581,20 @@
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>Kyler Murray (MIN)</t>
+          <t>Hunter Henry (NE)</t>
         </is>
       </c>
       <c r="C140" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D140" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -9604,20 +9604,20 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>Jordan Love (GB)</t>
+          <t>Brenton Strange (JAX)</t>
         </is>
       </c>
       <c r="C141" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>13.08</t>
         </is>
       </c>
     </row>
@@ -9627,20 +9627,20 @@
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>Baker Mayfield (TB)</t>
-        </is>
-      </c>
-      <c r="C142" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Denzel Boston (CLE)</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9650,20 +9650,20 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>Denzel Boston (CLE)</t>
-        </is>
-      </c>
-      <c r="C143" s="17" t="inlineStr">
+          <t>Makai Lemon (PHI)</t>
+        </is>
+      </c>
+      <c r="C143" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -9673,20 +9673,20 @@
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>Patrick Mahomes (KC)</t>
+          <t>Dalton Schultz (HOU)</t>
         </is>
       </c>
       <c r="C144" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>17.01</t>
         </is>
       </c>
     </row>
@@ -9696,20 +9696,20 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>Brenton Strange (JAX)</t>
+          <t>Calvin Ridley (TEN)</t>
         </is>
       </c>
       <c r="C145" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>22.01</t>
         </is>
       </c>
     </row>
@@ -9719,20 +9719,20 @@
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks (PHI)</t>
-        </is>
-      </c>
-      <c r="C146" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jacory Croskey-Merritt (WAS)</t>
+        </is>
+      </c>
+      <c r="C146" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10.06</t>
         </is>
       </c>
     </row>
@@ -9742,20 +9742,20 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Mark Andrews (BAL)</t>
-        </is>
-      </c>
-      <c r="C147" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jordan Mason (MIN)</t>
+        </is>
+      </c>
+      <c r="C147" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>10.07</t>
         </is>
       </c>
     </row>
@@ -9765,20 +9765,20 @@
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>Pat Bryant (DEN)</t>
-        </is>
-      </c>
-      <c r="C148" s="17" t="inlineStr">
+          <t>Tre Tucker (LV)</t>
+        </is>
+      </c>
+      <c r="C148" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>17.1</t>
         </is>
       </c>
     </row>
@@ -9788,20 +9788,20 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>Malik Willis (MIA)</t>
-        </is>
-      </c>
-      <c r="C149" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Keenan Allen (IND)</t>
+        </is>
+      </c>
+      <c r="C149" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>17.07</t>
         </is>
       </c>
     </row>
@@ -9811,20 +9811,20 @@
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>Jalen Nailor (LV)</t>
-        </is>
-      </c>
-      <c r="C150" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>T.J. Hockenson (MIN)</t>
+        </is>
+      </c>
+      <c r="C150" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Woody Marks (HOU)</t>
+          <t>Blake Corum (LAR)</t>
         </is>
       </c>
       <c r="C151" s="16" t="inlineStr">
@@ -9843,11 +9843,11 @@
         </is>
       </c>
       <c r="D151" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>9.08</t>
         </is>
       </c>
     </row>
@@ -9857,20 +9857,20 @@
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Hunter Henry (NE)</t>
-        </is>
-      </c>
-      <c r="C152" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tyjae Spears (TEN)</t>
+        </is>
+      </c>
+      <c r="C152" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -9880,20 +9880,20 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>Chig Okonkwo (WAS)</t>
+          <t>Kayshon Boutte (HOU)</t>
         </is>
       </c>
       <c r="C153" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>19.08</t>
         </is>
       </c>
     </row>
@@ -9903,20 +9903,20 @@
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>Chris Rodriguez Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C154" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rashod Bateman (BAL)</t>
+        </is>
+      </c>
+      <c r="C154" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>20.05</t>
         </is>
       </c>
     </row>
@@ -9926,20 +9926,20 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>Travis Hunter (JAX)</t>
-        </is>
-      </c>
-      <c r="C155" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Pat Freiermuth (PIT)</t>
+        </is>
+      </c>
+      <c r="C155" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -9949,20 +9949,20 @@
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Cooper Kupp (SEA)</t>
-        </is>
-      </c>
-      <c r="C156" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Greg Dulcich (MIA)</t>
+        </is>
+      </c>
+      <c r="C156" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -9972,20 +9972,20 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Jerry Jeudy (CLE)</t>
-        </is>
-      </c>
-      <c r="C157" s="17" t="inlineStr">
+          <t>Ja'Kobi Lane (BAL)</t>
+        </is>
+      </c>
+      <c r="C157" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D157" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E157" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>14.02</t>
         </is>
       </c>
     </row>
@@ -9995,20 +9995,20 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Cam Ward (TEN)</t>
+          <t>Cade Otton (TB)</t>
         </is>
       </c>
       <c r="C158" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.06</t>
         </is>
       </c>
     </row>
@@ -10018,16 +10018,16 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Isiah Pacheco (DET)</t>
-        </is>
-      </c>
-      <c r="C159" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jalen Nailor (LV)</t>
+        </is>
+      </c>
+      <c r="C159" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E159" s="14" t="inlineStr">
         <is>
@@ -10041,20 +10041,20 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>C.J. Stroud (HOU)</t>
+          <t>Chig Okonkwo (WAS)</t>
         </is>
       </c>
       <c r="C160" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -10064,20 +10064,20 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>DeMario Douglas (NE)</t>
-        </is>
-      </c>
-      <c r="C161" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Woody Marks (HOU)</t>
+        </is>
+      </c>
+      <c r="C161" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E161" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.04</t>
         </is>
       </c>
     </row>
@@ -10087,10 +10087,10 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Malachi Fields (NYG)</t>
-        </is>
-      </c>
-      <c r="C162" s="17" t="inlineStr">
+          <t>Devaughn Vele (NO)</t>
+        </is>
+      </c>
+      <c r="C162" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10110,12 +10110,12 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>Sam Darnold (SEA)</t>
-        </is>
-      </c>
-      <c r="C163" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Cooper Kupp (SEA)</t>
+        </is>
+      </c>
+      <c r="C163" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="E163" s="14" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>19.05</t>
         </is>
       </c>
     </row>
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Keaton Mitchell (LAC)</t>
-        </is>
-      </c>
-      <c r="C164" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kenyon Sadiq (NYJ)</t>
+        </is>
+      </c>
+      <c r="C164" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>13.1</t>
         </is>
       </c>
     </row>
@@ -10156,20 +10156,20 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>Adonai Mitchell (NYJ)</t>
-        </is>
-      </c>
-      <c r="C165" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>AJ Barner (SEA)</t>
+        </is>
+      </c>
+      <c r="C165" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E165" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10179,20 +10179,20 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane (BAL)</t>
-        </is>
-      </c>
-      <c r="C166" s="17" t="inlineStr">
+          <t>Jaylin Noel (HOU)</t>
+        </is>
+      </c>
+      <c r="C166" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>18.1</t>
         </is>
       </c>
     </row>
@@ -10202,20 +10202,20 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>Daniel Jones (IND)</t>
-        </is>
-      </c>
-      <c r="C167" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Zach Charbonnet (SEA)</t>
+        </is>
+      </c>
+      <c r="C167" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E167" s="14" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>13.04</t>
         </is>
       </c>
     </row>
@@ -10225,12 +10225,12 @@
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>Tank Dell (HOU)</t>
-        </is>
-      </c>
-      <c r="C168" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Alvin Kamara (NO)</t>
+        </is>
+      </c>
+      <c r="C168" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>14.07</t>
         </is>
       </c>
     </row>
@@ -10248,20 +10248,20 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>Germie Bernard (PIT)</t>
-        </is>
-      </c>
-      <c r="C169" s="17" t="inlineStr">
+          <t>Adonai Mitchell (NYJ)</t>
+        </is>
+      </c>
+      <c r="C169" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E169" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Zach Charbonnet (SEA)</t>
+          <t>Isiah Pacheco (DET)</t>
         </is>
       </c>
       <c r="C170" s="16" t="inlineStr">
@@ -10280,11 +10280,11 @@
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -10294,16 +10294,16 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>Cyrus Allen (KC)</t>
-        </is>
-      </c>
-      <c r="C171" s="17" t="inlineStr">
+          <t>Malik Washington (MIA)</t>
+        </is>
+      </c>
+      <c r="C171" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Tyler Allgeier (ARI)</t>
+          <t>Dylan Sampson (CLE)</t>
         </is>
       </c>
       <c r="C172" s="16" t="inlineStr">
@@ -10326,11 +10326,11 @@
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -10340,20 +10340,20 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>Dylan Sampson (CLE)</t>
-        </is>
-      </c>
-      <c r="C173" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Germie Bernard (PIT)</t>
+        </is>
+      </c>
+      <c r="C173" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10363,20 +10363,20 @@
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Kyle Williams (NE)</t>
-        </is>
-      </c>
-      <c r="C174" s="17" t="inlineStr">
+          <t>Jordyn Tyson (NO)</t>
+        </is>
+      </c>
+      <c r="C174" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>8.07</t>
         </is>
       </c>
     </row>
@@ -10386,20 +10386,20 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>Calvin Ridley (TEN)</t>
-        </is>
-      </c>
-      <c r="C175" s="17" t="inlineStr">
+          <t>Caleb Douglas (MIA)</t>
+        </is>
+      </c>
+      <c r="C175" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E175" s="14" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>18.09</t>
         </is>
       </c>
     </row>
@@ -10409,20 +10409,20 @@
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>T.J. Hockenson (MIN)</t>
+          <t>Omar Cooper Jr. (NYJ)</t>
         </is>
       </c>
       <c r="C176" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D176" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>17.02</t>
         </is>
       </c>
     </row>
@@ -10432,20 +10432,20 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Mike Washington Jr. (LV)</t>
-        </is>
-      </c>
-      <c r="C177" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dontayvion Wicks (PHI)</t>
+        </is>
+      </c>
+      <c r="C177" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E177" s="14" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10455,20 +10455,20 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Greg Dulcich (MIA)</t>
+          <t>Travis Hunter (JAX)</t>
         </is>
       </c>
       <c r="C178" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10478,12 +10478,12 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq (NYJ)</t>
-        </is>
-      </c>
-      <c r="C179" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Mike Washington Jr. (LV)</t>
+        </is>
+      </c>
+      <c r="C179" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="E179" s="14" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>15.05</t>
         </is>
       </c>
     </row>
@@ -10501,20 +10501,20 @@
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Jonah Coleman (DEN)</t>
-        </is>
-      </c>
-      <c r="C180" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Darius Slayton (NYG)</t>
+        </is>
+      </c>
+      <c r="C180" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10524,12 +10524,12 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>Tre' Harris (LAC)</t>
-        </is>
-      </c>
-      <c r="C181" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chris Rodriguez Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C181" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>12.08</t>
         </is>
       </c>
     </row>
@@ -10547,20 +10547,20 @@
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Keon Coleman (BUF)</t>
-        </is>
-      </c>
-      <c r="C182" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyler Allgeier (ARI)</t>
+        </is>
+      </c>
+      <c r="C182" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D182" s="14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -10570,20 +10570,20 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr. (NYG)</t>
-        </is>
-      </c>
-      <c r="C183" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tory Horton (SEA)</t>
+        </is>
+      </c>
+      <c r="C183" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D183" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E183" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10593,20 +10593,20 @@
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>Pat Freiermuth (PIT)</t>
+          <t>Tre' Harris (LAC)</t>
         </is>
       </c>
       <c r="C184" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D184" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10616,20 +10616,20 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Aaron Rodgers (PIT)</t>
-        </is>
-      </c>
-      <c r="C185" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jalen Tolbert (MIA)</t>
+        </is>
+      </c>
+      <c r="C185" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E185" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10639,20 +10639,20 @@
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Bryce Young (CAR)</t>
-        </is>
-      </c>
-      <c r="C186" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Ryan Flournoy (DAL)</t>
+        </is>
+      </c>
+      <c r="C186" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D186" s="14" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10662,20 +10662,20 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>Zachariah Branch (ATL)</t>
-        </is>
-      </c>
-      <c r="C187" s="17" t="inlineStr">
+          <t>Malachi Fields (NYG)</t>
+        </is>
+      </c>
+      <c r="C187" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D187" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E187" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>19.04</t>
         </is>
       </c>
     </row>
@@ -10685,20 +10685,20 @@
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Ryan Flournoy (DAL)</t>
-        </is>
-      </c>
-      <c r="C188" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Keaton Mitchell (LAC)</t>
+        </is>
+      </c>
+      <c r="C188" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D188" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10708,20 +10708,20 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Cade Otton (TB)</t>
-        </is>
-      </c>
-      <c r="C189" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tyrone Tracy Jr. (NYG)</t>
+        </is>
+      </c>
+      <c r="C189" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E189" s="14" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10754,20 +10754,20 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>Alvin Kamara (NO)</t>
-        </is>
-      </c>
-      <c r="C191" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DeMario Douglas (NE)</t>
+        </is>
+      </c>
+      <c r="C191" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E191" s="14" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10777,20 +10777,20 @@
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Caleb Douglas (MIA)</t>
-        </is>
-      </c>
-      <c r="C192" s="17" t="inlineStr">
+          <t>Zachariah Branch (ATL)</t>
+        </is>
+      </c>
+      <c r="C192" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D192" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -10800,20 +10800,20 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Geno Smith (NYJ)</t>
-        </is>
-      </c>
-      <c r="C193" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Keon Coleman (BUF)</t>
+        </is>
+      </c>
+      <c r="C193" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.07</t>
         </is>
       </c>
     </row>
@@ -10846,20 +10846,20 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Brian Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C195" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Pat Bryant (DEN)</t>
+        </is>
+      </c>
+      <c r="C195" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E195" s="14" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>19.11</t>
         </is>
       </c>
     </row>
@@ -10869,10 +10869,10 @@
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>Devaughn Vele (NO)</t>
-        </is>
-      </c>
-      <c r="C196" s="17" t="inlineStr">
+          <t>Tank Dell (HOU)</t>
+        </is>
+      </c>
+      <c r="C196" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="E196" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10892,20 +10892,20 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>AJ Barner (SEA)</t>
+          <t>Cyrus Allen (KC)</t>
         </is>
       </c>
       <c r="C197" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D197" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E197" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -10915,20 +10915,20 @@
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Jaylin Noel (HOU)</t>
-        </is>
-      </c>
-      <c r="C198" s="17" t="inlineStr">
+          <t>Kyle Williams (NE)</t>
+        </is>
+      </c>
+      <c r="C198" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D198" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>19.06</t>
         </is>
       </c>
     </row>
@@ -10938,20 +10938,20 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>Darius Slayton (NYG)</t>
-        </is>
-      </c>
-      <c r="C199" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonah Coleman (DEN)</t>
+        </is>
+      </c>
+      <c r="C199" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E199" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.03</t>
         </is>
       </c>
     </row>
@@ -10961,20 +10961,20 @@
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Oronde Gadsden (LAC)</t>
-        </is>
-      </c>
-      <c r="C200" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kenneth Walker (KC)</t>
+        </is>
+      </c>
+      <c r="C200" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D200" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -10984,20 +10984,20 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>Rashod Bateman (BAL)</t>
+          <t>Patrick Mahomes (KC)</t>
         </is>
       </c>
       <c r="C201" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D201" s="14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -11007,20 +11007,20 @@
       </c>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>Jalen Tolbert (MIA)</t>
-        </is>
-      </c>
-      <c r="C202" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brian Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C202" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D202" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E202" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.12</t>
         </is>
       </c>
     </row>
@@ -11030,20 +11030,20 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>Tory Horton (SEA)</t>
-        </is>
-      </c>
-      <c r="C203" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Oronde Gadsden (LAC)</t>
+        </is>
+      </c>
+      <c r="C203" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D203" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>

--- a/assets/data/12guys1cup-cheat-sheet.xlsx
+++ b/assets/data/12guys1cup-cheat-sheet.xlsx
@@ -62,12 +62,6 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00B8386B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="001565C0"/>
       <sz val="10"/>
     </font>
@@ -75,6 +69,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00E65100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00B8386B"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -125,17 +125,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D4E4F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -6476,20 +6476,20 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Josh Allen (BUF)</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Bijan Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.03</t>
         </is>
       </c>
     </row>
@@ -6499,20 +6499,20 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Bijan Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ja'Marr Chase (CIN)</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>
@@ -6525,7 +6525,7 @@
           <t>Puka Nacua (LAR)</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6545,20 +6545,20 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase (CIN)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Christian McCaffrey (SF)</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
     </row>
@@ -6568,20 +6568,20 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Christian McCaffrey (SF)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jaxon Smith-Njigba (SEA)</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6591,20 +6591,20 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba (SEA)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
+          <t>Amon-Ra St. Brown (DET)</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6614,20 +6614,20 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Lamar Jackson (BAL)</t>
+          <t>CeeDee Lamb (DAL)</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6637,20 +6637,20 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Jayden Daniels (WAS)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jonathan Taylor (IND)</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6660,20 +6660,20 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Drake Maye (NE)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>James Cook III (BUF)</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>1.11</t>
         </is>
       </c>
     </row>
@@ -6683,20 +6683,20 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Jalen Hurts (PHI)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>De'Von Achane (MIA)</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6706,20 +6706,20 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown (DET)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kenneth Walker (KC)</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -6729,12 +6729,12 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Joe Burrow (CIN)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Chase Brown (CIN)</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -6752,20 +6752,20 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Jonathan Taylor (IND)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Justin Jefferson (MIN)</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6775,20 +6775,20 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Jaxson Dart (NYG)</t>
+          <t>A.J. Brown (NE)</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -6798,20 +6798,20 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Trevor Lawrence (JAX)</t>
+          <t>Chris Olave (NO)</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>3.07</t>
         </is>
       </c>
     </row>
@@ -6821,20 +6821,20 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Brock Purdy (SF)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Brock Bowers (LV)</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -6844,20 +6844,20 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Dak Prescott (DAL)</t>
+          <t>Nico Collins (HOU)</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -6867,20 +6867,20 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Caleb Williams (CHI)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Trey McBride (ARI)</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -6890,20 +6890,20 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Justin Herbert (LAC)</t>
+          <t>Garrett Wilson (NYJ)</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -6913,20 +6913,20 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Bo Nix (DEN)</t>
+          <t>Drake London (ATL)</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -6936,20 +6936,20 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Matthew Stafford (LAR)</t>
+          <t>George Pickens (DAL)</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -6959,20 +6959,20 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>De'Von Achane (MIA)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rashee Rice (KC)</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -6982,20 +6982,20 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Kyler Murray (MIN)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Omarion Hampton (LAC)</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7005,20 +7005,20 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Jared Goff (DET)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Ashton Jeanty (LV)</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -7028,12 +7028,12 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Tyler Shough (NO)</t>
+          <t>Malik Nabers (NYG)</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -7051,12 +7051,12 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Baker Mayfield (TB)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Saquon Barkley (PHI)</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -7074,20 +7074,20 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Chase Brown (CIN)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Zay Flowers (BAL)</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>4.05</t>
         </is>
       </c>
     </row>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Drake London (ATL)</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Derrick Henry (BAL)</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.08</t>
         </is>
       </c>
     </row>
@@ -7120,20 +7120,20 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Derrick Henry (BAL)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DeVonta Smith (PHI)</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.12</t>
         </is>
       </c>
     </row>
@@ -7143,20 +7143,20 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Daniel Jones (IND)</t>
+          <t>Jaylen Waddle (DEN)</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -7166,12 +7166,12 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>CeeDee Lamb (DAL)</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jeremiyah Love (ARI)</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7189,12 +7189,12 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Jordan Love (GB)</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Kyren Williams (LAR)</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D36" s="14" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
@@ -7212,20 +7212,20 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Malik Willis (MIA)</t>
+          <t>Ladd McConkey (LAC)</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>4.02</t>
         </is>
       </c>
     </row>
@@ -7235,20 +7235,20 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Justin Jefferson (MIN)</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Breece Hall (NYJ)</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7258,20 +7258,20 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>James Cook III (BUF)</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Emeka Egbuka (TB)</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>4.03</t>
         </is>
       </c>
     </row>
@@ -7281,20 +7281,20 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>Rashee Rice (KC)</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>D'Andre Swift (CHI)</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D40" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -7304,20 +7304,20 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Sam Darnold (SEA)</t>
+          <t>Tetairoa McMillan (CAR)</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>4.01</t>
         </is>
       </c>
     </row>
@@ -7327,20 +7327,20 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Saquon Barkley (PHI)</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tee Higgins (CIN)</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D42" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>3.11</t>
         </is>
       </c>
     </row>
@@ -7350,20 +7350,20 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Chris Olave (NO)</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
+          <t>Carnell Tate (TEN)</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -7373,20 +7373,20 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>C.J. Stroud (HOU)</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Javonte Williams (DAL)</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7396,20 +7396,20 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Ashton Jeanty (LV)</t>
-        </is>
-      </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Josh Allen (BUF)</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.09</t>
         </is>
       </c>
     </row>
@@ -7419,20 +7419,20 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>A.J. Brown (NE)</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="inlineStr">
+          <t>Luther Burden III (CHI)</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D46" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -7442,20 +7442,20 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Trey McBride (ARI)</t>
-        </is>
-      </c>
-      <c r="C47" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Christian Watson (GB)</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -7465,20 +7465,20 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Bryce Young (CAR)</t>
-        </is>
-      </c>
-      <c r="C48" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Bucky Irving (TB)</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D48" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>4.06</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>Omarion Hampton (LAC)</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Parker Washington (JAX)</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D49" s="14" t="n">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>7.04</t>
         </is>
       </c>
     </row>
@@ -7511,20 +7511,20 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>George Pickens (DAL)</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Travis Etienne Jr. (NO)</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>4.09</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Jeremiyah Love (ARI)</t>
+          <t>Cam Skattebo (NYG)</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr">
@@ -7543,11 +7543,11 @@
         </is>
       </c>
       <c r="D51" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.08</t>
         </is>
       </c>
     </row>
@@ -7557,20 +7557,20 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Nico Collins (HOU)</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="inlineStr">
+          <t>Terry McLaurin (WAS)</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D52" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -7580,20 +7580,20 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Breece Hall (NYJ)</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jameson Williams (DET)</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -7603,20 +7603,20 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>Brock Bowers (LV)</t>
-        </is>
-      </c>
-      <c r="C54" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>DJ Moore (BUF)</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>5.09</t>
         </is>
       </c>
     </row>
@@ -7626,20 +7626,20 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Garrett Wilson (NYJ)</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Bhayshul Tuten (JAX)</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -7649,20 +7649,20 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Zay Flowers (BAL)</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="inlineStr">
+          <t>Davante Adams (LAR)</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>5.02</t>
         </is>
       </c>
     </row>
@@ -7672,10 +7672,10 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Malik Nabers (NYG)</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="inlineStr">
+          <t>Mike Evans (SF)</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -7695,20 +7695,20 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Javonte Williams (DAL)</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rome Odunze (CHI)</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D58" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>6.05</t>
         </is>
       </c>
     </row>
@@ -7718,20 +7718,20 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>DeVonta Smith (PHI)</t>
-        </is>
-      </c>
-      <c r="C59" s="18" t="inlineStr">
+          <t>Marvin Harrison Jr. (ARI)</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D59" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -7741,20 +7741,20 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr. (NO)</t>
-        </is>
-      </c>
-      <c r="C60" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DK Metcalf (PIT)</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D60" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -7764,20 +7764,20 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Kyren Williams (LAR)</t>
-        </is>
-      </c>
-      <c r="C61" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tyler Warren (IND)</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>4.11</t>
         </is>
       </c>
     </row>
@@ -7787,20 +7787,20 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Cam Skattebo (NYG)</t>
-        </is>
-      </c>
-      <c r="C62" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Colston Loveland (CHI)</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D62" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.04</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Geno Smith (NYJ)</t>
+          <t>Alec Pierce (IND)</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D63" s="14" t="n">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.05</t>
         </is>
       </c>
     </row>
@@ -7833,20 +7833,20 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan (CAR)</t>
-        </is>
-      </c>
-      <c r="C64" s="18" t="inlineStr">
+          <t>Brian Thomas Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D64" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>7.02</t>
         </is>
       </c>
     </row>
@@ -7856,20 +7856,20 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Cam Ward (TEN)</t>
-        </is>
-      </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Quinshon Judkins (CLE)</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D65" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -7879,20 +7879,20 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>Emeka Egbuka (TB)</t>
-        </is>
-      </c>
-      <c r="C66" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>TreVeyon Henderson (NE)</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D66" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -7902,20 +7902,20 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>Aaron Rodgers (PIT)</t>
-        </is>
-      </c>
-      <c r="C67" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>David Montgomery (HOU)</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D67" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -7925,20 +7925,20 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>D'Andre Swift (CHI)</t>
-        </is>
-      </c>
-      <c r="C68" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Lamar Jackson (BAL)</t>
+        </is>
+      </c>
+      <c r="C68" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D68" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>3.09</t>
         </is>
       </c>
     </row>
@@ -7948,20 +7948,20 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Davante Adams (LAR)</t>
-        </is>
-      </c>
-      <c r="C69" s="18" t="inlineStr">
+          <t>Chris Godwin Jr. (TB)</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D69" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>8.12</t>
         </is>
       </c>
     </row>
@@ -7971,20 +7971,20 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Tee Higgins (CIN)</t>
-        </is>
-      </c>
-      <c r="C70" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jadarian Price (SEA)</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D70" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>Bucky Irving (TB)</t>
+          <t>MarShawn Lloyd (GB)</t>
         </is>
       </c>
       <c r="C71" s="16" t="inlineStr">
@@ -8003,11 +8003,11 @@
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>15.06</t>
         </is>
       </c>
     </row>
@@ -8017,20 +8017,20 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Ladd McConkey (LAC)</t>
-        </is>
-      </c>
-      <c r="C72" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rhamondre Stevenson (NE)</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -8040,20 +8040,20 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Jameson Williams (DET)</t>
-        </is>
-      </c>
-      <c r="C73" s="18" t="inlineStr">
+          <t>Quentin Johnston (LAC)</t>
+        </is>
+      </c>
+      <c r="C73" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>10.05</t>
         </is>
       </c>
     </row>
@@ -8063,20 +8063,20 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Quinshon Judkins (CLE)</t>
-        </is>
-      </c>
-      <c r="C74" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Michael Pittman Jr. (PIT)</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D74" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>9.07</t>
         </is>
       </c>
     </row>
@@ -8086,20 +8086,20 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>Colston Loveland (CHI)</t>
-        </is>
-      </c>
-      <c r="C75" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Rico Dowdle (PIT)</t>
+        </is>
+      </c>
+      <c r="C75" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>8.01</t>
         </is>
       </c>
     </row>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Waddle (DEN)</t>
-        </is>
-      </c>
-      <c r="C76" s="18" t="inlineStr">
+          <t>Wan'Dale Robinson (TEN)</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D76" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>10.09</t>
         </is>
       </c>
     </row>
@@ -8132,20 +8132,20 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten (JAX)</t>
-        </is>
-      </c>
-      <c r="C77" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Harold Fannin Jr. (CLE)</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D77" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -8155,20 +8155,20 @@
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Terry McLaurin (WAS)</t>
-        </is>
-      </c>
-      <c r="C78" s="18" t="inlineStr">
+          <t>Michael Wilson (ARI)</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D78" s="14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>7.11</t>
         </is>
       </c>
     </row>
@@ -8178,10 +8178,10 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>DJ Moore (BUF)</t>
-        </is>
-      </c>
-      <c r="C79" s="18" t="inlineStr">
+          <t>Stefon Diggs (WAS)</t>
+        </is>
+      </c>
+      <c r="C79" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>10.02</t>
         </is>
       </c>
     </row>
@@ -8201,10 +8201,10 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Luther Burden III (CHI)</t>
-        </is>
-      </c>
-      <c r="C80" s="18" t="inlineStr">
+          <t>Courtland Sutton (DEN)</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8214,7 +8214,7 @@
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>7.09</t>
         </is>
       </c>
     </row>
@@ -8224,20 +8224,20 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>Rome Odunze (CHI)</t>
-        </is>
-      </c>
-      <c r="C81" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jacory Croskey-Merritt (WAS)</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D81" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>10.06</t>
         </is>
       </c>
     </row>
@@ -8247,20 +8247,20 @@
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Tyler Warren (IND)</t>
-        </is>
-      </c>
-      <c r="C82" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kenny Gainwell (TB)</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D82" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8270,20 +8270,20 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>Harold Fannin Jr. (CLE)</t>
-        </is>
-      </c>
-      <c r="C83" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jaylen Warren (PIT)</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D83" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -8293,20 +8293,20 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Courtland Sutton (DEN)</t>
-        </is>
-      </c>
-      <c r="C84" s="18" t="inlineStr">
+          <t>Jordan Addison (MIN)</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D84" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>9.09</t>
         </is>
       </c>
     </row>
@@ -8316,12 +8316,12 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>David Montgomery (HOU)</t>
-        </is>
-      </c>
-      <c r="C85" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>De'Zhaun Stribling (SF)</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D85" s="14" t="n">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>12.07</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Christian Watson (GB)</t>
+          <t>Tucker Kraft (GB)</t>
         </is>
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D86" s="14" t="n">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8362,20 +8362,20 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr. (ARI)</t>
-        </is>
-      </c>
-      <c r="C87" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jalen Hurts (PHI)</t>
+        </is>
+      </c>
+      <c r="C87" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D87" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>5.12</t>
         </is>
       </c>
     </row>
@@ -8385,20 +8385,20 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Warren (PIT)</t>
-        </is>
-      </c>
-      <c r="C88" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jayden Reed (GB)</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D88" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8408,20 +8408,20 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>Mike Evans (SF)</t>
-        </is>
-      </c>
-      <c r="C89" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jayden Daniels (WAS)</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D89" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.04</t>
         </is>
       </c>
     </row>
@@ -8431,20 +8431,20 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>DK Metcalf (PIT)</t>
-        </is>
-      </c>
-      <c r="C90" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Joe Burrow (CIN)</t>
+        </is>
+      </c>
+      <c r="C90" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D90" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -8454,20 +8454,20 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>Alec Pierce (IND)</t>
+          <t>George Kittle (SF)</t>
         </is>
       </c>
       <c r="C91" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson (NE)</t>
+          <t>Chuba Hubbard (CAR)</t>
         </is>
       </c>
       <c r="C92" s="16" t="inlineStr">
@@ -8486,11 +8486,11 @@
         </is>
       </c>
       <c r="D92" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>7.05</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson (NE)</t>
+          <t>J.K. Dobbins (DEN)</t>
         </is>
       </c>
       <c r="C93" s="16" t="inlineStr">
@@ -8509,11 +8509,11 @@
         </is>
       </c>
       <c r="D93" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>8.1</t>
         </is>
       </c>
     </row>
@@ -8523,12 +8523,12 @@
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>Michael Pittman Jr. (PIT)</t>
-        </is>
-      </c>
-      <c r="C94" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tony Pollard (TEN)</t>
+        </is>
+      </c>
+      <c r="C94" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D94" s="14" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>7.12</t>
         </is>
       </c>
     </row>
@@ -8546,20 +8546,20 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>Kyle Pitts Sr. (ATL)</t>
-        </is>
-      </c>
-      <c r="C95" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Josh Downs (IND)</t>
+        </is>
+      </c>
+      <c r="C95" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D95" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>10.01</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Tony Pollard (TEN)</t>
+          <t>Jonathon Brooks (CAR)</t>
         </is>
       </c>
       <c r="C96" s="16" t="inlineStr">
@@ -8578,11 +8578,11 @@
         </is>
       </c>
       <c r="D96" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>9.1</t>
         </is>
       </c>
     </row>
@@ -8592,20 +8592,20 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>Jadarian Price (SEA)</t>
-        </is>
-      </c>
-      <c r="C97" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jakobi Meyers (JAX)</t>
+        </is>
+      </c>
+      <c r="C97" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>10.1</t>
         </is>
       </c>
     </row>
@@ -8615,20 +8615,20 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>George Kittle (SF)</t>
-        </is>
-      </c>
-      <c r="C98" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Romeo Doubs (NE)</t>
+        </is>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D98" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -8638,20 +8638,20 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>Parker Washington (JAX)</t>
+          <t>Sam LaPorta (DET)</t>
         </is>
       </c>
       <c r="C99" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -8661,20 +8661,20 @@
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>Sam LaPorta (DET)</t>
-        </is>
-      </c>
-      <c r="C100" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Khalil Shakir (BUF)</t>
+        </is>
+      </c>
+      <c r="C100" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D100" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>12.11</t>
         </is>
       </c>
     </row>
@@ -8684,20 +8684,20 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>Travis Kelce (KC)</t>
-        </is>
-      </c>
-      <c r="C101" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kyle Monangai (CHI)</t>
+        </is>
+      </c>
+      <c r="C101" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -8707,20 +8707,20 @@
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C102" s="18" t="inlineStr">
+          <t>Makai Lemon (PHI)</t>
+        </is>
+      </c>
+      <c r="C102" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D102" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -8730,20 +8730,20 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>Rico Dowdle (PIT)</t>
-        </is>
-      </c>
-      <c r="C103" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Xavier Worthy (KC)</t>
+        </is>
+      </c>
+      <c r="C103" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -8753,20 +8753,20 @@
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>Dallas Goedert (PHI)</t>
-        </is>
-      </c>
-      <c r="C104" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Malik Washington (MIA)</t>
+        </is>
+      </c>
+      <c r="C104" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D104" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -8776,20 +8776,20 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson (TEN)</t>
-        </is>
-      </c>
-      <c r="C105" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jordan Mason (MIN)</t>
+        </is>
+      </c>
+      <c r="C105" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.07</t>
         </is>
       </c>
     </row>
@@ -8799,20 +8799,20 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>Jakobi Meyers (JAX)</t>
-        </is>
-      </c>
-      <c r="C106" s="18" t="inlineStr">
+          <t>Jalen Coker (CAR)</t>
+        </is>
+      </c>
+      <c r="C106" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D106" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>13.02</t>
         </is>
       </c>
     </row>
@@ -8822,20 +8822,20 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Carnell Tate (TEN)</t>
-        </is>
-      </c>
-      <c r="C107" s="18" t="inlineStr">
+          <t>Rashid Shaheed (SEA)</t>
+        </is>
+      </c>
+      <c r="C107" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>13.03</t>
         </is>
       </c>
     </row>
@@ -8845,20 +8845,20 @@
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>Michael Wilson (ARI)</t>
-        </is>
-      </c>
-      <c r="C108" s="18" t="inlineStr">
+          <t>KC Concepcion (CLE)</t>
+        </is>
+      </c>
+      <c r="C108" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D108" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>11.01</t>
         </is>
       </c>
     </row>
@@ -8868,20 +8868,20 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>Jayden Reed (GB)</t>
-        </is>
-      </c>
-      <c r="C109" s="18" t="inlineStr">
+          <t>Kayshon Boutte (HOU)</t>
+        </is>
+      </c>
+      <c r="C109" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>19.08</t>
         </is>
       </c>
     </row>
@@ -8891,20 +8891,20 @@
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>J.K. Dobbins (DEN)</t>
-        </is>
-      </c>
-      <c r="C110" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Drake Maye (NE)</t>
+        </is>
+      </c>
+      <c r="C110" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D110" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -8914,20 +8914,20 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr. (TB)</t>
-        </is>
-      </c>
-      <c r="C111" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rachaad White (WAS)</t>
+        </is>
+      </c>
+      <c r="C111" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -8937,20 +8937,20 @@
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Chuba Hubbard (CAR)</t>
-        </is>
-      </c>
-      <c r="C112" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Matthew Golden (GB)</t>
+        </is>
+      </c>
+      <c r="C112" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D112" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>11.07</t>
         </is>
       </c>
     </row>
@@ -8960,20 +8960,20 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>Tucker Kraft (GB)</t>
+          <t>Jaxson Dart (NYG)</t>
         </is>
       </c>
       <c r="C113" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -8983,20 +8983,20 @@
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Kenny Gainwell (TB)</t>
-        </is>
-      </c>
-      <c r="C114" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kyle Pitts Sr. (ATL)</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D114" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>6.1</t>
         </is>
       </c>
     </row>
@@ -9006,20 +9006,20 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>Quentin Johnston (LAC)</t>
-        </is>
-      </c>
-      <c r="C115" s="18" t="inlineStr">
+          <t>Keenan Allen (IND)</t>
+        </is>
+      </c>
+      <c r="C115" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>17.07</t>
         </is>
       </c>
     </row>
@@ -9029,20 +9029,20 @@
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>Stefon Diggs (WAS)</t>
-        </is>
-      </c>
-      <c r="C116" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Caleb Williams (CHI)</t>
+        </is>
+      </c>
+      <c r="C116" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D116" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -9052,20 +9052,20 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>Jordan Addison (MIN)</t>
-        </is>
-      </c>
-      <c r="C117" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Trevor Lawrence (JAX)</t>
+        </is>
+      </c>
+      <c r="C117" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>Jonathon Brooks (CAR)</t>
+          <t>Blake Corum (LAR)</t>
         </is>
       </c>
       <c r="C118" s="16" t="inlineStr">
@@ -9084,11 +9084,11 @@
         </is>
       </c>
       <c r="D118" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.08</t>
         </is>
       </c>
     </row>
@@ -9098,20 +9098,20 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>Xavier Worthy (KC)</t>
-        </is>
-      </c>
-      <c r="C119" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>RJ Harvey (DEN)</t>
+        </is>
+      </c>
+      <c r="C119" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>7.08</t>
         </is>
       </c>
     </row>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Jake Ferguson (DAL)</t>
-        </is>
-      </c>
-      <c r="C120" s="19" t="inlineStr">
+          <t>Juwan Johnson (NO)</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D120" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9144,20 +9144,20 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>Mark Andrews (BAL)</t>
-        </is>
-      </c>
-      <c r="C121" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jordyn Tyson (NO)</t>
+        </is>
+      </c>
+      <c r="C121" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D121" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>8.07</t>
         </is>
       </c>
     </row>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling (SF)</t>
+          <t>Dalton Schultz (HOU)</t>
         </is>
       </c>
       <c r="C122" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>17.01</t>
         </is>
       </c>
     </row>
@@ -9190,20 +9190,20 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>Matthew Golden (GB)</t>
+          <t>Travis Kelce (KC)</t>
         </is>
       </c>
       <c r="C123" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>8.08</t>
         </is>
       </c>
     </row>
@@ -9213,20 +9213,20 @@
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>Isaiah Likely (NYG)</t>
-        </is>
-      </c>
-      <c r="C124" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tre Tucker (LV)</t>
+        </is>
+      </c>
+      <c r="C124" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D124" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>17.1</t>
         </is>
       </c>
     </row>
@@ -9236,20 +9236,20 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>Khalil Shakir (BUF)</t>
-        </is>
-      </c>
-      <c r="C125" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Aaron Jones Sr. (MIN)</t>
+        </is>
+      </c>
+      <c r="C125" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -9259,20 +9259,20 @@
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>KC Concepcion (CLE)</t>
+          <t>Jake Ferguson (DAL)</t>
         </is>
       </c>
       <c r="C126" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>9.02</t>
         </is>
       </c>
     </row>
@@ -9282,20 +9282,20 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>Josh Downs (IND)</t>
-        </is>
-      </c>
-      <c r="C127" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dak Prescott (DAL)</t>
+        </is>
+      </c>
+      <c r="C127" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>7.07</t>
         </is>
       </c>
     </row>
@@ -9305,20 +9305,20 @@
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>Romeo Doubs (NE)</t>
+          <t>Dalton Kincaid (BUF)</t>
         </is>
       </c>
       <c r="C128" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D128" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -9328,12 +9328,12 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>Deebo Samuel Sr. (SF)</t>
+          <t>Isaiah Likely (NYG)</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D129" s="14" t="n">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>RJ Harvey (DEN)</t>
+          <t>Tyjae Spears (TEN)</t>
         </is>
       </c>
       <c r="C130" s="16" t="inlineStr">
@@ -9360,11 +9360,11 @@
         </is>
       </c>
       <c r="D130" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -9374,20 +9374,20 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr. (MIN)</t>
-        </is>
-      </c>
-      <c r="C131" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Justin Herbert (LAC)</t>
+        </is>
+      </c>
+      <c r="C131" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -9397,20 +9397,20 @@
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>Rachaad White (WAS)</t>
-        </is>
-      </c>
-      <c r="C132" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dallas Goedert (PHI)</t>
+        </is>
+      </c>
+      <c r="C132" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D132" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -9420,20 +9420,20 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>Dalton Kincaid (BUF)</t>
+          <t>Bo Nix (DEN)</t>
         </is>
       </c>
       <c r="C133" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D133" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>10.12</t>
         </is>
       </c>
     </row>
@@ -9443,20 +9443,20 @@
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Jalen Coker (CAR)</t>
-        </is>
-      </c>
-      <c r="C134" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brock Purdy (SF)</t>
+        </is>
+      </c>
+      <c r="C134" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D134" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>11.02</t>
         </is>
       </c>
     </row>
@@ -9466,20 +9466,20 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>Rashid Shaheed (SEA)</t>
-        </is>
-      </c>
-      <c r="C135" s="18" t="inlineStr">
+          <t>Omar Cooper Jr. (NYJ)</t>
+        </is>
+      </c>
+      <c r="C135" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>17.02</t>
         </is>
       </c>
     </row>
@@ -9489,20 +9489,20 @@
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd (GB)</t>
-        </is>
-      </c>
-      <c r="C136" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jared Goff (DET)</t>
+        </is>
+      </c>
+      <c r="C136" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D136" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>12.03</t>
         </is>
       </c>
     </row>
@@ -9512,20 +9512,20 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>Kyle Monangai (CHI)</t>
-        </is>
-      </c>
-      <c r="C137" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Deebo Samuel Sr. (SF)</t>
+        </is>
+      </c>
+      <c r="C137" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>11.11</t>
         </is>
       </c>
     </row>
@@ -9535,12 +9535,12 @@
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>Juwan Johnson (NO)</t>
+          <t>Tyler Shough (NO)</t>
         </is>
       </c>
       <c r="C138" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>16.07</t>
         </is>
       </c>
     </row>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>Jerry Jeudy (CLE)</t>
-        </is>
-      </c>
-      <c r="C139" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Matthew Stafford (LAR)</t>
+        </is>
+      </c>
+      <c r="C139" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>9.01</t>
         </is>
       </c>
     </row>
@@ -9581,20 +9581,20 @@
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>Hunter Henry (NE)</t>
+          <t>Kyler Murray (MIN)</t>
         </is>
       </c>
       <c r="C140" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D140" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>14.03</t>
         </is>
       </c>
     </row>
@@ -9604,20 +9604,20 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>Brenton Strange (JAX)</t>
+          <t>Jordan Love (GB)</t>
         </is>
       </c>
       <c r="C141" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>13.05</t>
         </is>
       </c>
     </row>
@@ -9627,20 +9627,20 @@
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>Denzel Boston (CLE)</t>
-        </is>
-      </c>
-      <c r="C142" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Baker Mayfield (TB)</t>
+        </is>
+      </c>
+      <c r="C142" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -9650,20 +9650,20 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>Makai Lemon (PHI)</t>
-        </is>
-      </c>
-      <c r="C143" s="18" t="inlineStr">
+          <t>Denzel Boston (CLE)</t>
+        </is>
+      </c>
+      <c r="C143" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9673,20 +9673,20 @@
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>Dalton Schultz (HOU)</t>
+          <t>Patrick Mahomes (KC)</t>
         </is>
       </c>
       <c r="C144" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -9696,20 +9696,20 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>Calvin Ridley (TEN)</t>
+          <t>Brenton Strange (JAX)</t>
         </is>
       </c>
       <c r="C145" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>13.08</t>
         </is>
       </c>
     </row>
@@ -9719,20 +9719,20 @@
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt (WAS)</t>
-        </is>
-      </c>
-      <c r="C146" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dontayvion Wicks (PHI)</t>
+        </is>
+      </c>
+      <c r="C146" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9742,20 +9742,20 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Jordan Mason (MIN)</t>
-        </is>
-      </c>
-      <c r="C147" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Mark Andrews (BAL)</t>
+        </is>
+      </c>
+      <c r="C147" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>11.09</t>
         </is>
       </c>
     </row>
@@ -9765,20 +9765,20 @@
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>Tre Tucker (LV)</t>
-        </is>
-      </c>
-      <c r="C148" s="18" t="inlineStr">
+          <t>Pat Bryant (DEN)</t>
+        </is>
+      </c>
+      <c r="C148" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>19.11</t>
         </is>
       </c>
     </row>
@@ -9788,20 +9788,20 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>Keenan Allen (IND)</t>
-        </is>
-      </c>
-      <c r="C149" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Malik Willis (MIA)</t>
+        </is>
+      </c>
+      <c r="C149" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -9811,20 +9811,20 @@
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>T.J. Hockenson (MIN)</t>
-        </is>
-      </c>
-      <c r="C150" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jalen Nailor (LV)</t>
+        </is>
+      </c>
+      <c r="C150" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Blake Corum (LAR)</t>
+          <t>Woody Marks (HOU)</t>
         </is>
       </c>
       <c r="C151" s="16" t="inlineStr">
@@ -9843,11 +9843,11 @@
         </is>
       </c>
       <c r="D151" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>14.04</t>
         </is>
       </c>
     </row>
@@ -9857,20 +9857,20 @@
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Tyjae Spears (TEN)</t>
-        </is>
-      </c>
-      <c r="C152" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Hunter Henry (NE)</t>
+        </is>
+      </c>
+      <c r="C152" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -9880,20 +9880,20 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>Kayshon Boutte (HOU)</t>
+          <t>Chig Okonkwo (WAS)</t>
         </is>
       </c>
       <c r="C153" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9903,20 +9903,20 @@
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>Rashod Bateman (BAL)</t>
-        </is>
-      </c>
-      <c r="C154" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chris Rodriguez Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C154" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>12.08</t>
         </is>
       </c>
     </row>
@@ -9926,20 +9926,20 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>Pat Freiermuth (PIT)</t>
-        </is>
-      </c>
-      <c r="C155" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Travis Hunter (JAX)</t>
+        </is>
+      </c>
+      <c r="C155" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9949,20 +9949,20 @@
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Greg Dulcich (MIA)</t>
-        </is>
-      </c>
-      <c r="C156" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Cooper Kupp (SEA)</t>
+        </is>
+      </c>
+      <c r="C156" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>19.05</t>
         </is>
       </c>
     </row>
@@ -9972,20 +9972,20 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane (BAL)</t>
-        </is>
-      </c>
-      <c r="C157" s="18" t="inlineStr">
+          <t>Jerry Jeudy (CLE)</t>
+        </is>
+      </c>
+      <c r="C157" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D157" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E157" s="14" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -9995,20 +9995,20 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Cade Otton (TB)</t>
+          <t>Cam Ward (TEN)</t>
         </is>
       </c>
       <c r="C158" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10018,16 +10018,16 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Jalen Nailor (LV)</t>
-        </is>
-      </c>
-      <c r="C159" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Isiah Pacheco (DET)</t>
+        </is>
+      </c>
+      <c r="C159" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E159" s="14" t="inlineStr">
         <is>
@@ -10041,20 +10041,20 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>Chig Okonkwo (WAS)</t>
+          <t>C.J. Stroud (HOU)</t>
         </is>
       </c>
       <c r="C160" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>18.01</t>
         </is>
       </c>
     </row>
@@ -10064,20 +10064,20 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>Woody Marks (HOU)</t>
-        </is>
-      </c>
-      <c r="C161" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DeMario Douglas (NE)</t>
+        </is>
+      </c>
+      <c r="C161" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E161" s="14" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10087,10 +10087,10 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Devaughn Vele (NO)</t>
-        </is>
-      </c>
-      <c r="C162" s="18" t="inlineStr">
+          <t>Malachi Fields (NYG)</t>
+        </is>
+      </c>
+      <c r="C162" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>19.04</t>
         </is>
       </c>
     </row>
@@ -10110,12 +10110,12 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>Cooper Kupp (SEA)</t>
-        </is>
-      </c>
-      <c r="C163" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Sam Darnold (SEA)</t>
+        </is>
+      </c>
+      <c r="C163" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="E163" s="14" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>14.05</t>
         </is>
       </c>
     </row>
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq (NYJ)</t>
-        </is>
-      </c>
-      <c r="C164" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Keaton Mitchell (LAC)</t>
+        </is>
+      </c>
+      <c r="C164" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10156,20 +10156,20 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>AJ Barner (SEA)</t>
-        </is>
-      </c>
-      <c r="C165" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Adonai Mitchell (NYJ)</t>
+        </is>
+      </c>
+      <c r="C165" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E165" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10179,20 +10179,20 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Jaylin Noel (HOU)</t>
-        </is>
-      </c>
-      <c r="C166" s="18" t="inlineStr">
+          <t>Ja'Kobi Lane (BAL)</t>
+        </is>
+      </c>
+      <c r="C166" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>14.02</t>
         </is>
       </c>
     </row>
@@ -10202,20 +10202,20 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>Zach Charbonnet (SEA)</t>
-        </is>
-      </c>
-      <c r="C167" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Daniel Jones (IND)</t>
+        </is>
+      </c>
+      <c r="C167" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E167" s="14" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>17.11</t>
         </is>
       </c>
     </row>
@@ -10225,12 +10225,12 @@
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>Alvin Kamara (NO)</t>
-        </is>
-      </c>
-      <c r="C168" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tank Dell (HOU)</t>
+        </is>
+      </c>
+      <c r="C168" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10248,20 +10248,20 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>Adonai Mitchell (NYJ)</t>
-        </is>
-      </c>
-      <c r="C169" s="18" t="inlineStr">
+          <t>Germie Bernard (PIT)</t>
+        </is>
+      </c>
+      <c r="C169" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E169" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Isiah Pacheco (DET)</t>
+          <t>Zach Charbonnet (SEA)</t>
         </is>
       </c>
       <c r="C170" s="16" t="inlineStr">
@@ -10280,11 +10280,11 @@
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>13.04</t>
         </is>
       </c>
     </row>
@@ -10294,16 +10294,16 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>Malik Washington (MIA)</t>
-        </is>
-      </c>
-      <c r="C171" s="18" t="inlineStr">
+          <t>Cyrus Allen (KC)</t>
+        </is>
+      </c>
+      <c r="C171" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Dylan Sampson (CLE)</t>
+          <t>Tyler Allgeier (ARI)</t>
         </is>
       </c>
       <c r="C172" s="16" t="inlineStr">
@@ -10326,11 +10326,11 @@
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -10340,20 +10340,20 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>Germie Bernard (PIT)</t>
-        </is>
-      </c>
-      <c r="C173" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dylan Sampson (CLE)</t>
+        </is>
+      </c>
+      <c r="C173" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -10363,20 +10363,20 @@
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Jordyn Tyson (NO)</t>
-        </is>
-      </c>
-      <c r="C174" s="18" t="inlineStr">
+          <t>Kyle Williams (NE)</t>
+        </is>
+      </c>
+      <c r="C174" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>19.06</t>
         </is>
       </c>
     </row>
@@ -10386,20 +10386,20 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>Caleb Douglas (MIA)</t>
-        </is>
-      </c>
-      <c r="C175" s="18" t="inlineStr">
+          <t>Calvin Ridley (TEN)</t>
+        </is>
+      </c>
+      <c r="C175" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E175" s="14" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>22.01</t>
         </is>
       </c>
     </row>
@@ -10409,20 +10409,20 @@
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>Omar Cooper Jr. (NYJ)</t>
+          <t>T.J. Hockenson (MIN)</t>
         </is>
       </c>
       <c r="C176" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D176" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -10432,20 +10432,20 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks (PHI)</t>
-        </is>
-      </c>
-      <c r="C177" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Mike Washington Jr. (LV)</t>
+        </is>
+      </c>
+      <c r="C177" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E177" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.05</t>
         </is>
       </c>
     </row>
@@ -10455,20 +10455,20 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Travis Hunter (JAX)</t>
+          <t>Greg Dulcich (MIA)</t>
         </is>
       </c>
       <c r="C178" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10478,12 +10478,12 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Mike Washington Jr. (LV)</t>
-        </is>
-      </c>
-      <c r="C179" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kenyon Sadiq (NYJ)</t>
+        </is>
+      </c>
+      <c r="C179" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="E179" s="14" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>13.1</t>
         </is>
       </c>
     </row>
@@ -10501,20 +10501,20 @@
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Darius Slayton (NYG)</t>
-        </is>
-      </c>
-      <c r="C180" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonah Coleman (DEN)</t>
+        </is>
+      </c>
+      <c r="C180" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.03</t>
         </is>
       </c>
     </row>
@@ -10524,12 +10524,12 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>Chris Rodriguez Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C181" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tre' Harris (LAC)</t>
+        </is>
+      </c>
+      <c r="C181" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10547,20 +10547,20 @@
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Tyler Allgeier (ARI)</t>
-        </is>
-      </c>
-      <c r="C182" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Keon Coleman (BUF)</t>
+        </is>
+      </c>
+      <c r="C182" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D182" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>20.07</t>
         </is>
       </c>
     </row>
@@ -10570,20 +10570,20 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>Tory Horton (SEA)</t>
-        </is>
-      </c>
-      <c r="C183" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyrone Tracy Jr. (NYG)</t>
+        </is>
+      </c>
+      <c r="C183" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D183" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E183" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10593,20 +10593,20 @@
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>Tre' Harris (LAC)</t>
+          <t>Pat Freiermuth (PIT)</t>
         </is>
       </c>
       <c r="C184" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D184" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10616,20 +10616,20 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Jalen Tolbert (MIA)</t>
-        </is>
-      </c>
-      <c r="C185" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Aaron Rodgers (PIT)</t>
+        </is>
+      </c>
+      <c r="C185" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E185" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10639,20 +10639,20 @@
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Ryan Flournoy (DAL)</t>
-        </is>
-      </c>
-      <c r="C186" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Bryce Young (CAR)</t>
+        </is>
+      </c>
+      <c r="C186" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D186" s="14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>19.12</t>
         </is>
       </c>
     </row>
@@ -10662,20 +10662,20 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>Malachi Fields (NYG)</t>
-        </is>
-      </c>
-      <c r="C187" s="18" t="inlineStr">
+          <t>Zachariah Branch (ATL)</t>
+        </is>
+      </c>
+      <c r="C187" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D187" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E187" s="14" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -10685,20 +10685,20 @@
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Keaton Mitchell (LAC)</t>
-        </is>
-      </c>
-      <c r="C188" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ryan Flournoy (DAL)</t>
+        </is>
+      </c>
+      <c r="C188" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D188" s="14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10708,20 +10708,20 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr. (NYG)</t>
-        </is>
-      </c>
-      <c r="C189" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Cade Otton (TB)</t>
+        </is>
+      </c>
+      <c r="C189" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E189" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>20.06</t>
         </is>
       </c>
     </row>
@@ -10754,20 +10754,20 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>DeMario Douglas (NE)</t>
-        </is>
-      </c>
-      <c r="C191" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Alvin Kamara (NO)</t>
+        </is>
+      </c>
+      <c r="C191" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E191" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.07</t>
         </is>
       </c>
     </row>
@@ -10777,20 +10777,20 @@
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Zachariah Branch (ATL)</t>
-        </is>
-      </c>
-      <c r="C192" s="18" t="inlineStr">
+          <t>Caleb Douglas (MIA)</t>
+        </is>
+      </c>
+      <c r="C192" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D192" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>18.09</t>
         </is>
       </c>
     </row>
@@ -10800,20 +10800,20 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Keon Coleman (BUF)</t>
-        </is>
-      </c>
-      <c r="C193" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Geno Smith (NYJ)</t>
+        </is>
+      </c>
+      <c r="C193" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10846,20 +10846,20 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Pat Bryant (DEN)</t>
-        </is>
-      </c>
-      <c r="C195" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brian Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C195" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E195" s="14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>13.12</t>
         </is>
       </c>
     </row>
@@ -10869,10 +10869,10 @@
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>Tank Dell (HOU)</t>
-        </is>
-      </c>
-      <c r="C196" s="18" t="inlineStr">
+          <t>Devaughn Vele (NO)</t>
+        </is>
+      </c>
+      <c r="C196" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="E196" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10892,20 +10892,20 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>Cyrus Allen (KC)</t>
+          <t>AJ Barner (SEA)</t>
         </is>
       </c>
       <c r="C197" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D197" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E197" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10915,20 +10915,20 @@
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Kyle Williams (NE)</t>
-        </is>
-      </c>
-      <c r="C198" s="18" t="inlineStr">
+          <t>Jaylin Noel (HOU)</t>
+        </is>
+      </c>
+      <c r="C198" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D198" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>18.1</t>
         </is>
       </c>
     </row>
@@ -10938,20 +10938,20 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>Jonah Coleman (DEN)</t>
-        </is>
-      </c>
-      <c r="C199" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Darius Slayton (NYG)</t>
+        </is>
+      </c>
+      <c r="C199" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E199" s="14" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10961,20 +10961,20 @@
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Kenneth Walker (KC)</t>
-        </is>
-      </c>
-      <c r="C200" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Oronde Gadsden (LAC)</t>
+        </is>
+      </c>
+      <c r="C200" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D200" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
@@ -10984,20 +10984,20 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>Patrick Mahomes (KC)</t>
+          <t>Rashod Bateman (BAL)</t>
         </is>
       </c>
       <c r="C201" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D201" s="14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>20.05</t>
         </is>
       </c>
     </row>
@@ -11007,20 +11007,20 @@
       </c>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>Brian Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C202" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jalen Tolbert (MIA)</t>
+        </is>
+      </c>
+      <c r="C202" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D202" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E202" s="14" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11030,20 +11030,20 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>Oronde Gadsden (LAC)</t>
-        </is>
-      </c>
-      <c r="C203" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tory Horton (SEA)</t>
+        </is>
+      </c>
+      <c r="C203" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D203" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>

--- a/assets/data/12guys1cup-cheat-sheet.xlsx
+++ b/assets/data/12guys1cup-cheat-sheet.xlsx
@@ -62,6 +62,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00B8386B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001565C0"/>
       <sz val="10"/>
     </font>
@@ -69,12 +75,6 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00E65100"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00B8386B"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -125,17 +125,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F8D7E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D4E4F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -6476,20 +6476,20 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Bijan Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Josh Allen (BUF)</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>2.09</t>
         </is>
       </c>
     </row>
@@ -6499,20 +6499,20 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase (CIN)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Bijan Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
     </row>
@@ -6525,7 +6525,7 @@
           <t>Puka Nacua (LAR)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6545,20 +6545,20 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Christian McCaffrey (SF)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ja'Marr Chase (CIN)</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>
@@ -6568,20 +6568,20 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba (SEA)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Christian McCaffrey (SF)</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
     </row>
@@ -6591,20 +6591,20 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown (DET)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
+          <t>Jaxon Smith-Njigba (SEA)</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6614,20 +6614,20 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>CeeDee Lamb (DAL)</t>
+          <t>Lamar Jackson (BAL)</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>3.09</t>
         </is>
       </c>
     </row>
@@ -6637,20 +6637,20 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Jonathan Taylor (IND)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jayden Daniels (WAS)</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>6.04</t>
         </is>
       </c>
     </row>
@@ -6660,20 +6660,20 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>James Cook III (BUF)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Drake Maye (NE)</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -6683,20 +6683,20 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>De'Von Achane (MIA)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jalen Hurts (PHI)</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>5.12</t>
         </is>
       </c>
     </row>
@@ -6706,20 +6706,20 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Kenneth Walker (KC)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Amon-Ra St. Brown (DET)</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6729,12 +6729,12 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Chase Brown (CIN)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Joe Burrow (CIN)</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -6752,20 +6752,20 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Justin Jefferson (MIN)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonathan Taylor (IND)</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6775,20 +6775,20 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>A.J. Brown (NE)</t>
+          <t>Jaxson Dart (NYG)</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -6798,20 +6798,20 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Chris Olave (NO)</t>
+          <t>Trevor Lawrence (JAX)</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -6821,20 +6821,20 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Brock Bowers (LV)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Brock Purdy (SF)</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>11.02</t>
         </is>
       </c>
     </row>
@@ -6844,20 +6844,20 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Nico Collins (HOU)</t>
+          <t>Dak Prescott (DAL)</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.07</t>
         </is>
       </c>
     </row>
@@ -6867,20 +6867,20 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Trey McBride (ARI)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Caleb Williams (CHI)</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -6890,20 +6890,20 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Garrett Wilson (NYJ)</t>
+          <t>Justin Herbert (LAC)</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -6913,20 +6913,20 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Drake London (ATL)</t>
+          <t>Bo Nix (DEN)</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>10.12</t>
         </is>
       </c>
     </row>
@@ -6936,20 +6936,20 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>George Pickens (DAL)</t>
+          <t>Matthew Stafford (LAR)</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>9.01</t>
         </is>
       </c>
     </row>
@@ -6959,20 +6959,20 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Rashee Rice (KC)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>De'Von Achane (MIA)</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6982,20 +6982,20 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Omarion Hampton (LAC)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kyler Murray (MIN)</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>14.03</t>
         </is>
       </c>
     </row>
@@ -7005,20 +7005,20 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Ashton Jeanty (LV)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jared Goff (DET)</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>12.03</t>
         </is>
       </c>
     </row>
@@ -7028,12 +7028,12 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Malik Nabers (NYG)</t>
+          <t>Tyler Shough (NO)</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>16.07</t>
         </is>
       </c>
     </row>
@@ -7051,12 +7051,12 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Saquon Barkley (PHI)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Baker Mayfield (TB)</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -7074,20 +7074,20 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Zay Flowers (BAL)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chase Brown (CIN)</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Derrick Henry (BAL)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Drake London (ATL)</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -7120,20 +7120,20 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>DeVonta Smith (PHI)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Derrick Henry (BAL)</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.08</t>
         </is>
       </c>
     </row>
@@ -7143,20 +7143,20 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Waddle (DEN)</t>
+          <t>Daniel Jones (IND)</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>17.11</t>
         </is>
       </c>
     </row>
@@ -7166,12 +7166,12 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>Jeremiyah Love (ARI)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>CeeDee Lamb (DAL)</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -7189,12 +7189,12 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Kyren Williams (LAR)</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jordan Love (GB)</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D36" s="14" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>13.05</t>
         </is>
       </c>
     </row>
@@ -7212,20 +7212,20 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Ladd McConkey (LAC)</t>
+          <t>Malik Willis (MIA)</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -7235,20 +7235,20 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Breece Hall (NYJ)</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Justin Jefferson (MIN)</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -7258,20 +7258,20 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Emeka Egbuka (TB)</t>
-        </is>
-      </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>James Cook III (BUF)</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>1.11</t>
         </is>
       </c>
     </row>
@@ -7281,20 +7281,20 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>D'Andre Swift (CHI)</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rashee Rice (KC)</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D40" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -7304,20 +7304,20 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan (CAR)</t>
+          <t>Sam Darnold (SEA)</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>14.05</t>
         </is>
       </c>
     </row>
@@ -7327,20 +7327,20 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Tee Higgins (CIN)</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Saquon Barkley (PHI)</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D42" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -7350,20 +7350,20 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Carnell Tate (TEN)</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
+          <t>Chris Olave (NO)</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>3.07</t>
         </is>
       </c>
     </row>
@@ -7373,20 +7373,20 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Javonte Williams (DAL)</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>C.J. Stroud (HOU)</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>18.01</t>
         </is>
       </c>
     </row>
@@ -7396,20 +7396,20 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Josh Allen (BUF)</t>
-        </is>
-      </c>
-      <c r="C45" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Ashton Jeanty (LV)</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -7419,20 +7419,20 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>Luther Burden III (CHI)</t>
-        </is>
-      </c>
-      <c r="C46" s="17" t="inlineStr">
+          <t>A.J. Brown (NE)</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D46" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -7442,20 +7442,20 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Christian Watson (GB)</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Trey McBride (ARI)</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -7465,20 +7465,20 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Bucky Irving (TB)</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Bryce Young (CAR)</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D48" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>19.12</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>Parker Washington (JAX)</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Omarion Hampton (LAC)</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D49" s="14" t="n">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7511,20 +7511,20 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr. (NO)</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>George Pickens (DAL)</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Cam Skattebo (NYG)</t>
+          <t>Jeremiyah Love (ARI)</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr">
@@ -7543,11 +7543,11 @@
         </is>
       </c>
       <c r="D51" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7557,20 +7557,20 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Terry McLaurin (WAS)</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="inlineStr">
+          <t>Nico Collins (HOU)</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D52" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7580,20 +7580,20 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Jameson Williams (DET)</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Breece Hall (NYJ)</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7603,20 +7603,20 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>DJ Moore (BUF)</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brock Bowers (LV)</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -7626,20 +7626,20 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten (JAX)</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Garrett Wilson (NYJ)</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -7649,20 +7649,20 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Davante Adams (LAR)</t>
-        </is>
-      </c>
-      <c r="C56" s="17" t="inlineStr">
+          <t>Zay Flowers (BAL)</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.05</t>
         </is>
       </c>
     </row>
@@ -7672,10 +7672,10 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Mike Evans (SF)</t>
-        </is>
-      </c>
-      <c r="C57" s="17" t="inlineStr">
+          <t>Malik Nabers (NYG)</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -7695,20 +7695,20 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Rome Odunze (CHI)</t>
-        </is>
-      </c>
-      <c r="C58" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Javonte Williams (DAL)</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D58" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7718,20 +7718,20 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr. (ARI)</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Travis Etienne Jr. (NO)</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D59" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>4.09</t>
         </is>
       </c>
     </row>
@@ -7741,20 +7741,20 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>DK Metcalf (PIT)</t>
-        </is>
-      </c>
-      <c r="C60" s="17" t="inlineStr">
+          <t>DeVonta Smith (PHI)</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D60" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>3.12</t>
         </is>
       </c>
     </row>
@@ -7764,20 +7764,20 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Tyler Warren (IND)</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kyren Williams (LAR)</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
@@ -7787,20 +7787,20 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Colston Loveland (CHI)</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Cam Skattebo (NYG)</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D62" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.08</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Alec Pierce (IND)</t>
+          <t>Geno Smith (NYJ)</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D63" s="14" t="n">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7833,20 +7833,20 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
+          <t>Tetairoa McMillan (CAR)</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D64" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>4.01</t>
         </is>
       </c>
     </row>
@@ -7856,20 +7856,20 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Quinshon Judkins (CLE)</t>
-        </is>
-      </c>
-      <c r="C65" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Cam Ward (TEN)</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D65" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -7879,20 +7879,20 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson (NE)</t>
-        </is>
-      </c>
-      <c r="C66" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Emeka Egbuka (TB)</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D66" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>4.03</t>
         </is>
       </c>
     </row>
@@ -7902,20 +7902,20 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>David Montgomery (HOU)</t>
-        </is>
-      </c>
-      <c r="C67" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Aaron Rodgers (PIT)</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D67" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -7925,20 +7925,20 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Lamar Jackson (BAL)</t>
-        </is>
-      </c>
-      <c r="C68" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>D'Andre Swift (CHI)</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D68" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -7948,20 +7948,20 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr. (TB)</t>
-        </is>
-      </c>
-      <c r="C69" s="17" t="inlineStr">
+          <t>Davante Adams (LAR)</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D69" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>5.02</t>
         </is>
       </c>
     </row>
@@ -7971,20 +7971,20 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Jadarian Price (SEA)</t>
-        </is>
-      </c>
-      <c r="C70" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tee Higgins (CIN)</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D70" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>3.11</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd (GB)</t>
+          <t>Bucky Irving (TB)</t>
         </is>
       </c>
       <c r="C71" s="16" t="inlineStr">
@@ -8003,11 +8003,11 @@
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>4.06</t>
         </is>
       </c>
     </row>
@@ -8017,20 +8017,20 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson (NE)</t>
-        </is>
-      </c>
-      <c r="C72" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ladd McConkey (LAC)</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.02</t>
         </is>
       </c>
     </row>
@@ -8040,20 +8040,20 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Quentin Johnston (LAC)</t>
-        </is>
-      </c>
-      <c r="C73" s="17" t="inlineStr">
+          <t>Jameson Williams (DET)</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -8063,20 +8063,20 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Michael Pittman Jr. (PIT)</t>
-        </is>
-      </c>
-      <c r="C74" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Quinshon Judkins (CLE)</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D74" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -8086,20 +8086,20 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>Rico Dowdle (PIT)</t>
-        </is>
-      </c>
-      <c r="C75" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Colston Loveland (CHI)</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>4.04</t>
         </is>
       </c>
     </row>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson (TEN)</t>
-        </is>
-      </c>
-      <c r="C76" s="17" t="inlineStr">
+          <t>Jaylen Waddle (DEN)</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D76" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -8132,20 +8132,20 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>Harold Fannin Jr. (CLE)</t>
-        </is>
-      </c>
-      <c r="C77" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Bhayshul Tuten (JAX)</t>
+        </is>
+      </c>
+      <c r="C77" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D77" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8155,20 +8155,20 @@
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Michael Wilson (ARI)</t>
-        </is>
-      </c>
-      <c r="C78" s="17" t="inlineStr">
+          <t>Terry McLaurin (WAS)</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D78" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -8178,10 +8178,10 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>Stefon Diggs (WAS)</t>
-        </is>
-      </c>
-      <c r="C79" s="17" t="inlineStr">
+          <t>DJ Moore (BUF)</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>5.09</t>
         </is>
       </c>
     </row>
@@ -8201,10 +8201,10 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Courtland Sutton (DEN)</t>
-        </is>
-      </c>
-      <c r="C80" s="17" t="inlineStr">
+          <t>Luther Burden III (CHI)</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8214,7 +8214,7 @@
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -8224,20 +8224,20 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt (WAS)</t>
-        </is>
-      </c>
-      <c r="C81" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rome Odunze (CHI)</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D81" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>6.05</t>
         </is>
       </c>
     </row>
@@ -8247,20 +8247,20 @@
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Kenny Gainwell (TB)</t>
-        </is>
-      </c>
-      <c r="C82" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tyler Warren (IND)</t>
+        </is>
+      </c>
+      <c r="C82" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D82" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>4.11</t>
         </is>
       </c>
     </row>
@@ -8270,20 +8270,20 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Warren (PIT)</t>
-        </is>
-      </c>
-      <c r="C83" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Harold Fannin Jr. (CLE)</t>
+        </is>
+      </c>
+      <c r="C83" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D83" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -8293,20 +8293,20 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Jordan Addison (MIN)</t>
-        </is>
-      </c>
-      <c r="C84" s="17" t="inlineStr">
+          <t>Courtland Sutton (DEN)</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D84" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>7.09</t>
         </is>
       </c>
     </row>
@@ -8316,12 +8316,12 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling (SF)</t>
-        </is>
-      </c>
-      <c r="C85" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>David Montgomery (HOU)</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D85" s="14" t="n">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Tucker Kraft (GB)</t>
+          <t>Christian Watson (GB)</t>
         </is>
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D86" s="14" t="n">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -8362,20 +8362,20 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>Jalen Hurts (PHI)</t>
-        </is>
-      </c>
-      <c r="C87" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Marvin Harrison Jr. (ARI)</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D87" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -8385,20 +8385,20 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Jayden Reed (GB)</t>
-        </is>
-      </c>
-      <c r="C88" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jaylen Warren (PIT)</t>
+        </is>
+      </c>
+      <c r="C88" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D88" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -8408,20 +8408,20 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>Jayden Daniels (WAS)</t>
-        </is>
-      </c>
-      <c r="C89" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Mike Evans (SF)</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D89" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8431,20 +8431,20 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Joe Burrow (CIN)</t>
-        </is>
-      </c>
-      <c r="C90" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>DK Metcalf (PIT)</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D90" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -8454,20 +8454,20 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>George Kittle (SF)</t>
+          <t>Alec Pierce (IND)</t>
         </is>
       </c>
       <c r="C91" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>9.05</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>Chuba Hubbard (CAR)</t>
+          <t>TreVeyon Henderson (NE)</t>
         </is>
       </c>
       <c r="C92" s="16" t="inlineStr">
@@ -8486,11 +8486,11 @@
         </is>
       </c>
       <c r="D92" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>J.K. Dobbins (DEN)</t>
+          <t>Rhamondre Stevenson (NE)</t>
         </is>
       </c>
       <c r="C93" s="16" t="inlineStr">
@@ -8509,11 +8509,11 @@
         </is>
       </c>
       <c r="D93" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -8523,12 +8523,12 @@
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>Tony Pollard (TEN)</t>
-        </is>
-      </c>
-      <c r="C94" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Michael Pittman Jr. (PIT)</t>
+        </is>
+      </c>
+      <c r="C94" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D94" s="14" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>9.07</t>
         </is>
       </c>
     </row>
@@ -8546,20 +8546,20 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>Josh Downs (IND)</t>
-        </is>
-      </c>
-      <c r="C95" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kyle Pitts Sr. (ATL)</t>
+        </is>
+      </c>
+      <c r="C95" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D95" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>6.1</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Jonathon Brooks (CAR)</t>
+          <t>Tony Pollard (TEN)</t>
         </is>
       </c>
       <c r="C96" s="16" t="inlineStr">
@@ -8578,11 +8578,11 @@
         </is>
       </c>
       <c r="D96" s="14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.12</t>
         </is>
       </c>
     </row>
@@ -8592,20 +8592,20 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>Jakobi Meyers (JAX)</t>
-        </is>
-      </c>
-      <c r="C97" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jadarian Price (SEA)</t>
+        </is>
+      </c>
+      <c r="C97" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -8615,20 +8615,20 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>Romeo Doubs (NE)</t>
-        </is>
-      </c>
-      <c r="C98" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>George Kittle (SF)</t>
+        </is>
+      </c>
+      <c r="C98" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D98" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -8638,20 +8638,20 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>Sam LaPorta (DET)</t>
+          <t>Parker Washington (JAX)</t>
         </is>
       </c>
       <c r="C99" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>7.04</t>
         </is>
       </c>
     </row>
@@ -8661,20 +8661,20 @@
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>Khalil Shakir (BUF)</t>
-        </is>
-      </c>
-      <c r="C100" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Sam LaPorta (DET)</t>
+        </is>
+      </c>
+      <c r="C100" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D100" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -8684,20 +8684,20 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>Kyle Monangai (CHI)</t>
-        </is>
-      </c>
-      <c r="C101" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Travis Kelce (KC)</t>
+        </is>
+      </c>
+      <c r="C101" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>8.08</t>
         </is>
       </c>
     </row>
@@ -8707,20 +8707,20 @@
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Makai Lemon (PHI)</t>
-        </is>
-      </c>
-      <c r="C102" s="17" t="inlineStr">
+          <t>Brian Thomas Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D102" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>7.02</t>
         </is>
       </c>
     </row>
@@ -8730,20 +8730,20 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>Xavier Worthy (KC)</t>
-        </is>
-      </c>
-      <c r="C103" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rico Dowdle (PIT)</t>
+        </is>
+      </c>
+      <c r="C103" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>8.01</t>
         </is>
       </c>
     </row>
@@ -8753,20 +8753,20 @@
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>Malik Washington (MIA)</t>
-        </is>
-      </c>
-      <c r="C104" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dallas Goedert (PHI)</t>
+        </is>
+      </c>
+      <c r="C104" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D104" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -8776,20 +8776,20 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>Jordan Mason (MIN)</t>
-        </is>
-      </c>
-      <c r="C105" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Wan'Dale Robinson (TEN)</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>10.09</t>
         </is>
       </c>
     </row>
@@ -8799,20 +8799,20 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>Jalen Coker (CAR)</t>
-        </is>
-      </c>
-      <c r="C106" s="17" t="inlineStr">
+          <t>Jakobi Meyers (JAX)</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D106" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>10.1</t>
         </is>
       </c>
     </row>
@@ -8822,20 +8822,20 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Rashid Shaheed (SEA)</t>
-        </is>
-      </c>
-      <c r="C107" s="17" t="inlineStr">
+          <t>Carnell Tate (TEN)</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -8845,20 +8845,20 @@
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>KC Concepcion (CLE)</t>
-        </is>
-      </c>
-      <c r="C108" s="17" t="inlineStr">
+          <t>Michael Wilson (ARI)</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D108" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>7.11</t>
         </is>
       </c>
     </row>
@@ -8868,20 +8868,20 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>Kayshon Boutte (HOU)</t>
-        </is>
-      </c>
-      <c r="C109" s="17" t="inlineStr">
+          <t>Jayden Reed (GB)</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8891,20 +8891,20 @@
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>Drake Maye (NE)</t>
-        </is>
-      </c>
-      <c r="C110" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>J.K. Dobbins (DEN)</t>
+        </is>
+      </c>
+      <c r="C110" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D110" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>8.1</t>
         </is>
       </c>
     </row>
@@ -8914,20 +8914,20 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>Rachaad White (WAS)</t>
-        </is>
-      </c>
-      <c r="C111" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Chris Godwin Jr. (TB)</t>
+        </is>
+      </c>
+      <c r="C111" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>8.12</t>
         </is>
       </c>
     </row>
@@ -8937,20 +8937,20 @@
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Matthew Golden (GB)</t>
-        </is>
-      </c>
-      <c r="C112" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chuba Hubbard (CAR)</t>
+        </is>
+      </c>
+      <c r="C112" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D112" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>7.05</t>
         </is>
       </c>
     </row>
@@ -8960,20 +8960,20 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>Jaxson Dart (NYG)</t>
+          <t>Tucker Kraft (GB)</t>
         </is>
       </c>
       <c r="C113" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8983,20 +8983,20 @@
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Kyle Pitts Sr. (ATL)</t>
-        </is>
-      </c>
-      <c r="C114" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kenny Gainwell (TB)</t>
+        </is>
+      </c>
+      <c r="C114" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D114" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -9006,20 +9006,20 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>Keenan Allen (IND)</t>
-        </is>
-      </c>
-      <c r="C115" s="17" t="inlineStr">
+          <t>Quentin Johnston (LAC)</t>
+        </is>
+      </c>
+      <c r="C115" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>10.05</t>
         </is>
       </c>
     </row>
@@ -9029,20 +9029,20 @@
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>Caleb Williams (CHI)</t>
-        </is>
-      </c>
-      <c r="C116" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Stefon Diggs (WAS)</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D116" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>10.02</t>
         </is>
       </c>
     </row>
@@ -9052,20 +9052,20 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>Trevor Lawrence (JAX)</t>
-        </is>
-      </c>
-      <c r="C117" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jordan Addison (MIN)</t>
+        </is>
+      </c>
+      <c r="C117" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>9.09</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>Blake Corum (LAR)</t>
+          <t>Jonathon Brooks (CAR)</t>
         </is>
       </c>
       <c r="C118" s="16" t="inlineStr">
@@ -9084,11 +9084,11 @@
         </is>
       </c>
       <c r="D118" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>9.1</t>
         </is>
       </c>
     </row>
@@ -9098,20 +9098,20 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>RJ Harvey (DEN)</t>
-        </is>
-      </c>
-      <c r="C119" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Xavier Worthy (KC)</t>
+        </is>
+      </c>
+      <c r="C119" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Juwan Johnson (NO)</t>
-        </is>
-      </c>
-      <c r="C120" s="18" t="inlineStr">
+          <t>Jake Ferguson (DAL)</t>
+        </is>
+      </c>
+      <c r="C120" s="19" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D120" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>9.02</t>
         </is>
       </c>
     </row>
@@ -9144,20 +9144,20 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>Jordyn Tyson (NO)</t>
-        </is>
-      </c>
-      <c r="C121" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Mark Andrews (BAL)</t>
+        </is>
+      </c>
+      <c r="C121" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D121" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>11.09</t>
         </is>
       </c>
     </row>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>Dalton Schultz (HOU)</t>
+          <t>De'Zhaun Stribling (SF)</t>
         </is>
       </c>
       <c r="C122" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>12.07</t>
         </is>
       </c>
     </row>
@@ -9190,20 +9190,20 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>Travis Kelce (KC)</t>
+          <t>Matthew Golden (GB)</t>
         </is>
       </c>
       <c r="C123" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>11.07</t>
         </is>
       </c>
     </row>
@@ -9213,20 +9213,20 @@
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>Tre Tucker (LV)</t>
-        </is>
-      </c>
-      <c r="C124" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Isaiah Likely (NYG)</t>
+        </is>
+      </c>
+      <c r="C124" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D124" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -9236,20 +9236,20 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr. (MIN)</t>
-        </is>
-      </c>
-      <c r="C125" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Khalil Shakir (BUF)</t>
+        </is>
+      </c>
+      <c r="C125" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>12.11</t>
         </is>
       </c>
     </row>
@@ -9259,20 +9259,20 @@
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>Jake Ferguson (DAL)</t>
+          <t>KC Concepcion (CLE)</t>
         </is>
       </c>
       <c r="C126" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>11.01</t>
         </is>
       </c>
     </row>
@@ -9282,20 +9282,20 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>Dak Prescott (DAL)</t>
-        </is>
-      </c>
-      <c r="C127" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Josh Downs (IND)</t>
+        </is>
+      </c>
+      <c r="C127" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>10.01</t>
         </is>
       </c>
     </row>
@@ -9305,20 +9305,20 @@
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>Dalton Kincaid (BUF)</t>
+          <t>Romeo Doubs (NE)</t>
         </is>
       </c>
       <c r="C128" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D128" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -9328,12 +9328,12 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>Isaiah Likely (NYG)</t>
+          <t>Deebo Samuel Sr. (SF)</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D129" s="14" t="n">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>11.11</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>Tyjae Spears (TEN)</t>
+          <t>RJ Harvey (DEN)</t>
         </is>
       </c>
       <c r="C130" s="16" t="inlineStr">
@@ -9360,11 +9360,11 @@
         </is>
       </c>
       <c r="D130" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>7.08</t>
         </is>
       </c>
     </row>
@@ -9374,20 +9374,20 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>Justin Herbert (LAC)</t>
-        </is>
-      </c>
-      <c r="C131" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Aaron Jones Sr. (MIN)</t>
+        </is>
+      </c>
+      <c r="C131" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -9397,20 +9397,20 @@
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>Dallas Goedert (PHI)</t>
-        </is>
-      </c>
-      <c r="C132" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Rachaad White (WAS)</t>
+        </is>
+      </c>
+      <c r="C132" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D132" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -9420,20 +9420,20 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>Bo Nix (DEN)</t>
+          <t>Dalton Kincaid (BUF)</t>
         </is>
       </c>
       <c r="C133" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D133" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -9443,20 +9443,20 @@
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Brock Purdy (SF)</t>
-        </is>
-      </c>
-      <c r="C134" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jalen Coker (CAR)</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D134" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>13.02</t>
         </is>
       </c>
     </row>
@@ -9466,20 +9466,20 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>Omar Cooper Jr. (NYJ)</t>
-        </is>
-      </c>
-      <c r="C135" s="17" t="inlineStr">
+          <t>Rashid Shaheed (SEA)</t>
+        </is>
+      </c>
+      <c r="C135" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>13.03</t>
         </is>
       </c>
     </row>
@@ -9489,20 +9489,20 @@
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>Jared Goff (DET)</t>
-        </is>
-      </c>
-      <c r="C136" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>MarShawn Lloyd (GB)</t>
+        </is>
+      </c>
+      <c r="C136" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D136" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>15.06</t>
         </is>
       </c>
     </row>
@@ -9512,20 +9512,20 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>Deebo Samuel Sr. (SF)</t>
-        </is>
-      </c>
-      <c r="C137" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kyle Monangai (CHI)</t>
+        </is>
+      </c>
+      <c r="C137" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -9535,12 +9535,12 @@
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>Tyler Shough (NO)</t>
+          <t>Juwan Johnson (NO)</t>
         </is>
       </c>
       <c r="C138" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>Matthew Stafford (LAR)</t>
-        </is>
-      </c>
-      <c r="C139" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jerry Jeudy (CLE)</t>
+        </is>
+      </c>
+      <c r="C139" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -9581,20 +9581,20 @@
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>Kyler Murray (MIN)</t>
+          <t>Hunter Henry (NE)</t>
         </is>
       </c>
       <c r="C140" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D140" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -9604,20 +9604,20 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>Jordan Love (GB)</t>
+          <t>Brenton Strange (JAX)</t>
         </is>
       </c>
       <c r="C141" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>13.08</t>
         </is>
       </c>
     </row>
@@ -9627,20 +9627,20 @@
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>Baker Mayfield (TB)</t>
-        </is>
-      </c>
-      <c r="C142" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Denzel Boston (CLE)</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9650,20 +9650,20 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>Denzel Boston (CLE)</t>
-        </is>
-      </c>
-      <c r="C143" s="17" t="inlineStr">
+          <t>Makai Lemon (PHI)</t>
+        </is>
+      </c>
+      <c r="C143" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -9673,20 +9673,20 @@
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>Patrick Mahomes (KC)</t>
+          <t>Dalton Schultz (HOU)</t>
         </is>
       </c>
       <c r="C144" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>17.01</t>
         </is>
       </c>
     </row>
@@ -9696,20 +9696,20 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>Brenton Strange (JAX)</t>
+          <t>Calvin Ridley (TEN)</t>
         </is>
       </c>
       <c r="C145" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>22.01</t>
         </is>
       </c>
     </row>
@@ -9719,20 +9719,20 @@
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks (PHI)</t>
-        </is>
-      </c>
-      <c r="C146" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jacory Croskey-Merritt (WAS)</t>
+        </is>
+      </c>
+      <c r="C146" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10.06</t>
         </is>
       </c>
     </row>
@@ -9742,20 +9742,20 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Mark Andrews (BAL)</t>
-        </is>
-      </c>
-      <c r="C147" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jordan Mason (MIN)</t>
+        </is>
+      </c>
+      <c r="C147" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>10.07</t>
         </is>
       </c>
     </row>
@@ -9765,20 +9765,20 @@
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>Pat Bryant (DEN)</t>
-        </is>
-      </c>
-      <c r="C148" s="17" t="inlineStr">
+          <t>Tre Tucker (LV)</t>
+        </is>
+      </c>
+      <c r="C148" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>17.1</t>
         </is>
       </c>
     </row>
@@ -9788,20 +9788,20 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>Malik Willis (MIA)</t>
-        </is>
-      </c>
-      <c r="C149" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Keenan Allen (IND)</t>
+        </is>
+      </c>
+      <c r="C149" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>17.07</t>
         </is>
       </c>
     </row>
@@ -9811,20 +9811,20 @@
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>Jalen Nailor (LV)</t>
-        </is>
-      </c>
-      <c r="C150" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>T.J. Hockenson (MIN)</t>
+        </is>
+      </c>
+      <c r="C150" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Woody Marks (HOU)</t>
+          <t>Blake Corum (LAR)</t>
         </is>
       </c>
       <c r="C151" s="16" t="inlineStr">
@@ -9843,11 +9843,11 @@
         </is>
       </c>
       <c r="D151" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>9.08</t>
         </is>
       </c>
     </row>
@@ -9857,20 +9857,20 @@
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Hunter Henry (NE)</t>
-        </is>
-      </c>
-      <c r="C152" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tyjae Spears (TEN)</t>
+        </is>
+      </c>
+      <c r="C152" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -9880,20 +9880,20 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>Chig Okonkwo (WAS)</t>
+          <t>Kayshon Boutte (HOU)</t>
         </is>
       </c>
       <c r="C153" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>19.08</t>
         </is>
       </c>
     </row>
@@ -9903,20 +9903,20 @@
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>Chris Rodriguez Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C154" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rashod Bateman (BAL)</t>
+        </is>
+      </c>
+      <c r="C154" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>20.05</t>
         </is>
       </c>
     </row>
@@ -9926,20 +9926,20 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>Travis Hunter (JAX)</t>
-        </is>
-      </c>
-      <c r="C155" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Pat Freiermuth (PIT)</t>
+        </is>
+      </c>
+      <c r="C155" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -9949,20 +9949,20 @@
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Cooper Kupp (SEA)</t>
-        </is>
-      </c>
-      <c r="C156" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Greg Dulcich (MIA)</t>
+        </is>
+      </c>
+      <c r="C156" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -9972,20 +9972,20 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Jerry Jeudy (CLE)</t>
-        </is>
-      </c>
-      <c r="C157" s="17" t="inlineStr">
+          <t>Ja'Kobi Lane (BAL)</t>
+        </is>
+      </c>
+      <c r="C157" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D157" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E157" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>14.02</t>
         </is>
       </c>
     </row>
@@ -9995,20 +9995,20 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Cam Ward (TEN)</t>
+          <t>Cade Otton (TB)</t>
         </is>
       </c>
       <c r="C158" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.06</t>
         </is>
       </c>
     </row>
@@ -10018,16 +10018,16 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Isiah Pacheco (DET)</t>
-        </is>
-      </c>
-      <c r="C159" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jalen Nailor (LV)</t>
+        </is>
+      </c>
+      <c r="C159" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E159" s="14" t="inlineStr">
         <is>
@@ -10041,12 +10041,12 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>C.J. Stroud (HOU)</t>
-        </is>
-      </c>
-      <c r="C160" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Devaughn Vele (NO)</t>
+        </is>
+      </c>
+      <c r="C160" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10064,20 +10064,20 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>DeMario Douglas (NE)</t>
-        </is>
-      </c>
-      <c r="C161" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chig Okonkwo (WAS)</t>
+        </is>
+      </c>
+      <c r="C161" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E161" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -10087,12 +10087,12 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Malachi Fields (NYG)</t>
-        </is>
-      </c>
-      <c r="C162" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Woody Marks (HOU)</t>
+        </is>
+      </c>
+      <c r="C162" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D162" s="14" t="n">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>14.04</t>
         </is>
       </c>
     </row>
@@ -10110,12 +10110,12 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>Sam Darnold (SEA)</t>
-        </is>
-      </c>
-      <c r="C163" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Cooper Kupp (SEA)</t>
+        </is>
+      </c>
+      <c r="C163" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="E163" s="14" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>19.05</t>
         </is>
       </c>
     </row>
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Keaton Mitchell (LAC)</t>
-        </is>
-      </c>
-      <c r="C164" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kenyon Sadiq (NYJ)</t>
+        </is>
+      </c>
+      <c r="C164" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>13.1</t>
         </is>
       </c>
     </row>
@@ -10156,20 +10156,20 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>Adonai Mitchell (NYJ)</t>
-        </is>
-      </c>
-      <c r="C165" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>AJ Barner (SEA)</t>
+        </is>
+      </c>
+      <c r="C165" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E165" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10179,20 +10179,20 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane (BAL)</t>
-        </is>
-      </c>
-      <c r="C166" s="17" t="inlineStr">
+          <t>Jaylin Noel (HOU)</t>
+        </is>
+      </c>
+      <c r="C166" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>18.1</t>
         </is>
       </c>
     </row>
@@ -10202,20 +10202,20 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>Daniel Jones (IND)</t>
-        </is>
-      </c>
-      <c r="C167" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Zach Charbonnet (SEA)</t>
+        </is>
+      </c>
+      <c r="C167" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E167" s="14" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>13.04</t>
         </is>
       </c>
     </row>
@@ -10225,12 +10225,12 @@
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>Tank Dell (HOU)</t>
-        </is>
-      </c>
-      <c r="C168" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Alvin Kamara (NO)</t>
+        </is>
+      </c>
+      <c r="C168" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>14.07</t>
         </is>
       </c>
     </row>
@@ -10248,20 +10248,20 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>Germie Bernard (PIT)</t>
-        </is>
-      </c>
-      <c r="C169" s="17" t="inlineStr">
+          <t>Adonai Mitchell (NYJ)</t>
+        </is>
+      </c>
+      <c r="C169" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E169" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Zach Charbonnet (SEA)</t>
+          <t>Isiah Pacheco (DET)</t>
         </is>
       </c>
       <c r="C170" s="16" t="inlineStr">
@@ -10280,11 +10280,11 @@
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -10294,16 +10294,16 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>Cyrus Allen (KC)</t>
-        </is>
-      </c>
-      <c r="C171" s="17" t="inlineStr">
+          <t>Malik Washington (MIA)</t>
+        </is>
+      </c>
+      <c r="C171" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Tyler Allgeier (ARI)</t>
+          <t>Dylan Sampson (CLE)</t>
         </is>
       </c>
       <c r="C172" s="16" t="inlineStr">
@@ -10326,11 +10326,11 @@
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -10340,20 +10340,20 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>Dylan Sampson (CLE)</t>
-        </is>
-      </c>
-      <c r="C173" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Germie Bernard (PIT)</t>
+        </is>
+      </c>
+      <c r="C173" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10363,20 +10363,20 @@
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Kyle Williams (NE)</t>
-        </is>
-      </c>
-      <c r="C174" s="17" t="inlineStr">
+          <t>Jordyn Tyson (NO)</t>
+        </is>
+      </c>
+      <c r="C174" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>8.07</t>
         </is>
       </c>
     </row>
@@ -10386,20 +10386,20 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>Calvin Ridley (TEN)</t>
-        </is>
-      </c>
-      <c r="C175" s="17" t="inlineStr">
+          <t>Dontayvion Wicks (PHI)</t>
+        </is>
+      </c>
+      <c r="C175" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E175" s="14" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10409,12 +10409,12 @@
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>T.J. Hockenson (MIN)</t>
+          <t>Caleb Douglas (MIA)</t>
         </is>
       </c>
       <c r="C176" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D176" s="14" t="n">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>18.09</t>
         </is>
       </c>
     </row>
@@ -10432,12 +10432,12 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Mike Washington Jr. (LV)</t>
-        </is>
-      </c>
-      <c r="C177" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Omar Cooper Jr. (NYJ)</t>
+        </is>
+      </c>
+      <c r="C177" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="E177" s="14" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>17.02</t>
         </is>
       </c>
     </row>
@@ -10455,20 +10455,20 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Greg Dulcich (MIA)</t>
+          <t>Travis Hunter (JAX)</t>
         </is>
       </c>
       <c r="C178" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10478,12 +10478,12 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq (NYJ)</t>
-        </is>
-      </c>
-      <c r="C179" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Mike Washington Jr. (LV)</t>
+        </is>
+      </c>
+      <c r="C179" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="E179" s="14" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>15.05</t>
         </is>
       </c>
     </row>
@@ -10501,20 +10501,20 @@
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Jonah Coleman (DEN)</t>
-        </is>
-      </c>
-      <c r="C180" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Darius Slayton (NYG)</t>
+        </is>
+      </c>
+      <c r="C180" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10524,12 +10524,12 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>Tre' Harris (LAC)</t>
-        </is>
-      </c>
-      <c r="C181" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chris Rodriguez Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C181" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>12.08</t>
         </is>
       </c>
     </row>
@@ -10547,20 +10547,20 @@
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Keon Coleman (BUF)</t>
-        </is>
-      </c>
-      <c r="C182" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyler Allgeier (ARI)</t>
+        </is>
+      </c>
+      <c r="C182" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D182" s="14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -10570,20 +10570,20 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr. (NYG)</t>
-        </is>
-      </c>
-      <c r="C183" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tory Horton (SEA)</t>
+        </is>
+      </c>
+      <c r="C183" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D183" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E183" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10593,20 +10593,20 @@
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>Pat Freiermuth (PIT)</t>
+          <t>Tre' Harris (LAC)</t>
         </is>
       </c>
       <c r="C184" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D184" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10616,20 +10616,20 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Aaron Rodgers (PIT)</t>
-        </is>
-      </c>
-      <c r="C185" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jalen Tolbert (MIA)</t>
+        </is>
+      </c>
+      <c r="C185" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E185" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10639,20 +10639,20 @@
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Bryce Young (CAR)</t>
-        </is>
-      </c>
-      <c r="C186" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Ryan Flournoy (DAL)</t>
+        </is>
+      </c>
+      <c r="C186" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D186" s="14" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10662,20 +10662,20 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>Zachariah Branch (ATL)</t>
-        </is>
-      </c>
-      <c r="C187" s="17" t="inlineStr">
+          <t>Malachi Fields (NYG)</t>
+        </is>
+      </c>
+      <c r="C187" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D187" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E187" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>19.04</t>
         </is>
       </c>
     </row>
@@ -10685,20 +10685,20 @@
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Ryan Flournoy (DAL)</t>
-        </is>
-      </c>
-      <c r="C188" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Keaton Mitchell (LAC)</t>
+        </is>
+      </c>
+      <c r="C188" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D188" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10708,20 +10708,20 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Cade Otton (TB)</t>
-        </is>
-      </c>
-      <c r="C189" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tyrone Tracy Jr. (NYG)</t>
+        </is>
+      </c>
+      <c r="C189" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E189" s="14" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10754,20 +10754,20 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>Alvin Kamara (NO)</t>
-        </is>
-      </c>
-      <c r="C191" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DeMario Douglas (NE)</t>
+        </is>
+      </c>
+      <c r="C191" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E191" s="14" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10777,20 +10777,20 @@
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Caleb Douglas (MIA)</t>
-        </is>
-      </c>
-      <c r="C192" s="17" t="inlineStr">
+          <t>Zachariah Branch (ATL)</t>
+        </is>
+      </c>
+      <c r="C192" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D192" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -10800,20 +10800,20 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Geno Smith (NYJ)</t>
-        </is>
-      </c>
-      <c r="C193" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Keon Coleman (BUF)</t>
+        </is>
+      </c>
+      <c r="C193" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.07</t>
         </is>
       </c>
     </row>
@@ -10846,20 +10846,20 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Brian Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C195" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Pat Bryant (DEN)</t>
+        </is>
+      </c>
+      <c r="C195" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E195" s="14" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>19.11</t>
         </is>
       </c>
     </row>
@@ -10869,10 +10869,10 @@
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>Devaughn Vele (NO)</t>
-        </is>
-      </c>
-      <c r="C196" s="17" t="inlineStr">
+          <t>Tank Dell (HOU)</t>
+        </is>
+      </c>
+      <c r="C196" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="E196" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10892,20 +10892,20 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>AJ Barner (SEA)</t>
+          <t>Cyrus Allen (KC)</t>
         </is>
       </c>
       <c r="C197" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D197" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E197" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -10915,20 +10915,20 @@
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Jaylin Noel (HOU)</t>
-        </is>
-      </c>
-      <c r="C198" s="17" t="inlineStr">
+          <t>Kyle Williams (NE)</t>
+        </is>
+      </c>
+      <c r="C198" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D198" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>19.06</t>
         </is>
       </c>
     </row>
@@ -10938,20 +10938,20 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>Darius Slayton (NYG)</t>
-        </is>
-      </c>
-      <c r="C199" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonah Coleman (DEN)</t>
+        </is>
+      </c>
+      <c r="C199" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E199" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.03</t>
         </is>
       </c>
     </row>
@@ -10961,20 +10961,20 @@
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Oronde Gadsden (LAC)</t>
-        </is>
-      </c>
-      <c r="C200" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kenneth Walker (KC)</t>
+        </is>
+      </c>
+      <c r="C200" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D200" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -10984,20 +10984,20 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>Rashod Bateman (BAL)</t>
+          <t>Patrick Mahomes (KC)</t>
         </is>
       </c>
       <c r="C201" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D201" s="14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -11007,20 +11007,20 @@
       </c>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>Jalen Tolbert (MIA)</t>
-        </is>
-      </c>
-      <c r="C202" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brian Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C202" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D202" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E202" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.12</t>
         </is>
       </c>
     </row>
@@ -11030,20 +11030,20 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>Tory Horton (SEA)</t>
-        </is>
-      </c>
-      <c r="C203" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Oronde Gadsden (LAC)</t>
+        </is>
+      </c>
+      <c r="C203" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D203" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>

--- a/assets/data/12guys1cup-cheat-sheet.xlsx
+++ b/assets/data/12guys1cup-cheat-sheet.xlsx
@@ -62,12 +62,6 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00B8386B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="001565C0"/>
       <sz val="10"/>
     </font>
@@ -75,6 +69,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00E65100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00B8386B"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -125,17 +125,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D4E4F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -6476,20 +6476,20 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Josh Allen (BUF)</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Bijan Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.03</t>
         </is>
       </c>
     </row>
@@ -6499,20 +6499,20 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Bijan Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ja'Marr Chase (CIN)</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>
@@ -6525,7 +6525,7 @@
           <t>Puka Nacua (LAR)</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6545,20 +6545,20 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase (CIN)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Christian McCaffrey (SF)</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
     </row>
@@ -6568,20 +6568,20 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Christian McCaffrey (SF)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jaxon Smith-Njigba (SEA)</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6591,20 +6591,20 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba (SEA)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
+          <t>Amon-Ra St. Brown (DET)</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6614,20 +6614,20 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Lamar Jackson (BAL)</t>
+          <t>CeeDee Lamb (DAL)</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6637,20 +6637,20 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Jayden Daniels (WAS)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jonathan Taylor (IND)</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6660,20 +6660,20 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Drake Maye (NE)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>James Cook III (BUF)</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>1.11</t>
         </is>
       </c>
     </row>
@@ -6683,20 +6683,20 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Jalen Hurts (PHI)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>De'Von Achane (MIA)</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6706,20 +6706,20 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown (DET)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kenneth Walker (KC)</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -6729,12 +6729,12 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Joe Burrow (CIN)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Chase Brown (CIN)</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -6752,20 +6752,20 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Jonathan Taylor (IND)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Justin Jefferson (MIN)</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6775,20 +6775,20 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Jaxson Dart (NYG)</t>
+          <t>A.J. Brown (NE)</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -6798,20 +6798,20 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Trevor Lawrence (JAX)</t>
+          <t>Chris Olave (NO)</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>3.07</t>
         </is>
       </c>
     </row>
@@ -6821,20 +6821,20 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Brock Purdy (SF)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Brock Bowers (LV)</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -6844,20 +6844,20 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Dak Prescott (DAL)</t>
+          <t>Nico Collins (HOU)</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -6867,20 +6867,20 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Caleb Williams (CHI)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Trey McBride (ARI)</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -6890,20 +6890,20 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Justin Herbert (LAC)</t>
+          <t>Garrett Wilson (NYJ)</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -6913,20 +6913,20 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Bo Nix (DEN)</t>
+          <t>Drake London (ATL)</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -6936,20 +6936,20 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Matthew Stafford (LAR)</t>
+          <t>George Pickens (DAL)</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -6959,20 +6959,20 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>De'Von Achane (MIA)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rashee Rice (KC)</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -6982,20 +6982,20 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Kyler Murray (MIN)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Omarion Hampton (LAC)</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7005,20 +7005,20 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Jared Goff (DET)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Ashton Jeanty (LV)</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -7028,12 +7028,12 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Tyler Shough (NO)</t>
+          <t>Malik Nabers (NYG)</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -7051,12 +7051,12 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Baker Mayfield (TB)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Saquon Barkley (PHI)</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -7074,20 +7074,20 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Chase Brown (CIN)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Zay Flowers (BAL)</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>4.05</t>
         </is>
       </c>
     </row>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Drake London (ATL)</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Derrick Henry (BAL)</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.08</t>
         </is>
       </c>
     </row>
@@ -7120,20 +7120,20 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Derrick Henry (BAL)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DeVonta Smith (PHI)</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.12</t>
         </is>
       </c>
     </row>
@@ -7143,20 +7143,20 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Daniel Jones (IND)</t>
+          <t>Jaylen Waddle (DEN)</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -7166,12 +7166,12 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>CeeDee Lamb (DAL)</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jeremiyah Love (ARI)</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7189,12 +7189,12 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Jordan Love (GB)</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Kyren Williams (LAR)</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D36" s="14" t="n">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
@@ -7212,20 +7212,20 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Malik Willis (MIA)</t>
+          <t>Ladd McConkey (LAC)</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>4.02</t>
         </is>
       </c>
     </row>
@@ -7235,20 +7235,20 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Justin Jefferson (MIN)</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Breece Hall (NYJ)</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7258,20 +7258,20 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>James Cook III (BUF)</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Emeka Egbuka (TB)</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>4.03</t>
         </is>
       </c>
     </row>
@@ -7281,20 +7281,20 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>Rashee Rice (KC)</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>D'Andre Swift (CHI)</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D40" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -7304,20 +7304,20 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Sam Darnold (SEA)</t>
+          <t>Tetairoa McMillan (CAR)</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>4.01</t>
         </is>
       </c>
     </row>
@@ -7327,20 +7327,20 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Saquon Barkley (PHI)</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tee Higgins (CIN)</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D42" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>3.11</t>
         </is>
       </c>
     </row>
@@ -7350,20 +7350,20 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Chris Olave (NO)</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
+          <t>Carnell Tate (TEN)</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -7373,20 +7373,20 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>C.J. Stroud (HOU)</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Javonte Williams (DAL)</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7396,20 +7396,20 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Ashton Jeanty (LV)</t>
-        </is>
-      </c>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Josh Allen (BUF)</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.09</t>
         </is>
       </c>
     </row>
@@ -7419,20 +7419,20 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>A.J. Brown (NE)</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="inlineStr">
+          <t>Luther Burden III (CHI)</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D46" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -7442,20 +7442,20 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Trey McBride (ARI)</t>
-        </is>
-      </c>
-      <c r="C47" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Christian Watson (GB)</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -7465,20 +7465,20 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Bryce Young (CAR)</t>
-        </is>
-      </c>
-      <c r="C48" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Bucky Irving (TB)</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D48" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>4.06</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>Omarion Hampton (LAC)</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Parker Washington (JAX)</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D49" s="14" t="n">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>7.04</t>
         </is>
       </c>
     </row>
@@ -7511,20 +7511,20 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>George Pickens (DAL)</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Travis Etienne Jr. (NO)</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>4.09</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Jeremiyah Love (ARI)</t>
+          <t>Cam Skattebo (NYG)</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr">
@@ -7543,11 +7543,11 @@
         </is>
       </c>
       <c r="D51" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.08</t>
         </is>
       </c>
     </row>
@@ -7557,20 +7557,20 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Nico Collins (HOU)</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="inlineStr">
+          <t>Terry McLaurin (WAS)</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D52" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -7580,20 +7580,20 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Breece Hall (NYJ)</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jameson Williams (DET)</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -7603,20 +7603,20 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>Brock Bowers (LV)</t>
-        </is>
-      </c>
-      <c r="C54" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>DJ Moore (BUF)</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>5.09</t>
         </is>
       </c>
     </row>
@@ -7626,20 +7626,20 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Garrett Wilson (NYJ)</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Bhayshul Tuten (JAX)</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -7649,20 +7649,20 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Zay Flowers (BAL)</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="inlineStr">
+          <t>Davante Adams (LAR)</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>5.02</t>
         </is>
       </c>
     </row>
@@ -7672,10 +7672,10 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Malik Nabers (NYG)</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="inlineStr">
+          <t>Mike Evans (SF)</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -7695,20 +7695,20 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Javonte Williams (DAL)</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rome Odunze (CHI)</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D58" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>6.05</t>
         </is>
       </c>
     </row>
@@ -7718,20 +7718,20 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr. (NO)</t>
-        </is>
-      </c>
-      <c r="C59" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Marvin Harrison Jr. (ARI)</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D59" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -7741,20 +7741,20 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>DeVonta Smith (PHI)</t>
-        </is>
-      </c>
-      <c r="C60" s="18" t="inlineStr">
+          <t>DK Metcalf (PIT)</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D60" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -7764,20 +7764,20 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Kyren Williams (LAR)</t>
-        </is>
-      </c>
-      <c r="C61" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tyler Warren (IND)</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>4.11</t>
         </is>
       </c>
     </row>
@@ -7787,20 +7787,20 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Cam Skattebo (NYG)</t>
-        </is>
-      </c>
-      <c r="C62" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Colston Loveland (CHI)</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D62" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.04</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Geno Smith (NYJ)</t>
+          <t>Alec Pierce (IND)</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D63" s="14" t="n">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.05</t>
         </is>
       </c>
     </row>
@@ -7833,20 +7833,20 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan (CAR)</t>
-        </is>
-      </c>
-      <c r="C64" s="18" t="inlineStr">
+          <t>Brian Thomas Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D64" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>7.02</t>
         </is>
       </c>
     </row>
@@ -7856,20 +7856,20 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Cam Ward (TEN)</t>
-        </is>
-      </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Quinshon Judkins (CLE)</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D65" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -7879,20 +7879,20 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>Emeka Egbuka (TB)</t>
-        </is>
-      </c>
-      <c r="C66" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>TreVeyon Henderson (NE)</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D66" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -7902,20 +7902,20 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>Aaron Rodgers (PIT)</t>
-        </is>
-      </c>
-      <c r="C67" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>David Montgomery (HOU)</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D67" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -7925,20 +7925,20 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>D'Andre Swift (CHI)</t>
-        </is>
-      </c>
-      <c r="C68" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Lamar Jackson (BAL)</t>
+        </is>
+      </c>
+      <c r="C68" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D68" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>3.09</t>
         </is>
       </c>
     </row>
@@ -7948,20 +7948,20 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Davante Adams (LAR)</t>
-        </is>
-      </c>
-      <c r="C69" s="18" t="inlineStr">
+          <t>Chris Godwin Jr. (TB)</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D69" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>8.12</t>
         </is>
       </c>
     </row>
@@ -7971,20 +7971,20 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Tee Higgins (CIN)</t>
-        </is>
-      </c>
-      <c r="C70" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jadarian Price (SEA)</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D70" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>Bucky Irving (TB)</t>
+          <t>MarShawn Lloyd (GB)</t>
         </is>
       </c>
       <c r="C71" s="16" t="inlineStr">
@@ -8003,11 +8003,11 @@
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>15.06</t>
         </is>
       </c>
     </row>
@@ -8017,20 +8017,20 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Ladd McConkey (LAC)</t>
-        </is>
-      </c>
-      <c r="C72" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rhamondre Stevenson (NE)</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -8040,20 +8040,20 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Jameson Williams (DET)</t>
-        </is>
-      </c>
-      <c r="C73" s="18" t="inlineStr">
+          <t>Quentin Johnston (LAC)</t>
+        </is>
+      </c>
+      <c r="C73" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>10.05</t>
         </is>
       </c>
     </row>
@@ -8063,20 +8063,20 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Quinshon Judkins (CLE)</t>
-        </is>
-      </c>
-      <c r="C74" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Michael Pittman Jr. (PIT)</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D74" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>9.07</t>
         </is>
       </c>
     </row>
@@ -8086,20 +8086,20 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>Colston Loveland (CHI)</t>
-        </is>
-      </c>
-      <c r="C75" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Rico Dowdle (PIT)</t>
+        </is>
+      </c>
+      <c r="C75" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>8.01</t>
         </is>
       </c>
     </row>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Waddle (DEN)</t>
-        </is>
-      </c>
-      <c r="C76" s="18" t="inlineStr">
+          <t>Wan'Dale Robinson (TEN)</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D76" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>10.09</t>
         </is>
       </c>
     </row>
@@ -8132,20 +8132,20 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten (JAX)</t>
-        </is>
-      </c>
-      <c r="C77" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Harold Fannin Jr. (CLE)</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D77" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -8155,20 +8155,20 @@
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Terry McLaurin (WAS)</t>
-        </is>
-      </c>
-      <c r="C78" s="18" t="inlineStr">
+          <t>Michael Wilson (ARI)</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D78" s="14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>7.11</t>
         </is>
       </c>
     </row>
@@ -8178,10 +8178,10 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>DJ Moore (BUF)</t>
-        </is>
-      </c>
-      <c r="C79" s="18" t="inlineStr">
+          <t>Stefon Diggs (WAS)</t>
+        </is>
+      </c>
+      <c r="C79" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>10.02</t>
         </is>
       </c>
     </row>
@@ -8201,10 +8201,10 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Luther Burden III (CHI)</t>
-        </is>
-      </c>
-      <c r="C80" s="18" t="inlineStr">
+          <t>Courtland Sutton (DEN)</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8214,7 +8214,7 @@
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>7.09</t>
         </is>
       </c>
     </row>
@@ -8224,20 +8224,20 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>Rome Odunze (CHI)</t>
-        </is>
-      </c>
-      <c r="C81" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jacory Croskey-Merritt (WAS)</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D81" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>10.06</t>
         </is>
       </c>
     </row>
@@ -8247,20 +8247,20 @@
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Tyler Warren (IND)</t>
-        </is>
-      </c>
-      <c r="C82" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kenny Gainwell (TB)</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D82" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8270,20 +8270,20 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>Harold Fannin Jr. (CLE)</t>
-        </is>
-      </c>
-      <c r="C83" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jaylen Warren (PIT)</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D83" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -8293,20 +8293,20 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Courtland Sutton (DEN)</t>
-        </is>
-      </c>
-      <c r="C84" s="18" t="inlineStr">
+          <t>Jordan Addison (MIN)</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D84" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>9.09</t>
         </is>
       </c>
     </row>
@@ -8316,12 +8316,12 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>David Montgomery (HOU)</t>
-        </is>
-      </c>
-      <c r="C85" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>De'Zhaun Stribling (SF)</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D85" s="14" t="n">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>12.07</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Christian Watson (GB)</t>
+          <t>Tucker Kraft (GB)</t>
         </is>
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D86" s="14" t="n">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8362,20 +8362,20 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr. (ARI)</t>
-        </is>
-      </c>
-      <c r="C87" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jalen Hurts (PHI)</t>
+        </is>
+      </c>
+      <c r="C87" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D87" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>5.12</t>
         </is>
       </c>
     </row>
@@ -8385,20 +8385,20 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Warren (PIT)</t>
-        </is>
-      </c>
-      <c r="C88" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jayden Reed (GB)</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D88" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8408,20 +8408,20 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>Mike Evans (SF)</t>
-        </is>
-      </c>
-      <c r="C89" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jayden Daniels (WAS)</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D89" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.04</t>
         </is>
       </c>
     </row>
@@ -8431,20 +8431,20 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>DK Metcalf (PIT)</t>
-        </is>
-      </c>
-      <c r="C90" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Joe Burrow (CIN)</t>
+        </is>
+      </c>
+      <c r="C90" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D90" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -8454,20 +8454,20 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>Alec Pierce (IND)</t>
+          <t>George Kittle (SF)</t>
         </is>
       </c>
       <c r="C91" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson (NE)</t>
+          <t>Chuba Hubbard (CAR)</t>
         </is>
       </c>
       <c r="C92" s="16" t="inlineStr">
@@ -8486,11 +8486,11 @@
         </is>
       </c>
       <c r="D92" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>7.05</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson (NE)</t>
+          <t>J.K. Dobbins (DEN)</t>
         </is>
       </c>
       <c r="C93" s="16" t="inlineStr">
@@ -8509,11 +8509,11 @@
         </is>
       </c>
       <c r="D93" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>8.1</t>
         </is>
       </c>
     </row>
@@ -8523,12 +8523,12 @@
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>Michael Pittman Jr. (PIT)</t>
-        </is>
-      </c>
-      <c r="C94" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tony Pollard (TEN)</t>
+        </is>
+      </c>
+      <c r="C94" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D94" s="14" t="n">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>7.12</t>
         </is>
       </c>
     </row>
@@ -8546,20 +8546,20 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>Kyle Pitts Sr. (ATL)</t>
-        </is>
-      </c>
-      <c r="C95" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Josh Downs (IND)</t>
+        </is>
+      </c>
+      <c r="C95" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D95" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>10.01</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Tony Pollard (TEN)</t>
+          <t>Jonathon Brooks (CAR)</t>
         </is>
       </c>
       <c r="C96" s="16" t="inlineStr">
@@ -8578,11 +8578,11 @@
         </is>
       </c>
       <c r="D96" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>9.1</t>
         </is>
       </c>
     </row>
@@ -8592,20 +8592,20 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>Jadarian Price (SEA)</t>
-        </is>
-      </c>
-      <c r="C97" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jakobi Meyers (JAX)</t>
+        </is>
+      </c>
+      <c r="C97" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>10.1</t>
         </is>
       </c>
     </row>
@@ -8615,20 +8615,20 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>George Kittle (SF)</t>
-        </is>
-      </c>
-      <c r="C98" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Romeo Doubs (NE)</t>
+        </is>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D98" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -8638,20 +8638,20 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>Parker Washington (JAX)</t>
+          <t>Sam LaPorta (DET)</t>
         </is>
       </c>
       <c r="C99" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -8661,20 +8661,20 @@
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>Sam LaPorta (DET)</t>
-        </is>
-      </c>
-      <c r="C100" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Khalil Shakir (BUF)</t>
+        </is>
+      </c>
+      <c r="C100" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D100" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>12.11</t>
         </is>
       </c>
     </row>
@@ -8684,20 +8684,20 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>Travis Kelce (KC)</t>
-        </is>
-      </c>
-      <c r="C101" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kyle Monangai (CHI)</t>
+        </is>
+      </c>
+      <c r="C101" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -8707,20 +8707,20 @@
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C102" s="18" t="inlineStr">
+          <t>Makai Lemon (PHI)</t>
+        </is>
+      </c>
+      <c r="C102" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D102" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -8730,20 +8730,20 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>Rico Dowdle (PIT)</t>
-        </is>
-      </c>
-      <c r="C103" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Xavier Worthy (KC)</t>
+        </is>
+      </c>
+      <c r="C103" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -8753,20 +8753,20 @@
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>Dallas Goedert (PHI)</t>
-        </is>
-      </c>
-      <c r="C104" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Malik Washington (MIA)</t>
+        </is>
+      </c>
+      <c r="C104" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D104" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -8776,20 +8776,20 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson (TEN)</t>
-        </is>
-      </c>
-      <c r="C105" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jordan Mason (MIN)</t>
+        </is>
+      </c>
+      <c r="C105" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.07</t>
         </is>
       </c>
     </row>
@@ -8799,20 +8799,20 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>Jakobi Meyers (JAX)</t>
-        </is>
-      </c>
-      <c r="C106" s="18" t="inlineStr">
+          <t>Jalen Coker (CAR)</t>
+        </is>
+      </c>
+      <c r="C106" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D106" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>13.02</t>
         </is>
       </c>
     </row>
@@ -8822,20 +8822,20 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Carnell Tate (TEN)</t>
-        </is>
-      </c>
-      <c r="C107" s="18" t="inlineStr">
+          <t>Rashid Shaheed (SEA)</t>
+        </is>
+      </c>
+      <c r="C107" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>13.03</t>
         </is>
       </c>
     </row>
@@ -8845,20 +8845,20 @@
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>Michael Wilson (ARI)</t>
-        </is>
-      </c>
-      <c r="C108" s="18" t="inlineStr">
+          <t>KC Concepcion (CLE)</t>
+        </is>
+      </c>
+      <c r="C108" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D108" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>11.01</t>
         </is>
       </c>
     </row>
@@ -8868,20 +8868,20 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>Jayden Reed (GB)</t>
-        </is>
-      </c>
-      <c r="C109" s="18" t="inlineStr">
+          <t>Kayshon Boutte (HOU)</t>
+        </is>
+      </c>
+      <c r="C109" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>19.08</t>
         </is>
       </c>
     </row>
@@ -8891,20 +8891,20 @@
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>J.K. Dobbins (DEN)</t>
-        </is>
-      </c>
-      <c r="C110" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Drake Maye (NE)</t>
+        </is>
+      </c>
+      <c r="C110" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D110" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -8914,20 +8914,20 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr. (TB)</t>
-        </is>
-      </c>
-      <c r="C111" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rachaad White (WAS)</t>
+        </is>
+      </c>
+      <c r="C111" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -8937,20 +8937,20 @@
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Chuba Hubbard (CAR)</t>
-        </is>
-      </c>
-      <c r="C112" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Matthew Golden (GB)</t>
+        </is>
+      </c>
+      <c r="C112" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D112" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>11.07</t>
         </is>
       </c>
     </row>
@@ -8960,20 +8960,20 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>Tucker Kraft (GB)</t>
+          <t>Jaxson Dart (NYG)</t>
         </is>
       </c>
       <c r="C113" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -8983,20 +8983,20 @@
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Kenny Gainwell (TB)</t>
-        </is>
-      </c>
-      <c r="C114" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kyle Pitts Sr. (ATL)</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D114" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>6.1</t>
         </is>
       </c>
     </row>
@@ -9006,20 +9006,20 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>Quentin Johnston (LAC)</t>
-        </is>
-      </c>
-      <c r="C115" s="18" t="inlineStr">
+          <t>Keenan Allen (IND)</t>
+        </is>
+      </c>
+      <c r="C115" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>17.07</t>
         </is>
       </c>
     </row>
@@ -9029,20 +9029,20 @@
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>Stefon Diggs (WAS)</t>
-        </is>
-      </c>
-      <c r="C116" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Caleb Williams (CHI)</t>
+        </is>
+      </c>
+      <c r="C116" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D116" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -9052,20 +9052,20 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>Jordan Addison (MIN)</t>
-        </is>
-      </c>
-      <c r="C117" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Trevor Lawrence (JAX)</t>
+        </is>
+      </c>
+      <c r="C117" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>Jonathon Brooks (CAR)</t>
+          <t>Blake Corum (LAR)</t>
         </is>
       </c>
       <c r="C118" s="16" t="inlineStr">
@@ -9084,11 +9084,11 @@
         </is>
       </c>
       <c r="D118" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.08</t>
         </is>
       </c>
     </row>
@@ -9098,20 +9098,20 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>Xavier Worthy (KC)</t>
-        </is>
-      </c>
-      <c r="C119" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>RJ Harvey (DEN)</t>
+        </is>
+      </c>
+      <c r="C119" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>7.08</t>
         </is>
       </c>
     </row>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Jake Ferguson (DAL)</t>
-        </is>
-      </c>
-      <c r="C120" s="19" t="inlineStr">
+          <t>Juwan Johnson (NO)</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D120" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9144,20 +9144,20 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>Mark Andrews (BAL)</t>
-        </is>
-      </c>
-      <c r="C121" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jordyn Tyson (NO)</t>
+        </is>
+      </c>
+      <c r="C121" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D121" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>8.07</t>
         </is>
       </c>
     </row>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling (SF)</t>
+          <t>Dalton Schultz (HOU)</t>
         </is>
       </c>
       <c r="C122" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>17.01</t>
         </is>
       </c>
     </row>
@@ -9190,20 +9190,20 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>Matthew Golden (GB)</t>
+          <t>Travis Kelce (KC)</t>
         </is>
       </c>
       <c r="C123" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>8.08</t>
         </is>
       </c>
     </row>
@@ -9213,20 +9213,20 @@
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>Isaiah Likely (NYG)</t>
-        </is>
-      </c>
-      <c r="C124" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tre Tucker (LV)</t>
+        </is>
+      </c>
+      <c r="C124" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D124" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>17.1</t>
         </is>
       </c>
     </row>
@@ -9236,20 +9236,20 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>Khalil Shakir (BUF)</t>
-        </is>
-      </c>
-      <c r="C125" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Aaron Jones Sr. (MIN)</t>
+        </is>
+      </c>
+      <c r="C125" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -9259,20 +9259,20 @@
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>KC Concepcion (CLE)</t>
+          <t>Jake Ferguson (DAL)</t>
         </is>
       </c>
       <c r="C126" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>9.02</t>
         </is>
       </c>
     </row>
@@ -9282,20 +9282,20 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>Josh Downs (IND)</t>
-        </is>
-      </c>
-      <c r="C127" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dak Prescott (DAL)</t>
+        </is>
+      </c>
+      <c r="C127" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>7.07</t>
         </is>
       </c>
     </row>
@@ -9305,20 +9305,20 @@
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>Romeo Doubs (NE)</t>
+          <t>Dalton Kincaid (BUF)</t>
         </is>
       </c>
       <c r="C128" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D128" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -9328,12 +9328,12 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>Deebo Samuel Sr. (SF)</t>
+          <t>Isaiah Likely (NYG)</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D129" s="14" t="n">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>RJ Harvey (DEN)</t>
+          <t>Tyjae Spears (TEN)</t>
         </is>
       </c>
       <c r="C130" s="16" t="inlineStr">
@@ -9360,11 +9360,11 @@
         </is>
       </c>
       <c r="D130" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -9374,20 +9374,20 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr. (MIN)</t>
-        </is>
-      </c>
-      <c r="C131" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Justin Herbert (LAC)</t>
+        </is>
+      </c>
+      <c r="C131" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -9397,20 +9397,20 @@
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>Rachaad White (WAS)</t>
-        </is>
-      </c>
-      <c r="C132" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dallas Goedert (PHI)</t>
+        </is>
+      </c>
+      <c r="C132" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D132" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -9420,20 +9420,20 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>Dalton Kincaid (BUF)</t>
+          <t>Bo Nix (DEN)</t>
         </is>
       </c>
       <c r="C133" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D133" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>10.12</t>
         </is>
       </c>
     </row>
@@ -9443,20 +9443,20 @@
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Jalen Coker (CAR)</t>
-        </is>
-      </c>
-      <c r="C134" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brock Purdy (SF)</t>
+        </is>
+      </c>
+      <c r="C134" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D134" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>11.02</t>
         </is>
       </c>
     </row>
@@ -9466,20 +9466,20 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>Rashid Shaheed (SEA)</t>
-        </is>
-      </c>
-      <c r="C135" s="18" t="inlineStr">
+          <t>Omar Cooper Jr. (NYJ)</t>
+        </is>
+      </c>
+      <c r="C135" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>17.02</t>
         </is>
       </c>
     </row>
@@ -9489,20 +9489,20 @@
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd (GB)</t>
-        </is>
-      </c>
-      <c r="C136" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jared Goff (DET)</t>
+        </is>
+      </c>
+      <c r="C136" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D136" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>12.03</t>
         </is>
       </c>
     </row>
@@ -9512,20 +9512,20 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>Kyle Monangai (CHI)</t>
-        </is>
-      </c>
-      <c r="C137" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Deebo Samuel Sr. (SF)</t>
+        </is>
+      </c>
+      <c r="C137" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>11.11</t>
         </is>
       </c>
     </row>
@@ -9535,12 +9535,12 @@
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>Juwan Johnson (NO)</t>
+          <t>Tyler Shough (NO)</t>
         </is>
       </c>
       <c r="C138" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>16.07</t>
         </is>
       </c>
     </row>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>Jerry Jeudy (CLE)</t>
-        </is>
-      </c>
-      <c r="C139" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Matthew Stafford (LAR)</t>
+        </is>
+      </c>
+      <c r="C139" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>9.01</t>
         </is>
       </c>
     </row>
@@ -9581,20 +9581,20 @@
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>Hunter Henry (NE)</t>
+          <t>Kyler Murray (MIN)</t>
         </is>
       </c>
       <c r="C140" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D140" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>14.03</t>
         </is>
       </c>
     </row>
@@ -9604,20 +9604,20 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>Brenton Strange (JAX)</t>
+          <t>Jordan Love (GB)</t>
         </is>
       </c>
       <c r="C141" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>13.05</t>
         </is>
       </c>
     </row>
@@ -9627,20 +9627,20 @@
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>Denzel Boston (CLE)</t>
-        </is>
-      </c>
-      <c r="C142" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Baker Mayfield (TB)</t>
+        </is>
+      </c>
+      <c r="C142" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -9650,20 +9650,20 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>Makai Lemon (PHI)</t>
-        </is>
-      </c>
-      <c r="C143" s="18" t="inlineStr">
+          <t>Denzel Boston (CLE)</t>
+        </is>
+      </c>
+      <c r="C143" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9673,20 +9673,20 @@
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>Dalton Schultz (HOU)</t>
+          <t>Patrick Mahomes (KC)</t>
         </is>
       </c>
       <c r="C144" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -9696,20 +9696,20 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>Calvin Ridley (TEN)</t>
+          <t>Brenton Strange (JAX)</t>
         </is>
       </c>
       <c r="C145" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>13.08</t>
         </is>
       </c>
     </row>
@@ -9719,20 +9719,20 @@
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt (WAS)</t>
-        </is>
-      </c>
-      <c r="C146" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dontayvion Wicks (PHI)</t>
+        </is>
+      </c>
+      <c r="C146" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9742,20 +9742,20 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Jordan Mason (MIN)</t>
-        </is>
-      </c>
-      <c r="C147" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Mark Andrews (BAL)</t>
+        </is>
+      </c>
+      <c r="C147" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>11.09</t>
         </is>
       </c>
     </row>
@@ -9765,20 +9765,20 @@
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>Tre Tucker (LV)</t>
-        </is>
-      </c>
-      <c r="C148" s="18" t="inlineStr">
+          <t>Pat Bryant (DEN)</t>
+        </is>
+      </c>
+      <c r="C148" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>19.11</t>
         </is>
       </c>
     </row>
@@ -9788,20 +9788,20 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>Keenan Allen (IND)</t>
-        </is>
-      </c>
-      <c r="C149" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Malik Willis (MIA)</t>
+        </is>
+      </c>
+      <c r="C149" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -9811,20 +9811,20 @@
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>T.J. Hockenson (MIN)</t>
-        </is>
-      </c>
-      <c r="C150" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jalen Nailor (LV)</t>
+        </is>
+      </c>
+      <c r="C150" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Blake Corum (LAR)</t>
+          <t>Woody Marks (HOU)</t>
         </is>
       </c>
       <c r="C151" s="16" t="inlineStr">
@@ -9843,11 +9843,11 @@
         </is>
       </c>
       <c r="D151" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>14.04</t>
         </is>
       </c>
     </row>
@@ -9857,20 +9857,20 @@
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Tyjae Spears (TEN)</t>
-        </is>
-      </c>
-      <c r="C152" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Hunter Henry (NE)</t>
+        </is>
+      </c>
+      <c r="C152" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -9880,20 +9880,20 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>Kayshon Boutte (HOU)</t>
+          <t>Chig Okonkwo (WAS)</t>
         </is>
       </c>
       <c r="C153" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9903,20 +9903,20 @@
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>Rashod Bateman (BAL)</t>
-        </is>
-      </c>
-      <c r="C154" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chris Rodriguez Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C154" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>12.08</t>
         </is>
       </c>
     </row>
@@ -9926,20 +9926,20 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>Pat Freiermuth (PIT)</t>
-        </is>
-      </c>
-      <c r="C155" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Travis Hunter (JAX)</t>
+        </is>
+      </c>
+      <c r="C155" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9949,20 +9949,20 @@
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Greg Dulcich (MIA)</t>
-        </is>
-      </c>
-      <c r="C156" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Cooper Kupp (SEA)</t>
+        </is>
+      </c>
+      <c r="C156" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>19.05</t>
         </is>
       </c>
     </row>
@@ -9972,20 +9972,20 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane (BAL)</t>
-        </is>
-      </c>
-      <c r="C157" s="18" t="inlineStr">
+          <t>Jerry Jeudy (CLE)</t>
+        </is>
+      </c>
+      <c r="C157" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D157" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E157" s="14" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -9995,20 +9995,20 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Cade Otton (TB)</t>
+          <t>Cam Ward (TEN)</t>
         </is>
       </c>
       <c r="C158" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10018,16 +10018,16 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Jalen Nailor (LV)</t>
-        </is>
-      </c>
-      <c r="C159" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Isiah Pacheco (DET)</t>
+        </is>
+      </c>
+      <c r="C159" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E159" s="14" t="inlineStr">
         <is>
@@ -10041,12 +10041,12 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>Devaughn Vele (NO)</t>
-        </is>
-      </c>
-      <c r="C160" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>C.J. Stroud (HOU)</t>
+        </is>
+      </c>
+      <c r="C160" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>18.01</t>
         </is>
       </c>
     </row>
@@ -10064,20 +10064,20 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>Chig Okonkwo (WAS)</t>
-        </is>
-      </c>
-      <c r="C161" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>DeMario Douglas (NE)</t>
+        </is>
+      </c>
+      <c r="C161" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E161" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10087,12 +10087,12 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Woody Marks (HOU)</t>
-        </is>
-      </c>
-      <c r="C162" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Malachi Fields (NYG)</t>
+        </is>
+      </c>
+      <c r="C162" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D162" s="14" t="n">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>19.04</t>
         </is>
       </c>
     </row>
@@ -10110,12 +10110,12 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>Cooper Kupp (SEA)</t>
-        </is>
-      </c>
-      <c r="C163" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Sam Darnold (SEA)</t>
+        </is>
+      </c>
+      <c r="C163" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="E163" s="14" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>14.05</t>
         </is>
       </c>
     </row>
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq (NYJ)</t>
-        </is>
-      </c>
-      <c r="C164" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Keaton Mitchell (LAC)</t>
+        </is>
+      </c>
+      <c r="C164" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10156,20 +10156,20 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>AJ Barner (SEA)</t>
-        </is>
-      </c>
-      <c r="C165" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Adonai Mitchell (NYJ)</t>
+        </is>
+      </c>
+      <c r="C165" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E165" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10179,20 +10179,20 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Jaylin Noel (HOU)</t>
-        </is>
-      </c>
-      <c r="C166" s="18" t="inlineStr">
+          <t>Ja'Kobi Lane (BAL)</t>
+        </is>
+      </c>
+      <c r="C166" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>14.02</t>
         </is>
       </c>
     </row>
@@ -10202,20 +10202,20 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>Zach Charbonnet (SEA)</t>
-        </is>
-      </c>
-      <c r="C167" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Daniel Jones (IND)</t>
+        </is>
+      </c>
+      <c r="C167" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E167" s="14" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>17.11</t>
         </is>
       </c>
     </row>
@@ -10225,12 +10225,12 @@
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>Alvin Kamara (NO)</t>
-        </is>
-      </c>
-      <c r="C168" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tank Dell (HOU)</t>
+        </is>
+      </c>
+      <c r="C168" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10248,20 +10248,20 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>Adonai Mitchell (NYJ)</t>
-        </is>
-      </c>
-      <c r="C169" s="18" t="inlineStr">
+          <t>Germie Bernard (PIT)</t>
+        </is>
+      </c>
+      <c r="C169" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E169" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Isiah Pacheco (DET)</t>
+          <t>Zach Charbonnet (SEA)</t>
         </is>
       </c>
       <c r="C170" s="16" t="inlineStr">
@@ -10280,11 +10280,11 @@
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>13.04</t>
         </is>
       </c>
     </row>
@@ -10294,16 +10294,16 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>Malik Washington (MIA)</t>
-        </is>
-      </c>
-      <c r="C171" s="18" t="inlineStr">
+          <t>Cyrus Allen (KC)</t>
+        </is>
+      </c>
+      <c r="C171" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Dylan Sampson (CLE)</t>
+          <t>Tyler Allgeier (ARI)</t>
         </is>
       </c>
       <c r="C172" s="16" t="inlineStr">
@@ -10326,11 +10326,11 @@
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -10340,20 +10340,20 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>Germie Bernard (PIT)</t>
-        </is>
-      </c>
-      <c r="C173" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dylan Sampson (CLE)</t>
+        </is>
+      </c>
+      <c r="C173" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -10363,20 +10363,20 @@
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Jordyn Tyson (NO)</t>
-        </is>
-      </c>
-      <c r="C174" s="18" t="inlineStr">
+          <t>Kyle Williams (NE)</t>
+        </is>
+      </c>
+      <c r="C174" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>19.06</t>
         </is>
       </c>
     </row>
@@ -10386,20 +10386,20 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks (PHI)</t>
-        </is>
-      </c>
-      <c r="C175" s="18" t="inlineStr">
+          <t>Calvin Ridley (TEN)</t>
+        </is>
+      </c>
+      <c r="C175" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E175" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22.01</t>
         </is>
       </c>
     </row>
@@ -10409,12 +10409,12 @@
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>Caleb Douglas (MIA)</t>
+          <t>T.J. Hockenson (MIN)</t>
         </is>
       </c>
       <c r="C176" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D176" s="14" t="n">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -10432,12 +10432,12 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Omar Cooper Jr. (NYJ)</t>
-        </is>
-      </c>
-      <c r="C177" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Mike Washington Jr. (LV)</t>
+        </is>
+      </c>
+      <c r="C177" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="E177" s="14" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>15.05</t>
         </is>
       </c>
     </row>
@@ -10455,20 +10455,20 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Travis Hunter (JAX)</t>
+          <t>Greg Dulcich (MIA)</t>
         </is>
       </c>
       <c r="C178" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10478,12 +10478,12 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Mike Washington Jr. (LV)</t>
-        </is>
-      </c>
-      <c r="C179" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kenyon Sadiq (NYJ)</t>
+        </is>
+      </c>
+      <c r="C179" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="E179" s="14" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>13.1</t>
         </is>
       </c>
     </row>
@@ -10501,20 +10501,20 @@
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Darius Slayton (NYG)</t>
-        </is>
-      </c>
-      <c r="C180" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonah Coleman (DEN)</t>
+        </is>
+      </c>
+      <c r="C180" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.03</t>
         </is>
       </c>
     </row>
@@ -10524,12 +10524,12 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>Chris Rodriguez Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C181" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tre' Harris (LAC)</t>
+        </is>
+      </c>
+      <c r="C181" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10547,20 +10547,20 @@
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Tyler Allgeier (ARI)</t>
-        </is>
-      </c>
-      <c r="C182" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Keon Coleman (BUF)</t>
+        </is>
+      </c>
+      <c r="C182" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D182" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>20.07</t>
         </is>
       </c>
     </row>
@@ -10570,20 +10570,20 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>Tory Horton (SEA)</t>
-        </is>
-      </c>
-      <c r="C183" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyrone Tracy Jr. (NYG)</t>
+        </is>
+      </c>
+      <c r="C183" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D183" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E183" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10593,20 +10593,20 @@
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>Tre' Harris (LAC)</t>
+          <t>Pat Freiermuth (PIT)</t>
         </is>
       </c>
       <c r="C184" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D184" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10616,20 +10616,20 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Jalen Tolbert (MIA)</t>
-        </is>
-      </c>
-      <c r="C185" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Aaron Rodgers (PIT)</t>
+        </is>
+      </c>
+      <c r="C185" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E185" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10639,20 +10639,20 @@
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Ryan Flournoy (DAL)</t>
-        </is>
-      </c>
-      <c r="C186" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Bryce Young (CAR)</t>
+        </is>
+      </c>
+      <c r="C186" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D186" s="14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>19.12</t>
         </is>
       </c>
     </row>
@@ -10662,20 +10662,20 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>Malachi Fields (NYG)</t>
-        </is>
-      </c>
-      <c r="C187" s="18" t="inlineStr">
+          <t>Zachariah Branch (ATL)</t>
+        </is>
+      </c>
+      <c r="C187" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D187" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E187" s="14" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -10685,20 +10685,20 @@
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Keaton Mitchell (LAC)</t>
-        </is>
-      </c>
-      <c r="C188" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ryan Flournoy (DAL)</t>
+        </is>
+      </c>
+      <c r="C188" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D188" s="14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10708,20 +10708,20 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr. (NYG)</t>
-        </is>
-      </c>
-      <c r="C189" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Cade Otton (TB)</t>
+        </is>
+      </c>
+      <c r="C189" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E189" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>20.06</t>
         </is>
       </c>
     </row>
@@ -10754,20 +10754,20 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>DeMario Douglas (NE)</t>
-        </is>
-      </c>
-      <c r="C191" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Alvin Kamara (NO)</t>
+        </is>
+      </c>
+      <c r="C191" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E191" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.07</t>
         </is>
       </c>
     </row>
@@ -10777,20 +10777,20 @@
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Zachariah Branch (ATL)</t>
-        </is>
-      </c>
-      <c r="C192" s="18" t="inlineStr">
+          <t>Caleb Douglas (MIA)</t>
+        </is>
+      </c>
+      <c r="C192" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D192" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>18.09</t>
         </is>
       </c>
     </row>
@@ -10800,20 +10800,20 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Keon Coleman (BUF)</t>
-        </is>
-      </c>
-      <c r="C193" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Geno Smith (NYJ)</t>
+        </is>
+      </c>
+      <c r="C193" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10846,20 +10846,20 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Pat Bryant (DEN)</t>
-        </is>
-      </c>
-      <c r="C195" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brian Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C195" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E195" s="14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>13.12</t>
         </is>
       </c>
     </row>
@@ -10869,10 +10869,10 @@
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>Tank Dell (HOU)</t>
-        </is>
-      </c>
-      <c r="C196" s="18" t="inlineStr">
+          <t>Devaughn Vele (NO)</t>
+        </is>
+      </c>
+      <c r="C196" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="E196" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10892,20 +10892,20 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>Cyrus Allen (KC)</t>
+          <t>AJ Barner (SEA)</t>
         </is>
       </c>
       <c r="C197" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D197" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E197" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10915,20 +10915,20 @@
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Kyle Williams (NE)</t>
-        </is>
-      </c>
-      <c r="C198" s="18" t="inlineStr">
+          <t>Jaylin Noel (HOU)</t>
+        </is>
+      </c>
+      <c r="C198" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D198" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>18.1</t>
         </is>
       </c>
     </row>
@@ -10938,20 +10938,20 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>Jonah Coleman (DEN)</t>
-        </is>
-      </c>
-      <c r="C199" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Darius Slayton (NYG)</t>
+        </is>
+      </c>
+      <c r="C199" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E199" s="14" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10961,20 +10961,20 @@
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Kenneth Walker (KC)</t>
-        </is>
-      </c>
-      <c r="C200" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Oronde Gadsden (LAC)</t>
+        </is>
+      </c>
+      <c r="C200" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D200" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
@@ -10984,20 +10984,20 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>Patrick Mahomes (KC)</t>
+          <t>Rashod Bateman (BAL)</t>
         </is>
       </c>
       <c r="C201" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D201" s="14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>20.05</t>
         </is>
       </c>
     </row>
@@ -11007,20 +11007,20 @@
       </c>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>Brian Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C202" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jalen Tolbert (MIA)</t>
+        </is>
+      </c>
+      <c r="C202" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D202" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E202" s="14" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11030,20 +11030,20 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>Oronde Gadsden (LAC)</t>
-        </is>
-      </c>
-      <c r="C203" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tory Horton (SEA)</t>
+        </is>
+      </c>
+      <c r="C203" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D203" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>

--- a/assets/data/12guys1cup-cheat-sheet.xlsx
+++ b/assets/data/12guys1cup-cheat-sheet.xlsx
@@ -6499,7 +6499,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase (CIN)</t>
+          <t>Puka Nacua (LAR)</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
@@ -6508,11 +6508,11 @@
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
     </row>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Puka Nacua (LAR)</t>
+          <t>Ja'Marr Chase (CIN)</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
@@ -6531,11 +6531,11 @@
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>
@@ -6614,20 +6614,20 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>CeeDee Lamb (DAL)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonathan Taylor (IND)</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Jonathan Taylor (IND)</t>
+          <t>De'Von Achane (MIA)</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -6646,11 +6646,11 @@
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>James Cook III (BUF)</t>
+          <t>Chase Brown (CIN)</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -6669,11 +6669,11 @@
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -6683,20 +6683,20 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>De'Von Achane (MIA)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Drake London (ATL)</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Kenneth Walker (KC)</t>
+          <t>Derrick Henry (BAL)</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -6715,11 +6715,11 @@
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.08</t>
         </is>
       </c>
     </row>
@@ -6729,12 +6729,12 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Chase Brown (CIN)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Justin Jefferson (MIN)</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Justin Jefferson (MIN)</t>
+          <t>CeeDee Lamb (DAL)</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
@@ -6761,11 +6761,11 @@
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6775,20 +6775,20 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>A.J. Brown (NE)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>James Cook III (BUF)</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.11</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Chris Olave (NO)</t>
+          <t>Rashee Rice (KC)</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
@@ -6807,11 +6807,11 @@
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -6821,20 +6821,20 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Brock Bowers (LV)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Saquon Barkley (PHI)</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Nico Collins (HOU)</t>
+          <t>Chris Olave (NO)</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.07</t>
         </is>
       </c>
     </row>
@@ -6867,20 +6867,20 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Trey McBride (ARI)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Ashton Jeanty (LV)</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Garrett Wilson (NYJ)</t>
+          <t>A.J. Brown (NE)</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
@@ -6899,11 +6899,11 @@
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -6913,20 +6913,20 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Drake London (ATL)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Trey McBride (ARI)</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -6936,20 +6936,20 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>George Pickens (DAL)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Omarion Hampton (LAC)</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Rashee Rice (KC)</t>
+          <t>George Pickens (DAL)</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
@@ -6968,11 +6968,11 @@
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Omarion Hampton (LAC)</t>
+          <t>Jeremiyah Love (ARI)</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
@@ -6991,11 +6991,11 @@
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7005,20 +7005,20 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Ashton Jeanty (LV)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Nico Collins (HOU)</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7028,20 +7028,20 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Malik Nabers (NYG)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Breece Hall (NYJ)</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7051,20 +7051,20 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Saquon Barkley (PHI)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Brock Bowers (LV)</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Zay Flowers (BAL)</t>
+          <t>Garrett Wilson (NYJ)</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -7097,12 +7097,12 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Derrick Henry (BAL)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Zay Flowers (BAL)</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>4.05</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>DeVonta Smith (PHI)</t>
+          <t>Malik Nabers (NYG)</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
@@ -7129,11 +7129,11 @@
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -7143,20 +7143,20 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Waddle (DEN)</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Javonte Williams (DAL)</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7166,20 +7166,20 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>Jeremiyah Love (ARI)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DeVonta Smith (PHI)</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.12</t>
         </is>
       </c>
     </row>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Kyren Williams (LAR)</t>
+          <t>Travis Etienne Jr. (NO)</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
@@ -7198,11 +7198,11 @@
         </is>
       </c>
       <c r="D36" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>4.09</t>
         </is>
       </c>
     </row>
@@ -7212,20 +7212,20 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Ladd McConkey (LAC)</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kyren Williams (LAR)</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Breece Hall (NYJ)</t>
+          <t>Cam Skattebo (NYG)</t>
         </is>
       </c>
       <c r="C38" s="16" t="inlineStr">
@@ -7244,11 +7244,11 @@
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4.08</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Emeka Egbuka (TB)</t>
+          <t>Tetairoa McMillan (CAR)</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
@@ -7267,11 +7267,11 @@
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.01</t>
         </is>
       </c>
     </row>
@@ -7281,12 +7281,12 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>D'Andre Swift (CHI)</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Emeka Egbuka (TB)</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D40" s="14" t="n">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.03</t>
         </is>
       </c>
     </row>
@@ -7304,20 +7304,20 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan (CAR)</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>D'Andre Swift (CHI)</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Tee Higgins (CIN)</t>
+          <t>Davante Adams (LAR)</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
@@ -7336,11 +7336,11 @@
         </is>
       </c>
       <c r="D42" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>5.02</t>
         </is>
       </c>
     </row>
@@ -7350,7 +7350,7 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Carnell Tate (TEN)</t>
+          <t>Tee Higgins (CIN)</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
@@ -7359,11 +7359,11 @@
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>3.11</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Javonte Williams (DAL)</t>
+          <t>Bucky Irving (TB)</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
@@ -7382,11 +7382,11 @@
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4.06</t>
         </is>
       </c>
     </row>
@@ -7396,12 +7396,12 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Josh Allen (BUF)</t>
-        </is>
-      </c>
-      <c r="C45" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Ladd McConkey (LAC)</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>4.02</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>Luther Burden III (CHI)</t>
+          <t>Jameson Williams (DET)</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
@@ -7428,11 +7428,11 @@
         </is>
       </c>
       <c r="D46" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Christian Watson (GB)</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Quinshon Judkins (CLE)</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Bucky Irving (TB)</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Colston Loveland (CHI)</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D48" s="14" t="n">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>Parker Washington (JAX)</t>
+          <t>Jaylen Waddle (DEN)</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
@@ -7497,11 +7497,11 @@
         </is>
       </c>
       <c r="D49" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr. (NO)</t>
+          <t>Bhayshul Tuten (JAX)</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
@@ -7520,11 +7520,11 @@
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -7534,20 +7534,20 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Cam Skattebo (NYG)</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Terry McLaurin (WAS)</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D51" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Terry McLaurin (WAS)</t>
+          <t>DJ Moore (BUF)</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.09</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Jameson Williams (DET)</t>
+          <t>Luther Burden III (CHI)</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
@@ -7589,11 +7589,11 @@
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>DJ Moore (BUF)</t>
+          <t>Rome Odunze (CHI)</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
@@ -7612,11 +7612,11 @@
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>6.05</t>
         </is>
       </c>
     </row>
@@ -7626,20 +7626,20 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten (JAX)</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tyler Warren (IND)</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>4.11</t>
         </is>
       </c>
     </row>
@@ -7649,12 +7649,12 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Davante Adams (LAR)</t>
-        </is>
-      </c>
-      <c r="C56" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Harold Fannin Jr. (CLE)</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7672,7 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Mike Evans (SF)</t>
+          <t>Courtland Sutton (DEN)</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
@@ -7681,11 +7681,11 @@
         </is>
       </c>
       <c r="D57" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>7.09</t>
         </is>
       </c>
     </row>
@@ -7695,20 +7695,20 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Rome Odunze (CHI)</t>
-        </is>
-      </c>
-      <c r="C58" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>David Montgomery (HOU)</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D58" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr. (ARI)</t>
+          <t>Christian Watson (GB)</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
@@ -7727,11 +7727,11 @@
         </is>
       </c>
       <c r="D59" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>DK Metcalf (PIT)</t>
+          <t>Marvin Harrison Jr. (ARI)</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="D60" s="14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
@@ -7764,20 +7764,20 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Tyler Warren (IND)</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jaylen Warren (PIT)</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -7787,20 +7787,20 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Colston Loveland (CHI)</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Mike Evans (SF)</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D62" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Alec Pierce (IND)</t>
+          <t>DK Metcalf (PIT)</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
@@ -7819,11 +7819,11 @@
         </is>
       </c>
       <c r="D63" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -7833,20 +7833,20 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>TreVeyon Henderson (NE)</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D64" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -7856,20 +7856,20 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Quinshon Judkins (CLE)</t>
-        </is>
-      </c>
-      <c r="C65" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Alec Pierce (IND)</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D65" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>9.05</t>
         </is>
       </c>
     </row>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson (NE)</t>
+          <t>Rhamondre Stevenson (NE)</t>
         </is>
       </c>
       <c r="C66" s="16" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -7902,20 +7902,20 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>David Montgomery (HOU)</t>
-        </is>
-      </c>
-      <c r="C67" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Michael Pittman Jr. (PIT)</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D67" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>9.07</t>
         </is>
       </c>
     </row>
@@ -7925,20 +7925,20 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Lamar Jackson (BAL)</t>
-        </is>
-      </c>
-      <c r="C68" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tony Pollard (TEN)</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D68" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>7.12</t>
         </is>
       </c>
     </row>
@@ -7948,20 +7948,20 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr. (TB)</t>
-        </is>
-      </c>
-      <c r="C69" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jadarian Price (SEA)</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D69" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -7971,12 +7971,12 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Jadarian Price (SEA)</t>
-        </is>
-      </c>
-      <c r="C70" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kyle Pitts Sr. (ATL)</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D70" s="14" t="n">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.1</t>
         </is>
       </c>
     </row>
@@ -7994,20 +7994,20 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd (GB)</t>
-        </is>
-      </c>
-      <c r="C71" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>George Kittle (SF)</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -8017,20 +8017,20 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson (NE)</t>
-        </is>
-      </c>
-      <c r="C72" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Parker Washington (JAX)</t>
+        </is>
+      </c>
+      <c r="C72" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.04</t>
         </is>
       </c>
     </row>
@@ -8040,20 +8040,20 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Quentin Johnston (LAC)</t>
-        </is>
-      </c>
-      <c r="C73" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Sam LaPorta (DET)</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -8063,20 +8063,20 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Michael Pittman Jr. (PIT)</t>
-        </is>
-      </c>
-      <c r="C74" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Travis Kelce (KC)</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D74" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>8.08</t>
         </is>
       </c>
     </row>
@@ -8086,20 +8086,20 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>Rico Dowdle (PIT)</t>
-        </is>
-      </c>
-      <c r="C75" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Brian Thomas Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C75" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.02</t>
         </is>
       </c>
     </row>
@@ -8109,12 +8109,12 @@
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson (TEN)</t>
-        </is>
-      </c>
-      <c r="C76" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rico Dowdle (PIT)</t>
+        </is>
+      </c>
+      <c r="C76" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D76" s="14" t="n">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>8.01</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>Harold Fannin Jr. (CLE)</t>
+          <t>Dallas Goedert (PHI)</t>
         </is>
       </c>
       <c r="C77" s="18" t="inlineStr">
@@ -8141,11 +8141,11 @@
         </is>
       </c>
       <c r="D77" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Michael Wilson (ARI)</t>
+          <t>Wan'Dale Robinson (TEN)</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
@@ -8164,11 +8164,11 @@
         </is>
       </c>
       <c r="D78" s="14" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>10.09</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>Stefon Diggs (WAS)</t>
+          <t>Carnell Tate (TEN)</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
@@ -8187,11 +8187,11 @@
         </is>
       </c>
       <c r="D79" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Courtland Sutton (DEN)</t>
+          <t>Michael Wilson (ARI)</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
@@ -8210,11 +8210,11 @@
         </is>
       </c>
       <c r="D80" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>7.11</t>
         </is>
       </c>
     </row>
@@ -8224,20 +8224,20 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt (WAS)</t>
-        </is>
-      </c>
-      <c r="C81" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jayden Reed (GB)</t>
+        </is>
+      </c>
+      <c r="C81" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D81" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Kenny Gainwell (TB)</t>
+          <t>J.K. Dobbins (DEN)</t>
         </is>
       </c>
       <c r="C82" s="16" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>8.1</t>
         </is>
       </c>
     </row>
@@ -8270,20 +8270,20 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Warren (PIT)</t>
-        </is>
-      </c>
-      <c r="C83" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jakobi Meyers (JAX)</t>
+        </is>
+      </c>
+      <c r="C83" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D83" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>10.1</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Jordan Addison (MIN)</t>
+          <t>Chris Godwin Jr. (TB)</t>
         </is>
       </c>
       <c r="C84" s="17" t="inlineStr">
@@ -8302,11 +8302,11 @@
         </is>
       </c>
       <c r="D84" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>8.12</t>
         </is>
       </c>
     </row>
@@ -8316,20 +8316,20 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling (SF)</t>
-        </is>
-      </c>
-      <c r="C85" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chuba Hubbard (CAR)</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D85" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>7.05</t>
         </is>
       </c>
     </row>
@@ -8362,12 +8362,12 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>Jalen Hurts (PHI)</t>
-        </is>
-      </c>
-      <c r="C87" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Kenny Gainwell (TB)</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D87" s="14" t="n">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8385,7 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Jayden Reed (GB)</t>
+          <t>Quentin Johnston (LAC)</t>
         </is>
       </c>
       <c r="C88" s="17" t="inlineStr">
@@ -8394,11 +8394,11 @@
         </is>
       </c>
       <c r="D88" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>10.05</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>Jayden Daniels (WAS)</t>
-        </is>
-      </c>
-      <c r="C89" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Stefon Diggs (WAS)</t>
+        </is>
+      </c>
+      <c r="C89" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D89" s="14" t="n">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>10.02</t>
         </is>
       </c>
     </row>
@@ -8431,12 +8431,12 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Joe Burrow (CIN)</t>
-        </is>
-      </c>
-      <c r="C90" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jordan Addison (MIN)</t>
+        </is>
+      </c>
+      <c r="C90" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D90" s="14" t="n">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>9.09</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>George Kittle (SF)</t>
+          <t>Jake Ferguson (DAL)</t>
         </is>
       </c>
       <c r="C91" s="18" t="inlineStr">
@@ -8463,11 +8463,11 @@
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>9.02</t>
         </is>
       </c>
     </row>
@@ -8477,20 +8477,20 @@
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>Chuba Hubbard (CAR)</t>
-        </is>
-      </c>
-      <c r="C92" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Mark Andrews (BAL)</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D92" s="14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>11.09</t>
         </is>
       </c>
     </row>
@@ -8500,20 +8500,20 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>J.K. Dobbins (DEN)</t>
-        </is>
-      </c>
-      <c r="C93" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Xavier Worthy (KC)</t>
+        </is>
+      </c>
+      <c r="C93" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D93" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -8523,20 +8523,20 @@
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>Tony Pollard (TEN)</t>
-        </is>
-      </c>
-      <c r="C94" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>De'Zhaun Stribling (SF)</t>
+        </is>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D94" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>12.07</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>Josh Downs (IND)</t>
+          <t>Matthew Golden (GB)</t>
         </is>
       </c>
       <c r="C95" s="17" t="inlineStr">
@@ -8555,11 +8555,11 @@
         </is>
       </c>
       <c r="D95" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>11.07</t>
         </is>
       </c>
     </row>
@@ -8569,20 +8569,20 @@
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Jonathon Brooks (CAR)</t>
-        </is>
-      </c>
-      <c r="C96" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Isaiah Likely (NYG)</t>
+        </is>
+      </c>
+      <c r="C96" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D96" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -8592,20 +8592,20 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>Jakobi Meyers (JAX)</t>
-        </is>
-      </c>
-      <c r="C97" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonathon Brooks (CAR)</t>
+        </is>
+      </c>
+      <c r="C97" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.1</t>
         </is>
       </c>
     </row>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>Romeo Doubs (NE)</t>
+          <t>Khalil Shakir (BUF)</t>
         </is>
       </c>
       <c r="C98" s="17" t="inlineStr">
@@ -8624,11 +8624,11 @@
         </is>
       </c>
       <c r="D98" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>12.11</t>
         </is>
       </c>
     </row>
@@ -8638,20 +8638,20 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>Sam LaPorta (DET)</t>
-        </is>
-      </c>
-      <c r="C99" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>KC Concepcion (CLE)</t>
+        </is>
+      </c>
+      <c r="C99" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>11.01</t>
         </is>
       </c>
     </row>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>Khalil Shakir (BUF)</t>
+          <t>Romeo Doubs (NE)</t>
         </is>
       </c>
       <c r="C100" s="17" t="inlineStr">
@@ -8670,11 +8670,11 @@
         </is>
       </c>
       <c r="D100" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -8684,20 +8684,20 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>Kyle Monangai (CHI)</t>
-        </is>
-      </c>
-      <c r="C101" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Josh Downs (IND)</t>
+        </is>
+      </c>
+      <c r="C101" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>10.01</t>
         </is>
       </c>
     </row>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Makai Lemon (PHI)</t>
+          <t>Deebo Samuel Sr. (SF)</t>
         </is>
       </c>
       <c r="C102" s="17" t="inlineStr">
@@ -8716,11 +8716,11 @@
         </is>
       </c>
       <c r="D102" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>11.11</t>
         </is>
       </c>
     </row>
@@ -8730,20 +8730,20 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>Xavier Worthy (KC)</t>
-        </is>
-      </c>
-      <c r="C103" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>RJ Harvey (DEN)</t>
+        </is>
+      </c>
+      <c r="C103" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>7.08</t>
         </is>
       </c>
     </row>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>Malik Washington (MIA)</t>
-        </is>
-      </c>
-      <c r="C104" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Aaron Jones Sr. (MIN)</t>
+        </is>
+      </c>
+      <c r="C104" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D104" s="14" t="n">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>Jordan Mason (MIN)</t>
+          <t>MarShawn Lloyd (GB)</t>
         </is>
       </c>
       <c r="C105" s="16" t="inlineStr">
@@ -8785,11 +8785,11 @@
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>15.06</t>
         </is>
       </c>
     </row>
@@ -8799,20 +8799,20 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>Jalen Coker (CAR)</t>
-        </is>
-      </c>
-      <c r="C106" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rachaad White (WAS)</t>
+        </is>
+      </c>
+      <c r="C106" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D106" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -8822,20 +8822,20 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Rashid Shaheed (SEA)</t>
-        </is>
-      </c>
-      <c r="C107" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dalton Kincaid (BUF)</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>KC Concepcion (CLE)</t>
+          <t>Jalen Coker (CAR)</t>
         </is>
       </c>
       <c r="C108" s="17" t="inlineStr">
@@ -8854,11 +8854,11 @@
         </is>
       </c>
       <c r="D108" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>13.02</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>Kayshon Boutte (HOU)</t>
+          <t>Rashid Shaheed (SEA)</t>
         </is>
       </c>
       <c r="C109" s="17" t="inlineStr">
@@ -8877,11 +8877,11 @@
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>13.03</t>
         </is>
       </c>
     </row>
@@ -8891,20 +8891,20 @@
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>Drake Maye (NE)</t>
-        </is>
-      </c>
-      <c r="C110" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Kyle Monangai (CHI)</t>
+        </is>
+      </c>
+      <c r="C110" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D110" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -8914,20 +8914,20 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>Rachaad White (WAS)</t>
-        </is>
-      </c>
-      <c r="C111" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Juwan Johnson (NO)</t>
+        </is>
+      </c>
+      <c r="C111" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Matthew Golden (GB)</t>
+          <t>Jerry Jeudy (CLE)</t>
         </is>
       </c>
       <c r="C112" s="17" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -8960,20 +8960,20 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>Jaxson Dart (NYG)</t>
-        </is>
-      </c>
-      <c r="C113" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Hunter Henry (NE)</t>
+        </is>
+      </c>
+      <c r="C113" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Kyle Pitts Sr. (ATL)</t>
+          <t>Brenton Strange (JAX)</t>
         </is>
       </c>
       <c r="C114" s="18" t="inlineStr">
@@ -8992,11 +8992,11 @@
         </is>
       </c>
       <c r="D114" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>13.08</t>
         </is>
       </c>
     </row>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>Keenan Allen (IND)</t>
+          <t>Denzel Boston (CLE)</t>
         </is>
       </c>
       <c r="C115" s="17" t="inlineStr">
@@ -9015,11 +9015,11 @@
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9029,12 +9029,12 @@
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>Caleb Williams (CHI)</t>
-        </is>
-      </c>
-      <c r="C116" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Makai Lemon (PHI)</t>
+        </is>
+      </c>
+      <c r="C116" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D116" s="14" t="n">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -9052,20 +9052,20 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>Trevor Lawrence (JAX)</t>
-        </is>
-      </c>
-      <c r="C117" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Dalton Schultz (HOU)</t>
+        </is>
+      </c>
+      <c r="C117" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>17.01</t>
         </is>
       </c>
     </row>
@@ -9075,20 +9075,20 @@
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>Blake Corum (LAR)</t>
-        </is>
-      </c>
-      <c r="C118" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Calvin Ridley (TEN)</t>
+        </is>
+      </c>
+      <c r="C118" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D118" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>22.01</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>RJ Harvey (DEN)</t>
+          <t>Jacory Croskey-Merritt (WAS)</t>
         </is>
       </c>
       <c r="C119" s="16" t="inlineStr">
@@ -9107,11 +9107,11 @@
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>10.06</t>
         </is>
       </c>
     </row>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Juwan Johnson (NO)</t>
-        </is>
-      </c>
-      <c r="C120" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jordan Mason (MIN)</t>
+        </is>
+      </c>
+      <c r="C120" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D120" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>10.07</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>Jordyn Tyson (NO)</t>
+          <t>Tre Tucker (LV)</t>
         </is>
       </c>
       <c r="C121" s="17" t="inlineStr">
@@ -9153,11 +9153,11 @@
         </is>
       </c>
       <c r="D121" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>17.1</t>
         </is>
       </c>
     </row>
@@ -9167,20 +9167,20 @@
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>Dalton Schultz (HOU)</t>
-        </is>
-      </c>
-      <c r="C122" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Keenan Allen (IND)</t>
+        </is>
+      </c>
+      <c r="C122" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>17.07</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9190,7 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>Travis Kelce (KC)</t>
+          <t>T.J. Hockenson (MIN)</t>
         </is>
       </c>
       <c r="C123" s="18" t="inlineStr">
@@ -9199,11 +9199,11 @@
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -9213,20 +9213,20 @@
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>Tre Tucker (LV)</t>
-        </is>
-      </c>
-      <c r="C124" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Blake Corum (LAR)</t>
+        </is>
+      </c>
+      <c r="C124" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D124" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>9.08</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr. (MIN)</t>
+          <t>Tyjae Spears (TEN)</t>
         </is>
       </c>
       <c r="C125" s="16" t="inlineStr">
@@ -9245,11 +9245,11 @@
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -9259,20 +9259,20 @@
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>Jake Ferguson (DAL)</t>
-        </is>
-      </c>
-      <c r="C126" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kayshon Boutte (HOU)</t>
+        </is>
+      </c>
+      <c r="C126" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>19.08</t>
         </is>
       </c>
     </row>
@@ -9282,20 +9282,20 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>Dak Prescott (DAL)</t>
-        </is>
-      </c>
-      <c r="C127" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Rashod Bateman (BAL)</t>
+        </is>
+      </c>
+      <c r="C127" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>20.05</t>
         </is>
       </c>
     </row>
@@ -9305,7 +9305,7 @@
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>Dalton Kincaid (BUF)</t>
+          <t>Pat Freiermuth (PIT)</t>
         </is>
       </c>
       <c r="C128" s="18" t="inlineStr">
@@ -9314,11 +9314,11 @@
         </is>
       </c>
       <c r="D128" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>Isaiah Likely (NYG)</t>
+          <t>Greg Dulcich (MIA)</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
@@ -9337,11 +9337,11 @@
         </is>
       </c>
       <c r="D129" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -9351,20 +9351,20 @@
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>Tyjae Spears (TEN)</t>
-        </is>
-      </c>
-      <c r="C130" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kenyon Sadiq (NYJ)</t>
+        </is>
+      </c>
+      <c r="C130" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D130" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>13.1</t>
         </is>
       </c>
     </row>
@@ -9374,20 +9374,20 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>Justin Herbert (LAC)</t>
-        </is>
-      </c>
-      <c r="C131" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Ja'Kobi Lane (BAL)</t>
+        </is>
+      </c>
+      <c r="C131" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>14.02</t>
         </is>
       </c>
     </row>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>Dallas Goedert (PHI)</t>
+          <t>Cade Otton (TB)</t>
         </is>
       </c>
       <c r="C132" s="18" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>20.06</t>
         </is>
       </c>
     </row>
@@ -9420,20 +9420,20 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>Bo Nix (DEN)</t>
-        </is>
-      </c>
-      <c r="C133" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jalen Nailor (LV)</t>
+        </is>
+      </c>
+      <c r="C133" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D133" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -9443,12 +9443,12 @@
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Brock Purdy (SF)</t>
-        </is>
-      </c>
-      <c r="C134" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Devaughn Vele (NO)</t>
+        </is>
+      </c>
+      <c r="C134" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D134" s="14" t="n">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -9466,20 +9466,20 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>Omar Cooper Jr. (NYJ)</t>
-        </is>
-      </c>
-      <c r="C135" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chig Okonkwo (WAS)</t>
+        </is>
+      </c>
+      <c r="C135" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9489,20 +9489,20 @@
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>Jared Goff (DET)</t>
-        </is>
-      </c>
-      <c r="C136" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Woody Marks (HOU)</t>
+        </is>
+      </c>
+      <c r="C136" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D136" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>14.04</t>
         </is>
       </c>
     </row>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>Deebo Samuel Sr. (SF)</t>
+          <t>Cooper Kupp (SEA)</t>
         </is>
       </c>
       <c r="C137" s="17" t="inlineStr">
@@ -9521,11 +9521,11 @@
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>19.05</t>
         </is>
       </c>
     </row>
@@ -9535,20 +9535,20 @@
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>Tyler Shough (NO)</t>
-        </is>
-      </c>
-      <c r="C138" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>AJ Barner (SEA)</t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -9558,20 +9558,20 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>Matthew Stafford (LAR)</t>
-        </is>
-      </c>
-      <c r="C139" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jaylin Noel (HOU)</t>
+        </is>
+      </c>
+      <c r="C139" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>18.1</t>
         </is>
       </c>
     </row>
@@ -9581,20 +9581,20 @@
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>Kyler Murray (MIN)</t>
-        </is>
-      </c>
-      <c r="C140" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Zach Charbonnet (SEA)</t>
+        </is>
+      </c>
+      <c r="C140" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D140" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>13.04</t>
         </is>
       </c>
     </row>
@@ -9604,20 +9604,20 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>Jordan Love (GB)</t>
-        </is>
-      </c>
-      <c r="C141" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Adonai Mitchell (NYJ)</t>
+        </is>
+      </c>
+      <c r="C141" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -9627,20 +9627,20 @@
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>Baker Mayfield (TB)</t>
-        </is>
-      </c>
-      <c r="C142" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Malik Washington (MIA)</t>
+        </is>
+      </c>
+      <c r="C142" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -9650,12 +9650,12 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>Denzel Boston (CLE)</t>
-        </is>
-      </c>
-      <c r="C143" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dylan Sampson (CLE)</t>
+        </is>
+      </c>
+      <c r="C143" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -9673,20 +9673,20 @@
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>Patrick Mahomes (KC)</t>
-        </is>
-      </c>
-      <c r="C144" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Alvin Kamara (NO)</t>
+        </is>
+      </c>
+      <c r="C144" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>14.07</t>
         </is>
       </c>
     </row>
@@ -9696,20 +9696,20 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>Brenton Strange (JAX)</t>
-        </is>
-      </c>
-      <c r="C145" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Germie Bernard (PIT)</t>
+        </is>
+      </c>
+      <c r="C145" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks (PHI)</t>
+          <t>Jordyn Tyson (NO)</t>
         </is>
       </c>
       <c r="C146" s="17" t="inlineStr">
@@ -9728,11 +9728,11 @@
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.07</t>
         </is>
       </c>
     </row>
@@ -9742,20 +9742,20 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Mark Andrews (BAL)</t>
-        </is>
-      </c>
-      <c r="C147" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Caleb Douglas (MIA)</t>
+        </is>
+      </c>
+      <c r="C147" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>18.09</t>
         </is>
       </c>
     </row>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>Pat Bryant (DEN)</t>
+          <t>Omar Cooper Jr. (NYJ)</t>
         </is>
       </c>
       <c r="C148" s="17" t="inlineStr">
@@ -9774,11 +9774,11 @@
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>17.02</t>
         </is>
       </c>
     </row>
@@ -9788,20 +9788,20 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>Malik Willis (MIA)</t>
-        </is>
-      </c>
-      <c r="C149" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Dontayvion Wicks (PHI)</t>
+        </is>
+      </c>
+      <c r="C149" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9811,7 +9811,7 @@
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>Jalen Nailor (LV)</t>
+          <t>Travis Hunter (JAX)</t>
         </is>
       </c>
       <c r="C150" s="17" t="inlineStr">
@@ -9820,11 +9820,11 @@
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Woody Marks (HOU)</t>
+          <t>Mike Washington Jr. (LV)</t>
         </is>
       </c>
       <c r="C151" s="16" t="inlineStr">
@@ -9843,11 +9843,11 @@
         </is>
       </c>
       <c r="D151" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>15.05</t>
         </is>
       </c>
     </row>
@@ -9857,20 +9857,20 @@
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Hunter Henry (NE)</t>
-        </is>
-      </c>
-      <c r="C152" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Darius Slayton (NYG)</t>
+        </is>
+      </c>
+      <c r="C152" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9880,12 +9880,12 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>Chig Okonkwo (WAS)</t>
-        </is>
-      </c>
-      <c r="C153" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Chris Rodriguez Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C153" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>12.08</t>
         </is>
       </c>
     </row>
@@ -9903,20 +9903,20 @@
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>Chris Rodriguez Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C154" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tory Horton (SEA)</t>
+        </is>
+      </c>
+      <c r="C154" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -9926,20 +9926,20 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>Travis Hunter (JAX)</t>
-        </is>
-      </c>
-      <c r="C155" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyler Allgeier (ARI)</t>
+        </is>
+      </c>
+      <c r="C155" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -9949,7 +9949,7 @@
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Cooper Kupp (SEA)</t>
+          <t>Tre' Harris (LAC)</t>
         </is>
       </c>
       <c r="C156" s="17" t="inlineStr">
@@ -9958,11 +9958,11 @@
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Jerry Jeudy (CLE)</t>
+          <t>Jalen Tolbert (MIA)</t>
         </is>
       </c>
       <c r="C157" s="17" t="inlineStr">
@@ -9981,11 +9981,11 @@
         </is>
       </c>
       <c r="D157" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E157" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9995,20 +9995,20 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Cam Ward (TEN)</t>
-        </is>
-      </c>
-      <c r="C158" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Ryan Flournoy (DAL)</t>
+        </is>
+      </c>
+      <c r="C158" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10018,20 +10018,20 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Isiah Pacheco (DET)</t>
-        </is>
-      </c>
-      <c r="C159" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Malachi Fields (NYG)</t>
+        </is>
+      </c>
+      <c r="C159" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E159" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>19.04</t>
         </is>
       </c>
     </row>
@@ -10041,20 +10041,20 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>C.J. Stroud (HOU)</t>
-        </is>
-      </c>
-      <c r="C160" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Keaton Mitchell (LAC)</t>
+        </is>
+      </c>
+      <c r="C160" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10064,20 +10064,20 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>DeMario Douglas (NE)</t>
-        </is>
-      </c>
-      <c r="C161" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Isiah Pacheco (DET)</t>
+        </is>
+      </c>
+      <c r="C161" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E161" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -10087,20 +10087,20 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Malachi Fields (NYG)</t>
-        </is>
-      </c>
-      <c r="C162" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tank Bigsby (PHI)</t>
+        </is>
+      </c>
+      <c r="C162" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D162" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10110,12 +10110,12 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>Sam Darnold (SEA)</t>
-        </is>
-      </c>
-      <c r="C163" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>DeMario Douglas (NE)</t>
+        </is>
+      </c>
+      <c r="C163" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="E163" s="14" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Keaton Mitchell (LAC)</t>
-        </is>
-      </c>
-      <c r="C164" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Zachariah Branch (ATL)</t>
+        </is>
+      </c>
+      <c r="C164" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>Adonai Mitchell (NYJ)</t>
+          <t>Keon Coleman (BUF)</t>
         </is>
       </c>
       <c r="C165" s="17" t="inlineStr">
@@ -10165,11 +10165,11 @@
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E165" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.07</t>
         </is>
       </c>
     </row>
@@ -10179,20 +10179,20 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane (BAL)</t>
-        </is>
-      </c>
-      <c r="C166" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Najee Harris (NYG)</t>
+        </is>
+      </c>
+      <c r="C166" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10202,20 +10202,20 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>Daniel Jones (IND)</t>
-        </is>
-      </c>
-      <c r="C167" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Pat Bryant (DEN)</t>
+        </is>
+      </c>
+      <c r="C167" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E167" s="14" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>19.11</t>
         </is>
       </c>
     </row>
@@ -10225,12 +10225,12 @@
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>Tank Dell (HOU)</t>
-        </is>
-      </c>
-      <c r="C168" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyrone Tracy Jr. (NYG)</t>
+        </is>
+      </c>
+      <c r="C168" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>Germie Bernard (PIT)</t>
+          <t>Tank Dell (HOU)</t>
         </is>
       </c>
       <c r="C169" s="17" t="inlineStr">
@@ -10257,11 +10257,11 @@
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E169" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10271,20 +10271,20 @@
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Zach Charbonnet (SEA)</t>
-        </is>
-      </c>
-      <c r="C170" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Cyrus Allen (KC)</t>
+        </is>
+      </c>
+      <c r="C170" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>Cyrus Allen (KC)</t>
+          <t>Kyle Williams (NE)</t>
         </is>
       </c>
       <c r="C171" s="17" t="inlineStr">
@@ -10303,11 +10303,11 @@
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>19.06</t>
         </is>
       </c>
     </row>
@@ -10317,7 +10317,7 @@
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Tyler Allgeier (ARI)</t>
+          <t>Jonah Coleman (DEN)</t>
         </is>
       </c>
       <c r="C172" s="16" t="inlineStr">
@@ -10326,11 +10326,11 @@
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>15.03</t>
         </is>
       </c>
     </row>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>Dylan Sampson (CLE)</t>
+          <t>Kenneth Walker (KC)</t>
         </is>
       </c>
       <c r="C173" s="16" t="inlineStr">
@@ -10349,11 +10349,11 @@
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -10363,20 +10363,20 @@
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Kyle Williams (NE)</t>
-        </is>
-      </c>
-      <c r="C174" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Josh Allen (BUF)</t>
+        </is>
+      </c>
+      <c r="C174" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>2.09</t>
         </is>
       </c>
     </row>
@@ -10386,20 +10386,20 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>Calvin Ridley (TEN)</t>
-        </is>
-      </c>
-      <c r="C175" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Lamar Jackson (BAL)</t>
+        </is>
+      </c>
+      <c r="C175" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E175" s="14" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>3.09</t>
         </is>
       </c>
     </row>
@@ -10409,20 +10409,20 @@
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>T.J. Hockenson (MIN)</t>
-        </is>
-      </c>
-      <c r="C176" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jalen Hurts (PHI)</t>
+        </is>
+      </c>
+      <c r="C176" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D176" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>5.12</t>
         </is>
       </c>
     </row>
@@ -10432,20 +10432,20 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Mike Washington Jr. (LV)</t>
-        </is>
-      </c>
-      <c r="C177" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jayden Daniels (WAS)</t>
+        </is>
+      </c>
+      <c r="C177" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E177" s="14" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>6.04</t>
         </is>
       </c>
     </row>
@@ -10455,12 +10455,12 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Greg Dulcich (MIA)</t>
-        </is>
-      </c>
-      <c r="C178" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Joe Burrow (CIN)</t>
+        </is>
+      </c>
+      <c r="C178" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -10478,20 +10478,20 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq (NYJ)</t>
-        </is>
-      </c>
-      <c r="C179" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Drake Maye (NE)</t>
+        </is>
+      </c>
+      <c r="C179" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E179" s="14" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -10501,20 +10501,20 @@
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Jonah Coleman (DEN)</t>
-        </is>
-      </c>
-      <c r="C180" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jaxson Dart (NYG)</t>
+        </is>
+      </c>
+      <c r="C180" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -10524,20 +10524,20 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>Tre' Harris (LAC)</t>
-        </is>
-      </c>
-      <c r="C181" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Caleb Williams (CHI)</t>
+        </is>
+      </c>
+      <c r="C181" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Keon Coleman (BUF)</t>
-        </is>
-      </c>
-      <c r="C182" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Trevor Lawrence (JAX)</t>
+        </is>
+      </c>
+      <c r="C182" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D182" s="14" t="n">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -10570,20 +10570,20 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr. (NYG)</t>
-        </is>
-      </c>
-      <c r="C183" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dak Prescott (DAL)</t>
+        </is>
+      </c>
+      <c r="C183" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D183" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E183" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>7.07</t>
         </is>
       </c>
     </row>
@@ -10593,20 +10593,20 @@
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>Pat Freiermuth (PIT)</t>
-        </is>
-      </c>
-      <c r="C184" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Justin Herbert (LAC)</t>
+        </is>
+      </c>
+      <c r="C184" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D184" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Aaron Rodgers (PIT)</t>
+          <t>Bo Nix (DEN)</t>
         </is>
       </c>
       <c r="C185" s="19" t="inlineStr">
@@ -10625,11 +10625,11 @@
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E185" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>10.12</t>
         </is>
       </c>
     </row>
@@ -10639,7 +10639,7 @@
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Bryce Young (CAR)</t>
+          <t>Brock Purdy (SF)</t>
         </is>
       </c>
       <c r="C186" s="19" t="inlineStr">
@@ -10648,11 +10648,11 @@
         </is>
       </c>
       <c r="D186" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>11.02</t>
         </is>
       </c>
     </row>
@@ -10662,20 +10662,20 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>Zachariah Branch (ATL)</t>
-        </is>
-      </c>
-      <c r="C187" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jared Goff (DET)</t>
+        </is>
+      </c>
+      <c r="C187" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D187" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E187" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>12.03</t>
         </is>
       </c>
     </row>
@@ -10685,20 +10685,20 @@
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Ryan Flournoy (DAL)</t>
-        </is>
-      </c>
-      <c r="C188" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyler Shough (NO)</t>
+        </is>
+      </c>
+      <c r="C188" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D188" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>16.07</t>
         </is>
       </c>
     </row>
@@ -10708,20 +10708,20 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Cade Otton (TB)</t>
-        </is>
-      </c>
-      <c r="C189" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Matthew Stafford (LAR)</t>
+        </is>
+      </c>
+      <c r="C189" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E189" s="14" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>9.01</t>
         </is>
       </c>
     </row>
@@ -10731,20 +10731,20 @@
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Tank Bigsby (PHI)</t>
-        </is>
-      </c>
-      <c r="C190" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kyler Murray (MIN)</t>
+        </is>
+      </c>
+      <c r="C190" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D190" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E190" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>14.03</t>
         </is>
       </c>
     </row>
@@ -10754,20 +10754,20 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>Alvin Kamara (NO)</t>
-        </is>
-      </c>
-      <c r="C191" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jordan Love (GB)</t>
+        </is>
+      </c>
+      <c r="C191" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E191" s="14" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>13.05</t>
         </is>
       </c>
     </row>
@@ -10777,20 +10777,20 @@
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Caleb Douglas (MIA)</t>
-        </is>
-      </c>
-      <c r="C192" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Baker Mayfield (TB)</t>
+        </is>
+      </c>
+      <c r="C192" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D192" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Geno Smith (NYJ)</t>
+          <t>Patrick Mahomes (KC)</t>
         </is>
       </c>
       <c r="C193" s="19" t="inlineStr">
@@ -10809,11 +10809,11 @@
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -10823,20 +10823,20 @@
       </c>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>Najee Harris (NYG)</t>
-        </is>
-      </c>
-      <c r="C194" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Malik Willis (MIA)</t>
+        </is>
+      </c>
+      <c r="C194" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D194" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E194" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -10846,20 +10846,20 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Brian Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C195" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Cam Ward (TEN)</t>
+        </is>
+      </c>
+      <c r="C195" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E195" s="14" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>Devaughn Vele (NO)</t>
-        </is>
-      </c>
-      <c r="C196" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>C.J. Stroud (HOU)</t>
+        </is>
+      </c>
+      <c r="C196" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D196" s="14" t="n">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="E196" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>18.01</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>AJ Barner (SEA)</t>
-        </is>
-      </c>
-      <c r="C197" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Sam Darnold (SEA)</t>
+        </is>
+      </c>
+      <c r="C197" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D197" s="14" t="n">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="E197" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>14.05</t>
         </is>
       </c>
     </row>
@@ -10915,20 +10915,20 @@
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Jaylin Noel (HOU)</t>
-        </is>
-      </c>
-      <c r="C198" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Daniel Jones (IND)</t>
+        </is>
+      </c>
+      <c r="C198" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D198" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>17.11</t>
         </is>
       </c>
     </row>
@@ -10938,20 +10938,20 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>Darius Slayton (NYG)</t>
-        </is>
-      </c>
-      <c r="C199" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Aaron Rodgers (PIT)</t>
+        </is>
+      </c>
+      <c r="C199" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E199" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10961,20 +10961,20 @@
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Oronde Gadsden (LAC)</t>
-        </is>
-      </c>
-      <c r="C200" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Bryce Young (CAR)</t>
+        </is>
+      </c>
+      <c r="C200" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D200" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>19.12</t>
         </is>
       </c>
     </row>
@@ -10984,12 +10984,12 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>Rashod Bateman (BAL)</t>
-        </is>
-      </c>
-      <c r="C201" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Geno Smith (NYJ)</t>
+        </is>
+      </c>
+      <c r="C201" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D201" s="14" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11007,20 +11007,20 @@
       </c>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>Jalen Tolbert (MIA)</t>
-        </is>
-      </c>
-      <c r="C202" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brian Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C202" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D202" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E202" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.12</t>
         </is>
       </c>
     </row>
@@ -11030,20 +11030,20 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>Tory Horton (SEA)</t>
-        </is>
-      </c>
-      <c r="C203" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Oronde Gadsden (LAC)</t>
+        </is>
+      </c>
+      <c r="C203" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D203" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>

--- a/assets/data/12guys1cup-cheat-sheet.xlsx
+++ b/assets/data/12guys1cup-cheat-sheet.xlsx
@@ -6499,7 +6499,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Puka Nacua (LAR)</t>
+          <t>Ja'Marr Chase (CIN)</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
@@ -6508,11 +6508,11 @@
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase (CIN)</t>
+          <t>Puka Nacua (LAR)</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
@@ -6531,11 +6531,11 @@
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
     </row>
@@ -6614,20 +6614,20 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Jonathan Taylor (IND)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>CeeDee Lamb (DAL)</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>De'Von Achane (MIA)</t>
+          <t>Jonathan Taylor (IND)</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -6646,11 +6646,11 @@
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Chase Brown (CIN)</t>
+          <t>James Cook III (BUF)</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -6669,11 +6669,11 @@
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.11</t>
         </is>
       </c>
     </row>
@@ -6683,20 +6683,20 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Drake London (ATL)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>De'Von Achane (MIA)</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Derrick Henry (BAL)</t>
+          <t>Kenneth Walker (KC)</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
@@ -6715,11 +6715,11 @@
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -6729,12 +6729,12 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Justin Jefferson (MIN)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chase Brown (CIN)</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>CeeDee Lamb (DAL)</t>
+          <t>Justin Jefferson (MIN)</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
@@ -6761,11 +6761,11 @@
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6775,20 +6775,20 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>James Cook III (BUF)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>A.J. Brown (NE)</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Rashee Rice (KC)</t>
+          <t>Chris Olave (NO)</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
@@ -6807,11 +6807,11 @@
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.07</t>
         </is>
       </c>
     </row>
@@ -6821,20 +6821,20 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Saquon Barkley (PHI)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Brock Bowers (LV)</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Chris Olave (NO)</t>
+          <t>Nico Collins (HOU)</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -6867,20 +6867,20 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Ashton Jeanty (LV)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Trey McBride (ARI)</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>A.J. Brown (NE)</t>
+          <t>Garrett Wilson (NYJ)</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
@@ -6899,11 +6899,11 @@
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -6913,20 +6913,20 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Trey McBride (ARI)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Drake London (ATL)</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -6936,20 +6936,20 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Omarion Hampton (LAC)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>George Pickens (DAL)</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>George Pickens (DAL)</t>
+          <t>Rashee Rice (KC)</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
@@ -6968,11 +6968,11 @@
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Jeremiyah Love (ARI)</t>
+          <t>Omarion Hampton (LAC)</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
@@ -6991,11 +6991,11 @@
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7005,20 +7005,20 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Nico Collins (HOU)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Ashton Jeanty (LV)</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -7028,20 +7028,20 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Breece Hall (NYJ)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Malik Nabers (NYG)</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -7051,20 +7051,20 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Brock Bowers (LV)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Saquon Barkley (PHI)</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Garrett Wilson (NYJ)</t>
+          <t>Zay Flowers (BAL)</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.05</t>
         </is>
       </c>
     </row>
@@ -7097,12 +7097,12 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Zay Flowers (BAL)</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Derrick Henry (BAL)</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>2.08</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Malik Nabers (NYG)</t>
+          <t>DeVonta Smith (PHI)</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
@@ -7129,11 +7129,11 @@
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.12</t>
         </is>
       </c>
     </row>
@@ -7143,20 +7143,20 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Javonte Williams (DAL)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jaylen Waddle (DEN)</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -7166,20 +7166,20 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>DeVonta Smith (PHI)</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jeremiyah Love (ARI)</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr. (NO)</t>
+          <t>Kyren Williams (LAR)</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
@@ -7198,11 +7198,11 @@
         </is>
       </c>
       <c r="D36" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
@@ -7212,20 +7212,20 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Kyren Williams (LAR)</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ladd McConkey (LAC)</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>4.02</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7235,7 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Cam Skattebo (NYG)</t>
+          <t>Breece Hall (NYJ)</t>
         </is>
       </c>
       <c r="C38" s="16" t="inlineStr">
@@ -7244,11 +7244,11 @@
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan (CAR)</t>
+          <t>Emeka Egbuka (TB)</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
@@ -7267,11 +7267,11 @@
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.03</t>
         </is>
       </c>
     </row>
@@ -7281,12 +7281,12 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>Emeka Egbuka (TB)</t>
-        </is>
-      </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>D'Andre Swift (CHI)</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D40" s="14" t="n">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -7304,20 +7304,20 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>D'Andre Swift (CHI)</t>
-        </is>
-      </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tetairoa McMillan (CAR)</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.01</t>
         </is>
       </c>
     </row>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Davante Adams (LAR)</t>
+          <t>Tee Higgins (CIN)</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
@@ -7336,11 +7336,11 @@
         </is>
       </c>
       <c r="D42" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>3.11</t>
         </is>
       </c>
     </row>
@@ -7350,7 +7350,7 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Tee Higgins (CIN)</t>
+          <t>Carnell Tate (TEN)</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
@@ -7359,11 +7359,11 @@
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Bucky Irving (TB)</t>
+          <t>Javonte Williams (DAL)</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
@@ -7382,11 +7382,11 @@
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7396,12 +7396,12 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Ladd McConkey (LAC)</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Josh Allen (BUF)</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>2.09</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>Jameson Williams (DET)</t>
+          <t>Luther Burden III (CHI)</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
@@ -7428,11 +7428,11 @@
         </is>
       </c>
       <c r="D46" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Quinshon Judkins (CLE)</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Christian Watson (GB)</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Colston Loveland (CHI)</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Bucky Irving (TB)</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D48" s="14" t="n">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.06</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Waddle (DEN)</t>
+          <t>Parker Washington (JAX)</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
@@ -7497,11 +7497,11 @@
         </is>
       </c>
       <c r="D49" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>7.04</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten (JAX)</t>
+          <t>Travis Etienne Jr. (NO)</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
@@ -7520,11 +7520,11 @@
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>4.09</t>
         </is>
       </c>
     </row>
@@ -7534,20 +7534,20 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Terry McLaurin (WAS)</t>
-        </is>
-      </c>
-      <c r="C51" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Cam Skattebo (NYG)</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D51" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>4.08</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>DJ Moore (BUF)</t>
+          <t>Terry McLaurin (WAS)</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Luther Burden III (CHI)</t>
+          <t>Jameson Williams (DET)</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
@@ -7589,11 +7589,11 @@
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>Rome Odunze (CHI)</t>
+          <t>DJ Moore (BUF)</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
@@ -7612,11 +7612,11 @@
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>5.09</t>
         </is>
       </c>
     </row>
@@ -7626,20 +7626,20 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Tyler Warren (IND)</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Bhayshul Tuten (JAX)</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -7649,12 +7649,12 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Harold Fannin Jr. (CLE)</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Davante Adams (LAR)</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.02</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7672,7 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Courtland Sutton (DEN)</t>
+          <t>Mike Evans (SF)</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
@@ -7681,11 +7681,11 @@
         </is>
       </c>
       <c r="D57" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -7695,20 +7695,20 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>David Montgomery (HOU)</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rome Odunze (CHI)</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D58" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>6.05</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Christian Watson (GB)</t>
+          <t>Marvin Harrison Jr. (ARI)</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
@@ -7727,11 +7727,11 @@
         </is>
       </c>
       <c r="D59" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr. (ARI)</t>
+          <t>DK Metcalf (PIT)</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="D60" s="14" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
@@ -7764,20 +7764,20 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Warren (PIT)</t>
-        </is>
-      </c>
-      <c r="C61" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tyler Warren (IND)</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>4.11</t>
         </is>
       </c>
     </row>
@@ -7787,20 +7787,20 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Mike Evans (SF)</t>
-        </is>
-      </c>
-      <c r="C62" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Colston Loveland (CHI)</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D62" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>4.04</t>
         </is>
       </c>
     </row>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>DK Metcalf (PIT)</t>
+          <t>Alec Pierce (IND)</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
@@ -7819,11 +7819,11 @@
         </is>
       </c>
       <c r="D63" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>9.05</t>
         </is>
       </c>
     </row>
@@ -7833,20 +7833,20 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson (NE)</t>
-        </is>
-      </c>
-      <c r="C64" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Brian Thomas Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D64" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>7.02</t>
         </is>
       </c>
     </row>
@@ -7856,20 +7856,20 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Alec Pierce (IND)</t>
-        </is>
-      </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Quinshon Judkins (CLE)</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D65" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson (NE)</t>
+          <t>TreVeyon Henderson (NE)</t>
         </is>
       </c>
       <c r="C66" s="16" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -7902,20 +7902,20 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>Michael Pittman Jr. (PIT)</t>
-        </is>
-      </c>
-      <c r="C67" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>David Montgomery (HOU)</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D67" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -7925,20 +7925,20 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Tony Pollard (TEN)</t>
-        </is>
-      </c>
-      <c r="C68" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Lamar Jackson (BAL)</t>
+        </is>
+      </c>
+      <c r="C68" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D68" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>3.09</t>
         </is>
       </c>
     </row>
@@ -7948,20 +7948,20 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Jadarian Price (SEA)</t>
-        </is>
-      </c>
-      <c r="C69" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Chris Godwin Jr. (TB)</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D69" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>8.12</t>
         </is>
       </c>
     </row>
@@ -7971,12 +7971,12 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Kyle Pitts Sr. (ATL)</t>
-        </is>
-      </c>
-      <c r="C70" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jadarian Price (SEA)</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D70" s="14" t="n">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -7994,20 +7994,20 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>George Kittle (SF)</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>MarShawn Lloyd (GB)</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>15.06</t>
         </is>
       </c>
     </row>
@@ -8017,20 +8017,20 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Parker Washington (JAX)</t>
-        </is>
-      </c>
-      <c r="C72" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rhamondre Stevenson (NE)</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -8040,20 +8040,20 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Sam LaPorta (DET)</t>
-        </is>
-      </c>
-      <c r="C73" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Quentin Johnston (LAC)</t>
+        </is>
+      </c>
+      <c r="C73" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>10.05</t>
         </is>
       </c>
     </row>
@@ -8063,20 +8063,20 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Travis Kelce (KC)</t>
-        </is>
-      </c>
-      <c r="C74" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Michael Pittman Jr. (PIT)</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D74" s="14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>9.07</t>
         </is>
       </c>
     </row>
@@ -8086,20 +8086,20 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C75" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rico Dowdle (PIT)</t>
+        </is>
+      </c>
+      <c r="C75" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>8.01</t>
         </is>
       </c>
     </row>
@@ -8109,12 +8109,12 @@
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Rico Dowdle (PIT)</t>
-        </is>
-      </c>
-      <c r="C76" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Wan'Dale Robinson (TEN)</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D76" s="14" t="n">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>10.09</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>Dallas Goedert (PHI)</t>
+          <t>Harold Fannin Jr. (CLE)</t>
         </is>
       </c>
       <c r="C77" s="18" t="inlineStr">
@@ -8141,11 +8141,11 @@
         </is>
       </c>
       <c r="D77" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson (TEN)</t>
+          <t>Michael Wilson (ARI)</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
@@ -8164,11 +8164,11 @@
         </is>
       </c>
       <c r="D78" s="14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>7.11</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>Carnell Tate (TEN)</t>
+          <t>Stefon Diggs (WAS)</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
@@ -8187,11 +8187,11 @@
         </is>
       </c>
       <c r="D79" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>10.02</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Michael Wilson (ARI)</t>
+          <t>Courtland Sutton (DEN)</t>
         </is>
       </c>
       <c r="C80" s="17" t="inlineStr">
@@ -8210,11 +8210,11 @@
         </is>
       </c>
       <c r="D80" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.09</t>
         </is>
       </c>
     </row>
@@ -8224,20 +8224,20 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>Jayden Reed (GB)</t>
-        </is>
-      </c>
-      <c r="C81" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jacory Croskey-Merritt (WAS)</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D81" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>10.06</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>J.K. Dobbins (DEN)</t>
+          <t>Kenny Gainwell (TB)</t>
         </is>
       </c>
       <c r="C82" s="16" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8270,20 +8270,20 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>Jakobi Meyers (JAX)</t>
-        </is>
-      </c>
-      <c r="C83" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jaylen Warren (PIT)</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D83" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr. (TB)</t>
+          <t>Jordan Addison (MIN)</t>
         </is>
       </c>
       <c r="C84" s="17" t="inlineStr">
@@ -8302,11 +8302,11 @@
         </is>
       </c>
       <c r="D84" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>9.09</t>
         </is>
       </c>
     </row>
@@ -8316,20 +8316,20 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>Chuba Hubbard (CAR)</t>
-        </is>
-      </c>
-      <c r="C85" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>De'Zhaun Stribling (SF)</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D85" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>12.07</t>
         </is>
       </c>
     </row>
@@ -8362,12 +8362,12 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>Kenny Gainwell (TB)</t>
-        </is>
-      </c>
-      <c r="C87" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jalen Hurts (PHI)</t>
+        </is>
+      </c>
+      <c r="C87" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D87" s="14" t="n">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>5.12</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8385,7 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Quentin Johnston (LAC)</t>
+          <t>Jayden Reed (GB)</t>
         </is>
       </c>
       <c r="C88" s="17" t="inlineStr">
@@ -8394,11 +8394,11 @@
         </is>
       </c>
       <c r="D88" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>Stefon Diggs (WAS)</t>
-        </is>
-      </c>
-      <c r="C89" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jayden Daniels (WAS)</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D89" s="14" t="n">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>6.04</t>
         </is>
       </c>
     </row>
@@ -8431,12 +8431,12 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Jordan Addison (MIN)</t>
-        </is>
-      </c>
-      <c r="C90" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Joe Burrow (CIN)</t>
+        </is>
+      </c>
+      <c r="C90" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D90" s="14" t="n">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>Jake Ferguson (DAL)</t>
+          <t>George Kittle (SF)</t>
         </is>
       </c>
       <c r="C91" s="18" t="inlineStr">
@@ -8463,11 +8463,11 @@
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -8477,20 +8477,20 @@
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>Mark Andrews (BAL)</t>
-        </is>
-      </c>
-      <c r="C92" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Chuba Hubbard (CAR)</t>
+        </is>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D92" s="14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>7.05</t>
         </is>
       </c>
     </row>
@@ -8500,20 +8500,20 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>Xavier Worthy (KC)</t>
-        </is>
-      </c>
-      <c r="C93" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>J.K. Dobbins (DEN)</t>
+        </is>
+      </c>
+      <c r="C93" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D93" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>8.1</t>
         </is>
       </c>
     </row>
@@ -8523,20 +8523,20 @@
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling (SF)</t>
-        </is>
-      </c>
-      <c r="C94" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tony Pollard (TEN)</t>
+        </is>
+      </c>
+      <c r="C94" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D94" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>7.12</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>Matthew Golden (GB)</t>
+          <t>Josh Downs (IND)</t>
         </is>
       </c>
       <c r="C95" s="17" t="inlineStr">
@@ -8555,11 +8555,11 @@
         </is>
       </c>
       <c r="D95" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>10.01</t>
         </is>
       </c>
     </row>
@@ -8569,20 +8569,20 @@
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Isaiah Likely (NYG)</t>
-        </is>
-      </c>
-      <c r="C96" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jonathon Brooks (CAR)</t>
+        </is>
+      </c>
+      <c r="C96" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D96" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>9.1</t>
         </is>
       </c>
     </row>
@@ -8592,20 +8592,20 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>Jonathon Brooks (CAR)</t>
-        </is>
-      </c>
-      <c r="C97" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jakobi Meyers (JAX)</t>
+        </is>
+      </c>
+      <c r="C97" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>10.1</t>
         </is>
       </c>
     </row>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>Khalil Shakir (BUF)</t>
+          <t>Romeo Doubs (NE)</t>
         </is>
       </c>
       <c r="C98" s="17" t="inlineStr">
@@ -8624,11 +8624,11 @@
         </is>
       </c>
       <c r="D98" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -8638,20 +8638,20 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>KC Concepcion (CLE)</t>
-        </is>
-      </c>
-      <c r="C99" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Sam LaPorta (DET)</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>Romeo Doubs (NE)</t>
+          <t>Khalil Shakir (BUF)</t>
         </is>
       </c>
       <c r="C100" s="17" t="inlineStr">
@@ -8670,11 +8670,11 @@
         </is>
       </c>
       <c r="D100" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>12.11</t>
         </is>
       </c>
     </row>
@@ -8684,20 +8684,20 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>Josh Downs (IND)</t>
-        </is>
-      </c>
-      <c r="C101" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kyle Monangai (CHI)</t>
+        </is>
+      </c>
+      <c r="C101" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Deebo Samuel Sr. (SF)</t>
+          <t>Makai Lemon (PHI)</t>
         </is>
       </c>
       <c r="C102" s="17" t="inlineStr">
@@ -8716,11 +8716,11 @@
         </is>
       </c>
       <c r="D102" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -8730,20 +8730,20 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>RJ Harvey (DEN)</t>
-        </is>
-      </c>
-      <c r="C103" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Xavier Worthy (KC)</t>
+        </is>
+      </c>
+      <c r="C103" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr. (MIN)</t>
-        </is>
-      </c>
-      <c r="C104" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Malik Washington (MIA)</t>
+        </is>
+      </c>
+      <c r="C104" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D104" s="14" t="n">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd (GB)</t>
+          <t>Jordan Mason (MIN)</t>
         </is>
       </c>
       <c r="C105" s="16" t="inlineStr">
@@ -8785,11 +8785,11 @@
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>10.07</t>
         </is>
       </c>
     </row>
@@ -8799,20 +8799,20 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>Rachaad White (WAS)</t>
-        </is>
-      </c>
-      <c r="C106" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jalen Coker (CAR)</t>
+        </is>
+      </c>
+      <c r="C106" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D106" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>13.02</t>
         </is>
       </c>
     </row>
@@ -8822,20 +8822,20 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Dalton Kincaid (BUF)</t>
-        </is>
-      </c>
-      <c r="C107" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Rashid Shaheed (SEA)</t>
+        </is>
+      </c>
+      <c r="C107" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>13.03</t>
         </is>
       </c>
     </row>
@@ -8845,7 +8845,7 @@
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>Jalen Coker (CAR)</t>
+          <t>KC Concepcion (CLE)</t>
         </is>
       </c>
       <c r="C108" s="17" t="inlineStr">
@@ -8854,11 +8854,11 @@
         </is>
       </c>
       <c r="D108" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>11.01</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>Rashid Shaheed (SEA)</t>
+          <t>Kayshon Boutte (HOU)</t>
         </is>
       </c>
       <c r="C109" s="17" t="inlineStr">
@@ -8877,11 +8877,11 @@
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>19.08</t>
         </is>
       </c>
     </row>
@@ -8891,20 +8891,20 @@
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>Kyle Monangai (CHI)</t>
-        </is>
-      </c>
-      <c r="C110" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Drake Maye (NE)</t>
+        </is>
+      </c>
+      <c r="C110" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D110" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -8914,20 +8914,20 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>Juwan Johnson (NO)</t>
-        </is>
-      </c>
-      <c r="C111" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Rachaad White (WAS)</t>
+        </is>
+      </c>
+      <c r="C111" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -8937,7 +8937,7 @@
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Jerry Jeudy (CLE)</t>
+          <t>Matthew Golden (GB)</t>
         </is>
       </c>
       <c r="C112" s="17" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>11.07</t>
         </is>
       </c>
     </row>
@@ -8960,20 +8960,20 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>Hunter Henry (NE)</t>
-        </is>
-      </c>
-      <c r="C113" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jaxson Dart (NYG)</t>
+        </is>
+      </c>
+      <c r="C113" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Brenton Strange (JAX)</t>
+          <t>Kyle Pitts Sr. (ATL)</t>
         </is>
       </c>
       <c r="C114" s="18" t="inlineStr">
@@ -8992,11 +8992,11 @@
         </is>
       </c>
       <c r="D114" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>6.1</t>
         </is>
       </c>
     </row>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>Denzel Boston (CLE)</t>
+          <t>Keenan Allen (IND)</t>
         </is>
       </c>
       <c r="C115" s="17" t="inlineStr">
@@ -9015,11 +9015,11 @@
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>17.07</t>
         </is>
       </c>
     </row>
@@ -9029,12 +9029,12 @@
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>Makai Lemon (PHI)</t>
-        </is>
-      </c>
-      <c r="C116" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Caleb Williams (CHI)</t>
+        </is>
+      </c>
+      <c r="C116" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D116" s="14" t="n">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -9052,20 +9052,20 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>Dalton Schultz (HOU)</t>
-        </is>
-      </c>
-      <c r="C117" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Trevor Lawrence (JAX)</t>
+        </is>
+      </c>
+      <c r="C117" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -9075,20 +9075,20 @@
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>Calvin Ridley (TEN)</t>
-        </is>
-      </c>
-      <c r="C118" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Blake Corum (LAR)</t>
+        </is>
+      </c>
+      <c r="C118" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D118" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>9.08</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt (WAS)</t>
+          <t>RJ Harvey (DEN)</t>
         </is>
       </c>
       <c r="C119" s="16" t="inlineStr">
@@ -9107,11 +9107,11 @@
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>7.08</t>
         </is>
       </c>
     </row>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Jordan Mason (MIN)</t>
-        </is>
-      </c>
-      <c r="C120" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Juwan Johnson (NO)</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D120" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>Tre Tucker (LV)</t>
+          <t>Jordyn Tyson (NO)</t>
         </is>
       </c>
       <c r="C121" s="17" t="inlineStr">
@@ -9153,11 +9153,11 @@
         </is>
       </c>
       <c r="D121" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>8.07</t>
         </is>
       </c>
     </row>
@@ -9167,20 +9167,20 @@
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>Keenan Allen (IND)</t>
-        </is>
-      </c>
-      <c r="C122" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dalton Schultz (HOU)</t>
+        </is>
+      </c>
+      <c r="C122" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>17.01</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9190,7 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>T.J. Hockenson (MIN)</t>
+          <t>Travis Kelce (KC)</t>
         </is>
       </c>
       <c r="C123" s="18" t="inlineStr">
@@ -9199,11 +9199,11 @@
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>8.08</t>
         </is>
       </c>
     </row>
@@ -9213,20 +9213,20 @@
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>Blake Corum (LAR)</t>
-        </is>
-      </c>
-      <c r="C124" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tre Tucker (LV)</t>
+        </is>
+      </c>
+      <c r="C124" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D124" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>17.1</t>
         </is>
       </c>
     </row>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>Tyjae Spears (TEN)</t>
+          <t>Aaron Jones Sr. (MIN)</t>
         </is>
       </c>
       <c r="C125" s="16" t="inlineStr">
@@ -9245,11 +9245,11 @@
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -9259,20 +9259,20 @@
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>Kayshon Boutte (HOU)</t>
-        </is>
-      </c>
-      <c r="C126" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jake Ferguson (DAL)</t>
+        </is>
+      </c>
+      <c r="C126" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>9.02</t>
         </is>
       </c>
     </row>
@@ -9282,20 +9282,20 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>Rashod Bateman (BAL)</t>
-        </is>
-      </c>
-      <c r="C127" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dak Prescott (DAL)</t>
+        </is>
+      </c>
+      <c r="C127" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>7.07</t>
         </is>
       </c>
     </row>
@@ -9305,7 +9305,7 @@
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>Pat Freiermuth (PIT)</t>
+          <t>Dalton Kincaid (BUF)</t>
         </is>
       </c>
       <c r="C128" s="18" t="inlineStr">
@@ -9314,11 +9314,11 @@
         </is>
       </c>
       <c r="D128" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>Greg Dulcich (MIA)</t>
+          <t>Isaiah Likely (NYG)</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
@@ -9337,11 +9337,11 @@
         </is>
       </c>
       <c r="D129" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -9351,20 +9351,20 @@
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq (NYJ)</t>
-        </is>
-      </c>
-      <c r="C130" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tyjae Spears (TEN)</t>
+        </is>
+      </c>
+      <c r="C130" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D130" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -9374,20 +9374,20 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane (BAL)</t>
-        </is>
-      </c>
-      <c r="C131" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Justin Herbert (LAC)</t>
+        </is>
+      </c>
+      <c r="C131" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>Cade Otton (TB)</t>
+          <t>Dallas Goedert (PHI)</t>
         </is>
       </c>
       <c r="C132" s="18" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -9420,20 +9420,20 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>Jalen Nailor (LV)</t>
-        </is>
-      </c>
-      <c r="C133" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Bo Nix (DEN)</t>
+        </is>
+      </c>
+      <c r="C133" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D133" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>10.12</t>
         </is>
       </c>
     </row>
@@ -9443,12 +9443,12 @@
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Devaughn Vele (NO)</t>
-        </is>
-      </c>
-      <c r="C134" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brock Purdy (SF)</t>
+        </is>
+      </c>
+      <c r="C134" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D134" s="14" t="n">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>11.02</t>
         </is>
       </c>
     </row>
@@ -9466,20 +9466,20 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>Chig Okonkwo (WAS)</t>
-        </is>
-      </c>
-      <c r="C135" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Omar Cooper Jr. (NYJ)</t>
+        </is>
+      </c>
+      <c r="C135" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>17.02</t>
         </is>
       </c>
     </row>
@@ -9489,20 +9489,20 @@
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>Woody Marks (HOU)</t>
-        </is>
-      </c>
-      <c r="C136" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jared Goff (DET)</t>
+        </is>
+      </c>
+      <c r="C136" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D136" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>12.03</t>
         </is>
       </c>
     </row>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>Cooper Kupp (SEA)</t>
+          <t>Deebo Samuel Sr. (SF)</t>
         </is>
       </c>
       <c r="C137" s="17" t="inlineStr">
@@ -9521,11 +9521,11 @@
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>11.11</t>
         </is>
       </c>
     </row>
@@ -9535,20 +9535,20 @@
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>AJ Barner (SEA)</t>
-        </is>
-      </c>
-      <c r="C138" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tyler Shough (NO)</t>
+        </is>
+      </c>
+      <c r="C138" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>16.07</t>
         </is>
       </c>
     </row>
@@ -9558,20 +9558,20 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>Jaylin Noel (HOU)</t>
-        </is>
-      </c>
-      <c r="C139" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Matthew Stafford (LAR)</t>
+        </is>
+      </c>
+      <c r="C139" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>9.01</t>
         </is>
       </c>
     </row>
@@ -9581,20 +9581,20 @@
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>Zach Charbonnet (SEA)</t>
-        </is>
-      </c>
-      <c r="C140" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kyler Murray (MIN)</t>
+        </is>
+      </c>
+      <c r="C140" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D140" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>14.03</t>
         </is>
       </c>
     </row>
@@ -9604,20 +9604,20 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>Adonai Mitchell (NYJ)</t>
-        </is>
-      </c>
-      <c r="C141" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jordan Love (GB)</t>
+        </is>
+      </c>
+      <c r="C141" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>13.05</t>
         </is>
       </c>
     </row>
@@ -9627,20 +9627,20 @@
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>Malik Washington (MIA)</t>
-        </is>
-      </c>
-      <c r="C142" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Baker Mayfield (TB)</t>
+        </is>
+      </c>
+      <c r="C142" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -9650,12 +9650,12 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>Dylan Sampson (CLE)</t>
-        </is>
-      </c>
-      <c r="C143" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Denzel Boston (CLE)</t>
+        </is>
+      </c>
+      <c r="C143" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9673,20 +9673,20 @@
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>Alvin Kamara (NO)</t>
-        </is>
-      </c>
-      <c r="C144" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Patrick Mahomes (KC)</t>
+        </is>
+      </c>
+      <c r="C144" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -9696,20 +9696,20 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>Germie Bernard (PIT)</t>
-        </is>
-      </c>
-      <c r="C145" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brenton Strange (JAX)</t>
+        </is>
+      </c>
+      <c r="C145" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>13.08</t>
         </is>
       </c>
     </row>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>Jordyn Tyson (NO)</t>
+          <t>Dontayvion Wicks (PHI)</t>
         </is>
       </c>
       <c r="C146" s="17" t="inlineStr">
@@ -9728,11 +9728,11 @@
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9742,20 +9742,20 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Caleb Douglas (MIA)</t>
-        </is>
-      </c>
-      <c r="C147" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Mark Andrews (BAL)</t>
+        </is>
+      </c>
+      <c r="C147" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>11.09</t>
         </is>
       </c>
     </row>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>Omar Cooper Jr. (NYJ)</t>
+          <t>Pat Bryant (DEN)</t>
         </is>
       </c>
       <c r="C148" s="17" t="inlineStr">
@@ -9774,11 +9774,11 @@
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>19.11</t>
         </is>
       </c>
     </row>
@@ -9788,20 +9788,20 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks (PHI)</t>
-        </is>
-      </c>
-      <c r="C149" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Malik Willis (MIA)</t>
+        </is>
+      </c>
+      <c r="C149" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -9811,7 +9811,7 @@
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>Travis Hunter (JAX)</t>
+          <t>Jalen Nailor (LV)</t>
         </is>
       </c>
       <c r="C150" s="17" t="inlineStr">
@@ -9820,11 +9820,11 @@
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Mike Washington Jr. (LV)</t>
+          <t>Woody Marks (HOU)</t>
         </is>
       </c>
       <c r="C151" s="16" t="inlineStr">
@@ -9843,11 +9843,11 @@
         </is>
       </c>
       <c r="D151" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>14.04</t>
         </is>
       </c>
     </row>
@@ -9857,20 +9857,20 @@
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Darius Slayton (NYG)</t>
-        </is>
-      </c>
-      <c r="C152" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Hunter Henry (NE)</t>
+        </is>
+      </c>
+      <c r="C152" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -9880,12 +9880,12 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>Chris Rodriguez Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C153" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Chig Okonkwo (WAS)</t>
+        </is>
+      </c>
+      <c r="C153" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9903,20 +9903,20 @@
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>Tory Horton (SEA)</t>
-        </is>
-      </c>
-      <c r="C154" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chris Rodriguez Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C154" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>12.08</t>
         </is>
       </c>
     </row>
@@ -9926,20 +9926,20 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>Tyler Allgeier (ARI)</t>
-        </is>
-      </c>
-      <c r="C155" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Travis Hunter (JAX)</t>
+        </is>
+      </c>
+      <c r="C155" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9949,7 +9949,7 @@
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Tre' Harris (LAC)</t>
+          <t>Cooper Kupp (SEA)</t>
         </is>
       </c>
       <c r="C156" s="17" t="inlineStr">
@@ -9958,11 +9958,11 @@
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>19.05</t>
         </is>
       </c>
     </row>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Jalen Tolbert (MIA)</t>
+          <t>Jerry Jeudy (CLE)</t>
         </is>
       </c>
       <c r="C157" s="17" t="inlineStr">
@@ -9981,11 +9981,11 @@
         </is>
       </c>
       <c r="D157" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E157" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -9995,20 +9995,20 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Ryan Flournoy (DAL)</t>
-        </is>
-      </c>
-      <c r="C158" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Cam Ward (TEN)</t>
+        </is>
+      </c>
+      <c r="C158" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10018,20 +10018,20 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Malachi Fields (NYG)</t>
-        </is>
-      </c>
-      <c r="C159" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Isiah Pacheco (DET)</t>
+        </is>
+      </c>
+      <c r="C159" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E159" s="14" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -10041,20 +10041,20 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>Keaton Mitchell (LAC)</t>
-        </is>
-      </c>
-      <c r="C160" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>C.J. Stroud (HOU)</t>
+        </is>
+      </c>
+      <c r="C160" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>18.01</t>
         </is>
       </c>
     </row>
@@ -10064,20 +10064,20 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>Isiah Pacheco (DET)</t>
-        </is>
-      </c>
-      <c r="C161" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DeMario Douglas (NE)</t>
+        </is>
+      </c>
+      <c r="C161" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E161" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10087,20 +10087,20 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Tank Bigsby (PHI)</t>
-        </is>
-      </c>
-      <c r="C162" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Malachi Fields (NYG)</t>
+        </is>
+      </c>
+      <c r="C162" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D162" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>19.04</t>
         </is>
       </c>
     </row>
@@ -10110,12 +10110,12 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>DeMario Douglas (NE)</t>
-        </is>
-      </c>
-      <c r="C163" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Sam Darnold (SEA)</t>
+        </is>
+      </c>
+      <c r="C163" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="E163" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.05</t>
         </is>
       </c>
     </row>
@@ -10133,20 +10133,20 @@
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Zachariah Branch (ATL)</t>
-        </is>
-      </c>
-      <c r="C164" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Keaton Mitchell (LAC)</t>
+        </is>
+      </c>
+      <c r="C164" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>Keon Coleman (BUF)</t>
+          <t>Adonai Mitchell (NYJ)</t>
         </is>
       </c>
       <c r="C165" s="17" t="inlineStr">
@@ -10165,11 +10165,11 @@
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E165" s="14" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10179,20 +10179,20 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Najee Harris (NYG)</t>
-        </is>
-      </c>
-      <c r="C166" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ja'Kobi Lane (BAL)</t>
+        </is>
+      </c>
+      <c r="C166" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.02</t>
         </is>
       </c>
     </row>
@@ -10202,20 +10202,20 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>Pat Bryant (DEN)</t>
-        </is>
-      </c>
-      <c r="C167" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Daniel Jones (IND)</t>
+        </is>
+      </c>
+      <c r="C167" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E167" s="14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>17.11</t>
         </is>
       </c>
     </row>
@@ -10225,12 +10225,12 @@
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr. (NYG)</t>
-        </is>
-      </c>
-      <c r="C168" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tank Dell (HOU)</t>
+        </is>
+      </c>
+      <c r="C168" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>Tank Dell (HOU)</t>
+          <t>Germie Bernard (PIT)</t>
         </is>
       </c>
       <c r="C169" s="17" t="inlineStr">
@@ -10257,11 +10257,11 @@
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E169" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10271,20 +10271,20 @@
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Cyrus Allen (KC)</t>
-        </is>
-      </c>
-      <c r="C170" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Zach Charbonnet (SEA)</t>
+        </is>
+      </c>
+      <c r="C170" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>13.04</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>Kyle Williams (NE)</t>
+          <t>Cyrus Allen (KC)</t>
         </is>
       </c>
       <c r="C171" s="17" t="inlineStr">
@@ -10303,11 +10303,11 @@
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -10317,7 +10317,7 @@
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Jonah Coleman (DEN)</t>
+          <t>Tyler Allgeier (ARI)</t>
         </is>
       </c>
       <c r="C172" s="16" t="inlineStr">
@@ -10326,11 +10326,11 @@
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>Kenneth Walker (KC)</t>
+          <t>Dylan Sampson (CLE)</t>
         </is>
       </c>
       <c r="C173" s="16" t="inlineStr">
@@ -10349,11 +10349,11 @@
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -10363,20 +10363,20 @@
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Josh Allen (BUF)</t>
-        </is>
-      </c>
-      <c r="C174" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Kyle Williams (NE)</t>
+        </is>
+      </c>
+      <c r="C174" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>19.06</t>
         </is>
       </c>
     </row>
@@ -10386,20 +10386,20 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>Lamar Jackson (BAL)</t>
-        </is>
-      </c>
-      <c r="C175" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Calvin Ridley (TEN)</t>
+        </is>
+      </c>
+      <c r="C175" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E175" s="14" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>22.01</t>
         </is>
       </c>
     </row>
@@ -10409,20 +10409,20 @@
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>Jalen Hurts (PHI)</t>
-        </is>
-      </c>
-      <c r="C176" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>T.J. Hockenson (MIN)</t>
+        </is>
+      </c>
+      <c r="C176" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D176" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -10432,20 +10432,20 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Jayden Daniels (WAS)</t>
-        </is>
-      </c>
-      <c r="C177" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Mike Washington Jr. (LV)</t>
+        </is>
+      </c>
+      <c r="C177" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E177" s="14" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>15.05</t>
         </is>
       </c>
     </row>
@@ -10455,12 +10455,12 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Joe Burrow (CIN)</t>
-        </is>
-      </c>
-      <c r="C178" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Greg Dulcich (MIA)</t>
+        </is>
+      </c>
+      <c r="C178" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10478,20 +10478,20 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Drake Maye (NE)</t>
-        </is>
-      </c>
-      <c r="C179" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Kenyon Sadiq (NYJ)</t>
+        </is>
+      </c>
+      <c r="C179" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E179" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>13.1</t>
         </is>
       </c>
     </row>
@@ -10501,20 +10501,20 @@
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Jaxson Dart (NYG)</t>
-        </is>
-      </c>
-      <c r="C180" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jonah Coleman (DEN)</t>
+        </is>
+      </c>
+      <c r="C180" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>15.03</t>
         </is>
       </c>
     </row>
@@ -10524,20 +10524,20 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>Caleb Williams (CHI)</t>
-        </is>
-      </c>
-      <c r="C181" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tre' Harris (LAC)</t>
+        </is>
+      </c>
+      <c r="C181" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Trevor Lawrence (JAX)</t>
-        </is>
-      </c>
-      <c r="C182" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Keon Coleman (BUF)</t>
+        </is>
+      </c>
+      <c r="C182" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D182" s="14" t="n">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>20.07</t>
         </is>
       </c>
     </row>
@@ -10570,20 +10570,20 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>Dak Prescott (DAL)</t>
-        </is>
-      </c>
-      <c r="C183" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tyrone Tracy Jr. (NYG)</t>
+        </is>
+      </c>
+      <c r="C183" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D183" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E183" s="14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10593,20 +10593,20 @@
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>Justin Herbert (LAC)</t>
-        </is>
-      </c>
-      <c r="C184" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Pat Freiermuth (PIT)</t>
+        </is>
+      </c>
+      <c r="C184" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D184" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Bo Nix (DEN)</t>
+          <t>Aaron Rodgers (PIT)</t>
         </is>
       </c>
       <c r="C185" s="19" t="inlineStr">
@@ -10625,11 +10625,11 @@
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E185" s="14" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10639,7 +10639,7 @@
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Brock Purdy (SF)</t>
+          <t>Bryce Young (CAR)</t>
         </is>
       </c>
       <c r="C186" s="19" t="inlineStr">
@@ -10648,11 +10648,11 @@
         </is>
       </c>
       <c r="D186" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>19.12</t>
         </is>
       </c>
     </row>
@@ -10662,20 +10662,20 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>Jared Goff (DET)</t>
-        </is>
-      </c>
-      <c r="C187" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Zachariah Branch (ATL)</t>
+        </is>
+      </c>
+      <c r="C187" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D187" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E187" s="14" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -10685,20 +10685,20 @@
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Tyler Shough (NO)</t>
-        </is>
-      </c>
-      <c r="C188" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Ryan Flournoy (DAL)</t>
+        </is>
+      </c>
+      <c r="C188" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D188" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10708,20 +10708,20 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Matthew Stafford (LAR)</t>
-        </is>
-      </c>
-      <c r="C189" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Cade Otton (TB)</t>
+        </is>
+      </c>
+      <c r="C189" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E189" s="14" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>20.06</t>
         </is>
       </c>
     </row>
@@ -10731,20 +10731,20 @@
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Kyler Murray (MIN)</t>
-        </is>
-      </c>
-      <c r="C190" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tank Bigsby (PHI)</t>
+        </is>
+      </c>
+      <c r="C190" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D190" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E190" s="14" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10754,20 +10754,20 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>Jordan Love (GB)</t>
-        </is>
-      </c>
-      <c r="C191" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Alvin Kamara (NO)</t>
+        </is>
+      </c>
+      <c r="C191" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E191" s="14" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>14.07</t>
         </is>
       </c>
     </row>
@@ -10777,20 +10777,20 @@
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Baker Mayfield (TB)</t>
-        </is>
-      </c>
-      <c r="C192" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Caleb Douglas (MIA)</t>
+        </is>
+      </c>
+      <c r="C192" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D192" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>18.09</t>
         </is>
       </c>
     </row>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Patrick Mahomes (KC)</t>
+          <t>Geno Smith (NYJ)</t>
         </is>
       </c>
       <c r="C193" s="19" t="inlineStr">
@@ -10809,11 +10809,11 @@
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10823,20 +10823,20 @@
       </c>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>Malik Willis (MIA)</t>
-        </is>
-      </c>
-      <c r="C194" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Najee Harris (NYG)</t>
+        </is>
+      </c>
+      <c r="C194" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D194" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E194" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10846,20 +10846,20 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Cam Ward (TEN)</t>
-        </is>
-      </c>
-      <c r="C195" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Brian Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C195" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E195" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>13.12</t>
         </is>
       </c>
     </row>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>C.J. Stroud (HOU)</t>
-        </is>
-      </c>
-      <c r="C196" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Devaughn Vele (NO)</t>
+        </is>
+      </c>
+      <c r="C196" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D196" s="14" t="n">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="E196" s="14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10892,12 +10892,12 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>Sam Darnold (SEA)</t>
-        </is>
-      </c>
-      <c r="C197" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>AJ Barner (SEA)</t>
+        </is>
+      </c>
+      <c r="C197" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D197" s="14" t="n">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="E197" s="14" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10915,20 +10915,20 @@
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Daniel Jones (IND)</t>
-        </is>
-      </c>
-      <c r="C198" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jaylin Noel (HOU)</t>
+        </is>
+      </c>
+      <c r="C198" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D198" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>18.1</t>
         </is>
       </c>
     </row>
@@ -10938,20 +10938,20 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>Aaron Rodgers (PIT)</t>
-        </is>
-      </c>
-      <c r="C199" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Darius Slayton (NYG)</t>
+        </is>
+      </c>
+      <c r="C199" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E199" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10961,20 +10961,20 @@
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Bryce Young (CAR)</t>
-        </is>
-      </c>
-      <c r="C200" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Oronde Gadsden (LAC)</t>
+        </is>
+      </c>
+      <c r="C200" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D200" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
@@ -10984,12 +10984,12 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>Geno Smith (NYJ)</t>
-        </is>
-      </c>
-      <c r="C201" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Rashod Bateman (BAL)</t>
+        </is>
+      </c>
+      <c r="C201" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D201" s="14" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.05</t>
         </is>
       </c>
     </row>
@@ -11007,20 +11007,20 @@
       </c>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>Brian Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C202" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jalen Tolbert (MIA)</t>
+        </is>
+      </c>
+      <c r="C202" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D202" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E202" s="14" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11030,20 +11030,20 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>Oronde Gadsden (LAC)</t>
-        </is>
-      </c>
-      <c r="C203" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tory Horton (SEA)</t>
+        </is>
+      </c>
+      <c r="C203" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D203" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>

--- a/assets/data/12guys1cup-cheat-sheet.xlsx
+++ b/assets/data/12guys1cup-cheat-sheet.xlsx
@@ -62,6 +62,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00B8386B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001565C0"/>
       <sz val="10"/>
     </font>
@@ -69,12 +75,6 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00E65100"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00B8386B"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -125,17 +125,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F8D7E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D4E4F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -6476,20 +6476,20 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Bijan Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Josh Allen (BUF)</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>2.09</t>
         </is>
       </c>
     </row>
@@ -6499,20 +6499,20 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase (CIN)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Bijan Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
     </row>
@@ -6522,20 +6522,20 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Puka Nacua (LAR)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
+          <t>Ja'Marr Chase (CIN)</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>
@@ -6545,20 +6545,20 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Christian McCaffrey (SF)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Puka Nacua (LAR)</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
     </row>
@@ -6568,20 +6568,20 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba (SEA)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
+          <t>Amon-Ra St. Brown (DET)</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6591,20 +6591,20 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown (DET)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Christian McCaffrey (SF)</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.06</t>
         </is>
       </c>
     </row>
@@ -6614,20 +6614,20 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>CeeDee Lamb (DAL)</t>
+          <t>Lamar Jackson (BAL)</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>3.09</t>
         </is>
       </c>
     </row>
@@ -6637,20 +6637,20 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Jonathan Taylor (IND)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Drake Maye (NE)</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -6660,20 +6660,20 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>James Cook III (BUF)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jaxon Smith-Njigba (SEA)</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6683,20 +6683,20 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>De'Von Achane (MIA)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jalen Hurts (PHI)</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>5.12</t>
         </is>
       </c>
     </row>
@@ -6706,20 +6706,20 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Kenneth Walker (KC)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dak Prescott (DAL)</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>7.07</t>
         </is>
       </c>
     </row>
@@ -6729,12 +6729,12 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Chase Brown (CIN)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Joe Burrow (CIN)</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -6752,20 +6752,20 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Justin Jefferson (MIN)</t>
+          <t>Jayden Daniels (WAS)</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>6.04</t>
         </is>
       </c>
     </row>
@@ -6775,20 +6775,20 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>A.J. Brown (NE)</t>
+          <t>Trevor Lawrence (JAX)</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Chris Olave (NO)</t>
+          <t>Brock Purdy (SF)</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>11.02</t>
         </is>
       </c>
     </row>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Brock Bowers (LV)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jonathan Taylor (IND)</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D20" s="14" t="n">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6844,20 +6844,20 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Nico Collins (HOU)</t>
+          <t>Justin Herbert (LAC)</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -6867,20 +6867,20 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Trey McBride (ARI)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Caleb Williams (CHI)</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -6890,20 +6890,20 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Garrett Wilson (NYJ)</t>
+          <t>Jaxson Dart (NYG)</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -6913,20 +6913,20 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Drake London (ATL)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>De'Von Achane (MIA)</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6936,20 +6936,20 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>George Pickens (DAL)</t>
+          <t>Kyler Murray (MIN)</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>14.03</t>
         </is>
       </c>
     </row>
@@ -6959,20 +6959,20 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Rashee Rice (KC)</t>
+          <t>Matthew Stafford (LAR)</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>9.01</t>
         </is>
       </c>
     </row>
@@ -6982,20 +6982,20 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Omarion Hampton (LAC)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Bo Nix (DEN)</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>10.12</t>
         </is>
       </c>
     </row>
@@ -7005,20 +7005,20 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Ashton Jeanty (LV)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jared Goff (DET)</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>12.03</t>
         </is>
       </c>
     </row>
@@ -7028,20 +7028,20 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Malik Nabers (NYG)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chase Brown (CIN)</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7051,12 +7051,12 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Saquon Barkley (PHI)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Baker Mayfield (TB)</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -7074,20 +7074,20 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Zay Flowers (BAL)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
+          <t>CeeDee Lamb (DAL)</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Derrick Henry (BAL)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tyler Shough (NO)</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>16.07</t>
         </is>
       </c>
     </row>
@@ -7120,20 +7120,20 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>DeVonta Smith (PHI)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Derrick Henry (BAL)</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.08</t>
         </is>
       </c>
     </row>
@@ -7143,20 +7143,20 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Waddle (DEN)</t>
+          <t>Jordan Love (GB)</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>13.05</t>
         </is>
       </c>
     </row>
@@ -7166,20 +7166,20 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>Jeremiyah Love (ARI)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Sam Darnold (SEA)</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>14.05</t>
         </is>
       </c>
     </row>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Kyren Williams (LAR)</t>
+          <t>Saquon Barkley (PHI)</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
@@ -7198,11 +7198,11 @@
         </is>
       </c>
       <c r="D36" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -7212,20 +7212,20 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Ladd McConkey (LAC)</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
+          <t>Rashee Rice (KC)</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -7235,20 +7235,20 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Breece Hall (NYJ)</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Justin Jefferson (MIN)</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -7258,20 +7258,20 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Emeka Egbuka (TB)</t>
+          <t>Daniel Jones (IND)</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>17.11</t>
         </is>
       </c>
     </row>
@@ -7281,20 +7281,20 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>D'Andre Swift (CHI)</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Drake London (ATL)</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D40" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -7304,20 +7304,20 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan (CAR)</t>
+          <t>Malik Willis (MIA)</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -7327,20 +7327,20 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Tee Higgins (CIN)</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>James Cook III (BUF)</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D42" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>1.11</t>
         </is>
       </c>
     </row>
@@ -7350,20 +7350,20 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Carnell Tate (TEN)</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
+          <t>A.J. Brown (NE)</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -7373,20 +7373,20 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Javonte Williams (DAL)</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Chris Olave (NO)</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.07</t>
         </is>
       </c>
     </row>
@@ -7396,20 +7396,20 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Josh Allen (BUF)</t>
-        </is>
-      </c>
-      <c r="C45" s="19" t="inlineStr">
+          <t>C.J. Stroud (HOU)</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>18.01</t>
         </is>
       </c>
     </row>
@@ -7419,20 +7419,20 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>Luther Burden III (CHI)</t>
-        </is>
-      </c>
-      <c r="C46" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Trey McBride (ARI)</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D46" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -7442,20 +7442,20 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Christian Watson (GB)</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Ashton Jeanty (LV)</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -7465,20 +7465,20 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Bucky Irving (TB)</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Bryce Young (CAR)</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D48" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>19.12</t>
         </is>
       </c>
     </row>
@@ -7488,20 +7488,20 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>Parker Washington (JAX)</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="inlineStr">
+          <t>George Pickens (DAL)</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D49" s="14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -7511,20 +7511,20 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr. (NO)</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Zay Flowers (BAL)</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.05</t>
         </is>
       </c>
     </row>
@@ -7534,12 +7534,12 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Cam Skattebo (NYG)</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Nico Collins (HOU)</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D51" s="14" t="n">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Terry McLaurin (WAS)</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Omarion Hampton (LAC)</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D52" s="14" t="n">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7580,20 +7580,20 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Jameson Williams (DET)</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Breece Hall (NYJ)</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7603,20 +7603,20 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>DJ Moore (BUF)</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brock Bowers (LV)</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -7626,20 +7626,20 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten (JAX)</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Garrett Wilson (NYJ)</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -7649,20 +7649,20 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Davante Adams (LAR)</t>
-        </is>
-      </c>
-      <c r="C56" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Cam Skattebo (NYG)</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.08</t>
         </is>
       </c>
     </row>
@@ -7672,20 +7672,20 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Mike Evans (SF)</t>
-        </is>
-      </c>
-      <c r="C57" s="17" t="inlineStr">
+          <t>DeVonta Smith (PHI)</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D57" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>3.12</t>
         </is>
       </c>
     </row>
@@ -7695,20 +7695,20 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Rome Odunze (CHI)</t>
-        </is>
-      </c>
-      <c r="C58" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Travis Etienne Jr. (NO)</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D58" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>4.09</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr. (ARI)</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jeremiyah Love (ARI)</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D59" s="14" t="n">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7741,20 +7741,20 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>DK Metcalf (PIT)</t>
-        </is>
-      </c>
-      <c r="C60" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Javonte Williams (DAL)</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D60" s="14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7764,20 +7764,20 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Tyler Warren (IND)</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Cam Ward (TEN)</t>
+        </is>
+      </c>
+      <c r="C61" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -7787,20 +7787,20 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Colston Loveland (CHI)</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Geno Smith (NYJ)</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D62" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7810,20 +7810,20 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Alec Pierce (IND)</t>
+          <t>Aaron Rodgers (PIT)</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D63" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -7833,20 +7833,20 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kyren Williams (LAR)</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D64" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Quinshon Judkins (CLE)</t>
+          <t>D'Andre Swift (CHI)</t>
         </is>
       </c>
       <c r="C65" s="16" t="inlineStr">
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="D65" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
@@ -7879,12 +7879,12 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson (NE)</t>
-        </is>
-      </c>
-      <c r="C66" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Davante Adams (LAR)</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D66" s="14" t="n">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.02</t>
         </is>
       </c>
     </row>
@@ -7902,20 +7902,20 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>David Montgomery (HOU)</t>
-        </is>
-      </c>
-      <c r="C67" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tetairoa McMillan (CAR)</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D67" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.01</t>
         </is>
       </c>
     </row>
@@ -7925,20 +7925,20 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Lamar Jackson (BAL)</t>
-        </is>
-      </c>
-      <c r="C68" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tee Higgins (CIN)</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D68" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.11</t>
         </is>
       </c>
     </row>
@@ -7948,10 +7948,10 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr. (TB)</t>
-        </is>
-      </c>
-      <c r="C69" s="17" t="inlineStr">
+          <t>Emeka Egbuka (TB)</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>4.03</t>
         </is>
       </c>
     </row>
@@ -7971,20 +7971,20 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Jadarian Price (SEA)</t>
-        </is>
-      </c>
-      <c r="C70" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jameson Williams (DET)</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D70" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -7994,20 +7994,20 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd (GB)</t>
-        </is>
-      </c>
-      <c r="C71" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ladd McConkey (LAC)</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>4.02</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson (NE)</t>
+          <t>Bucky Irving (TB)</t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr">
@@ -8026,11 +8026,11 @@
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.06</t>
         </is>
       </c>
     </row>
@@ -8040,20 +8040,20 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Quentin Johnston (LAC)</t>
-        </is>
-      </c>
-      <c r="C73" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Colston Loveland (CHI)</t>
+        </is>
+      </c>
+      <c r="C73" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>4.04</t>
         </is>
       </c>
     </row>
@@ -8063,20 +8063,20 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Michael Pittman Jr. (PIT)</t>
-        </is>
-      </c>
-      <c r="C74" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Quinshon Judkins (CLE)</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D74" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -8086,20 +8086,20 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>Rico Dowdle (PIT)</t>
-        </is>
-      </c>
-      <c r="C75" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jaylen Waddle (DEN)</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson (TEN)</t>
-        </is>
-      </c>
-      <c r="C76" s="17" t="inlineStr">
+          <t>Malik Nabers (NYG)</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D76" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -8132,20 +8132,20 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>Harold Fannin Jr. (CLE)</t>
-        </is>
-      </c>
-      <c r="C77" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>David Montgomery (HOU)</t>
+        </is>
+      </c>
+      <c r="C77" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D77" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -8155,20 +8155,20 @@
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Michael Wilson (ARI)</t>
-        </is>
-      </c>
-      <c r="C78" s="17" t="inlineStr">
+          <t>Luther Burden III (CHI)</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D78" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -8178,10 +8178,10 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>Stefon Diggs (WAS)</t>
-        </is>
-      </c>
-      <c r="C79" s="17" t="inlineStr">
+          <t>Terry McLaurin (WAS)</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -8201,20 +8201,20 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Courtland Sutton (DEN)</t>
-        </is>
-      </c>
-      <c r="C80" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyler Warren (IND)</t>
+        </is>
+      </c>
+      <c r="C80" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D80" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>4.11</t>
         </is>
       </c>
     </row>
@@ -8224,20 +8224,20 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt (WAS)</t>
-        </is>
-      </c>
-      <c r="C81" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Mike Evans (SF)</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D81" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Kenny Gainwell (TB)</t>
+          <t>Jaylen Warren (PIT)</t>
         </is>
       </c>
       <c r="C82" s="16" t="inlineStr">
@@ -8256,11 +8256,11 @@
         </is>
       </c>
       <c r="D82" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -8270,20 +8270,20 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Warren (PIT)</t>
-        </is>
-      </c>
-      <c r="C83" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DJ Moore (BUF)</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D83" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.09</t>
         </is>
       </c>
     </row>
@@ -8293,20 +8293,20 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Jordan Addison (MIN)</t>
-        </is>
-      </c>
-      <c r="C84" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Harold Fannin Jr. (CLE)</t>
+        </is>
+      </c>
+      <c r="C84" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D84" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -8316,20 +8316,20 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling (SF)</t>
-        </is>
-      </c>
-      <c r="C85" s="17" t="inlineStr">
+          <t>Christian Watson (GB)</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D85" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -8339,20 +8339,20 @@
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Tucker Kraft (GB)</t>
+          <t>Parker Washington (JAX)</t>
         </is>
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D86" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>7.04</t>
         </is>
       </c>
     </row>
@@ -8362,20 +8362,20 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>Jalen Hurts (PHI)</t>
-        </is>
-      </c>
-      <c r="C87" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Rhamondre Stevenson (NE)</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D87" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -8385,20 +8385,20 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Jayden Reed (GB)</t>
-        </is>
-      </c>
-      <c r="C88" s="17" t="inlineStr">
+          <t>Alec Pierce (IND)</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D88" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>9.05</t>
         </is>
       </c>
     </row>
@@ -8408,20 +8408,20 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>Jayden Daniels (WAS)</t>
-        </is>
-      </c>
-      <c r="C89" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>DK Metcalf (PIT)</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D89" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -8431,20 +8431,20 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Joe Burrow (CIN)</t>
-        </is>
-      </c>
-      <c r="C90" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Rome Odunze (CHI)</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D90" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>6.05</t>
         </is>
       </c>
     </row>
@@ -8454,20 +8454,20 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>George Kittle (SF)</t>
-        </is>
-      </c>
-      <c r="C91" s="18" t="inlineStr">
+          <t>Sam LaPorta (DET)</t>
+        </is>
+      </c>
+      <c r="C91" s="19" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -8477,20 +8477,20 @@
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>Chuba Hubbard (CAR)</t>
-        </is>
-      </c>
-      <c r="C92" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Marvin Harrison Jr. (ARI)</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D92" s="14" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>J.K. Dobbins (DEN)</t>
+          <t>Bhayshul Tuten (JAX)</t>
         </is>
       </c>
       <c r="C93" s="16" t="inlineStr">
@@ -8509,11 +8509,11 @@
         </is>
       </c>
       <c r="D93" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8523,20 +8523,20 @@
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>Tony Pollard (TEN)</t>
-        </is>
-      </c>
-      <c r="C94" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>George Kittle (SF)</t>
+        </is>
+      </c>
+      <c r="C94" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D94" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -8546,20 +8546,20 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>Josh Downs (IND)</t>
-        </is>
-      </c>
-      <c r="C95" s="17" t="inlineStr">
+          <t>Michael Pittman Jr. (PIT)</t>
+        </is>
+      </c>
+      <c r="C95" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D95" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>9.07</t>
         </is>
       </c>
     </row>
@@ -8569,20 +8569,20 @@
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Jonathon Brooks (CAR)</t>
-        </is>
-      </c>
-      <c r="C96" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Courtland Sutton (DEN)</t>
+        </is>
+      </c>
+      <c r="C96" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D96" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.09</t>
         </is>
       </c>
     </row>
@@ -8592,20 +8592,20 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>Jakobi Meyers (JAX)</t>
-        </is>
-      </c>
-      <c r="C97" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Travis Kelce (KC)</t>
+        </is>
+      </c>
+      <c r="C97" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.08</t>
         </is>
       </c>
     </row>
@@ -8615,20 +8615,20 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>Romeo Doubs (NE)</t>
-        </is>
-      </c>
-      <c r="C98" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dallas Goedert (PHI)</t>
+        </is>
+      </c>
+      <c r="C98" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D98" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -8638,20 +8638,20 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>Sam LaPorta (DET)</t>
-        </is>
-      </c>
-      <c r="C99" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>TreVeyon Henderson (NE)</t>
+        </is>
+      </c>
+      <c r="C99" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -8661,20 +8661,20 @@
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>Khalil Shakir (BUF)</t>
-        </is>
-      </c>
-      <c r="C100" s="17" t="inlineStr">
+          <t>Chris Godwin Jr. (TB)</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D100" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>8.12</t>
         </is>
       </c>
     </row>
@@ -8684,20 +8684,20 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>Kyle Monangai (CHI)</t>
-        </is>
-      </c>
-      <c r="C101" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kyle Pitts Sr. (ATL)</t>
+        </is>
+      </c>
+      <c r="C101" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>6.1</t>
         </is>
       </c>
     </row>
@@ -8707,20 +8707,20 @@
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Makai Lemon (PHI)</t>
-        </is>
-      </c>
-      <c r="C102" s="17" t="inlineStr">
+          <t>Jakobi Meyers (JAX)</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D102" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>10.1</t>
         </is>
       </c>
     </row>
@@ -8730,20 +8730,20 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>Xavier Worthy (KC)</t>
-        </is>
-      </c>
-      <c r="C103" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tony Pollard (TEN)</t>
+        </is>
+      </c>
+      <c r="C103" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>7.12</t>
         </is>
       </c>
     </row>
@@ -8753,20 +8753,20 @@
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>Malik Washington (MIA)</t>
-        </is>
-      </c>
-      <c r="C104" s="17" t="inlineStr">
+          <t>Michael Wilson (ARI)</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D104" s="14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>7.11</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>Jordan Mason (MIN)</t>
+          <t>Chuba Hubbard (CAR)</t>
         </is>
       </c>
       <c r="C105" s="16" t="inlineStr">
@@ -8785,11 +8785,11 @@
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>7.05</t>
         </is>
       </c>
     </row>
@@ -8799,20 +8799,20 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>Jalen Coker (CAR)</t>
-        </is>
-      </c>
-      <c r="C106" s="17" t="inlineStr">
+          <t>Jayden Reed (GB)</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D106" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8822,20 +8822,20 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Rashid Shaheed (SEA)</t>
-        </is>
-      </c>
-      <c r="C107" s="17" t="inlineStr">
+          <t>Carnell Tate (TEN)</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -8845,20 +8845,20 @@
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>KC Concepcion (CLE)</t>
-        </is>
-      </c>
-      <c r="C108" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>J.K. Dobbins (DEN)</t>
+        </is>
+      </c>
+      <c r="C108" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D108" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>8.1</t>
         </is>
       </c>
     </row>
@@ -8868,20 +8868,20 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>Kayshon Boutte (HOU)</t>
-        </is>
-      </c>
-      <c r="C109" s="17" t="inlineStr">
+          <t>Jordan Addison (MIN)</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>9.09</t>
         </is>
       </c>
     </row>
@@ -8891,20 +8891,20 @@
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>Drake Maye (NE)</t>
-        </is>
-      </c>
-      <c r="C110" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Wan'Dale Robinson (TEN)</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D110" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>10.09</t>
         </is>
       </c>
     </row>
@@ -8914,20 +8914,20 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>Rachaad White (WAS)</t>
-        </is>
-      </c>
-      <c r="C111" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tucker Kraft (GB)</t>
+        </is>
+      </c>
+      <c r="C111" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8937,20 +8937,20 @@
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Matthew Golden (GB)</t>
-        </is>
-      </c>
-      <c r="C112" s="17" t="inlineStr">
+          <t>Brian Thomas Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D112" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>7.02</t>
         </is>
       </c>
     </row>
@@ -8960,20 +8960,20 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>Jaxson Dart (NYG)</t>
-        </is>
-      </c>
-      <c r="C113" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Rico Dowdle (PIT)</t>
+        </is>
+      </c>
+      <c r="C113" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>8.01</t>
         </is>
       </c>
     </row>
@@ -8983,20 +8983,20 @@
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Kyle Pitts Sr. (ATL)</t>
-        </is>
-      </c>
-      <c r="C114" s="18" t="inlineStr">
+          <t>Mark Andrews (BAL)</t>
+        </is>
+      </c>
+      <c r="C114" s="19" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D114" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>11.09</t>
         </is>
       </c>
     </row>
@@ -9006,20 +9006,20 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>Keenan Allen (IND)</t>
-        </is>
-      </c>
-      <c r="C115" s="17" t="inlineStr">
+          <t>Quentin Johnston (LAC)</t>
+        </is>
+      </c>
+      <c r="C115" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>10.05</t>
         </is>
       </c>
     </row>
@@ -9029,20 +9029,20 @@
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>Caleb Williams (CHI)</t>
-        </is>
-      </c>
-      <c r="C116" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Khalil Shakir (BUF)</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D116" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>12.11</t>
         </is>
       </c>
     </row>
@@ -9052,20 +9052,20 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>Trevor Lawrence (JAX)</t>
-        </is>
-      </c>
-      <c r="C117" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Aaron Jones Sr. (MIN)</t>
+        </is>
+      </c>
+      <c r="C117" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -9075,12 +9075,12 @@
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>Blake Corum (LAR)</t>
-        </is>
-      </c>
-      <c r="C118" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Romeo Doubs (NE)</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D118" s="14" t="n">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -9098,20 +9098,20 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>RJ Harvey (DEN)</t>
-        </is>
-      </c>
-      <c r="C119" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Stefon Diggs (WAS)</t>
+        </is>
+      </c>
+      <c r="C119" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>10.02</t>
         </is>
       </c>
     </row>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Juwan Johnson (NO)</t>
+          <t>Xavier Worthy (KC)</t>
         </is>
       </c>
       <c r="C120" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D120" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -9144,20 +9144,20 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>Jordyn Tyson (NO)</t>
-        </is>
-      </c>
-      <c r="C121" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jadarian Price (SEA)</t>
+        </is>
+      </c>
+      <c r="C121" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D121" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>Dalton Schultz (HOU)</t>
+          <t>Deebo Samuel Sr. (SF)</t>
         </is>
       </c>
       <c r="C122" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>11.11</t>
         </is>
       </c>
     </row>
@@ -9190,20 +9190,20 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>Travis Kelce (KC)</t>
-        </is>
-      </c>
-      <c r="C123" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>RJ Harvey (DEN)</t>
+        </is>
+      </c>
+      <c r="C123" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>7.08</t>
         </is>
       </c>
     </row>
@@ -9213,20 +9213,20 @@
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>Tre Tucker (LV)</t>
-        </is>
-      </c>
-      <c r="C124" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Isaiah Likely (NYG)</t>
+        </is>
+      </c>
+      <c r="C124" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D124" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -9236,20 +9236,20 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr. (MIN)</t>
-        </is>
-      </c>
-      <c r="C125" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Josh Downs (IND)</t>
+        </is>
+      </c>
+      <c r="C125" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>10.01</t>
         </is>
       </c>
     </row>
@@ -9259,20 +9259,20 @@
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>Jake Ferguson (DAL)</t>
+          <t>Matthew Golden (GB)</t>
         </is>
       </c>
       <c r="C126" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>11.07</t>
         </is>
       </c>
     </row>
@@ -9282,12 +9282,12 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>Dak Prescott (DAL)</t>
+          <t>Jake Ferguson (DAL)</t>
         </is>
       </c>
       <c r="C127" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>9.02</t>
         </is>
       </c>
     </row>
@@ -9305,20 +9305,20 @@
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>Dalton Kincaid (BUF)</t>
-        </is>
-      </c>
-      <c r="C128" s="18" t="inlineStr">
+          <t>Hunter Henry (NE)</t>
+        </is>
+      </c>
+      <c r="C128" s="19" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D128" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -9328,12 +9328,12 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>Isaiah Likely (NYG)</t>
+          <t>De'Zhaun Stribling (SF)</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D129" s="14" t="n">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>12.07</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>Tyjae Spears (TEN)</t>
+          <t>Kyle Monangai (CHI)</t>
         </is>
       </c>
       <c r="C130" s="16" t="inlineStr">
@@ -9360,11 +9360,11 @@
         </is>
       </c>
       <c r="D130" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -9374,12 +9374,12 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>Justin Herbert (LAC)</t>
+          <t>Dalton Kincaid (BUF)</t>
         </is>
       </c>
       <c r="C131" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -9397,12 +9397,12 @@
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>Dallas Goedert (PHI)</t>
-        </is>
-      </c>
-      <c r="C132" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kenny Gainwell (TB)</t>
+        </is>
+      </c>
+      <c r="C132" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D132" s="14" t="n">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -9420,12 +9420,12 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>Bo Nix (DEN)</t>
-        </is>
-      </c>
-      <c r="C133" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Makai Lemon (PHI)</t>
+        </is>
+      </c>
+      <c r="C133" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D133" s="14" t="n">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -9443,20 +9443,20 @@
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Brock Purdy (SF)</t>
-        </is>
-      </c>
-      <c r="C134" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Rashid Shaheed (SEA)</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D134" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>13.03</t>
         </is>
       </c>
     </row>
@@ -9466,20 +9466,20 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>Omar Cooper Jr. (NYJ)</t>
-        </is>
-      </c>
-      <c r="C135" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brenton Strange (JAX)</t>
+        </is>
+      </c>
+      <c r="C135" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>13.08</t>
         </is>
       </c>
     </row>
@@ -9489,20 +9489,20 @@
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>Jared Goff (DET)</t>
+          <t>Juwan Johnson (NO)</t>
         </is>
       </c>
       <c r="C136" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D136" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9512,20 +9512,20 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>Deebo Samuel Sr. (SF)</t>
-        </is>
-      </c>
-      <c r="C137" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rachaad White (WAS)</t>
+        </is>
+      </c>
+      <c r="C137" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -9535,20 +9535,20 @@
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>Tyler Shough (NO)</t>
-        </is>
-      </c>
-      <c r="C138" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>KC Concepcion (CLE)</t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>11.01</t>
         </is>
       </c>
     </row>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>Matthew Stafford (LAR)</t>
-        </is>
-      </c>
-      <c r="C139" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jerry Jeudy (CLE)</t>
+        </is>
+      </c>
+      <c r="C139" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -9581,20 +9581,20 @@
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>Kyler Murray (MIN)</t>
-        </is>
-      </c>
-      <c r="C140" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jacory Croskey-Merritt (WAS)</t>
+        </is>
+      </c>
+      <c r="C140" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D140" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>10.06</t>
         </is>
       </c>
     </row>
@@ -9604,20 +9604,20 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>Jordan Love (GB)</t>
-        </is>
-      </c>
-      <c r="C141" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jonathon Brooks (CAR)</t>
+        </is>
+      </c>
+      <c r="C141" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>9.1</t>
         </is>
       </c>
     </row>
@@ -9627,20 +9627,20 @@
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>Baker Mayfield (TB)</t>
-        </is>
-      </c>
-      <c r="C142" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jalen Coker (CAR)</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>13.02</t>
         </is>
       </c>
     </row>
@@ -9650,20 +9650,20 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>Denzel Boston (CLE)</t>
-        </is>
-      </c>
-      <c r="C143" s="17" t="inlineStr">
+          <t>Calvin Ridley (TEN)</t>
+        </is>
+      </c>
+      <c r="C143" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>22.01</t>
         </is>
       </c>
     </row>
@@ -9673,20 +9673,20 @@
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>Patrick Mahomes (KC)</t>
-        </is>
-      </c>
-      <c r="C144" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Cooper Kupp (SEA)</t>
+        </is>
+      </c>
+      <c r="C144" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>19.05</t>
         </is>
       </c>
     </row>
@@ -9696,20 +9696,20 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>Brenton Strange (JAX)</t>
-        </is>
-      </c>
-      <c r="C145" s="18" t="inlineStr">
+          <t>Dalton Schultz (HOU)</t>
+        </is>
+      </c>
+      <c r="C145" s="19" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>17.01</t>
         </is>
       </c>
     </row>
@@ -9719,20 +9719,20 @@
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks (PHI)</t>
-        </is>
-      </c>
-      <c r="C146" s="17" t="inlineStr">
+          <t>Keenan Allen (IND)</t>
+        </is>
+      </c>
+      <c r="C146" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17.07</t>
         </is>
       </c>
     </row>
@@ -9742,20 +9742,20 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Mark Andrews (BAL)</t>
-        </is>
-      </c>
-      <c r="C147" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jordan Mason (MIN)</t>
+        </is>
+      </c>
+      <c r="C147" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>10.07</t>
         </is>
       </c>
     </row>
@@ -9765,20 +9765,20 @@
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>Pat Bryant (DEN)</t>
-        </is>
-      </c>
-      <c r="C148" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>T.J. Hockenson (MIN)</t>
+        </is>
+      </c>
+      <c r="C148" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -9788,12 +9788,12 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>Malik Willis (MIA)</t>
+          <t>Greg Dulcich (MIA)</t>
         </is>
       </c>
       <c r="C149" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -9811,20 +9811,20 @@
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>Jalen Nailor (LV)</t>
-        </is>
-      </c>
-      <c r="C150" s="17" t="inlineStr">
+          <t>Kayshon Boutte (HOU)</t>
+        </is>
+      </c>
+      <c r="C150" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>19.08</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Woody Marks (HOU)</t>
-        </is>
-      </c>
-      <c r="C151" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jordyn Tyson (NO)</t>
+        </is>
+      </c>
+      <c r="C151" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D151" s="14" t="n">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>8.07</t>
         </is>
       </c>
     </row>
@@ -9857,12 +9857,12 @@
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Hunter Henry (NE)</t>
+          <t>Denzel Boston (CLE)</t>
         </is>
       </c>
       <c r="C152" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9880,20 +9880,20 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>Chig Okonkwo (WAS)</t>
-        </is>
-      </c>
-      <c r="C153" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Blake Corum (LAR)</t>
+        </is>
+      </c>
+      <c r="C153" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>9.08</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>Chris Rodriguez Jr. (JAX)</t>
+          <t>MarShawn Lloyd (GB)</t>
         </is>
       </c>
       <c r="C154" s="16" t="inlineStr">
@@ -9912,11 +9912,11 @@
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>15.06</t>
         </is>
       </c>
     </row>
@@ -9926,20 +9926,20 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>Travis Hunter (JAX)</t>
-        </is>
-      </c>
-      <c r="C155" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Woody Marks (HOU)</t>
+        </is>
+      </c>
+      <c r="C155" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>14.04</t>
         </is>
       </c>
     </row>
@@ -9949,20 +9949,20 @@
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Cooper Kupp (SEA)</t>
-        </is>
-      </c>
-      <c r="C156" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kenyon Sadiq (NYJ)</t>
+        </is>
+      </c>
+      <c r="C156" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>13.1</t>
         </is>
       </c>
     </row>
@@ -9972,20 +9972,20 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Jerry Jeudy (CLE)</t>
-        </is>
-      </c>
-      <c r="C157" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Pat Freiermuth (PIT)</t>
+        </is>
+      </c>
+      <c r="C157" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D157" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E157" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -9995,12 +9995,12 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Cam Ward (TEN)</t>
-        </is>
-      </c>
-      <c r="C158" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tyjae Spears (TEN)</t>
+        </is>
+      </c>
+      <c r="C158" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -10018,20 +10018,20 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Isiah Pacheco (DET)</t>
-        </is>
-      </c>
-      <c r="C159" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tre Tucker (LV)</t>
+        </is>
+      </c>
+      <c r="C159" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E159" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>17.1</t>
         </is>
       </c>
     </row>
@@ -10041,20 +10041,20 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>C.J. Stroud (HOU)</t>
+          <t>Cade Otton (TB)</t>
         </is>
       </c>
       <c r="C160" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>20.06</t>
         </is>
       </c>
     </row>
@@ -10064,20 +10064,20 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>DeMario Douglas (NE)</t>
-        </is>
-      </c>
-      <c r="C161" s="17" t="inlineStr">
+          <t>Rashod Bateman (BAL)</t>
+        </is>
+      </c>
+      <c r="C161" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E161" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.05</t>
         </is>
       </c>
     </row>
@@ -10087,20 +10087,20 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Malachi Fields (NYG)</t>
-        </is>
-      </c>
-      <c r="C162" s="17" t="inlineStr">
+          <t>Jalen Nailor (LV)</t>
+        </is>
+      </c>
+      <c r="C162" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D162" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -10110,20 +10110,20 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>Sam Darnold (SEA)</t>
+          <t>Chig Okonkwo (WAS)</t>
         </is>
       </c>
       <c r="C163" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E163" s="14" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Keaton Mitchell (LAC)</t>
+          <t>Alvin Kamara (NO)</t>
         </is>
       </c>
       <c r="C164" s="16" t="inlineStr">
@@ -10142,11 +10142,11 @@
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>14.07</t>
         </is>
       </c>
     </row>
@@ -10156,20 +10156,20 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>Adonai Mitchell (NYJ)</t>
-        </is>
-      </c>
-      <c r="C165" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Zach Charbonnet (SEA)</t>
+        </is>
+      </c>
+      <c r="C165" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E165" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>13.04</t>
         </is>
       </c>
     </row>
@@ -10179,20 +10179,20 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane (BAL)</t>
-        </is>
-      </c>
-      <c r="C166" s="17" t="inlineStr">
+          <t>Jaylin Noel (HOU)</t>
+        </is>
+      </c>
+      <c r="C166" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>18.1</t>
         </is>
       </c>
     </row>
@@ -10202,20 +10202,20 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>Daniel Jones (IND)</t>
-        </is>
-      </c>
-      <c r="C167" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Malik Washington (MIA)</t>
+        </is>
+      </c>
+      <c r="C167" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E167" s="14" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -10225,20 +10225,20 @@
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>Tank Dell (HOU)</t>
-        </is>
-      </c>
-      <c r="C168" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>AJ Barner (SEA)</t>
+        </is>
+      </c>
+      <c r="C168" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10248,20 +10248,20 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>Germie Bernard (PIT)</t>
-        </is>
-      </c>
-      <c r="C169" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dylan Sampson (CLE)</t>
+        </is>
+      </c>
+      <c r="C169" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E169" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -10271,20 +10271,20 @@
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Zach Charbonnet (SEA)</t>
-        </is>
-      </c>
-      <c r="C170" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Omar Cooper Jr. (NYJ)</t>
+        </is>
+      </c>
+      <c r="C170" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>17.02</t>
         </is>
       </c>
     </row>
@@ -10294,20 +10294,20 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>Cyrus Allen (KC)</t>
-        </is>
-      </c>
-      <c r="C171" s="17" t="inlineStr">
+          <t>Travis Hunter (JAX)</t>
+        </is>
+      </c>
+      <c r="C171" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10317,20 +10317,20 @@
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Tyler Allgeier (ARI)</t>
-        </is>
-      </c>
-      <c r="C172" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jalen Tolbert (MIA)</t>
+        </is>
+      </c>
+      <c r="C172" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10340,20 +10340,20 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>Dylan Sampson (CLE)</t>
-        </is>
-      </c>
-      <c r="C173" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Devaughn Vele (NO)</t>
+        </is>
+      </c>
+      <c r="C173" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10363,20 +10363,20 @@
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Kyle Williams (NE)</t>
-        </is>
-      </c>
-      <c r="C174" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyler Allgeier (ARI)</t>
+        </is>
+      </c>
+      <c r="C174" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -10386,20 +10386,20 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>Calvin Ridley (TEN)</t>
-        </is>
-      </c>
-      <c r="C175" s="17" t="inlineStr">
+          <t>Tre' Harris (LAC)</t>
+        </is>
+      </c>
+      <c r="C175" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E175" s="14" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10409,20 +10409,20 @@
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>T.J. Hockenson (MIN)</t>
+          <t>Germie Bernard (PIT)</t>
         </is>
       </c>
       <c r="C176" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D176" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10432,20 +10432,20 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Mike Washington Jr. (LV)</t>
-        </is>
-      </c>
-      <c r="C177" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dontayvion Wicks (PHI)</t>
+        </is>
+      </c>
+      <c r="C177" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E177" s="14" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10455,12 +10455,12 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Greg Dulcich (MIA)</t>
-        </is>
-      </c>
-      <c r="C178" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Isiah Pacheco (DET)</t>
+        </is>
+      </c>
+      <c r="C178" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -10478,12 +10478,12 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq (NYJ)</t>
+          <t>Adonai Mitchell (NYJ)</t>
         </is>
       </c>
       <c r="C179" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="E179" s="14" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10501,20 +10501,20 @@
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Jonah Coleman (DEN)</t>
-        </is>
-      </c>
-      <c r="C180" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ja'Kobi Lane (BAL)</t>
+        </is>
+      </c>
+      <c r="C180" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.02</t>
         </is>
       </c>
     </row>
@@ -10524,20 +10524,20 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>Tre' Harris (LAC)</t>
-        </is>
-      </c>
-      <c r="C181" s="17" t="inlineStr">
+          <t>DeMario Douglas (NE)</t>
+        </is>
+      </c>
+      <c r="C181" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Keon Coleman (BUF)</t>
-        </is>
-      </c>
-      <c r="C182" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chris Rodriguez Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C182" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D182" s="14" t="n">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>12.08</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr. (NYG)</t>
+          <t>Mike Washington Jr. (LV)</t>
         </is>
       </c>
       <c r="C183" s="16" t="inlineStr">
@@ -10579,11 +10579,11 @@
         </is>
       </c>
       <c r="D183" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E183" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>15.05</t>
         </is>
       </c>
     </row>
@@ -10593,20 +10593,20 @@
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>Pat Freiermuth (PIT)</t>
+          <t>Darius Slayton (NYG)</t>
         </is>
       </c>
       <c r="C184" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D184" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10616,20 +10616,20 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Aaron Rodgers (PIT)</t>
-        </is>
-      </c>
-      <c r="C185" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Zachariah Branch (ATL)</t>
+        </is>
+      </c>
+      <c r="C185" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E185" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -10639,20 +10639,20 @@
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Bryce Young (CAR)</t>
-        </is>
-      </c>
-      <c r="C186" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Keaton Mitchell (LAC)</t>
+        </is>
+      </c>
+      <c r="C186" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D186" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10662,20 +10662,20 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>Zachariah Branch (ATL)</t>
-        </is>
-      </c>
-      <c r="C187" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tank Bigsby (PHI)</t>
+        </is>
+      </c>
+      <c r="C187" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D187" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E187" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10685,20 +10685,20 @@
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Ryan Flournoy (DAL)</t>
-        </is>
-      </c>
-      <c r="C188" s="17" t="inlineStr">
+          <t>Malachi Fields (NYG)</t>
+        </is>
+      </c>
+      <c r="C188" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D188" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>19.04</t>
         </is>
       </c>
     </row>
@@ -10708,20 +10708,20 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Cade Otton (TB)</t>
+          <t>Caleb Douglas (MIA)</t>
         </is>
       </c>
       <c r="C189" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E189" s="14" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>18.09</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Tank Bigsby (PHI)</t>
+          <t>Tyrone Tracy Jr. (NYG)</t>
         </is>
       </c>
       <c r="C190" s="16" t="inlineStr">
@@ -10740,11 +10740,11 @@
         </is>
       </c>
       <c r="D190" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E190" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10754,20 +10754,20 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>Alvin Kamara (NO)</t>
-        </is>
-      </c>
-      <c r="C191" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Pat Bryant (DEN)</t>
+        </is>
+      </c>
+      <c r="C191" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E191" s="14" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>19.11</t>
         </is>
       </c>
     </row>
@@ -10777,20 +10777,20 @@
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Caleb Douglas (MIA)</t>
-        </is>
-      </c>
-      <c r="C192" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Najee Harris (NYG)</t>
+        </is>
+      </c>
+      <c r="C192" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D192" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10800,20 +10800,20 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Geno Smith (NYJ)</t>
-        </is>
-      </c>
-      <c r="C193" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tory Horton (SEA)</t>
+        </is>
+      </c>
+      <c r="C193" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10823,20 +10823,20 @@
       </c>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>Najee Harris (NYG)</t>
-        </is>
-      </c>
-      <c r="C194" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ryan Flournoy (DAL)</t>
+        </is>
+      </c>
+      <c r="C194" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D194" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E194" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10846,20 +10846,20 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Brian Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C195" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Keon Coleman (BUF)</t>
+        </is>
+      </c>
+      <c r="C195" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E195" s="14" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>20.07</t>
         </is>
       </c>
     </row>
@@ -10869,10 +10869,10 @@
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>Devaughn Vele (NO)</t>
-        </is>
-      </c>
-      <c r="C196" s="17" t="inlineStr">
+          <t>Tank Dell (HOU)</t>
+        </is>
+      </c>
+      <c r="C196" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="E196" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10892,20 +10892,20 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>AJ Barner (SEA)</t>
+          <t>Cyrus Allen (KC)</t>
         </is>
       </c>
       <c r="C197" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D197" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E197" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -10915,20 +10915,20 @@
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Jaylin Noel (HOU)</t>
-        </is>
-      </c>
-      <c r="C198" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonah Coleman (DEN)</t>
+        </is>
+      </c>
+      <c r="C198" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D198" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>15.03</t>
         </is>
       </c>
     </row>
@@ -10938,20 +10938,20 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>Darius Slayton (NYG)</t>
-        </is>
-      </c>
-      <c r="C199" s="17" t="inlineStr">
+          <t>Kyle Williams (NE)</t>
+        </is>
+      </c>
+      <c r="C199" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E199" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19.06</t>
         </is>
       </c>
     </row>
@@ -10961,20 +10961,20 @@
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Oronde Gadsden (LAC)</t>
-        </is>
-      </c>
-      <c r="C200" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kenneth Walker (KC)</t>
+        </is>
+      </c>
+      <c r="C200" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D200" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -10984,20 +10984,20 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>Rashod Bateman (BAL)</t>
+          <t>Patrick Mahomes (KC)</t>
         </is>
       </c>
       <c r="C201" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D201" s="14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -11007,20 +11007,20 @@
       </c>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>Jalen Tolbert (MIA)</t>
-        </is>
-      </c>
-      <c r="C202" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brian Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C202" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D202" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E202" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.12</t>
         </is>
       </c>
     </row>
@@ -11030,20 +11030,20 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>Tory Horton (SEA)</t>
-        </is>
-      </c>
-      <c r="C203" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Oronde Gadsden (LAC)</t>
+        </is>
+      </c>
+      <c r="C203" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D203" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>

--- a/assets/data/12guys1cup-cheat-sheet.xlsx
+++ b/assets/data/12guys1cup-cheat-sheet.xlsx
@@ -62,12 +62,6 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00B8386B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="001565C0"/>
       <sz val="10"/>
     </font>
@@ -75,6 +69,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00E65100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00B8386B"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -125,17 +125,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D4E4F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -6476,20 +6476,20 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Josh Allen (BUF)</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Bijan Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.03</t>
         </is>
       </c>
     </row>
@@ -6499,20 +6499,20 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Bijan Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ja'Marr Chase (CIN)</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>
@@ -6522,20 +6522,20 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase (CIN)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
+          <t>Puka Nacua (LAR)</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
     </row>
@@ -6545,20 +6545,20 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Puka Nacua (LAR)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Christian McCaffrey (SF)</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
     </row>
@@ -6568,20 +6568,20 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown (DET)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
+          <t>Jaxon Smith-Njigba (SEA)</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6591,20 +6591,20 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Christian McCaffrey (SF)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Amon-Ra St. Brown (DET)</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6614,20 +6614,20 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Lamar Jackson (BAL)</t>
+          <t>CeeDee Lamb (DAL)</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6637,20 +6637,20 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Drake Maye (NE)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jonathan Taylor (IND)</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6660,20 +6660,20 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba (SEA)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>James Cook III (BUF)</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.11</t>
         </is>
       </c>
     </row>
@@ -6683,20 +6683,20 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Jalen Hurts (PHI)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>De'Von Achane (MIA)</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6706,20 +6706,20 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Dak Prescott (DAL)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Kenneth Walker (KC)</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -6729,12 +6729,12 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Joe Burrow (CIN)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Chase Brown (CIN)</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -6752,20 +6752,20 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Jayden Daniels (WAS)</t>
+          <t>Justin Jefferson (MIN)</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6775,20 +6775,20 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Trevor Lawrence (JAX)</t>
+          <t>A.J. Brown (NE)</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Brock Purdy (SF)</t>
+          <t>Chris Olave (NO)</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>3.07</t>
         </is>
       </c>
     </row>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Jonathan Taylor (IND)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Brock Bowers (LV)</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D20" s="14" t="n">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -6844,20 +6844,20 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Justin Herbert (LAC)</t>
+          <t>Nico Collins (HOU)</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -6867,20 +6867,20 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Caleb Williams (CHI)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Trey McBride (ARI)</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -6890,20 +6890,20 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Jaxson Dart (NYG)</t>
+          <t>Garrett Wilson (NYJ)</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -6913,20 +6913,20 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>De'Von Achane (MIA)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Drake London (ATL)</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -6936,20 +6936,20 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Kyler Murray (MIN)</t>
+          <t>George Pickens (DAL)</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -6959,20 +6959,20 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Matthew Stafford (LAR)</t>
+          <t>Rashee Rice (KC)</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -6982,20 +6982,20 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Bo Nix (DEN)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Omarion Hampton (LAC)</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7005,20 +7005,20 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Jared Goff (DET)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Ashton Jeanty (LV)</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -7028,20 +7028,20 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Chase Brown (CIN)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Malik Nabers (NYG)</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -7051,12 +7051,12 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Baker Mayfield (TB)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Saquon Barkley (PHI)</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -7074,20 +7074,20 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>CeeDee Lamb (DAL)</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
+          <t>Zay Flowers (BAL)</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>4.05</t>
         </is>
       </c>
     </row>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Tyler Shough (NO)</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Derrick Henry (BAL)</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>2.08</t>
         </is>
       </c>
     </row>
@@ -7120,20 +7120,20 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>Derrick Henry (BAL)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DeVonta Smith (PHI)</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.12</t>
         </is>
       </c>
     </row>
@@ -7143,20 +7143,20 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Jordan Love (GB)</t>
+          <t>Jaylen Waddle (DEN)</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -7166,20 +7166,20 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>Sam Darnold (SEA)</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jeremiyah Love (ARI)</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Saquon Barkley (PHI)</t>
+          <t>Kyren Williams (LAR)</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
@@ -7198,11 +7198,11 @@
         </is>
       </c>
       <c r="D36" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
@@ -7212,20 +7212,20 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Rashee Rice (KC)</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="inlineStr">
+          <t>Ladd McConkey (LAC)</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>4.02</t>
         </is>
       </c>
     </row>
@@ -7235,20 +7235,20 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Justin Jefferson (MIN)</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Breece Hall (NYJ)</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7258,20 +7258,20 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Daniel Jones (IND)</t>
+          <t>Emeka Egbuka (TB)</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>4.03</t>
         </is>
       </c>
     </row>
@@ -7281,20 +7281,20 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>Drake London (ATL)</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>D'Andre Swift (CHI)</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D40" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -7304,20 +7304,20 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Malik Willis (MIA)</t>
+          <t>Tetairoa McMillan (CAR)</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>4.01</t>
         </is>
       </c>
     </row>
@@ -7327,20 +7327,20 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>James Cook III (BUF)</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tee Higgins (CIN)</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D42" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>3.11</t>
         </is>
       </c>
     </row>
@@ -7350,20 +7350,20 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>A.J. Brown (NE)</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
+          <t>Carnell Tate (TEN)</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -7373,20 +7373,20 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Chris Olave (NO)</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Javonte Williams (DAL)</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7396,20 +7396,20 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>C.J. Stroud (HOU)</t>
-        </is>
-      </c>
-      <c r="C45" s="17" t="inlineStr">
+          <t>Josh Allen (BUF)</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>2.09</t>
         </is>
       </c>
     </row>
@@ -7419,20 +7419,20 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>Trey McBride (ARI)</t>
-        </is>
-      </c>
-      <c r="C46" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Luther Burden III (CHI)</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D46" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -7442,20 +7442,20 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Ashton Jeanty (LV)</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Christian Watson (GB)</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -7465,20 +7465,20 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Bryce Young (CAR)</t>
-        </is>
-      </c>
-      <c r="C48" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Bucky Irving (TB)</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D48" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>4.06</t>
         </is>
       </c>
     </row>
@@ -7488,20 +7488,20 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>George Pickens (DAL)</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="inlineStr">
+          <t>Parker Washington (JAX)</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D49" s="14" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>7.04</t>
         </is>
       </c>
     </row>
@@ -7511,20 +7511,20 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Zay Flowers (BAL)</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Travis Etienne Jr. (NO)</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>4.09</t>
         </is>
       </c>
     </row>
@@ -7534,12 +7534,12 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Nico Collins (HOU)</t>
-        </is>
-      </c>
-      <c r="C51" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Cam Skattebo (NYG)</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D51" s="14" t="n">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.08</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Omarion Hampton (LAC)</t>
-        </is>
-      </c>
-      <c r="C52" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Terry McLaurin (WAS)</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D52" s="14" t="n">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -7580,20 +7580,20 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Breece Hall (NYJ)</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jameson Williams (DET)</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -7603,20 +7603,20 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>Brock Bowers (LV)</t>
-        </is>
-      </c>
-      <c r="C54" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>DJ Moore (BUF)</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>5.09</t>
         </is>
       </c>
     </row>
@@ -7626,20 +7626,20 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Garrett Wilson (NYJ)</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Bhayshul Tuten (JAX)</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -7649,20 +7649,20 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Cam Skattebo (NYG)</t>
-        </is>
-      </c>
-      <c r="C56" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Davante Adams (LAR)</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>5.02</t>
         </is>
       </c>
     </row>
@@ -7672,20 +7672,20 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>DeVonta Smith (PHI)</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="inlineStr">
+          <t>Mike Evans (SF)</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D57" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -7695,20 +7695,20 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr. (NO)</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Rome Odunze (CHI)</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D58" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>6.05</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Jeremiyah Love (ARI)</t>
-        </is>
-      </c>
-      <c r="C59" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Marvin Harrison Jr. (ARI)</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D59" s="14" t="n">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -7741,20 +7741,20 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>Javonte Williams (DAL)</t>
-        </is>
-      </c>
-      <c r="C60" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DK Metcalf (PIT)</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D60" s="14" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -7764,20 +7764,20 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Cam Ward (TEN)</t>
-        </is>
-      </c>
-      <c r="C61" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tyler Warren (IND)</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>4.11</t>
         </is>
       </c>
     </row>
@@ -7787,20 +7787,20 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Geno Smith (NYJ)</t>
-        </is>
-      </c>
-      <c r="C62" s="17" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Colston Loveland (CHI)</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D62" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.04</t>
         </is>
       </c>
     </row>
@@ -7810,20 +7810,20 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Aaron Rodgers (PIT)</t>
+          <t>Alec Pierce (IND)</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D63" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>9.05</t>
         </is>
       </c>
     </row>
@@ -7833,20 +7833,20 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Kyren Williams (LAR)</t>
-        </is>
-      </c>
-      <c r="C64" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Brian Thomas Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D64" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>7.02</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>D'Andre Swift (CHI)</t>
+          <t>Quinshon Judkins (CLE)</t>
         </is>
       </c>
       <c r="C65" s="16" t="inlineStr">
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="D65" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
@@ -7879,12 +7879,12 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>Davante Adams (LAR)</t>
-        </is>
-      </c>
-      <c r="C66" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>TreVeyon Henderson (NE)</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D66" s="14" t="n">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -7902,20 +7902,20 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan (CAR)</t>
-        </is>
-      </c>
-      <c r="C67" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>David Montgomery (HOU)</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D67" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -7925,20 +7925,20 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Tee Higgins (CIN)</t>
-        </is>
-      </c>
-      <c r="C68" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Lamar Jackson (BAL)</t>
+        </is>
+      </c>
+      <c r="C68" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D68" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.09</t>
         </is>
       </c>
     </row>
@@ -7948,10 +7948,10 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Emeka Egbuka (TB)</t>
-        </is>
-      </c>
-      <c r="C69" s="18" t="inlineStr">
+          <t>Chris Godwin Jr. (TB)</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>8.12</t>
         </is>
       </c>
     </row>
@@ -7971,20 +7971,20 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Jameson Williams (DET)</t>
-        </is>
-      </c>
-      <c r="C70" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jadarian Price (SEA)</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D70" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -7994,20 +7994,20 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>Ladd McConkey (LAC)</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>MarShawn Lloyd (GB)</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>15.06</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Bucky Irving (TB)</t>
+          <t>Rhamondre Stevenson (NE)</t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr">
@@ -8026,11 +8026,11 @@
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -8040,20 +8040,20 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Colston Loveland (CHI)</t>
-        </is>
-      </c>
-      <c r="C73" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Quentin Johnston (LAC)</t>
+        </is>
+      </c>
+      <c r="C73" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>10.05</t>
         </is>
       </c>
     </row>
@@ -8063,20 +8063,20 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Quinshon Judkins (CLE)</t>
-        </is>
-      </c>
-      <c r="C74" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Michael Pittman Jr. (PIT)</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D74" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>9.07</t>
         </is>
       </c>
     </row>
@@ -8086,20 +8086,20 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Waddle (DEN)</t>
-        </is>
-      </c>
-      <c r="C75" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rico Dowdle (PIT)</t>
+        </is>
+      </c>
+      <c r="C75" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>8.01</t>
         </is>
       </c>
     </row>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Malik Nabers (NYG)</t>
-        </is>
-      </c>
-      <c r="C76" s="18" t="inlineStr">
+          <t>Wan'Dale Robinson (TEN)</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D76" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>10.09</t>
         </is>
       </c>
     </row>
@@ -8132,20 +8132,20 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>David Montgomery (HOU)</t>
-        </is>
-      </c>
-      <c r="C77" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Harold Fannin Jr. (CLE)</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D77" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -8155,20 +8155,20 @@
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Luther Burden III (CHI)</t>
-        </is>
-      </c>
-      <c r="C78" s="18" t="inlineStr">
+          <t>Michael Wilson (ARI)</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D78" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>7.11</t>
         </is>
       </c>
     </row>
@@ -8178,10 +8178,10 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>Terry McLaurin (WAS)</t>
-        </is>
-      </c>
-      <c r="C79" s="18" t="inlineStr">
+          <t>Stefon Diggs (WAS)</t>
+        </is>
+      </c>
+      <c r="C79" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>10.02</t>
         </is>
       </c>
     </row>
@@ -8201,20 +8201,20 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Tyler Warren (IND)</t>
-        </is>
-      </c>
-      <c r="C80" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Courtland Sutton (DEN)</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D80" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>7.09</t>
         </is>
       </c>
     </row>
@@ -8224,20 +8224,20 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>Mike Evans (SF)</t>
-        </is>
-      </c>
-      <c r="C81" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jacory Croskey-Merritt (WAS)</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D81" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>10.06</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Warren (PIT)</t>
+          <t>Kenny Gainwell (TB)</t>
         </is>
       </c>
       <c r="C82" s="16" t="inlineStr">
@@ -8256,11 +8256,11 @@
         </is>
       </c>
       <c r="D82" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8270,20 +8270,20 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>DJ Moore (BUF)</t>
-        </is>
-      </c>
-      <c r="C83" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jaylen Warren (PIT)</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D83" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -8293,20 +8293,20 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Harold Fannin Jr. (CLE)</t>
-        </is>
-      </c>
-      <c r="C84" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jordan Addison (MIN)</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D84" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>9.09</t>
         </is>
       </c>
     </row>
@@ -8316,20 +8316,20 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>Christian Watson (GB)</t>
-        </is>
-      </c>
-      <c r="C85" s="18" t="inlineStr">
+          <t>De'Zhaun Stribling (SF)</t>
+        </is>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D85" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>12.07</t>
         </is>
       </c>
     </row>
@@ -8339,20 +8339,20 @@
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Parker Washington (JAX)</t>
+          <t>Tucker Kraft (GB)</t>
         </is>
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D86" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8362,20 +8362,20 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson (NE)</t>
-        </is>
-      </c>
-      <c r="C87" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jalen Hurts (PHI)</t>
+        </is>
+      </c>
+      <c r="C87" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D87" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>5.12</t>
         </is>
       </c>
     </row>
@@ -8385,20 +8385,20 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Alec Pierce (IND)</t>
-        </is>
-      </c>
-      <c r="C88" s="18" t="inlineStr">
+          <t>Jayden Reed (GB)</t>
+        </is>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D88" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8408,20 +8408,20 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>DK Metcalf (PIT)</t>
-        </is>
-      </c>
-      <c r="C89" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jayden Daniels (WAS)</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D89" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>6.04</t>
         </is>
       </c>
     </row>
@@ -8431,20 +8431,20 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Rome Odunze (CHI)</t>
-        </is>
-      </c>
-      <c r="C90" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Joe Burrow (CIN)</t>
+        </is>
+      </c>
+      <c r="C90" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D90" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -8454,20 +8454,20 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>Sam LaPorta (DET)</t>
-        </is>
-      </c>
-      <c r="C91" s="19" t="inlineStr">
+          <t>George Kittle (SF)</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -8477,20 +8477,20 @@
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr. (ARI)</t>
-        </is>
-      </c>
-      <c r="C92" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chuba Hubbard (CAR)</t>
+        </is>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D92" s="14" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>7.05</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten (JAX)</t>
+          <t>J.K. Dobbins (DEN)</t>
         </is>
       </c>
       <c r="C93" s="16" t="inlineStr">
@@ -8509,11 +8509,11 @@
         </is>
       </c>
       <c r="D93" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>8.1</t>
         </is>
       </c>
     </row>
@@ -8523,20 +8523,20 @@
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>George Kittle (SF)</t>
-        </is>
-      </c>
-      <c r="C94" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tony Pollard (TEN)</t>
+        </is>
+      </c>
+      <c r="C94" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D94" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>7.12</t>
         </is>
       </c>
     </row>
@@ -8546,20 +8546,20 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>Michael Pittman Jr. (PIT)</t>
-        </is>
-      </c>
-      <c r="C95" s="18" t="inlineStr">
+          <t>Josh Downs (IND)</t>
+        </is>
+      </c>
+      <c r="C95" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D95" s="14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>10.01</t>
         </is>
       </c>
     </row>
@@ -8569,20 +8569,20 @@
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Courtland Sutton (DEN)</t>
-        </is>
-      </c>
-      <c r="C96" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonathon Brooks (CAR)</t>
+        </is>
+      </c>
+      <c r="C96" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D96" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>9.1</t>
         </is>
       </c>
     </row>
@@ -8592,20 +8592,20 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>Travis Kelce (KC)</t>
-        </is>
-      </c>
-      <c r="C97" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jakobi Meyers (JAX)</t>
+        </is>
+      </c>
+      <c r="C97" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>10.1</t>
         </is>
       </c>
     </row>
@@ -8615,20 +8615,20 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>Dallas Goedert (PHI)</t>
-        </is>
-      </c>
-      <c r="C98" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Romeo Doubs (NE)</t>
+        </is>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D98" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -8638,20 +8638,20 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson (NE)</t>
-        </is>
-      </c>
-      <c r="C99" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Sam LaPorta (DET)</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -8661,20 +8661,20 @@
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr. (TB)</t>
-        </is>
-      </c>
-      <c r="C100" s="18" t="inlineStr">
+          <t>Khalil Shakir (BUF)</t>
+        </is>
+      </c>
+      <c r="C100" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D100" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>12.11</t>
         </is>
       </c>
     </row>
@@ -8684,20 +8684,20 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>Kyle Pitts Sr. (ATL)</t>
-        </is>
-      </c>
-      <c r="C101" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kyle Monangai (CHI)</t>
+        </is>
+      </c>
+      <c r="C101" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -8707,20 +8707,20 @@
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Jakobi Meyers (JAX)</t>
-        </is>
-      </c>
-      <c r="C102" s="18" t="inlineStr">
+          <t>Makai Lemon (PHI)</t>
+        </is>
+      </c>
+      <c r="C102" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D102" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -8730,20 +8730,20 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>Tony Pollard (TEN)</t>
-        </is>
-      </c>
-      <c r="C103" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Xavier Worthy (KC)</t>
+        </is>
+      </c>
+      <c r="C103" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -8753,20 +8753,20 @@
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>Michael Wilson (ARI)</t>
-        </is>
-      </c>
-      <c r="C104" s="18" t="inlineStr">
+          <t>Malik Washington (MIA)</t>
+        </is>
+      </c>
+      <c r="C104" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D104" s="14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>Chuba Hubbard (CAR)</t>
+          <t>Jordan Mason (MIN)</t>
         </is>
       </c>
       <c r="C105" s="16" t="inlineStr">
@@ -8785,11 +8785,11 @@
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>10.07</t>
         </is>
       </c>
     </row>
@@ -8799,20 +8799,20 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>Jayden Reed (GB)</t>
-        </is>
-      </c>
-      <c r="C106" s="18" t="inlineStr">
+          <t>Jalen Coker (CAR)</t>
+        </is>
+      </c>
+      <c r="C106" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D106" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>13.02</t>
         </is>
       </c>
     </row>
@@ -8822,20 +8822,20 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Carnell Tate (TEN)</t>
-        </is>
-      </c>
-      <c r="C107" s="18" t="inlineStr">
+          <t>Rashid Shaheed (SEA)</t>
+        </is>
+      </c>
+      <c r="C107" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>13.03</t>
         </is>
       </c>
     </row>
@@ -8845,20 +8845,20 @@
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>J.K. Dobbins (DEN)</t>
-        </is>
-      </c>
-      <c r="C108" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>KC Concepcion (CLE)</t>
+        </is>
+      </c>
+      <c r="C108" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D108" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>11.01</t>
         </is>
       </c>
     </row>
@@ -8868,20 +8868,20 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>Jordan Addison (MIN)</t>
-        </is>
-      </c>
-      <c r="C109" s="18" t="inlineStr">
+          <t>Kayshon Boutte (HOU)</t>
+        </is>
+      </c>
+      <c r="C109" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>19.08</t>
         </is>
       </c>
     </row>
@@ -8891,20 +8891,20 @@
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson (TEN)</t>
-        </is>
-      </c>
-      <c r="C110" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Drake Maye (NE)</t>
+        </is>
+      </c>
+      <c r="C110" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D110" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -8914,20 +8914,20 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>Tucker Kraft (GB)</t>
-        </is>
-      </c>
-      <c r="C111" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Rachaad White (WAS)</t>
+        </is>
+      </c>
+      <c r="C111" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -8937,20 +8937,20 @@
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C112" s="18" t="inlineStr">
+          <t>Matthew Golden (GB)</t>
+        </is>
+      </c>
+      <c r="C112" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D112" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>11.07</t>
         </is>
       </c>
     </row>
@@ -8960,20 +8960,20 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>Rico Dowdle (PIT)</t>
-        </is>
-      </c>
-      <c r="C113" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jaxson Dart (NYG)</t>
+        </is>
+      </c>
+      <c r="C113" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -8983,20 +8983,20 @@
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Mark Andrews (BAL)</t>
-        </is>
-      </c>
-      <c r="C114" s="19" t="inlineStr">
+          <t>Kyle Pitts Sr. (ATL)</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D114" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>6.1</t>
         </is>
       </c>
     </row>
@@ -9006,20 +9006,20 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>Quentin Johnston (LAC)</t>
-        </is>
-      </c>
-      <c r="C115" s="18" t="inlineStr">
+          <t>Keenan Allen (IND)</t>
+        </is>
+      </c>
+      <c r="C115" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>17.07</t>
         </is>
       </c>
     </row>
@@ -9029,20 +9029,20 @@
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>Khalil Shakir (BUF)</t>
-        </is>
-      </c>
-      <c r="C116" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Caleb Williams (CHI)</t>
+        </is>
+      </c>
+      <c r="C116" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D116" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -9052,20 +9052,20 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr. (MIN)</t>
-        </is>
-      </c>
-      <c r="C117" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Trevor Lawrence (JAX)</t>
+        </is>
+      </c>
+      <c r="C117" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -9075,12 +9075,12 @@
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>Romeo Doubs (NE)</t>
-        </is>
-      </c>
-      <c r="C118" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Blake Corum (LAR)</t>
+        </is>
+      </c>
+      <c r="C118" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D118" s="14" t="n">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>9.08</t>
         </is>
       </c>
     </row>
@@ -9098,20 +9098,20 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>Stefon Diggs (WAS)</t>
-        </is>
-      </c>
-      <c r="C119" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>RJ Harvey (DEN)</t>
+        </is>
+      </c>
+      <c r="C119" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>7.08</t>
         </is>
       </c>
     </row>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Xavier Worthy (KC)</t>
+          <t>Juwan Johnson (NO)</t>
         </is>
       </c>
       <c r="C120" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D120" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9144,20 +9144,20 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>Jadarian Price (SEA)</t>
-        </is>
-      </c>
-      <c r="C121" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jordyn Tyson (NO)</t>
+        </is>
+      </c>
+      <c r="C121" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D121" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>8.07</t>
         </is>
       </c>
     </row>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>Deebo Samuel Sr. (SF)</t>
+          <t>Dalton Schultz (HOU)</t>
         </is>
       </c>
       <c r="C122" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>17.01</t>
         </is>
       </c>
     </row>
@@ -9190,20 +9190,20 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>RJ Harvey (DEN)</t>
-        </is>
-      </c>
-      <c r="C123" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Travis Kelce (KC)</t>
+        </is>
+      </c>
+      <c r="C123" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>8.08</t>
         </is>
       </c>
     </row>
@@ -9213,20 +9213,20 @@
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>Isaiah Likely (NYG)</t>
-        </is>
-      </c>
-      <c r="C124" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tre Tucker (LV)</t>
+        </is>
+      </c>
+      <c r="C124" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D124" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>17.1</t>
         </is>
       </c>
     </row>
@@ -9236,20 +9236,20 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>Josh Downs (IND)</t>
-        </is>
-      </c>
-      <c r="C125" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Aaron Jones Sr. (MIN)</t>
+        </is>
+      </c>
+      <c r="C125" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -9259,20 +9259,20 @@
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>Matthew Golden (GB)</t>
+          <t>Jake Ferguson (DAL)</t>
         </is>
       </c>
       <c r="C126" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>9.02</t>
         </is>
       </c>
     </row>
@@ -9282,12 +9282,12 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>Jake Ferguson (DAL)</t>
+          <t>Dak Prescott (DAL)</t>
         </is>
       </c>
       <c r="C127" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>7.07</t>
         </is>
       </c>
     </row>
@@ -9305,20 +9305,20 @@
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>Hunter Henry (NE)</t>
-        </is>
-      </c>
-      <c r="C128" s="19" t="inlineStr">
+          <t>Dalton Kincaid (BUF)</t>
+        </is>
+      </c>
+      <c r="C128" s="18" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D128" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -9328,12 +9328,12 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling (SF)</t>
+          <t>Isaiah Likely (NYG)</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D129" s="14" t="n">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>Kyle Monangai (CHI)</t>
+          <t>Tyjae Spears (TEN)</t>
         </is>
       </c>
       <c r="C130" s="16" t="inlineStr">
@@ -9360,11 +9360,11 @@
         </is>
       </c>
       <c r="D130" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -9374,12 +9374,12 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>Dalton Kincaid (BUF)</t>
+          <t>Justin Herbert (LAC)</t>
         </is>
       </c>
       <c r="C131" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -9397,12 +9397,12 @@
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>Kenny Gainwell (TB)</t>
-        </is>
-      </c>
-      <c r="C132" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dallas Goedert (PHI)</t>
+        </is>
+      </c>
+      <c r="C132" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D132" s="14" t="n">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -9420,12 +9420,12 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>Makai Lemon (PHI)</t>
-        </is>
-      </c>
-      <c r="C133" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Bo Nix (DEN)</t>
+        </is>
+      </c>
+      <c r="C133" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D133" s="14" t="n">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>10.12</t>
         </is>
       </c>
     </row>
@@ -9443,20 +9443,20 @@
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Rashid Shaheed (SEA)</t>
-        </is>
-      </c>
-      <c r="C134" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brock Purdy (SF)</t>
+        </is>
+      </c>
+      <c r="C134" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D134" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>11.02</t>
         </is>
       </c>
     </row>
@@ -9466,20 +9466,20 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>Brenton Strange (JAX)</t>
-        </is>
-      </c>
-      <c r="C135" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Omar Cooper Jr. (NYJ)</t>
+        </is>
+      </c>
+      <c r="C135" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>17.02</t>
         </is>
       </c>
     </row>
@@ -9489,20 +9489,20 @@
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>Juwan Johnson (NO)</t>
+          <t>Jared Goff (DET)</t>
         </is>
       </c>
       <c r="C136" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D136" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>12.03</t>
         </is>
       </c>
     </row>
@@ -9512,20 +9512,20 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>Rachaad White (WAS)</t>
-        </is>
-      </c>
-      <c r="C137" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Deebo Samuel Sr. (SF)</t>
+        </is>
+      </c>
+      <c r="C137" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>11.11</t>
         </is>
       </c>
     </row>
@@ -9535,20 +9535,20 @@
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>KC Concepcion (CLE)</t>
-        </is>
-      </c>
-      <c r="C138" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyler Shough (NO)</t>
+        </is>
+      </c>
+      <c r="C138" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>16.07</t>
         </is>
       </c>
     </row>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>Jerry Jeudy (CLE)</t>
-        </is>
-      </c>
-      <c r="C139" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Matthew Stafford (LAR)</t>
+        </is>
+      </c>
+      <c r="C139" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>9.01</t>
         </is>
       </c>
     </row>
@@ -9581,20 +9581,20 @@
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt (WAS)</t>
-        </is>
-      </c>
-      <c r="C140" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kyler Murray (MIN)</t>
+        </is>
+      </c>
+      <c r="C140" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D140" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>14.03</t>
         </is>
       </c>
     </row>
@@ -9604,20 +9604,20 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>Jonathon Brooks (CAR)</t>
-        </is>
-      </c>
-      <c r="C141" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jordan Love (GB)</t>
+        </is>
+      </c>
+      <c r="C141" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>13.05</t>
         </is>
       </c>
     </row>
@@ -9627,20 +9627,20 @@
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>Jalen Coker (CAR)</t>
-        </is>
-      </c>
-      <c r="C142" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Baker Mayfield (TB)</t>
+        </is>
+      </c>
+      <c r="C142" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -9650,20 +9650,20 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>Calvin Ridley (TEN)</t>
-        </is>
-      </c>
-      <c r="C143" s="18" t="inlineStr">
+          <t>Denzel Boston (CLE)</t>
+        </is>
+      </c>
+      <c r="C143" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9673,20 +9673,20 @@
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>Cooper Kupp (SEA)</t>
-        </is>
-      </c>
-      <c r="C144" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Patrick Mahomes (KC)</t>
+        </is>
+      </c>
+      <c r="C144" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -9696,20 +9696,20 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>Dalton Schultz (HOU)</t>
-        </is>
-      </c>
-      <c r="C145" s="19" t="inlineStr">
+          <t>Brenton Strange (JAX)</t>
+        </is>
+      </c>
+      <c r="C145" s="18" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>13.08</t>
         </is>
       </c>
     </row>
@@ -9719,20 +9719,20 @@
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>Keenan Allen (IND)</t>
-        </is>
-      </c>
-      <c r="C146" s="18" t="inlineStr">
+          <t>Dontayvion Wicks (PHI)</t>
+        </is>
+      </c>
+      <c r="C146" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9742,20 +9742,20 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Jordan Mason (MIN)</t>
-        </is>
-      </c>
-      <c r="C147" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Mark Andrews (BAL)</t>
+        </is>
+      </c>
+      <c r="C147" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>11.09</t>
         </is>
       </c>
     </row>
@@ -9765,20 +9765,20 @@
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>T.J. Hockenson (MIN)</t>
-        </is>
-      </c>
-      <c r="C148" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Pat Bryant (DEN)</t>
+        </is>
+      </c>
+      <c r="C148" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>19.11</t>
         </is>
       </c>
     </row>
@@ -9788,12 +9788,12 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>Greg Dulcich (MIA)</t>
+          <t>Malik Willis (MIA)</t>
         </is>
       </c>
       <c r="C149" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -9811,20 +9811,20 @@
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>Kayshon Boutte (HOU)</t>
-        </is>
-      </c>
-      <c r="C150" s="18" t="inlineStr">
+          <t>Jalen Nailor (LV)</t>
+        </is>
+      </c>
+      <c r="C150" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Jordyn Tyson (NO)</t>
-        </is>
-      </c>
-      <c r="C151" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Woody Marks (HOU)</t>
+        </is>
+      </c>
+      <c r="C151" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D151" s="14" t="n">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>14.04</t>
         </is>
       </c>
     </row>
@@ -9857,12 +9857,12 @@
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Denzel Boston (CLE)</t>
+          <t>Hunter Henry (NE)</t>
         </is>
       </c>
       <c r="C152" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -9880,20 +9880,20 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>Blake Corum (LAR)</t>
-        </is>
-      </c>
-      <c r="C153" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Chig Okonkwo (WAS)</t>
+        </is>
+      </c>
+      <c r="C153" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd (GB)</t>
+          <t>Chris Rodriguez Jr. (JAX)</t>
         </is>
       </c>
       <c r="C154" s="16" t="inlineStr">
@@ -9912,11 +9912,11 @@
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>12.08</t>
         </is>
       </c>
     </row>
@@ -9926,20 +9926,20 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>Woody Marks (HOU)</t>
-        </is>
-      </c>
-      <c r="C155" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Travis Hunter (JAX)</t>
+        </is>
+      </c>
+      <c r="C155" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9949,20 +9949,20 @@
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq (NYJ)</t>
-        </is>
-      </c>
-      <c r="C156" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Cooper Kupp (SEA)</t>
+        </is>
+      </c>
+      <c r="C156" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>19.05</t>
         </is>
       </c>
     </row>
@@ -9972,20 +9972,20 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Pat Freiermuth (PIT)</t>
-        </is>
-      </c>
-      <c r="C157" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jerry Jeudy (CLE)</t>
+        </is>
+      </c>
+      <c r="C157" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D157" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E157" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -9995,12 +9995,12 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Tyjae Spears (TEN)</t>
-        </is>
-      </c>
-      <c r="C158" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Cam Ward (TEN)</t>
+        </is>
+      </c>
+      <c r="C158" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10018,20 +10018,20 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Tre Tucker (LV)</t>
-        </is>
-      </c>
-      <c r="C159" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Isiah Pacheco (DET)</t>
+        </is>
+      </c>
+      <c r="C159" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E159" s="14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -10041,20 +10041,20 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>Cade Otton (TB)</t>
+          <t>C.J. Stroud (HOU)</t>
         </is>
       </c>
       <c r="C160" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>18.01</t>
         </is>
       </c>
     </row>
@@ -10064,20 +10064,20 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>Rashod Bateman (BAL)</t>
-        </is>
-      </c>
-      <c r="C161" s="18" t="inlineStr">
+          <t>DeMario Douglas (NE)</t>
+        </is>
+      </c>
+      <c r="C161" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E161" s="14" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10087,20 +10087,20 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Jalen Nailor (LV)</t>
-        </is>
-      </c>
-      <c r="C162" s="18" t="inlineStr">
+          <t>Malachi Fields (NYG)</t>
+        </is>
+      </c>
+      <c r="C162" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D162" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>19.04</t>
         </is>
       </c>
     </row>
@@ -10110,20 +10110,20 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>Chig Okonkwo (WAS)</t>
+          <t>Sam Darnold (SEA)</t>
         </is>
       </c>
       <c r="C163" s="19" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E163" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>14.05</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Alvin Kamara (NO)</t>
+          <t>Keaton Mitchell (LAC)</t>
         </is>
       </c>
       <c r="C164" s="16" t="inlineStr">
@@ -10142,11 +10142,11 @@
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10156,20 +10156,20 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>Zach Charbonnet (SEA)</t>
-        </is>
-      </c>
-      <c r="C165" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Adonai Mitchell (NYJ)</t>
+        </is>
+      </c>
+      <c r="C165" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E165" s="14" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10179,20 +10179,20 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Jaylin Noel (HOU)</t>
-        </is>
-      </c>
-      <c r="C166" s="18" t="inlineStr">
+          <t>Ja'Kobi Lane (BAL)</t>
+        </is>
+      </c>
+      <c r="C166" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>14.02</t>
         </is>
       </c>
     </row>
@@ -10202,20 +10202,20 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>Malik Washington (MIA)</t>
-        </is>
-      </c>
-      <c r="C167" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Daniel Jones (IND)</t>
+        </is>
+      </c>
+      <c r="C167" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E167" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>17.11</t>
         </is>
       </c>
     </row>
@@ -10225,20 +10225,20 @@
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>AJ Barner (SEA)</t>
-        </is>
-      </c>
-      <c r="C168" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tank Dell (HOU)</t>
+        </is>
+      </c>
+      <c r="C168" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10248,20 +10248,20 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>Dylan Sampson (CLE)</t>
-        </is>
-      </c>
-      <c r="C169" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Germie Bernard (PIT)</t>
+        </is>
+      </c>
+      <c r="C169" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E169" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10271,20 +10271,20 @@
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Omar Cooper Jr. (NYJ)</t>
-        </is>
-      </c>
-      <c r="C170" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Zach Charbonnet (SEA)</t>
+        </is>
+      </c>
+      <c r="C170" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>13.04</t>
         </is>
       </c>
     </row>
@@ -10294,20 +10294,20 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>Travis Hunter (JAX)</t>
-        </is>
-      </c>
-      <c r="C171" s="18" t="inlineStr">
+          <t>Cyrus Allen (KC)</t>
+        </is>
+      </c>
+      <c r="C171" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -10317,20 +10317,20 @@
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Jalen Tolbert (MIA)</t>
-        </is>
-      </c>
-      <c r="C172" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyler Allgeier (ARI)</t>
+        </is>
+      </c>
+      <c r="C172" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -10340,20 +10340,20 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>Devaughn Vele (NO)</t>
-        </is>
-      </c>
-      <c r="C173" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dylan Sampson (CLE)</t>
+        </is>
+      </c>
+      <c r="C173" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -10363,20 +10363,20 @@
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Tyler Allgeier (ARI)</t>
-        </is>
-      </c>
-      <c r="C174" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kyle Williams (NE)</t>
+        </is>
+      </c>
+      <c r="C174" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>19.06</t>
         </is>
       </c>
     </row>
@@ -10386,20 +10386,20 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>Tre' Harris (LAC)</t>
-        </is>
-      </c>
-      <c r="C175" s="18" t="inlineStr">
+          <t>Calvin Ridley (TEN)</t>
+        </is>
+      </c>
+      <c r="C175" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E175" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>22.01</t>
         </is>
       </c>
     </row>
@@ -10409,20 +10409,20 @@
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>Germie Bernard (PIT)</t>
+          <t>T.J. Hockenson (MIN)</t>
         </is>
       </c>
       <c r="C176" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D176" s="14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -10432,20 +10432,20 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks (PHI)</t>
-        </is>
-      </c>
-      <c r="C177" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Mike Washington Jr. (LV)</t>
+        </is>
+      </c>
+      <c r="C177" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E177" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.05</t>
         </is>
       </c>
     </row>
@@ -10455,12 +10455,12 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Isiah Pacheco (DET)</t>
-        </is>
-      </c>
-      <c r="C178" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Greg Dulcich (MIA)</t>
+        </is>
+      </c>
+      <c r="C178" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10478,12 +10478,12 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Adonai Mitchell (NYJ)</t>
+          <t>Kenyon Sadiq (NYJ)</t>
         </is>
       </c>
       <c r="C179" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="E179" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>13.1</t>
         </is>
       </c>
     </row>
@@ -10501,20 +10501,20 @@
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane (BAL)</t>
-        </is>
-      </c>
-      <c r="C180" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonah Coleman (DEN)</t>
+        </is>
+      </c>
+      <c r="C180" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>15.03</t>
         </is>
       </c>
     </row>
@@ -10524,20 +10524,20 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>DeMario Douglas (NE)</t>
-        </is>
-      </c>
-      <c r="C181" s="18" t="inlineStr">
+          <t>Tre' Harris (LAC)</t>
+        </is>
+      </c>
+      <c r="C181" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Chris Rodriguez Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C182" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Keon Coleman (BUF)</t>
+        </is>
+      </c>
+      <c r="C182" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D182" s="14" t="n">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>20.07</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>Mike Washington Jr. (LV)</t>
+          <t>Tyrone Tracy Jr. (NYG)</t>
         </is>
       </c>
       <c r="C183" s="16" t="inlineStr">
@@ -10579,11 +10579,11 @@
         </is>
       </c>
       <c r="D183" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E183" s="14" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10593,20 +10593,20 @@
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>Darius Slayton (NYG)</t>
+          <t>Pat Freiermuth (PIT)</t>
         </is>
       </c>
       <c r="C184" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D184" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10616,20 +10616,20 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Zachariah Branch (ATL)</t>
-        </is>
-      </c>
-      <c r="C185" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Aaron Rodgers (PIT)</t>
+        </is>
+      </c>
+      <c r="C185" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E185" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10639,20 +10639,20 @@
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Keaton Mitchell (LAC)</t>
-        </is>
-      </c>
-      <c r="C186" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Bryce Young (CAR)</t>
+        </is>
+      </c>
+      <c r="C186" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D186" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>19.12</t>
         </is>
       </c>
     </row>
@@ -10662,20 +10662,20 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>Tank Bigsby (PHI)</t>
-        </is>
-      </c>
-      <c r="C187" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Zachariah Branch (ATL)</t>
+        </is>
+      </c>
+      <c r="C187" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D187" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E187" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -10685,20 +10685,20 @@
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Malachi Fields (NYG)</t>
-        </is>
-      </c>
-      <c r="C188" s="18" t="inlineStr">
+          <t>Ryan Flournoy (DAL)</t>
+        </is>
+      </c>
+      <c r="C188" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D188" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10708,20 +10708,20 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Caleb Douglas (MIA)</t>
+          <t>Cade Otton (TB)</t>
         </is>
       </c>
       <c r="C189" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E189" s="14" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>20.06</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr. (NYG)</t>
+          <t>Tank Bigsby (PHI)</t>
         </is>
       </c>
       <c r="C190" s="16" t="inlineStr">
@@ -10740,11 +10740,11 @@
         </is>
       </c>
       <c r="D190" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E190" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10754,20 +10754,20 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>Pat Bryant (DEN)</t>
-        </is>
-      </c>
-      <c r="C191" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Alvin Kamara (NO)</t>
+        </is>
+      </c>
+      <c r="C191" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E191" s="14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>14.07</t>
         </is>
       </c>
     </row>
@@ -10777,20 +10777,20 @@
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Najee Harris (NYG)</t>
-        </is>
-      </c>
-      <c r="C192" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Caleb Douglas (MIA)</t>
+        </is>
+      </c>
+      <c r="C192" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D192" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18.09</t>
         </is>
       </c>
     </row>
@@ -10800,20 +10800,20 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Tory Horton (SEA)</t>
-        </is>
-      </c>
-      <c r="C193" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Geno Smith (NYJ)</t>
+        </is>
+      </c>
+      <c r="C193" s="19" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10823,20 +10823,20 @@
       </c>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>Ryan Flournoy (DAL)</t>
-        </is>
-      </c>
-      <c r="C194" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Najee Harris (NYG)</t>
+        </is>
+      </c>
+      <c r="C194" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D194" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E194" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10846,20 +10846,20 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Keon Coleman (BUF)</t>
-        </is>
-      </c>
-      <c r="C195" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brian Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C195" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E195" s="14" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>13.12</t>
         </is>
       </c>
     </row>
@@ -10869,10 +10869,10 @@
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>Tank Dell (HOU)</t>
-        </is>
-      </c>
-      <c r="C196" s="18" t="inlineStr">
+          <t>Devaughn Vele (NO)</t>
+        </is>
+      </c>
+      <c r="C196" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="E196" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10892,20 +10892,20 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>Cyrus Allen (KC)</t>
+          <t>AJ Barner (SEA)</t>
         </is>
       </c>
       <c r="C197" s="18" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D197" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E197" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10915,20 +10915,20 @@
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Jonah Coleman (DEN)</t>
-        </is>
-      </c>
-      <c r="C198" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jaylin Noel (HOU)</t>
+        </is>
+      </c>
+      <c r="C198" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D198" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>18.1</t>
         </is>
       </c>
     </row>
@@ -10938,20 +10938,20 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>Kyle Williams (NE)</t>
-        </is>
-      </c>
-      <c r="C199" s="18" t="inlineStr">
+          <t>Darius Slayton (NYG)</t>
+        </is>
+      </c>
+      <c r="C199" s="17" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E199" s="14" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10961,20 +10961,20 @@
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Kenneth Walker (KC)</t>
-        </is>
-      </c>
-      <c r="C200" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Oronde Gadsden (LAC)</t>
+        </is>
+      </c>
+      <c r="C200" s="18" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D200" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>
@@ -10984,20 +10984,20 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>Patrick Mahomes (KC)</t>
+          <t>Rashod Bateman (BAL)</t>
         </is>
       </c>
       <c r="C201" s="17" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D201" s="14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>20.05</t>
         </is>
       </c>
     </row>
@@ -11007,20 +11007,20 @@
       </c>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>Brian Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C202" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jalen Tolbert (MIA)</t>
+        </is>
+      </c>
+      <c r="C202" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D202" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E202" s="14" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11030,20 +11030,20 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>Oronde Gadsden (LAC)</t>
-        </is>
-      </c>
-      <c r="C203" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Tory Horton (SEA)</t>
+        </is>
+      </c>
+      <c r="C203" s="17" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D203" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>

--- a/assets/data/12guys1cup-cheat-sheet.xlsx
+++ b/assets/data/12guys1cup-cheat-sheet.xlsx
@@ -62,6 +62,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00B8386B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001565C0"/>
       <sz val="10"/>
     </font>
@@ -69,12 +75,6 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00E65100"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00B8386B"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -125,17 +125,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F8D7E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D4E4F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -6476,20 +6476,20 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Bijan Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Josh Allen (BUF)</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>2.09</t>
         </is>
       </c>
     </row>
@@ -6499,20 +6499,20 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase (CIN)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Bijan Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
     </row>
@@ -6522,20 +6522,20 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Puka Nacua (LAR)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
+          <t>Ja'Marr Chase (CIN)</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
     </row>
@@ -6545,20 +6545,20 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Christian McCaffrey (SF)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Puka Nacua (LAR)</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
     </row>
@@ -6568,20 +6568,20 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba (SEA)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
+          <t>Amon-Ra St. Brown (DET)</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -6591,20 +6591,20 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown (DET)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Christian McCaffrey (SF)</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.06</t>
         </is>
       </c>
     </row>
@@ -6614,20 +6614,20 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>CeeDee Lamb (DAL)</t>
+          <t>Lamar Jackson (BAL)</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>3.09</t>
         </is>
       </c>
     </row>
@@ -6637,20 +6637,20 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Jonathan Taylor (IND)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Drake Maye (NE)</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -6660,20 +6660,20 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>James Cook III (BUF)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jaxon Smith-Njigba (SEA)</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6683,20 +6683,20 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>De'Von Achane (MIA)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jalen Hurts (PHI)</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>5.12</t>
         </is>
       </c>
     </row>
@@ -6706,20 +6706,20 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Kenneth Walker (KC)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dak Prescott (DAL)</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>7.07</t>
         </is>
       </c>
     </row>
@@ -6729,12 +6729,12 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Chase Brown (CIN)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Joe Burrow (CIN)</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -6752,20 +6752,20 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Justin Jefferson (MIN)</t>
+          <t>Jayden Daniels (WAS)</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>6.04</t>
         </is>
       </c>
     </row>
@@ -6775,20 +6775,20 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>A.J. Brown (NE)</t>
+          <t>Trevor Lawrence (JAX)</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Chris Olave (NO)</t>
+          <t>Brock Purdy (SF)</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>11.02</t>
         </is>
       </c>
     </row>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Brock Bowers (LV)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jonathan Taylor (IND)</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D20" s="14" t="n">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.07</t>
         </is>
       </c>
     </row>
@@ -6844,20 +6844,20 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Nico Collins (HOU)</t>
+          <t>Justin Herbert (LAC)</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -6867,20 +6867,20 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Trey McBride (ARI)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Caleb Williams (CHI)</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -6890,20 +6890,20 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Garrett Wilson (NYJ)</t>
+          <t>Jaxson Dart (NYG)</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -6913,20 +6913,20 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Drake London (ATL)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>De'Von Achane (MIA)</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -6936,20 +6936,20 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>George Pickens (DAL)</t>
+          <t>Kyler Murray (MIN)</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>14.03</t>
         </is>
       </c>
     </row>
@@ -6959,20 +6959,20 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Rashee Rice (KC)</t>
+          <t>Matthew Stafford (LAR)</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>9.01</t>
         </is>
       </c>
     </row>
@@ -6982,20 +6982,20 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Omarion Hampton (LAC)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Bo Nix (DEN)</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>10.12</t>
         </is>
       </c>
     </row>
@@ -7005,20 +7005,20 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Ashton Jeanty (LV)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jared Goff (DET)</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>12.03</t>
         </is>
       </c>
     </row>
@@ -7028,20 +7028,20 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Malik Nabers (NYG)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chase Brown (CIN)</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7051,12 +7051,12 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Saquon Barkley (PHI)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Baker Mayfield (TB)</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -7074,20 +7074,20 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Zay Flowers (BAL)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
+          <t>CeeDee Lamb (DAL)</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>1.09</t>
         </is>
       </c>
     </row>
@@ -7097,20 +7097,20 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Derrick Henry (BAL)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tyler Shough (NO)</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>16.07</t>
         </is>
       </c>
     </row>
@@ -7120,20 +7120,20 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>DeVonta Smith (PHI)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Derrick Henry (BAL)</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.08</t>
         </is>
       </c>
     </row>
@@ -7143,20 +7143,20 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Waddle (DEN)</t>
+          <t>Jordan Love (GB)</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>13.05</t>
         </is>
       </c>
     </row>
@@ -7166,20 +7166,20 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>Jeremiyah Love (ARI)</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Sam Darnold (SEA)</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E35" s="14" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>14.05</t>
         </is>
       </c>
     </row>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>Kyren Williams (LAR)</t>
+          <t>Saquon Barkley (PHI)</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
@@ -7198,11 +7198,11 @@
         </is>
       </c>
       <c r="D36" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -7212,20 +7212,20 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>Ladd McConkey (LAC)</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
+          <t>Rashee Rice (KC)</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E37" s="14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -7235,20 +7235,20 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>Breece Hall (NYJ)</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Justin Jefferson (MIN)</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
@@ -7258,20 +7258,20 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>Emeka Egbuka (TB)</t>
+          <t>Daniel Jones (IND)</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>17.11</t>
         </is>
       </c>
     </row>
@@ -7281,20 +7281,20 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>D'Andre Swift (CHI)</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Drake London (ATL)</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D40" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>2.06</t>
         </is>
       </c>
     </row>
@@ -7304,20 +7304,20 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan (CAR)</t>
+          <t>Malik Willis (MIA)</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -7327,20 +7327,20 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>Tee Higgins (CIN)</t>
-        </is>
-      </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>James Cook III (BUF)</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D42" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>1.11</t>
         </is>
       </c>
     </row>
@@ -7350,20 +7350,20 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>Carnell Tate (TEN)</t>
-        </is>
-      </c>
-      <c r="C43" s="17" t="inlineStr">
+          <t>A.J. Brown (NE)</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -7373,20 +7373,20 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>Javonte Williams (DAL)</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Chris Olave (NO)</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.07</t>
         </is>
       </c>
     </row>
@@ -7396,20 +7396,20 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>Josh Allen (BUF)</t>
-        </is>
-      </c>
-      <c r="C45" s="19" t="inlineStr">
+          <t>C.J. Stroud (HOU)</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E45" s="14" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>18.01</t>
         </is>
       </c>
     </row>
@@ -7419,20 +7419,20 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>Luther Burden III (CHI)</t>
-        </is>
-      </c>
-      <c r="C46" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Trey McBride (ARI)</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D46" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -7442,20 +7442,20 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>Christian Watson (GB)</t>
-        </is>
-      </c>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Ashton Jeanty (LV)</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -7465,20 +7465,20 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>Bucky Irving (TB)</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Bryce Young (CAR)</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D48" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>19.12</t>
         </is>
       </c>
     </row>
@@ -7488,20 +7488,20 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>Parker Washington (JAX)</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="inlineStr">
+          <t>George Pickens (DAL)</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D49" s="14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E49" s="14" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -7511,20 +7511,20 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>Travis Etienne Jr. (NO)</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Zay Flowers (BAL)</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.05</t>
         </is>
       </c>
     </row>
@@ -7534,12 +7534,12 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>Cam Skattebo (NYG)</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Nico Collins (HOU)</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D51" s="14" t="n">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="E51" s="14" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>Terry McLaurin (WAS)</t>
-        </is>
-      </c>
-      <c r="C52" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Omarion Hampton (LAC)</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D52" s="14" t="n">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>2.04</t>
         </is>
       </c>
     </row>
@@ -7580,20 +7580,20 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>Jameson Williams (DET)</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Breece Hall (NYJ)</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7603,20 +7603,20 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>DJ Moore (BUF)</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brock Bowers (LV)</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -7626,20 +7626,20 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>Bhayshul Tuten (JAX)</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Garrett Wilson (NYJ)</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -7649,20 +7649,20 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>Davante Adams (LAR)</t>
-        </is>
-      </c>
-      <c r="C56" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Travis Etienne Jr. (NO)</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.09</t>
         </is>
       </c>
     </row>
@@ -7672,20 +7672,20 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>Mike Evans (SF)</t>
-        </is>
-      </c>
-      <c r="C57" s="17" t="inlineStr">
+          <t>DeVonta Smith (PHI)</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D57" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>3.12</t>
         </is>
       </c>
     </row>
@@ -7695,20 +7695,20 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>Rome Odunze (CHI)</t>
-        </is>
-      </c>
-      <c r="C58" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Cam Skattebo (NYG)</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D58" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>4.08</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr. (ARI)</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Javonte Williams (DAL)</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D59" s="14" t="n">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>3.1</t>
         </is>
       </c>
     </row>
@@ -7741,20 +7741,20 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>DK Metcalf (PIT)</t>
-        </is>
-      </c>
-      <c r="C60" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jeremiyah Love (ARI)</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D60" s="14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -7764,20 +7764,20 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>Tyler Warren (IND)</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Cam Ward (TEN)</t>
+        </is>
+      </c>
+      <c r="C61" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -7787,20 +7787,20 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>Colston Loveland (CHI)</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Geno Smith (NYJ)</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>QB</t>
         </is>
       </c>
       <c r="D62" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7810,20 +7810,20 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>Alec Pierce (IND)</t>
+          <t>Aaron Rodgers (PIT)</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D63" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -7833,20 +7833,20 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>Brian Thomas Jr. (JAX)</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kyren Williams (LAR)</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D64" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>Quinshon Judkins (CLE)</t>
+          <t>D'Andre Swift (CHI)</t>
         </is>
       </c>
       <c r="C65" s="16" t="inlineStr">
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="D65" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
@@ -7879,12 +7879,12 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson (NE)</t>
-        </is>
-      </c>
-      <c r="C66" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Davante Adams (LAR)</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D66" s="14" t="n">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>5.02</t>
         </is>
       </c>
     </row>
@@ -7902,20 +7902,20 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>David Montgomery (HOU)</t>
-        </is>
-      </c>
-      <c r="C67" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tetairoa McMillan (CAR)</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D67" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.01</t>
         </is>
       </c>
     </row>
@@ -7925,20 +7925,20 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>Lamar Jackson (BAL)</t>
-        </is>
-      </c>
-      <c r="C68" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tee Higgins (CIN)</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D68" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.11</t>
         </is>
       </c>
     </row>
@@ -7948,10 +7948,10 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr. (TB)</t>
-        </is>
-      </c>
-      <c r="C69" s="17" t="inlineStr">
+          <t>Emeka Egbuka (TB)</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>4.03</t>
         </is>
       </c>
     </row>
@@ -7971,20 +7971,20 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>Jadarian Price (SEA)</t>
-        </is>
-      </c>
-      <c r="C70" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jameson Williams (DET)</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D70" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -7994,20 +7994,20 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd (GB)</t>
-        </is>
-      </c>
-      <c r="C71" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ladd McConkey (LAC)</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>4.02</t>
         </is>
       </c>
     </row>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Rhamondre Stevenson (NE)</t>
+          <t>Bucky Irving (TB)</t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr">
@@ -8026,11 +8026,11 @@
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.06</t>
         </is>
       </c>
     </row>
@@ -8040,20 +8040,20 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>Quentin Johnston (LAC)</t>
-        </is>
-      </c>
-      <c r="C73" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Colston Loveland (CHI)</t>
+        </is>
+      </c>
+      <c r="C73" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>4.04</t>
         </is>
       </c>
     </row>
@@ -8063,20 +8063,20 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>Michael Pittman Jr. (PIT)</t>
-        </is>
-      </c>
-      <c r="C74" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Quinshon Judkins (CLE)</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D74" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>5.06</t>
         </is>
       </c>
     </row>
@@ -8086,20 +8086,20 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>Rico Dowdle (PIT)</t>
-        </is>
-      </c>
-      <c r="C75" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jaylen Waddle (DEN)</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>4.1</t>
         </is>
       </c>
     </row>
@@ -8109,20 +8109,20 @@
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson (TEN)</t>
-        </is>
-      </c>
-      <c r="C76" s="17" t="inlineStr">
+          <t>Malik Nabers (NYG)</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D76" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -8132,20 +8132,20 @@
       </c>
       <c r="B77" s="15" t="inlineStr">
         <is>
-          <t>Harold Fannin Jr. (CLE)</t>
-        </is>
-      </c>
-      <c r="C77" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>David Montgomery (HOU)</t>
+        </is>
+      </c>
+      <c r="C77" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D77" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.01</t>
         </is>
       </c>
     </row>
@@ -8155,20 +8155,20 @@
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>Michael Wilson (ARI)</t>
-        </is>
-      </c>
-      <c r="C78" s="17" t="inlineStr">
+          <t>Luther Burden III (CHI)</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D78" s="14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>5.04</t>
         </is>
       </c>
     </row>
@@ -8178,10 +8178,10 @@
       </c>
       <c r="B79" s="15" t="inlineStr">
         <is>
-          <t>Stefon Diggs (WAS)</t>
-        </is>
-      </c>
-      <c r="C79" s="17" t="inlineStr">
+          <t>Terry McLaurin (WAS)</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -8201,20 +8201,20 @@
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>Courtland Sutton (DEN)</t>
-        </is>
-      </c>
-      <c r="C80" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyler Warren (IND)</t>
+        </is>
+      </c>
+      <c r="C80" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D80" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>4.11</t>
         </is>
       </c>
     </row>
@@ -8224,20 +8224,20 @@
       </c>
       <c r="B81" s="15" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt (WAS)</t>
-        </is>
-      </c>
-      <c r="C81" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Mike Evans (SF)</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D81" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>Kenny Gainwell (TB)</t>
+          <t>Jaylen Warren (PIT)</t>
         </is>
       </c>
       <c r="C82" s="16" t="inlineStr">
@@ -8256,11 +8256,11 @@
         </is>
       </c>
       <c r="D82" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>6.12</t>
         </is>
       </c>
     </row>
@@ -8270,20 +8270,20 @@
       </c>
       <c r="B83" s="15" t="inlineStr">
         <is>
-          <t>Jaylen Warren (PIT)</t>
-        </is>
-      </c>
-      <c r="C83" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>DJ Moore (BUF)</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D83" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.09</t>
         </is>
       </c>
     </row>
@@ -8293,20 +8293,20 @@
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Jordan Addison (MIN)</t>
-        </is>
-      </c>
-      <c r="C84" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Harold Fannin Jr. (CLE)</t>
+        </is>
+      </c>
+      <c r="C84" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D84" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -8316,20 +8316,20 @@
       </c>
       <c r="B85" s="15" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling (SF)</t>
-        </is>
-      </c>
-      <c r="C85" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rhamondre Stevenson (NE)</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D85" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Tucker Kraft (GB)</t>
+          <t>Christian Watson (GB)</t>
         </is>
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D86" s="14" t="n">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.09</t>
         </is>
       </c>
     </row>
@@ -8362,20 +8362,20 @@
       </c>
       <c r="B87" s="15" t="inlineStr">
         <is>
-          <t>Jalen Hurts (PHI)</t>
-        </is>
-      </c>
-      <c r="C87" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Parker Washington (JAX)</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D87" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>7.04</t>
         </is>
       </c>
     </row>
@@ -8385,20 +8385,20 @@
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>Jayden Reed (GB)</t>
-        </is>
-      </c>
-      <c r="C88" s="17" t="inlineStr">
+          <t>Alec Pierce (IND)</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D88" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>9.05</t>
         </is>
       </c>
     </row>
@@ -8408,20 +8408,20 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>Jayden Daniels (WAS)</t>
-        </is>
-      </c>
-      <c r="C89" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>DK Metcalf (PIT)</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D89" s="14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -8431,20 +8431,20 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>Joe Burrow (CIN)</t>
-        </is>
-      </c>
-      <c r="C90" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Rome Odunze (CHI)</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D90" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>6.05</t>
         </is>
       </c>
     </row>
@@ -8454,20 +8454,20 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>George Kittle (SF)</t>
-        </is>
-      </c>
-      <c r="C91" s="18" t="inlineStr">
+          <t>Sam LaPorta (DET)</t>
+        </is>
+      </c>
+      <c r="C91" s="19" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>5.11</t>
         </is>
       </c>
     </row>
@@ -8477,20 +8477,20 @@
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>Chuba Hubbard (CAR)</t>
-        </is>
-      </c>
-      <c r="C92" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>George Kittle (SF)</t>
+        </is>
+      </c>
+      <c r="C92" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D92" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>8.06</t>
         </is>
       </c>
     </row>
@@ -8500,20 +8500,20 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>J.K. Dobbins (DEN)</t>
-        </is>
-      </c>
-      <c r="C93" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Marvin Harrison Jr. (ARI)</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D93" s="14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.03</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>Tony Pollard (TEN)</t>
+          <t>Bhayshul Tuten (JAX)</t>
         </is>
       </c>
       <c r="C94" s="16" t="inlineStr">
@@ -8532,11 +8532,11 @@
         </is>
       </c>
       <c r="D94" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8546,20 +8546,20 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>Josh Downs (IND)</t>
-        </is>
-      </c>
-      <c r="C95" s="17" t="inlineStr">
+          <t>Michael Pittman Jr. (PIT)</t>
+        </is>
+      </c>
+      <c r="C95" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D95" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>9.07</t>
         </is>
       </c>
     </row>
@@ -8569,20 +8569,20 @@
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>Jonathon Brooks (CAR)</t>
-        </is>
-      </c>
-      <c r="C96" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Courtland Sutton (DEN)</t>
+        </is>
+      </c>
+      <c r="C96" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D96" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.09</t>
         </is>
       </c>
     </row>
@@ -8592,20 +8592,20 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>Jakobi Meyers (JAX)</t>
-        </is>
-      </c>
-      <c r="C97" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Travis Kelce (KC)</t>
+        </is>
+      </c>
+      <c r="C97" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>8.08</t>
         </is>
       </c>
     </row>
@@ -8615,20 +8615,20 @@
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>Romeo Doubs (NE)</t>
-        </is>
-      </c>
-      <c r="C98" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dallas Goedert (PHI)</t>
+        </is>
+      </c>
+      <c r="C98" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D98" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -8638,20 +8638,20 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>Sam LaPorta (DET)</t>
-        </is>
-      </c>
-      <c r="C99" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>TreVeyon Henderson (NE)</t>
+        </is>
+      </c>
+      <c r="C99" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -8661,20 +8661,20 @@
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>Khalil Shakir (BUF)</t>
-        </is>
-      </c>
-      <c r="C100" s="17" t="inlineStr">
+          <t>Chris Godwin Jr. (TB)</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D100" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>8.12</t>
         </is>
       </c>
     </row>
@@ -8684,20 +8684,20 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>Kyle Monangai (CHI)</t>
-        </is>
-      </c>
-      <c r="C101" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Kyle Pitts Sr. (ATL)</t>
+        </is>
+      </c>
+      <c r="C101" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>6.1</t>
         </is>
       </c>
     </row>
@@ -8707,20 +8707,20 @@
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Makai Lemon (PHI)</t>
-        </is>
-      </c>
-      <c r="C102" s="17" t="inlineStr">
+          <t>Jakobi Meyers (JAX)</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D102" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>10.1</t>
         </is>
       </c>
     </row>
@@ -8730,20 +8730,20 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>Xavier Worthy (KC)</t>
-        </is>
-      </c>
-      <c r="C103" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tony Pollard (TEN)</t>
+        </is>
+      </c>
+      <c r="C103" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>7.12</t>
         </is>
       </c>
     </row>
@@ -8753,20 +8753,20 @@
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>Malik Washington (MIA)</t>
-        </is>
-      </c>
-      <c r="C104" s="17" t="inlineStr">
+          <t>Michael Wilson (ARI)</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D104" s="14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>7.11</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>Jordan Mason (MIN)</t>
+          <t>Chuba Hubbard (CAR)</t>
         </is>
       </c>
       <c r="C105" s="16" t="inlineStr">
@@ -8785,11 +8785,11 @@
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>7.05</t>
         </is>
       </c>
     </row>
@@ -8799,20 +8799,20 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>Jalen Coker (CAR)</t>
-        </is>
-      </c>
-      <c r="C106" s="17" t="inlineStr">
+          <t>Jayden Reed (GB)</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D106" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -8822,20 +8822,20 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Rashid Shaheed (SEA)</t>
-        </is>
-      </c>
-      <c r="C107" s="17" t="inlineStr">
+          <t>Carnell Tate (TEN)</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -8845,20 +8845,20 @@
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>KC Concepcion (CLE)</t>
-        </is>
-      </c>
-      <c r="C108" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>J.K. Dobbins (DEN)</t>
+        </is>
+      </c>
+      <c r="C108" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D108" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>8.1</t>
         </is>
       </c>
     </row>
@@ -8868,20 +8868,20 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>Kayshon Boutte (HOU)</t>
-        </is>
-      </c>
-      <c r="C109" s="17" t="inlineStr">
+          <t>Jordan Addison (MIN)</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>9.09</t>
         </is>
       </c>
     </row>
@@ -8891,20 +8891,20 @@
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>Drake Maye (NE)</t>
-        </is>
-      </c>
-      <c r="C110" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Wan'Dale Robinson (TEN)</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D110" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>10.09</t>
         </is>
       </c>
     </row>
@@ -8914,20 +8914,20 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>Rachaad White (WAS)</t>
-        </is>
-      </c>
-      <c r="C111" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tucker Kraft (GB)</t>
+        </is>
+      </c>
+      <c r="C111" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>6.02</t>
         </is>
       </c>
     </row>
@@ -8937,20 +8937,20 @@
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>Matthew Golden (GB)</t>
-        </is>
-      </c>
-      <c r="C112" s="17" t="inlineStr">
+          <t>Brian Thomas Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D112" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>11.07</t>
+          <t>7.02</t>
         </is>
       </c>
     </row>
@@ -8960,20 +8960,20 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>Jaxson Dart (NYG)</t>
-        </is>
-      </c>
-      <c r="C113" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Rico Dowdle (PIT)</t>
+        </is>
+      </c>
+      <c r="C113" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>8.01</t>
         </is>
       </c>
     </row>
@@ -8983,20 +8983,20 @@
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>Kyle Pitts Sr. (ATL)</t>
-        </is>
-      </c>
-      <c r="C114" s="18" t="inlineStr">
+          <t>Mark Andrews (BAL)</t>
+        </is>
+      </c>
+      <c r="C114" s="19" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D114" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>11.09</t>
         </is>
       </c>
     </row>
@@ -9006,20 +9006,20 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>Keenan Allen (IND)</t>
-        </is>
-      </c>
-      <c r="C115" s="17" t="inlineStr">
+          <t>Quentin Johnston (LAC)</t>
+        </is>
+      </c>
+      <c r="C115" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>10.05</t>
         </is>
       </c>
     </row>
@@ -9029,20 +9029,20 @@
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>Caleb Williams (CHI)</t>
-        </is>
-      </c>
-      <c r="C116" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Khalil Shakir (BUF)</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D116" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>12.11</t>
         </is>
       </c>
     </row>
@@ -9052,20 +9052,20 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>Trevor Lawrence (JAX)</t>
-        </is>
-      </c>
-      <c r="C117" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Aaron Jones Sr. (MIN)</t>
+        </is>
+      </c>
+      <c r="C117" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>11.04</t>
         </is>
       </c>
     </row>
@@ -9075,12 +9075,12 @@
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>Blake Corum (LAR)</t>
-        </is>
-      </c>
-      <c r="C118" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Romeo Doubs (NE)</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D118" s="14" t="n">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
-          <t>9.08</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -9098,20 +9098,20 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>RJ Harvey (DEN)</t>
-        </is>
-      </c>
-      <c r="C119" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Stefon Diggs (WAS)</t>
+        </is>
+      </c>
+      <c r="C119" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>10.02</t>
         </is>
       </c>
     </row>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Juwan Johnson (NO)</t>
+          <t>Xavier Worthy (KC)</t>
         </is>
       </c>
       <c r="C120" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D120" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -9144,20 +9144,20 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>Jordyn Tyson (NO)</t>
-        </is>
-      </c>
-      <c r="C121" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jadarian Price (SEA)</t>
+        </is>
+      </c>
+      <c r="C121" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D121" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>8.07</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>Dalton Schultz (HOU)</t>
+          <t>Deebo Samuel Sr. (SF)</t>
         </is>
       </c>
       <c r="C122" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>17.01</t>
+          <t>11.11</t>
         </is>
       </c>
     </row>
@@ -9190,20 +9190,20 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>Travis Kelce (KC)</t>
-        </is>
-      </c>
-      <c r="C123" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>RJ Harvey (DEN)</t>
+        </is>
+      </c>
+      <c r="C123" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>7.08</t>
         </is>
       </c>
     </row>
@@ -9213,20 +9213,20 @@
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>Tre Tucker (LV)</t>
-        </is>
-      </c>
-      <c r="C124" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Isaiah Likely (NYG)</t>
+        </is>
+      </c>
+      <c r="C124" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D124" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -9236,20 +9236,20 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>Aaron Jones Sr. (MIN)</t>
-        </is>
-      </c>
-      <c r="C125" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Josh Downs (IND)</t>
+        </is>
+      </c>
+      <c r="C125" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>10.01</t>
         </is>
       </c>
     </row>
@@ -9259,20 +9259,20 @@
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>Jake Ferguson (DAL)</t>
+          <t>Matthew Golden (GB)</t>
         </is>
       </c>
       <c r="C126" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>11.07</t>
         </is>
       </c>
     </row>
@@ -9282,12 +9282,12 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>Dak Prescott (DAL)</t>
+          <t>Jake Ferguson (DAL)</t>
         </is>
       </c>
       <c r="C127" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>9.02</t>
         </is>
       </c>
     </row>
@@ -9305,20 +9305,20 @@
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>Dalton Kincaid (BUF)</t>
-        </is>
-      </c>
-      <c r="C128" s="18" t="inlineStr">
+          <t>Hunter Henry (NE)</t>
+        </is>
+      </c>
+      <c r="C128" s="19" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D128" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>12.1</t>
         </is>
       </c>
     </row>
@@ -9328,12 +9328,12 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>Isaiah Likely (NYG)</t>
+          <t>De'Zhaun Stribling (SF)</t>
         </is>
       </c>
       <c r="C129" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D129" s="14" t="n">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>12.07</t>
         </is>
       </c>
     </row>
@@ -9351,20 +9351,20 @@
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>Tyjae Spears (TEN)</t>
-        </is>
-      </c>
-      <c r="C130" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dalton Kincaid (BUF)</t>
+        </is>
+      </c>
+      <c r="C130" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D130" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -9374,20 +9374,20 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>Justin Herbert (LAC)</t>
-        </is>
-      </c>
-      <c r="C131" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Kyle Monangai (CHI)</t>
+        </is>
+      </c>
+      <c r="C131" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.04</t>
         </is>
       </c>
     </row>
@@ -9397,12 +9397,12 @@
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>Dallas Goedert (PHI)</t>
-        </is>
-      </c>
-      <c r="C132" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kenny Gainwell (TB)</t>
+        </is>
+      </c>
+      <c r="C132" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D132" s="14" t="n">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
@@ -9420,12 +9420,12 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>Bo Nix (DEN)</t>
-        </is>
-      </c>
-      <c r="C133" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Makai Lemon (PHI)</t>
+        </is>
+      </c>
+      <c r="C133" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D133" s="14" t="n">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>8.03</t>
         </is>
       </c>
     </row>
@@ -9443,20 +9443,20 @@
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>Brock Purdy (SF)</t>
-        </is>
-      </c>
-      <c r="C134" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Rashid Shaheed (SEA)</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D134" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>13.03</t>
         </is>
       </c>
     </row>
@@ -9466,20 +9466,20 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>Omar Cooper Jr. (NYJ)</t>
-        </is>
-      </c>
-      <c r="C135" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brenton Strange (JAX)</t>
+        </is>
+      </c>
+      <c r="C135" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>17.02</t>
+          <t>13.08</t>
         </is>
       </c>
     </row>
@@ -9489,20 +9489,20 @@
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>Jared Goff (DET)</t>
+          <t>Juwan Johnson (NO)</t>
         </is>
       </c>
       <c r="C136" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D136" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -9512,20 +9512,20 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>Deebo Samuel Sr. (SF)</t>
-        </is>
-      </c>
-      <c r="C137" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Rachaad White (WAS)</t>
+        </is>
+      </c>
+      <c r="C137" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.12</t>
         </is>
       </c>
     </row>
@@ -9535,20 +9535,20 @@
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>Tyler Shough (NO)</t>
-        </is>
-      </c>
-      <c r="C138" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>KC Concepcion (CLE)</t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>11.01</t>
         </is>
       </c>
     </row>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>Matthew Stafford (LAR)</t>
-        </is>
-      </c>
-      <c r="C139" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jerry Jeudy (CLE)</t>
+        </is>
+      </c>
+      <c r="C139" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -9581,20 +9581,20 @@
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>Kyler Murray (MIN)</t>
-        </is>
-      </c>
-      <c r="C140" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jacory Croskey-Merritt (WAS)</t>
+        </is>
+      </c>
+      <c r="C140" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D140" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>10.06</t>
         </is>
       </c>
     </row>
@@ -9604,20 +9604,20 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>Jordan Love (GB)</t>
-        </is>
-      </c>
-      <c r="C141" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jonathon Brooks (CAR)</t>
+        </is>
+      </c>
+      <c r="C141" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>9.1</t>
         </is>
       </c>
     </row>
@@ -9627,20 +9627,20 @@
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>Baker Mayfield (TB)</t>
-        </is>
-      </c>
-      <c r="C142" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Jalen Coker (CAR)</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>13.02</t>
         </is>
       </c>
     </row>
@@ -9650,20 +9650,20 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>Denzel Boston (CLE)</t>
-        </is>
-      </c>
-      <c r="C143" s="17" t="inlineStr">
+          <t>Calvin Ridley (TEN)</t>
+        </is>
+      </c>
+      <c r="C143" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>22.01</t>
         </is>
       </c>
     </row>
@@ -9673,20 +9673,20 @@
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>Patrick Mahomes (KC)</t>
-        </is>
-      </c>
-      <c r="C144" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Cooper Kupp (SEA)</t>
+        </is>
+      </c>
+      <c r="C144" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>19.05</t>
         </is>
       </c>
     </row>
@@ -9696,20 +9696,20 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>Brenton Strange (JAX)</t>
-        </is>
-      </c>
-      <c r="C145" s="18" t="inlineStr">
+          <t>Dalton Schultz (HOU)</t>
+        </is>
+      </c>
+      <c r="C145" s="19" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>17.01</t>
         </is>
       </c>
     </row>
@@ -9719,20 +9719,20 @@
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks (PHI)</t>
-        </is>
-      </c>
-      <c r="C146" s="17" t="inlineStr">
+          <t>Keenan Allen (IND)</t>
+        </is>
+      </c>
+      <c r="C146" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17.07</t>
         </is>
       </c>
     </row>
@@ -9742,20 +9742,20 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>Mark Andrews (BAL)</t>
-        </is>
-      </c>
-      <c r="C147" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jordan Mason (MIN)</t>
+        </is>
+      </c>
+      <c r="C147" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>10.07</t>
         </is>
       </c>
     </row>
@@ -9765,20 +9765,20 @@
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>Pat Bryant (DEN)</t>
-        </is>
-      </c>
-      <c r="C148" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>T.J. Hockenson (MIN)</t>
+        </is>
+      </c>
+      <c r="C148" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E148" s="14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -9788,12 +9788,12 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>Malik Willis (MIA)</t>
+          <t>Greg Dulcich (MIA)</t>
         </is>
       </c>
       <c r="C149" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -9811,20 +9811,20 @@
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>Jalen Nailor (LV)</t>
-        </is>
-      </c>
-      <c r="C150" s="17" t="inlineStr">
+          <t>Kayshon Boutte (HOU)</t>
+        </is>
+      </c>
+      <c r="C150" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E150" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>19.08</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>Woody Marks (HOU)</t>
-        </is>
-      </c>
-      <c r="C151" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jordyn Tyson (NO)</t>
+        </is>
+      </c>
+      <c r="C151" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D151" s="14" t="n">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>8.07</t>
         </is>
       </c>
     </row>
@@ -9857,12 +9857,12 @@
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Hunter Henry (NE)</t>
+          <t>Denzel Boston (CLE)</t>
         </is>
       </c>
       <c r="C152" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="E152" s="14" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -9880,20 +9880,20 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>Chig Okonkwo (WAS)</t>
-        </is>
-      </c>
-      <c r="C153" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Blake Corum (LAR)</t>
+        </is>
+      </c>
+      <c r="C153" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>9.08</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>Chris Rodriguez Jr. (JAX)</t>
+          <t>MarShawn Lloyd (GB)</t>
         </is>
       </c>
       <c r="C154" s="16" t="inlineStr">
@@ -9912,11 +9912,11 @@
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E154" s="14" t="inlineStr">
         <is>
-          <t>12.08</t>
+          <t>15.06</t>
         </is>
       </c>
     </row>
@@ -9926,20 +9926,20 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>Travis Hunter (JAX)</t>
-        </is>
-      </c>
-      <c r="C155" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Woody Marks (HOU)</t>
+        </is>
+      </c>
+      <c r="C155" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>14.04</t>
         </is>
       </c>
     </row>
@@ -9949,20 +9949,20 @@
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>Cooper Kupp (SEA)</t>
-        </is>
-      </c>
-      <c r="C156" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kenyon Sadiq (NYJ)</t>
+        </is>
+      </c>
+      <c r="C156" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E156" s="14" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>13.1</t>
         </is>
       </c>
     </row>
@@ -9972,20 +9972,20 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>Jerry Jeudy (CLE)</t>
-        </is>
-      </c>
-      <c r="C157" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Pat Freiermuth (PIT)</t>
+        </is>
+      </c>
+      <c r="C157" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D157" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E157" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -9995,12 +9995,12 @@
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>Cam Ward (TEN)</t>
-        </is>
-      </c>
-      <c r="C158" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tyjae Spears (TEN)</t>
+        </is>
+      </c>
+      <c r="C158" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="E158" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>14.09</t>
         </is>
       </c>
     </row>
@@ -10018,20 +10018,20 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>Isiah Pacheco (DET)</t>
-        </is>
-      </c>
-      <c r="C159" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Tre Tucker (LV)</t>
+        </is>
+      </c>
+      <c r="C159" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E159" s="14" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>17.1</t>
         </is>
       </c>
     </row>
@@ -10041,20 +10041,20 @@
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>C.J. Stroud (HOU)</t>
+          <t>Cade Otton (TB)</t>
         </is>
       </c>
       <c r="C160" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E160" s="14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>20.06</t>
         </is>
       </c>
     </row>
@@ -10064,20 +10064,20 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>DeMario Douglas (NE)</t>
-        </is>
-      </c>
-      <c r="C161" s="17" t="inlineStr">
+          <t>Rashod Bateman (BAL)</t>
+        </is>
+      </c>
+      <c r="C161" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E161" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.05</t>
         </is>
       </c>
     </row>
@@ -10087,20 +10087,20 @@
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>Malachi Fields (NYG)</t>
-        </is>
-      </c>
-      <c r="C162" s="17" t="inlineStr">
+          <t>Jalen Nailor (LV)</t>
+        </is>
+      </c>
+      <c r="C162" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D162" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E162" s="14" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -10110,20 +10110,20 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>Sam Darnold (SEA)</t>
+          <t>Chig Okonkwo (WAS)</t>
         </is>
       </c>
       <c r="C163" s="19" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E163" s="14" t="inlineStr">
         <is>
-          <t>14.05</t>
+          <t>16.09</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>Keaton Mitchell (LAC)</t>
+          <t>Alvin Kamara (NO)</t>
         </is>
       </c>
       <c r="C164" s="16" t="inlineStr">
@@ -10142,11 +10142,11 @@
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E164" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>14.07</t>
         </is>
       </c>
     </row>
@@ -10156,20 +10156,20 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>Adonai Mitchell (NYJ)</t>
-        </is>
-      </c>
-      <c r="C165" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Zach Charbonnet (SEA)</t>
+        </is>
+      </c>
+      <c r="C165" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E165" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>13.04</t>
         </is>
       </c>
     </row>
@@ -10179,20 +10179,20 @@
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane (BAL)</t>
-        </is>
-      </c>
-      <c r="C166" s="17" t="inlineStr">
+          <t>Jaylin Noel (HOU)</t>
+        </is>
+      </c>
+      <c r="C166" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E166" s="14" t="inlineStr">
         <is>
-          <t>14.02</t>
+          <t>18.1</t>
         </is>
       </c>
     </row>
@@ -10202,20 +10202,20 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>Daniel Jones (IND)</t>
-        </is>
-      </c>
-      <c r="C167" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Malik Washington (MIA)</t>
+        </is>
+      </c>
+      <c r="C167" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E167" s="14" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -10225,20 +10225,20 @@
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>Tank Dell (HOU)</t>
-        </is>
-      </c>
-      <c r="C168" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>AJ Barner (SEA)</t>
+        </is>
+      </c>
+      <c r="C168" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E168" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10248,20 +10248,20 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>Germie Bernard (PIT)</t>
-        </is>
-      </c>
-      <c r="C169" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Dylan Sampson (CLE)</t>
+        </is>
+      </c>
+      <c r="C169" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E169" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>16.11</t>
         </is>
       </c>
     </row>
@@ -10271,20 +10271,20 @@
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>Zach Charbonnet (SEA)</t>
-        </is>
-      </c>
-      <c r="C170" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Omar Cooper Jr. (NYJ)</t>
+        </is>
+      </c>
+      <c r="C170" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E170" s="14" t="inlineStr">
         <is>
-          <t>13.04</t>
+          <t>17.02</t>
         </is>
       </c>
     </row>
@@ -10294,20 +10294,20 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>Cyrus Allen (KC)</t>
-        </is>
-      </c>
-      <c r="C171" s="17" t="inlineStr">
+          <t>Travis Hunter (JAX)</t>
+        </is>
+      </c>
+      <c r="C171" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E171" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10317,20 +10317,20 @@
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>Tyler Allgeier (ARI)</t>
-        </is>
-      </c>
-      <c r="C172" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Jalen Tolbert (MIA)</t>
+        </is>
+      </c>
+      <c r="C172" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E172" s="14" t="inlineStr">
         <is>
-          <t>13.01</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10340,20 +10340,20 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>Dylan Sampson (CLE)</t>
-        </is>
-      </c>
-      <c r="C173" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Devaughn Vele (NO)</t>
+        </is>
+      </c>
+      <c r="C173" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E173" s="14" t="inlineStr">
         <is>
-          <t>16.11</t>
+          <t>20.12</t>
         </is>
       </c>
     </row>
@@ -10363,20 +10363,20 @@
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>Kyle Williams (NE)</t>
-        </is>
-      </c>
-      <c r="C174" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tyler Allgeier (ARI)</t>
+        </is>
+      </c>
+      <c r="C174" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E174" s="14" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>13.01</t>
         </is>
       </c>
     </row>
@@ -10386,20 +10386,20 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>Calvin Ridley (TEN)</t>
-        </is>
-      </c>
-      <c r="C175" s="17" t="inlineStr">
+          <t>Tre' Harris (LAC)</t>
+        </is>
+      </c>
+      <c r="C175" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E175" s="14" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10409,20 +10409,20 @@
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>T.J. Hockenson (MIN)</t>
+          <t>Germie Bernard (PIT)</t>
         </is>
       </c>
       <c r="C176" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D176" s="14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E176" s="14" t="inlineStr">
         <is>
-          <t>14.09</t>
+          <t>20.02</t>
         </is>
       </c>
     </row>
@@ -10432,20 +10432,20 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>Mike Washington Jr. (LV)</t>
-        </is>
-      </c>
-      <c r="C177" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Dontayvion Wicks (PHI)</t>
+        </is>
+      </c>
+      <c r="C177" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E177" s="14" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10455,12 +10455,12 @@
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>Greg Dulcich (MIA)</t>
-        </is>
-      </c>
-      <c r="C178" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Isiah Pacheco (DET)</t>
+        </is>
+      </c>
+      <c r="C178" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="E178" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>16.06</t>
         </is>
       </c>
     </row>
@@ -10478,12 +10478,12 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq (NYJ)</t>
+          <t>Adonai Mitchell (NYJ)</t>
         </is>
       </c>
       <c r="C179" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="E179" s="14" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10501,20 +10501,20 @@
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>Jonah Coleman (DEN)</t>
-        </is>
-      </c>
-      <c r="C180" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ja'Kobi Lane (BAL)</t>
+        </is>
+      </c>
+      <c r="C180" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>14.02</t>
         </is>
       </c>
     </row>
@@ -10524,20 +10524,20 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>Tre' Harris (LAC)</t>
-        </is>
-      </c>
-      <c r="C181" s="17" t="inlineStr">
+          <t>DeMario Douglas (NE)</t>
+        </is>
+      </c>
+      <c r="C181" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>20.02</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>Keon Coleman (BUF)</t>
-        </is>
-      </c>
-      <c r="C182" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Chris Rodriguez Jr. (JAX)</t>
+        </is>
+      </c>
+      <c r="C182" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D182" s="14" t="n">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="E182" s="14" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>12.08</t>
         </is>
       </c>
     </row>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>Tyrone Tracy Jr. (NYG)</t>
+          <t>Mike Washington Jr. (LV)</t>
         </is>
       </c>
       <c r="C183" s="16" t="inlineStr">
@@ -10579,11 +10579,11 @@
         </is>
       </c>
       <c r="D183" s="14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E183" s="14" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>15.05</t>
         </is>
       </c>
     </row>
@@ -10593,20 +10593,20 @@
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>Pat Freiermuth (PIT)</t>
+          <t>Darius Slayton (NYG)</t>
         </is>
       </c>
       <c r="C184" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D184" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E184" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10616,20 +10616,20 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>Aaron Rodgers (PIT)</t>
-        </is>
-      </c>
-      <c r="C185" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Zachariah Branch (ATL)</t>
+        </is>
+      </c>
+      <c r="C185" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E185" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>17.04</t>
         </is>
       </c>
     </row>
@@ -10639,20 +10639,20 @@
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>Bryce Young (CAR)</t>
-        </is>
-      </c>
-      <c r="C186" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Keaton Mitchell (LAC)</t>
+        </is>
+      </c>
+      <c r="C186" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D186" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>16.04</t>
         </is>
       </c>
     </row>
@@ -10662,20 +10662,20 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>Zachariah Branch (ATL)</t>
-        </is>
-      </c>
-      <c r="C187" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Tank Bigsby (PHI)</t>
+        </is>
+      </c>
+      <c r="C187" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D187" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E187" s="14" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10685,20 +10685,20 @@
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Ryan Flournoy (DAL)</t>
-        </is>
-      </c>
-      <c r="C188" s="17" t="inlineStr">
+          <t>Malachi Fields (NYG)</t>
+        </is>
+      </c>
+      <c r="C188" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D188" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>19.04</t>
         </is>
       </c>
     </row>
@@ -10708,20 +10708,20 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>Cade Otton (TB)</t>
+          <t>Caleb Douglas (MIA)</t>
         </is>
       </c>
       <c r="C189" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E189" s="14" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>18.09</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Tank Bigsby (PHI)</t>
+          <t>Tyrone Tracy Jr. (NYG)</t>
         </is>
       </c>
       <c r="C190" s="16" t="inlineStr">
@@ -10740,11 +10740,11 @@
         </is>
       </c>
       <c r="D190" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E190" s="14" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>14.11</t>
         </is>
       </c>
     </row>
@@ -10754,20 +10754,20 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>Alvin Kamara (NO)</t>
-        </is>
-      </c>
-      <c r="C191" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Pat Bryant (DEN)</t>
+        </is>
+      </c>
+      <c r="C191" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E191" s="14" t="inlineStr">
         <is>
-          <t>14.07</t>
+          <t>19.11</t>
         </is>
       </c>
     </row>
@@ -10777,20 +10777,20 @@
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Caleb Douglas (MIA)</t>
-        </is>
-      </c>
-      <c r="C192" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Najee Harris (NYG)</t>
+        </is>
+      </c>
+      <c r="C192" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D192" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
-          <t>18.09</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10800,20 +10800,20 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>Geno Smith (NYJ)</t>
-        </is>
-      </c>
-      <c r="C193" s="19" t="inlineStr">
-        <is>
-          <t>QB</t>
+          <t>Tory Horton (SEA)</t>
+        </is>
+      </c>
+      <c r="C193" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.01</t>
         </is>
       </c>
     </row>
@@ -10823,20 +10823,20 @@
       </c>
       <c r="B194" s="15" t="inlineStr">
         <is>
-          <t>Najee Harris (NYG)</t>
-        </is>
-      </c>
-      <c r="C194" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Ryan Flournoy (DAL)</t>
+        </is>
+      </c>
+      <c r="C194" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D194" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E194" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20.03</t>
         </is>
       </c>
     </row>
@@ -10846,20 +10846,20 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>Brian Robinson (ATL)</t>
-        </is>
-      </c>
-      <c r="C195" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Keon Coleman (BUF)</t>
+        </is>
+      </c>
+      <c r="C195" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E195" s="14" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>20.07</t>
         </is>
       </c>
     </row>
@@ -10869,10 +10869,10 @@
       </c>
       <c r="B196" s="15" t="inlineStr">
         <is>
-          <t>Devaughn Vele (NO)</t>
-        </is>
-      </c>
-      <c r="C196" s="17" t="inlineStr">
+          <t>Tank Dell (HOU)</t>
+        </is>
+      </c>
+      <c r="C196" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="E196" s="14" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>15.1</t>
         </is>
       </c>
     </row>
@@ -10892,20 +10892,20 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>AJ Barner (SEA)</t>
+          <t>Cyrus Allen (KC)</t>
         </is>
       </c>
       <c r="C197" s="18" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D197" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E197" s="14" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>15.07</t>
         </is>
       </c>
     </row>
@@ -10915,20 +10915,20 @@
       </c>
       <c r="B198" s="15" t="inlineStr">
         <is>
-          <t>Jaylin Noel (HOU)</t>
-        </is>
-      </c>
-      <c r="C198" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Jonah Coleman (DEN)</t>
+        </is>
+      </c>
+      <c r="C198" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D198" s="14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E198" s="14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>15.03</t>
         </is>
       </c>
     </row>
@@ -10938,20 +10938,20 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>Darius Slayton (NYG)</t>
-        </is>
-      </c>
-      <c r="C199" s="17" t="inlineStr">
+          <t>Kyle Williams (NE)</t>
+        </is>
+      </c>
+      <c r="C199" s="18" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E199" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19.06</t>
         </is>
       </c>
     </row>
@@ -10961,20 +10961,20 @@
       </c>
       <c r="B200" s="15" t="inlineStr">
         <is>
-          <t>Oronde Gadsden (LAC)</t>
-        </is>
-      </c>
-      <c r="C200" s="18" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Kenneth Walker (KC)</t>
+        </is>
+      </c>
+      <c r="C200" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D200" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E200" s="14" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -10984,20 +10984,20 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>Rashod Bateman (BAL)</t>
+          <t>Patrick Mahomes (KC)</t>
         </is>
       </c>
       <c r="C201" s="17" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D201" s="14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E201" s="14" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>9.12</t>
         </is>
       </c>
     </row>
@@ -11007,20 +11007,20 @@
       </c>
       <c r="B202" s="15" t="inlineStr">
         <is>
-          <t>Jalen Tolbert (MIA)</t>
-        </is>
-      </c>
-      <c r="C202" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Brian Robinson (ATL)</t>
+        </is>
+      </c>
+      <c r="C202" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D202" s="14" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E202" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13.12</t>
         </is>
       </c>
     </row>
@@ -11030,20 +11030,20 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>Tory Horton (SEA)</t>
-        </is>
-      </c>
-      <c r="C203" s="17" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Oronde Gadsden (LAC)</t>
+        </is>
+      </c>
+      <c r="C203" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D203" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E203" s="14" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>11.1</t>
         </is>
       </c>
     </row>

--- a/assets/data/12guys1cup-cheat-sheet.xlsx
+++ b/assets/data/12guys1cup-cheat-sheet.xlsx
@@ -8638,20 +8638,20 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>TreVeyon Henderson (NE)</t>
-        </is>
-      </c>
-      <c r="C99" s="16" t="inlineStr">
-        <is>
-          <t>RB</t>
+          <t>Chris Godwin Jr. (TB)</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>8.12</t>
         </is>
       </c>
     </row>
@@ -8661,20 +8661,20 @@
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>Chris Godwin Jr. (TB)</t>
-        </is>
-      </c>
-      <c r="C100" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>Kyle Pitts Sr. (ATL)</t>
+        </is>
+      </c>
+      <c r="C100" s="19" t="inlineStr">
+        <is>
+          <t>TE</t>
         </is>
       </c>
       <c r="D100" s="14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>6.1</t>
         </is>
       </c>
     </row>
@@ -8684,20 +8684,20 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>Kyle Pitts Sr. (ATL)</t>
-        </is>
-      </c>
-      <c r="C101" s="19" t="inlineStr">
-        <is>
-          <t>TE</t>
+          <t>Jakobi Meyers (JAX)</t>
+        </is>
+      </c>
+      <c r="C101" s="18" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>10.1</t>
         </is>
       </c>
     </row>
@@ -8707,20 +8707,20 @@
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>Jakobi Meyers (JAX)</t>
-        </is>
-      </c>
-      <c r="C102" s="18" t="inlineStr">
-        <is>
-          <t>WR</t>
+          <t>TreVeyon Henderson (NE)</t>
+        </is>
+      </c>
+      <c r="C102" s="16" t="inlineStr">
+        <is>
+          <t>RB</t>
         </is>
       </c>
       <c r="D102" s="14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>5.08</t>
         </is>
       </c>
     </row>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>Jayden Reed (GB)</t>
+          <t>Carnell Tate (TEN)</t>
         </is>
       </c>
       <c r="C106" s="18" t="inlineStr">
@@ -8808,11 +8808,11 @@
         </is>
       </c>
       <c r="D106" s="14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>10.04</t>
+          <t>6.07</t>
         </is>
       </c>
     </row>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Carnell Tate (TEN)</t>
+          <t>Jayden Reed (GB)</t>
         </is>
       </c>
       <c r="C107" s="18" t="inlineStr">
@@ -8831,11 +8831,11 @@
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>10.04</t>
         </is>
       </c>
     </row>
